--- a/data/BEC.MI.xlsx
+++ b/data/BEC.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96833848953247</t>
+    <t xml:space="preserve">4.96833801269531</t>
   </si>
   <si>
     <t xml:space="preserve">BEC.MI</t>
@@ -50,34 +50,34 @@
     <t xml:space="preserve">4.8704080581665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87693691253662</t>
+    <t xml:space="preserve">4.8769359588623</t>
   </si>
   <si>
     <t xml:space="preserve">4.92916631698608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77247762680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79859209060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83449983596802</t>
+    <t xml:space="preserve">4.77247714996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79859256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83450031280518</t>
   </si>
   <si>
     <t xml:space="preserve">4.73330545425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79532670974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80512094497681</t>
+    <t xml:space="preserve">4.79532814025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80511999130249</t>
   </si>
   <si>
     <t xml:space="preserve">4.76594877243042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7594199180603</t>
+    <t xml:space="preserve">4.75942087173462</t>
   </si>
   <si>
     <t xml:space="preserve">4.60273170471191</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">4.69739770889282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69413328170776</t>
+    <t xml:space="preserve">4.69413280487061</t>
   </si>
   <si>
     <t xml:space="preserve">4.63537454605103</t>
@@ -98,34 +98,34 @@
     <t xml:space="preserve">4.37422704696655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18489408493042</t>
+    <t xml:space="preserve">4.18489456176758</t>
   </si>
   <si>
     <t xml:space="preserve">4.07390642166138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08043575286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2338604927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40360593795776</t>
+    <t xml:space="preserve">4.08043527603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23386096954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40360641479492</t>
   </si>
   <si>
     <t xml:space="preserve">4.49174356460571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53091621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43298435211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50480079650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53744459152222</t>
+    <t xml:space="preserve">4.5309157371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43298530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50480127334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53744411468506</t>
   </si>
   <si>
     <t xml:space="preserve">4.42645692825317</t>
@@ -134,37 +134,37 @@
     <t xml:space="preserve">4.42319202423096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43951368331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41666316986084</t>
+    <t xml:space="preserve">4.43951416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.416663646698</t>
   </si>
   <si>
     <t xml:space="preserve">4.44930696487427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46562910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47868537902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60926055908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89652299880981</t>
+    <t xml:space="preserve">4.4656286239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47868633270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60926008224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8965220451355</t>
   </si>
   <si>
     <t xml:space="preserve">4.90957975387573</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93569469451904</t>
+    <t xml:space="preserve">4.93569421768188</t>
   </si>
   <si>
     <t xml:space="preserve">4.91284418106079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01403856277466</t>
+    <t xml:space="preserve">5.01403903961182</t>
   </si>
   <si>
     <t xml:space="preserve">4.94222354888916</t>
@@ -173,82 +173,82 @@
     <t xml:space="preserve">5.03362512588501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04015398025513</t>
+    <t xml:space="preserve">5.04015350341797</t>
   </si>
   <si>
     <t xml:space="preserve">5.09238338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94875192642212</t>
+    <t xml:space="preserve">4.94875240325928</t>
   </si>
   <si>
     <t xml:space="preserve">4.99445295333862</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84429359436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06953239440918</t>
+    <t xml:space="preserve">4.84429311752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0695333480835</t>
   </si>
   <si>
     <t xml:space="preserve">5.09891223907471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98792409896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04994630813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04341840744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05974006652832</t>
+    <t xml:space="preserve">4.98792362213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0499472618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04341745376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.059739112854</t>
   </si>
   <si>
     <t xml:space="preserve">4.98465967178345</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02709627151489</t>
+    <t xml:space="preserve">5.02709579467773</t>
   </si>
   <si>
     <t xml:space="preserve">4.99973821640015</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03393602371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9621205329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91766309738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94502115249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85610628128052</t>
+    <t xml:space="preserve">5.03393697738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96212148666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91766357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94502210617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85610675811768</t>
   </si>
   <si>
     <t xml:space="preserve">4.89030504226685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89714479446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79455089569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82190942764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98263931274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9245023727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00657749176025</t>
+    <t xml:space="preserve">4.89714336395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79455041885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82190895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98263883590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92450284957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00657892227173</t>
   </si>
   <si>
     <t xml:space="preserve">4.88346529006958</t>
@@ -257,16 +257,16 @@
     <t xml:space="preserve">4.94844150543213</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95870113372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9928994178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86636638641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85268640518188</t>
+    <t xml:space="preserve">4.95870065689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99289894104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86636590957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85268688201904</t>
   </si>
   <si>
     <t xml:space="preserve">4.93134260177612</t>
@@ -275,25 +275,25 @@
     <t xml:space="preserve">4.78771066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78429174423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8253288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77403211593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72273445129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67485857009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75693273544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56200408935547</t>
+    <t xml:space="preserve">4.78429126739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82532835006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77403163909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72273540496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67485761642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75693321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56200504302979</t>
   </si>
   <si>
     <t xml:space="preserve">4.54148578643799</t>
@@ -302,10 +302,10 @@
     <t xml:space="preserve">4.53122663497925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60304260253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63040113449097</t>
+    <t xml:space="preserve">4.6030421257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63040065765381</t>
   </si>
   <si>
     <t xml:space="preserve">4.55516529083252</t>
@@ -314,28 +314,28 @@
     <t xml:space="preserve">4.58252382278442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54832553863525</t>
+    <t xml:space="preserve">4.5483250617981</t>
   </si>
   <si>
     <t xml:space="preserve">4.45941114425659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53464603424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52780628204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52096748352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64407920837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74325323104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73983383178711</t>
+    <t xml:space="preserve">4.53464698791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52780723571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52096700668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64407968521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7432541847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73983335494995</t>
   </si>
   <si>
     <t xml:space="preserve">4.83558797836304</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">4.92108345031738</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92792177200317</t>
+    <t xml:space="preserve">4.92792224884033</t>
   </si>
   <si>
     <t xml:space="preserve">4.98605918884277</t>
@@ -356,43 +356,43 @@
     <t xml:space="preserve">4.91424322128296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9723801612854</t>
+    <t xml:space="preserve">4.97237968444824</t>
   </si>
   <si>
     <t xml:space="preserve">4.96896028518677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86978626251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93818187713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88004541397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9518609046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87320518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8629469871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76719236373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80139064788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80822944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76377248764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8424277305603</t>
+    <t xml:space="preserve">4.86978578567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93818235397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88004589080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95186138153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87320566177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86294651031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76719188690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80139017105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80822992324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76377201080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84242820739746</t>
   </si>
   <si>
     <t xml:space="preserve">4.72957468032837</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">4.84926748275757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81164932250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88688564300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02025699615479</t>
+    <t xml:space="preserve">4.81164979934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88688516616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02025747299194</t>
   </si>
   <si>
     <t xml:space="preserve">5.08865261077881</t>
@@ -419,10 +419,10 @@
     <t xml:space="preserve">5.0647144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04761552810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09549188613892</t>
+    <t xml:space="preserve">5.04761600494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09549236297607</t>
   </si>
   <si>
     <t xml:space="preserve">5.17756748199463</t>
@@ -431,40 +431,40 @@
     <t xml:space="preserve">5.23228454589844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12969064712524</t>
+    <t xml:space="preserve">5.12969017028809</t>
   </si>
   <si>
     <t xml:space="preserve">5.13994979858398</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16388845443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2117657661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30751943588257</t>
+    <t xml:space="preserve">5.16388893127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21176528930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30751991271973</t>
   </si>
   <si>
     <t xml:space="preserve">5.30068016052246</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13311052322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22544479370117</t>
+    <t xml:space="preserve">5.13311100006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22544431686401</t>
   </si>
   <si>
     <t xml:space="preserve">5.16730833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19808626174927</t>
+    <t xml:space="preserve">5.19808673858643</t>
   </si>
   <si>
     <t xml:space="preserve">5.29726028442383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47167015075684</t>
+    <t xml:space="preserve">5.47166967391968</t>
   </si>
   <si>
     <t xml:space="preserve">5.4032735824585</t>
@@ -473,22 +473,22 @@
     <t xml:space="preserve">5.36565589904785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36223697662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46482944488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36907529830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39643383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25964260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41353321075439</t>
+    <t xml:space="preserve">5.36223649978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46482992172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36907577514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39643478393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25964307785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41353225708008</t>
   </si>
   <si>
     <t xml:space="preserve">5.46141052246094</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">5.45457077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4682502746582</t>
+    <t xml:space="preserve">5.46824979782104</t>
   </si>
   <si>
     <t xml:space="preserve">5.47508955001831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39985370635986</t>
+    <t xml:space="preserve">5.39985418319702</t>
   </si>
   <si>
     <t xml:space="preserve">5.41695308685303</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">5.4306321144104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45799016952515</t>
+    <t xml:space="preserve">5.4579906463623</t>
   </si>
   <si>
     <t xml:space="preserve">5.50586843490601</t>
@@ -524,115 +524,115 @@
     <t xml:space="preserve">5.52980661392212</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60846185684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68369722366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73157358169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88204479217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9367618560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94360160827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05645418167114</t>
+    <t xml:space="preserve">5.60846090316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68369674682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73157453536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88204526901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93676233291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94360113143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05645322799683</t>
   </si>
   <si>
     <t xml:space="preserve">5.94018220901489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04961538314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07355403900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02567720413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97437906265259</t>
+    <t xml:space="preserve">6.04961490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07355356216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02567672729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97437953948975</t>
   </si>
   <si>
     <t xml:space="preserve">6.04277515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17272853851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39501428604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37449550628662</t>
+    <t xml:space="preserve">6.17272806167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39501476287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3744945526123</t>
   </si>
   <si>
     <t xml:space="preserve">6.4668288230896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32661819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11117124557495</t>
+    <t xml:space="preserve">6.32661771774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11117076873779</t>
   </si>
   <si>
     <t xml:space="preserve">5.89914417266846</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00515699386597</t>
+    <t xml:space="preserve">6.00515747070312</t>
   </si>
   <si>
     <t xml:space="preserve">6.2240252494812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26506280899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39843320846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48050880432129</t>
+    <t xml:space="preserve">6.26506185531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39843416213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40527296066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48050975799561</t>
   </si>
   <si>
     <t xml:space="preserve">6.41211318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44973134994507</t>
+    <t xml:space="preserve">6.44973182678223</t>
   </si>
   <si>
     <t xml:space="preserve">6.43605184555054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52838611602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66859722137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99689722061157</t>
+    <t xml:space="preserve">6.52838516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66859769821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99689769744873</t>
   </si>
   <si>
     <t xml:space="preserve">6.94218063354492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1200098991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4688286781311</t>
+    <t xml:space="preserve">7.12001037597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46882772445679</t>
   </si>
   <si>
     <t xml:space="preserve">7.66717672348022</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20066452026367</t>
+    <t xml:space="preserve">8.20066547393799</t>
   </si>
   <si>
     <t xml:space="preserve">8.40585327148438</t>
@@ -641,34 +641,34 @@
     <t xml:space="preserve">8.64523887634277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27590274810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35113620758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28957939147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24170303344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33745574951172</t>
+    <t xml:space="preserve">8.27589988708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35113716125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28958034515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24170207977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33745670318604</t>
   </si>
   <si>
     <t xml:space="preserve">8.33061695098877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31693840026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26906204223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22118473052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11859035491943</t>
+    <t xml:space="preserve">8.31693744659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26906108856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22118282318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11859130859375</t>
   </si>
   <si>
     <t xml:space="preserve">8.30325889587402</t>
@@ -677,118 +677,115 @@
     <t xml:space="preserve">8.48108768463135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72047233581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71363353729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79469108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49782371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52750968933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07478713989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31227970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43102645874023</t>
+    <t xml:space="preserve">8.72047328948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7136344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79469013214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49782466888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52751064300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07478809356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31228160858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43102836608887</t>
   </si>
   <si>
     <t xml:space="preserve">8.37165451049805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97830581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88924503326416</t>
+    <t xml:space="preserve">7.97830629348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88924551010132</t>
   </si>
   <si>
     <t xml:space="preserve">8.23806571960449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26033020019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21579837799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64625644683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75758266448975</t>
+    <t xml:space="preserve">8.26032829284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21579933166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6462574005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75758361816406</t>
   </si>
   <si>
     <t xml:space="preserve">8.8021125793457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69078636169434</t>
+    <t xml:space="preserve">8.69078731536865</t>
   </si>
   <si>
     <t xml:space="preserve">8.57946300506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66110038757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54977512359619</t>
+    <t xml:space="preserve">8.66110134124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54977607727051</t>
   </si>
   <si>
     <t xml:space="preserve">8.52008819580078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53493213653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60172653198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4829797744751</t>
+    <t xml:space="preserve">8.53493118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60172748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48298072814941</t>
   </si>
   <si>
     <t xml:space="preserve">8.59430503845215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46813583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14900493621826</t>
+    <t xml:space="preserve">8.46813774108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14900302886963</t>
   </si>
   <si>
     <t xml:space="preserve">8.31970310211182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12673854827881</t>
+    <t xml:space="preserve">8.12673950195312</t>
   </si>
   <si>
     <t xml:space="preserve">8.46071434020996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58688259124756</t>
+    <t xml:space="preserve">8.58688354492188</t>
   </si>
   <si>
     <t xml:space="preserve">8.7056303024292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72047328948975</t>
-  </si>
-  <si>
     <t xml:space="preserve">8.84664154052734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69820785522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74273777008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56461906433105</t>
+    <t xml:space="preserve">8.69820880889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74273872375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56461811065674</t>
   </si>
   <si>
     <t xml:space="preserve">8.43845081329346</t>
@@ -809,40 +806,40 @@
     <t xml:space="preserve">8.63141345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6165714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63883495330811</t>
+    <t xml:space="preserve">8.61656951904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63883590698242</t>
   </si>
   <si>
     <t xml:space="preserve">8.66852188110352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77984714508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88375091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83922100067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82437801361084</t>
+    <t xml:space="preserve">8.77984619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88375186920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83922004699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82437896728516</t>
   </si>
   <si>
     <t xml:space="preserve">8.68336486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6091480255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57204055786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49039936065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47555828094482</t>
+    <t xml:space="preserve">8.60914993286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57203960418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49040222167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47555732727051</t>
   </si>
   <si>
     <t xml:space="preserve">8.78726863861084</t>
@@ -851,16 +848,16 @@
     <t xml:space="preserve">8.71305179595947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65367889404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62399196624756</t>
+    <t xml:space="preserve">8.65367794036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62399101257324</t>
   </si>
   <si>
     <t xml:space="preserve">8.75016021728516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90601634979248</t>
+    <t xml:space="preserve">8.90601539611816</t>
   </si>
   <si>
     <t xml:space="preserve">8.89859294891357</t>
@@ -875,19 +872,19 @@
     <t xml:space="preserve">8.96538925170898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87632942199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97281169891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09155750274658</t>
+    <t xml:space="preserve">8.87632846832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97281074523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09155654907227</t>
   </si>
   <si>
     <t xml:space="preserve">9.21772575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52201557159424</t>
+    <t xml:space="preserve">9.52201652526855</t>
   </si>
   <si>
     <t xml:space="preserve">9.55170249938965</t>
@@ -896,10 +893,10 @@
     <t xml:space="preserve">9.5665454864502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45521926879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4774866104126</t>
+    <t xml:space="preserve">9.45522022247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47748565673828</t>
   </si>
   <si>
     <t xml:space="preserve">9.53685855865479</t>
@@ -908,10 +905,10 @@
     <t xml:space="preserve">9.35873794555664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59623241424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64076232910156</t>
+    <t xml:space="preserve">9.59623146057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64076137542725</t>
   </si>
   <si>
     <t xml:space="preserve">9.90794277191162</t>
@@ -923,16 +920,16 @@
     <t xml:space="preserve">9.76693153381348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72982311248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99700260162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95247268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0563764572144</t>
+    <t xml:space="preserve">9.72982215881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99700450897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95247173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.05637550354</t>
   </si>
   <si>
     <t xml:space="preserve">9.64818382263184</t>
@@ -941,7 +938,7 @@
     <t xml:space="preserve">9.95989418029785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82630348205566</t>
+    <t xml:space="preserve">9.8263053894043</t>
   </si>
   <si>
     <t xml:space="preserve">9.81146049499512</t>
@@ -950,31 +947,31 @@
     <t xml:space="preserve">9.7520866394043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85599040985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86341190338135</t>
+    <t xml:space="preserve">9.85599136352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86341094970703</t>
   </si>
   <si>
     <t xml:space="preserve">10.0415325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0118465423584</t>
+    <t xml:space="preserve">10.0118455886841</t>
   </si>
   <si>
     <t xml:space="preserve">9.9450511932373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90051937103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8317985534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97088384628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25290679931641</t>
+    <t xml:space="preserve">9.90052032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83179950714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97088289260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25290775299072</t>
   </si>
   <si>
     <t xml:space="preserve">8.16384792327881</t>
@@ -995,61 +992,61 @@
     <t xml:space="preserve">8.0673656463623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98572826385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78534126281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76307725906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7037034034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82987403869629</t>
+    <t xml:space="preserve">7.98572731018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78534173965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76307678222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70370388031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82987260818481</t>
   </si>
   <si>
     <t xml:space="preserve">7.6443305015564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72596836090088</t>
+    <t xml:space="preserve">7.72596883773804</t>
   </si>
   <si>
     <t xml:space="preserve">8.04510116577148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14158344268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91893100738525</t>
+    <t xml:space="preserve">8.14158248901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91893148422241</t>
   </si>
   <si>
     <t xml:space="preserve">8.08963012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11931800842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11189651489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0970516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00057125091553</t>
+    <t xml:space="preserve">8.11931705474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11189556121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09705066680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00057029724121</t>
   </si>
   <si>
     <t xml:space="preserve">8.1341609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28259372711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20837879180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34196853637695</t>
+    <t xml:space="preserve">8.28259468078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20837783813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34196758270264</t>
   </si>
   <si>
     <t xml:space="preserve">8.44587230682373</t>
@@ -1058,16 +1055,16 @@
     <t xml:space="preserve">8.92085933685303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0247631072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32712554931641</t>
+    <t xml:space="preserve">9.02476215362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32712459564209</t>
   </si>
   <si>
     <t xml:space="preserve">8.26775169372559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71854639053345</t>
+    <t xml:space="preserve">7.71854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">8.03025722503662</t>
@@ -1076,46 +1073,46 @@
     <t xml:space="preserve">8.01541328430176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10447311401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17869186401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22322082519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40134239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0544490814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93570423126221</t>
+    <t xml:space="preserve">8.10447406768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17869091033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22322177886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40134143829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05445003509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93570327758789</t>
   </si>
   <si>
     <t xml:space="preserve">8.72789573669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89117050170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00991916656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.277099609375</t>
+    <t xml:space="preserve">8.89117240905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00992012023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27710056304932</t>
   </si>
   <si>
     <t xml:space="preserve">9.30678558349609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24741172790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35131740570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52943801879883</t>
+    <t xml:space="preserve">9.24741363525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35131549835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5294361114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.47006416320801</t>
@@ -1130,43 +1127,43 @@
     <t xml:space="preserve">9.87083339691162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60365200042725</t>
+    <t xml:space="preserve">9.60365390777588</t>
   </si>
   <si>
     <t xml:space="preserve">10.0637979507446</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87998294830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54299259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55831050872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72680568695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60426425933838</t>
+    <t xml:space="preserve">9.87998485565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54299163818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55830955505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.726806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60426330566406</t>
   </si>
   <si>
     <t xml:space="preserve">9.46640300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57362651824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6195821762085</t>
+    <t xml:space="preserve">9.57362842559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61958122253418</t>
   </si>
   <si>
     <t xml:space="preserve">9.63489818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68085193634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48172283172607</t>
+    <t xml:space="preserve">9.68085289001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48172092437744</t>
   </si>
   <si>
     <t xml:space="preserve">9.43576717376709</t>
@@ -1181,13 +1178,13 @@
     <t xml:space="preserve">9.08345794677734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59328937530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53201770782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89964389801025</t>
+    <t xml:space="preserve">8.59328842163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53201675415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89964485168457</t>
   </si>
   <si>
     <t xml:space="preserve">8.96091556549072</t>
@@ -1205,13 +1202,13 @@
     <t xml:space="preserve">9.51235580444336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52767467498779</t>
+    <t xml:space="preserve">9.52767276763916</t>
   </si>
   <si>
     <t xml:space="preserve">9.38981437683105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35917949676514</t>
+    <t xml:space="preserve">9.35918045043945</t>
   </si>
   <si>
     <t xml:space="preserve">9.19068241119385</t>
@@ -1226,19 +1223,19 @@
     <t xml:space="preserve">9.32854270935059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42044925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22132015228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11409282684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1447286605835</t>
+    <t xml:space="preserve">9.42045021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22131824493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25195407867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11409378051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14472961425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.26727199554443</t>
@@ -1247,208 +1244,211 @@
     <t xml:space="preserve">9.45108509063721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69617080688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65021705627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80773735046387</t>
+    <t xml:space="preserve">9.69616985321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6502161026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80773830413818</t>
   </si>
   <si>
     <t xml:space="preserve">9.06814002990723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37449550628662</t>
+    <t xml:space="preserve">9.37449645996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03750514984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12941074371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02218627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91496276855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94559764862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17536544799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00686836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95657253265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0331630706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91061973571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97189140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78807735443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75744152069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09877586364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86900997161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74646759033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73114776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51669883728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47074604034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42479228973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01121139526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.225661277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65456008911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77710342407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8383731842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9302806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62392425537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7158317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50138282775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8230562210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60860538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57797050476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34820365905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30224895477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3328857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37883949279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28693199157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27161407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39415645599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13375473022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11843585968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45542812347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79241943359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85369205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70051288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66987705230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68519592285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54733467102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44011116027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88432788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40513229370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92593669891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80339527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29790878295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22897815704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07579898834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15238666534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9992094039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59734916687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31742668151855</t>
   </si>
   <si>
     <t xml:space="preserve">9.03750419616699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1294116973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02218723297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91496276855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94559860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17536544799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00686931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95657253265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0331630706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91061973571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97189140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78807735443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7574405670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09877681732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86900997161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74646663665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73114776611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51669883728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47074699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42479228973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01121139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.225661277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65456008911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77710247039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83837413787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9302806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62392425537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7158317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50138187408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82305431365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60860538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57796955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3482027053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30224990844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33288669586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37883853912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28693199157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27161407470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39415740966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13375377655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11843681335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45542812347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79242038726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85369205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70051193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66987800598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68519496917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54733467102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.440110206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88432598114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40513324737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92593765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80339431762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29790782928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22897815704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0757999420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15238952636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99921035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59735012054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31742668151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79757213592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87754821777344</t>
+    <t xml:space="preserve">8.79757022857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87755012512207</t>
   </si>
   <si>
     <t xml:space="preserve">8.83755970001221</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">9.23744964599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27743721008301</t>
+    <t xml:space="preserve">9.27743911743164</t>
   </si>
   <si>
     <t xml:space="preserve">9.47738361358643</t>
@@ -1475,112 +1475,112 @@
     <t xml:space="preserve">9.67732810974121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63733863830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39740657806396</t>
+    <t xml:space="preserve">9.63733959197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39740562438965</t>
   </si>
   <si>
     <t xml:space="preserve">9.19746112823486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07749462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4373950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5573616027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11748313903809</t>
+    <t xml:space="preserve">9.07749366760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43739604949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55735969543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11748218536377</t>
   </si>
   <si>
     <t xml:space="preserve">8.71759223937988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95752620697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99751567840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15747165679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91753673553467</t>
+    <t xml:space="preserve">8.95752716064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99751663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15747261047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91753768920898</t>
   </si>
   <si>
     <t xml:space="preserve">10.7970190048218</t>
   </si>
   <si>
-    <t xml:space="preserve">10.357141494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0772180557251</t>
+    <t xml:space="preserve">10.3571395874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0772171020508</t>
   </si>
   <si>
     <t xml:space="preserve">10.3171510696411</t>
   </si>
   <si>
-    <t xml:space="preserve">10.117205619812</t>
+    <t xml:space="preserve">10.1172046661377</t>
   </si>
   <si>
     <t xml:space="preserve">9.91726207733154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.997239112854</t>
+    <t xml:space="preserve">9.99724006652832</t>
   </si>
   <si>
     <t xml:space="preserve">10.0372285842896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7573070526123</t>
+    <t xml:space="preserve">9.75730609893799</t>
   </si>
   <si>
     <t xml:space="preserve">9.71731758117676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79729461669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83728408813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1571950912476</t>
+    <t xml:space="preserve">9.7972936630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83728313446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1571960449219</t>
   </si>
   <si>
     <t xml:space="preserve">10.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2371730804443</t>
+    <t xml:space="preserve">10.2371740341187</t>
   </si>
   <si>
     <t xml:space="preserve">10.3971300125122</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5570850372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4771070480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1971836090088</t>
+    <t xml:space="preserve">10.5570840835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4771089553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1971855163574</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170965194702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9969644546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1169309616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3168754577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2368965148926</t>
+    <t xml:space="preserve">10.9969635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1169290542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3168745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2368974685669</t>
   </si>
   <si>
     <t xml:space="preserve">11.3568639755249</t>
@@ -1592,10 +1592,10 @@
     <t xml:space="preserve">10.837007522583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1569194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0369539260864</t>
+    <t xml:space="preserve">11.1569204330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0369529724121</t>
   </si>
   <si>
     <t xml:space="preserve">10.8769969940186</t>
@@ -1607,82 +1607,82 @@
     <t xml:space="preserve">10.956974029541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7570295333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5970735549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4371175765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2768859863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4368419647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5568084716797</t>
+    <t xml:space="preserve">10.7570304870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.597074508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4371185302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2768869400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.436842918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.556809425354</t>
   </si>
   <si>
     <t xml:space="preserve">11.6767768859863</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7170419692993</t>
+    <t xml:space="preserve">10.717041015625</t>
   </si>
   <si>
     <t xml:space="preserve">8.11775779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16602182388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88582181930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46993780136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03805637359619</t>
+    <t xml:space="preserve">7.1660213470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88582277297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46993827819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03805685043335</t>
   </si>
   <si>
     <t xml:space="preserve">6.9100923538208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39823341369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20628690719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99834442138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55818939208984</t>
+    <t xml:space="preserve">6.39823293685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20628643035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9983434677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55818891525269</t>
   </si>
   <si>
     <t xml:space="preserve">7.30998134613037</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40595531463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32597780227661</t>
+    <t xml:space="preserve">7.40595483779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32597684860229</t>
   </si>
   <si>
     <t xml:space="preserve">7.11803436279297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73414087295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9740743637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29398584365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15002489089966</t>
+    <t xml:space="preserve">6.73414039611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97407484054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29398536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15002584457397</t>
   </si>
   <si>
     <t xml:space="preserve">6.86210489273071</t>
@@ -1691,25 +1691,25 @@
     <t xml:space="preserve">6.8141188621521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76613235473633</t>
+    <t xml:space="preserve">6.76613187789917</t>
   </si>
   <si>
     <t xml:space="preserve">6.94208335876465</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79812288284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92608785629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78212738037109</t>
+    <t xml:space="preserve">6.79812240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92608690261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78212785720825</t>
   </si>
   <si>
     <t xml:space="preserve">6.83011436462402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92877912521362</t>
+    <t xml:space="preserve">6.92877864837646</t>
   </si>
   <si>
     <t xml:space="preserve">7.01067972183228</t>
@@ -1718,28 +1718,28 @@
     <t xml:space="preserve">6.89601898193359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96153879165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73221826553345</t>
+    <t xml:space="preserve">6.96153926849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73221778869629</t>
   </si>
   <si>
     <t xml:space="preserve">6.74859762191772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0598201751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1253399848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22362089157104</t>
+    <t xml:space="preserve">7.05981922149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12533950805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22362041473389</t>
   </si>
   <si>
     <t xml:space="preserve">7.55122327804565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56760263442993</t>
+    <t xml:space="preserve">7.56760311126709</t>
   </si>
   <si>
     <t xml:space="preserve">8.0262451171875</t>
@@ -1751,28 +1751,28 @@
     <t xml:space="preserve">8.39479732513428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72239971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76335048675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88619995117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41855335235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92715072631836</t>
+    <t xml:space="preserve">8.72239875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76334953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88620090484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17285060882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41855239868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92714977264404</t>
   </si>
   <si>
     <t xml:space="preserve">9.13190174102783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96810054779053</t>
+    <t xml:space="preserve">8.96809959411621</t>
   </si>
   <si>
     <t xml:space="preserve">9.33665180206299</t>
@@ -1781,16 +1781,16 @@
     <t xml:space="preserve">8.84525012969971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09095096588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21380138397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25475215911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0090503692627</t>
+    <t xml:space="preserve">9.09095191955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21380233764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25475120544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00905132293701</t>
   </si>
   <si>
     <t xml:space="preserve">8.64049911499023</t>
@@ -1802,16 +1802,16 @@
     <t xml:space="preserve">8.17366600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19004726409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10814571380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15728569030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96072483062744</t>
+    <t xml:space="preserve">8.1900463104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10814476013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15728664398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96072578430176</t>
   </si>
   <si>
     <t xml:space="preserve">7.87882423400879</t>
@@ -1829,25 +1829,25 @@
     <t xml:space="preserve">7.51846265792847</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53484344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33828210830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48570203781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61674356460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69864273071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76416349411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73140430450439</t>
+    <t xml:space="preserve">7.53484296798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33828163146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48570251464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61674404144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69864416122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76416492462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73140335083008</t>
   </si>
   <si>
     <t xml:space="preserve">7.79692411422729</t>
@@ -1856,10 +1856,10 @@
     <t xml:space="preserve">7.66588306427002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63312244415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64950323104858</t>
+    <t xml:space="preserve">7.63312292098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64950370788574</t>
   </si>
   <si>
     <t xml:space="preserve">7.68226289749146</t>
@@ -1871,22 +1871,22 @@
     <t xml:space="preserve">7.74778366088867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43656158447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60036277770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35466051101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40380144119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24000120162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19086027145386</t>
+    <t xml:space="preserve">7.43656253814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6003623008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35466194152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40380191802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24000072479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19085931777954</t>
   </si>
   <si>
     <t xml:space="preserve">6.79773855209351</t>
@@ -1895,19 +1895,19 @@
     <t xml:space="preserve">6.68307733535767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56841707229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3882360458374</t>
+    <t xml:space="preserve">6.5684175491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38823652267456</t>
   </si>
   <si>
     <t xml:space="preserve">6.2244348526001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48651695251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42099666595459</t>
+    <t xml:space="preserve">6.48651647567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42099618911743</t>
   </si>
   <si>
     <t xml:space="preserve">6.71583795547485</t>
@@ -1916,82 +1916,82 @@
     <t xml:space="preserve">6.84687852859497</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0434398651123</t>
+    <t xml:space="preserve">7.04344034194946</t>
   </si>
   <si>
     <t xml:space="preserve">7.92796516418457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5176477432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27194595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97710418701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84606409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12452507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59954929351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43574714660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55859851837158</t>
+    <t xml:space="preserve">8.51764678955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27194786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97710514068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84606456756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12452602386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59954833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43574810028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5585994720459</t>
   </si>
   <si>
     <t xml:space="preserve">8.6814489364624</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47669696807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35384654998779</t>
+    <t xml:space="preserve">8.47669792175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35384750366211</t>
   </si>
   <si>
     <t xml:space="preserve">8.23099613189697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04262638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94434404373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86244440078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00986576080322</t>
+    <t xml:space="preserve">8.04262447357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94434452056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86244487762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00986480712891</t>
   </si>
   <si>
     <t xml:space="preserve">8.05900573730469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45950412750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90995597839355</t>
+    <t xml:space="preserve">9.45950317382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90995693206787</t>
   </si>
   <si>
     <t xml:space="preserve">10.1556577682495</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86900520324707</t>
+    <t xml:space="preserve">9.86900615692139</t>
   </si>
   <si>
     <t xml:space="preserve">9.62330436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50045299530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37760353088379</t>
+    <t xml:space="preserve">9.50045490264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37760257720947</t>
   </si>
   <si>
     <t xml:space="preserve">9.58235454559326</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">9.05000114440918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54140377044678</t>
+    <t xml:space="preserve">9.54140281677246</t>
   </si>
   <si>
     <t xml:space="preserve">9.22513484954834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18320274353027</t>
+    <t xml:space="preserve">9.18320178985596</t>
   </si>
   <si>
     <t xml:space="preserve">9.09933853149414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14127063751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39286518096924</t>
+    <t xml:space="preserve">9.14126968383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39286422729492</t>
   </si>
   <si>
     <t xml:space="preserve">9.30900001525879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5605936050415</t>
+    <t xml:space="preserve">9.56059455871582</t>
   </si>
   <si>
     <t xml:space="preserve">9.4347972869873</t>
@@ -2036,19 +2036,19 @@
     <t xml:space="preserve">9.64445972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51866245269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47672939300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77025699615479</t>
+    <t xml:space="preserve">9.51866340637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47673034667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77025604248047</t>
   </si>
   <si>
     <t xml:space="preserve">9.60252666473389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72832489013672</t>
+    <t xml:space="preserve">9.7283239364624</t>
   </si>
   <si>
     <t xml:space="preserve">10.3153781890869</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">10.1057157516479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3573112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2734470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1476497650146</t>
+    <t xml:space="preserve">10.357310295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2734451293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1476488113403</t>
   </si>
   <si>
     <t xml:space="preserve">10.0218505859375</t>
@@ -2078,19 +2078,19 @@
     <t xml:space="preserve">9.85412120819092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81218910217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8960542678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26706886291504</t>
+    <t xml:space="preserve">9.81218814849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89605331420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26706695556641</t>
   </si>
   <si>
     <t xml:space="preserve">9.97991847991943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68639278411865</t>
+    <t xml:space="preserve">9.68639183044434</t>
   </si>
   <si>
     <t xml:space="preserve">9.05740547180176</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">8.97354030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.399242401123</t>
+    <t xml:space="preserve">10.3992443084717</t>
   </si>
   <si>
     <t xml:space="preserve">10.5669736862183</t>
@@ -2114,13 +2114,13 @@
     <t xml:space="preserve">11.279824256897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.321756362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9443655014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2378921508789</t>
+    <t xml:space="preserve">11.3217573165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9443664550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2378911972046</t>
   </si>
   <si>
     <t xml:space="preserve">11.1959600448608</t>
@@ -2129,13 +2129,13 @@
     <t xml:space="preserve">11.4056224822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1540279388428</t>
+    <t xml:space="preserve">11.1540269851685</t>
   </si>
   <si>
     <t xml:space="preserve">11.7830142974854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7410821914673</t>
+    <t xml:space="preserve">11.741081237793</t>
   </si>
   <si>
     <t xml:space="preserve">12.0346078872681</t>
@@ -2150,13 +2150,13 @@
     <t xml:space="preserve">11.1120948791504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9862976074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0701608657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4894866943359</t>
+    <t xml:space="preserve">10.9862985610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0701627731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4894857406616</t>
   </si>
   <si>
     <t xml:space="preserve">11.3636894226074</t>
@@ -2174,19 +2174,19 @@
     <t xml:space="preserve">11.0282297134399</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4831075668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5250406265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6089038848877</t>
+    <t xml:space="preserve">10.4831085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5250415802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.608904838562</t>
   </si>
   <si>
     <t xml:space="preserve">10.818567276001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9024324417114</t>
+    <t xml:space="preserve">10.9024333953857</t>
   </si>
   <si>
     <t xml:space="preserve">11.4475536346436</t>
@@ -13120,7 +13120,7 @@
         <v>11.75</v>
       </c>
       <c r="G377" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -13146,7 +13146,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G378" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -13172,7 +13172,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G379" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -13198,7 +13198,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G380" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -13250,7 +13250,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G382" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -13302,7 +13302,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G384" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -13380,7 +13380,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G387" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -13406,7 +13406,7 @@
         <v>11.25</v>
       </c>
       <c r="G388" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13432,7 +13432,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G389" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13458,7 +13458,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G390" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -13536,7 +13536,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G393" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13562,7 +13562,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G394" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13588,7 +13588,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G395" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13614,7 +13614,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G396" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13640,7 +13640,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G397" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13692,7 +13692,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G399" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13718,7 +13718,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G400" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13744,7 +13744,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G401" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13770,7 +13770,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G402" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13822,7 +13822,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G404" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13848,7 +13848,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G405" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13952,7 +13952,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G409" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13978,7 +13978,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G410" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -14030,7 +14030,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G412" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -14108,7 +14108,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G415" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -14134,7 +14134,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G416" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -14160,7 +14160,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G417" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -14186,7 +14186,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G418" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -14212,7 +14212,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G419" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -14264,7 +14264,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G421" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -14290,7 +14290,7 @@
         <v>11.75</v>
       </c>
       <c r="G422" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -14316,7 +14316,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G423" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -14368,7 +14368,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G425" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14394,7 +14394,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G426" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14446,7 +14446,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G428" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14472,7 +14472,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G429" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14498,7 +14498,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G430" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14550,7 +14550,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G432" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14602,7 +14602,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G434" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14628,7 +14628,7 @@
         <v>12</v>
       </c>
       <c r="G435" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14654,7 +14654,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G436" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14680,7 +14680,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G437" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14706,7 +14706,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G438" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14732,7 +14732,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G439" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14758,7 +14758,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G440" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14784,7 +14784,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G441" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14810,7 +14810,7 @@
         <v>12.25</v>
       </c>
       <c r="G442" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14836,7 +14836,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G443" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14862,7 +14862,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G444" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14888,7 +14888,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G445" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14914,7 +14914,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G446" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14940,7 +14940,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G447" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14966,7 +14966,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G448" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14992,7 +14992,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G449" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15018,7 +15018,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G450" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15044,7 +15044,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G451" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15070,7 +15070,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G452" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15096,7 +15096,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G453" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15122,7 +15122,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G454" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15148,7 +15148,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G455" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15174,7 +15174,7 @@
         <v>13.3299999237061</v>
       </c>
       <c r="G456" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -15200,7 +15200,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G457" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15226,7 +15226,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G458" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15252,7 +15252,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G459" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -15278,7 +15278,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G460" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -15304,7 +15304,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G461" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15330,7 +15330,7 @@
         <v>13</v>
       </c>
       <c r="G462" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15356,7 +15356,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G463" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15382,7 +15382,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G464" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15408,7 +15408,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G465" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15434,7 +15434,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G466" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15460,7 +15460,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G467" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15486,7 +15486,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G468" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15512,7 +15512,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G469" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15538,7 +15538,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G470" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15564,7 +15564,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G471" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15590,7 +15590,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G472" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15616,7 +15616,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G473" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15642,7 +15642,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G474" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15668,7 +15668,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G475" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15694,7 +15694,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G476" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15720,7 +15720,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G477" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15746,7 +15746,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G478" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15772,7 +15772,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G479" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15798,7 +15798,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G480" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15824,7 +15824,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G481" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15850,7 +15850,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G482" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15928,7 +15928,7 @@
         <v>11</v>
       </c>
       <c r="G485" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15954,7 +15954,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G486" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15980,7 +15980,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G487" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16006,7 +16006,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G488" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -16032,7 +16032,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G489" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16058,7 +16058,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G490" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -16084,7 +16084,7 @@
         <v>12</v>
       </c>
       <c r="G491" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16136,7 +16136,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G493" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16162,7 +16162,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G494" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16188,7 +16188,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G495" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -16214,7 +16214,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G496" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -16240,7 +16240,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G497" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -16266,7 +16266,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G498" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -16292,7 +16292,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G499" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16318,7 +16318,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G500" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -16344,7 +16344,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G501" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16370,7 +16370,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G502" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16396,7 +16396,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G503" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16422,7 +16422,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G504" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16448,7 +16448,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G505" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16500,7 +16500,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G507" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16526,7 +16526,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G508" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16552,7 +16552,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G509" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16578,7 +16578,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G510" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16604,7 +16604,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G511" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16630,7 +16630,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G512" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16656,7 +16656,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G513" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16682,7 +16682,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G514" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16708,7 +16708,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G515" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16734,7 +16734,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G516" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16786,7 +16786,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G518" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16812,7 +16812,7 @@
         <v>11</v>
       </c>
       <c r="G519" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16864,7 +16864,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G521" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16916,7 +16916,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G523" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16942,7 +16942,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G524" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -17020,7 +17020,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G527" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -17046,7 +17046,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G528" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -17072,7 +17072,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G529" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -17098,7 +17098,7 @@
         <v>12</v>
       </c>
       <c r="G530" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17124,7 +17124,7 @@
         <v>12</v>
       </c>
       <c r="G531" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17150,7 +17150,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G532" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17176,7 +17176,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G533" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17202,7 +17202,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G534" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -17228,7 +17228,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G535" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17254,7 +17254,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G536" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17280,7 +17280,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G537" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17306,7 +17306,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G538" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17332,7 +17332,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G539" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17358,7 +17358,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G540" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17384,7 +17384,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G541" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17462,7 +17462,7 @@
         <v>11</v>
       </c>
       <c r="G544" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17488,7 +17488,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G545" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17514,7 +17514,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G546" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17540,7 +17540,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G547" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17618,7 +17618,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G550" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17696,7 +17696,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G553" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17722,7 +17722,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G554" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17774,7 +17774,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G556" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17826,7 +17826,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G558" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17852,7 +17852,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G559" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17878,7 +17878,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G560" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17904,7 +17904,7 @@
         <v>12</v>
       </c>
       <c r="G561" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17930,7 +17930,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G562" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17956,7 +17956,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G563" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17982,7 +17982,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G564" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -18008,7 +18008,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G565" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18034,7 +18034,7 @@
         <v>12</v>
       </c>
       <c r="G566" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18060,7 +18060,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G567" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18086,7 +18086,7 @@
         <v>12</v>
       </c>
       <c r="G568" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18112,7 +18112,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G569" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18138,7 +18138,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G570" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18164,7 +18164,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G571" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18190,7 +18190,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G572" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18216,7 +18216,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G573" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18242,7 +18242,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G574" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18268,7 +18268,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G575" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18294,7 +18294,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G576" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18320,7 +18320,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G577" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18346,7 +18346,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G578" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18372,7 +18372,7 @@
         <v>12.5</v>
       </c>
       <c r="G579" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18398,7 +18398,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G580" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18424,7 +18424,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G581" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18450,7 +18450,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G582" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18476,7 +18476,7 @@
         <v>12.5</v>
       </c>
       <c r="G583" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18502,7 +18502,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G584" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18528,7 +18528,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G585" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18554,7 +18554,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G586" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18580,7 +18580,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G587" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18606,7 +18606,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G588" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18632,7 +18632,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G589" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18658,7 +18658,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G590" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18684,7 +18684,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G591" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18710,7 +18710,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G592" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18736,7 +18736,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G593" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18762,7 +18762,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G594" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18788,7 +18788,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G595" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18814,7 +18814,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G596" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18840,7 +18840,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G597" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18866,7 +18866,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G598" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18892,7 +18892,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G599" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18918,7 +18918,7 @@
         <v>12.5</v>
       </c>
       <c r="G600" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18944,7 +18944,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G601" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18970,7 +18970,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G602" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18996,7 +18996,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G603" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19022,7 +19022,7 @@
         <v>12.5</v>
       </c>
       <c r="G604" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19048,7 +19048,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G605" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19074,7 +19074,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G606" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19100,7 +19100,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G607" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19126,7 +19126,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G608" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19152,7 +19152,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G609" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19178,7 +19178,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G610" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19204,7 +19204,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G611" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19230,7 +19230,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G612" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19256,7 +19256,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G613" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19282,7 +19282,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G614" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19308,7 +19308,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G615" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19334,7 +19334,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G616" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19360,7 +19360,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G617" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19386,7 +19386,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G618" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19412,7 +19412,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G619" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19438,7 +19438,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G620" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19464,7 +19464,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G621" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19490,7 +19490,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G622" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19516,7 +19516,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G623" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19542,7 +19542,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G624" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19568,7 +19568,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G625" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19594,7 +19594,7 @@
         <v>12.5</v>
       </c>
       <c r="G626" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19620,7 +19620,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G627" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19646,7 +19646,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G628" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19672,7 +19672,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G629" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19698,7 +19698,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G630" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19724,7 +19724,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G631" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19750,7 +19750,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G632" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19776,7 +19776,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G633" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19802,7 +19802,7 @@
         <v>12</v>
       </c>
       <c r="G634" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19828,7 +19828,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G635" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19854,7 +19854,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G636" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19880,7 +19880,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G637" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19906,7 +19906,7 @@
         <v>12.5</v>
       </c>
       <c r="G638" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19932,7 +19932,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G639" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19958,7 +19958,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G640" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19984,7 +19984,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G641" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20010,7 +20010,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G642" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20036,7 +20036,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G643" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20062,7 +20062,7 @@
         <v>12</v>
       </c>
       <c r="G644" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20088,7 +20088,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G645" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20114,7 +20114,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G646" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20140,7 +20140,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G647" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20166,7 +20166,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G648" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20192,7 +20192,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G649" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20218,7 +20218,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G650" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20244,7 +20244,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G651" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20270,7 +20270,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G652" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20296,7 +20296,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G653" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20322,7 +20322,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G654" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20348,7 +20348,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G655" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20374,7 +20374,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G656" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20400,7 +20400,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G657" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20426,7 +20426,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G658" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20452,7 +20452,7 @@
         <v>12.5</v>
       </c>
       <c r="G659" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20478,7 +20478,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G660" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20504,7 +20504,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G661" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20530,7 +20530,7 @@
         <v>12.5</v>
       </c>
       <c r="G662" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20556,7 +20556,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G663" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20582,7 +20582,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G664" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20608,7 +20608,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20634,7 +20634,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G666" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20660,7 +20660,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G667" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20686,7 +20686,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G668" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20712,7 +20712,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G669" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20738,7 +20738,7 @@
         <v>12</v>
       </c>
       <c r="G670" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20764,7 +20764,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G671" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20790,7 +20790,7 @@
         <v>11.5</v>
       </c>
       <c r="G672" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20816,7 +20816,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G673" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20842,7 +20842,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G674" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20868,7 +20868,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G675" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20894,7 +20894,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G676" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20920,7 +20920,7 @@
         <v>12</v>
       </c>
       <c r="G677" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20946,7 +20946,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G678" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20972,7 +20972,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G679" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20998,7 +20998,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G680" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21024,7 +21024,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G681" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21050,7 +21050,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G682" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21076,7 +21076,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G683" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21102,7 +21102,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G684" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21128,7 +21128,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G685" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21154,7 +21154,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G686" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21180,7 +21180,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G687" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21206,7 +21206,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G688" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21232,7 +21232,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21258,7 +21258,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G690" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21284,7 +21284,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G691" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21310,7 +21310,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G692" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21336,7 +21336,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G693" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21362,7 +21362,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G694" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21388,7 +21388,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G695" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21414,7 +21414,7 @@
         <v>12.5</v>
       </c>
       <c r="G696" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21440,7 +21440,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G697" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21466,7 +21466,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21492,7 +21492,7 @@
         <v>13</v>
       </c>
       <c r="G699" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21518,7 +21518,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21544,7 +21544,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G701" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21570,7 +21570,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G702" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21596,7 +21596,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G703" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21622,7 +21622,7 @@
         <v>13</v>
       </c>
       <c r="G704" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21648,7 +21648,7 @@
         <v>13</v>
       </c>
       <c r="G705" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21674,7 +21674,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21700,7 +21700,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G707" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21726,7 +21726,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G708" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21752,7 +21752,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G709" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21778,7 +21778,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G710" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21804,7 +21804,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G711" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21830,7 +21830,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G712" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21856,7 +21856,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G713" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21882,7 +21882,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G714" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21908,7 +21908,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G715" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21934,7 +21934,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G716" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21960,7 +21960,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G717" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21986,7 +21986,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G718" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22012,7 +22012,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G719" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22038,7 +22038,7 @@
         <v>11</v>
       </c>
       <c r="G720" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22064,7 +22064,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G721" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22090,7 +22090,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G722" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22116,7 +22116,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G723" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22142,7 +22142,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G724" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22168,7 +22168,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G725" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22194,7 +22194,7 @@
         <v>11.5</v>
       </c>
       <c r="G726" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22220,7 +22220,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G727" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22246,7 +22246,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G728" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22272,7 +22272,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G729" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22298,7 +22298,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G730" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22324,7 +22324,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G731" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22350,7 +22350,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G732" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22376,7 +22376,7 @@
         <v>11.5</v>
       </c>
       <c r="G733" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22402,7 +22402,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G734" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22428,7 +22428,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G735" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22454,7 +22454,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G736" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22480,7 +22480,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G737" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22506,7 +22506,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G738" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22532,7 +22532,7 @@
         <v>11.5</v>
       </c>
       <c r="G739" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22558,7 +22558,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G740" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22584,7 +22584,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G741" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22610,7 +22610,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G742" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22636,7 +22636,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G743" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22662,7 +22662,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G744" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22688,7 +22688,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G745" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22714,7 +22714,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G746" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22740,7 +22740,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G747" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22766,7 +22766,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G748" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22792,7 +22792,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G749" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22818,7 +22818,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G750" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22844,7 +22844,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G751" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22870,7 +22870,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G752" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22896,7 +22896,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G753" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22922,7 +22922,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G754" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22948,7 +22948,7 @@
         <v>11</v>
       </c>
       <c r="G755" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22974,7 +22974,7 @@
         <v>11</v>
       </c>
       <c r="G756" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23000,7 +23000,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G757" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23026,7 +23026,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G758" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23052,7 +23052,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G759" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23078,7 +23078,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G760" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23104,7 +23104,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G761" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23130,7 +23130,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G762" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23156,7 +23156,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G763" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23182,7 +23182,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G764" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23208,7 +23208,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G765" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23234,7 +23234,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G766" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23260,7 +23260,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G767" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23286,7 +23286,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G768" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23312,7 +23312,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G769" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23338,7 +23338,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G770" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23364,7 +23364,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G771" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23390,7 +23390,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G772" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23416,7 +23416,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G773" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23442,7 +23442,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G774" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23468,7 +23468,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G775" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23494,7 +23494,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G776" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23520,7 +23520,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G777" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23546,7 +23546,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G778" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23572,7 +23572,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G779" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23598,7 +23598,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G780" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23624,7 +23624,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G781" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23650,7 +23650,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G782" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23676,7 +23676,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G783" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23702,7 +23702,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23728,7 +23728,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G785" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23754,7 +23754,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G786" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23780,7 +23780,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G787" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23806,7 +23806,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G788" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23832,7 +23832,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G789" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23858,7 +23858,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G790" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23884,7 +23884,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G791" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23910,7 +23910,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G792" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23936,7 +23936,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G793" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23962,7 +23962,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G794" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23988,7 +23988,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G795" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24014,7 +24014,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G796" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24040,7 +24040,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G797" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24066,7 +24066,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G798" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24092,7 +24092,7 @@
         <v>11.5</v>
       </c>
       <c r="G799" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24118,7 +24118,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G800" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24144,7 +24144,7 @@
         <v>11.5</v>
       </c>
       <c r="G801" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24170,7 +24170,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G802" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24196,7 +24196,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G803" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24222,7 +24222,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G804" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24248,7 +24248,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G805" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24274,7 +24274,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G806" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24300,7 +24300,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G807" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24326,7 +24326,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G808" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24352,7 +24352,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G809" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24378,7 +24378,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G810" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24404,7 +24404,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G811" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24430,7 +24430,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G812" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24456,7 +24456,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G813" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24482,7 +24482,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G814" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24508,7 +24508,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G815" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24534,7 +24534,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G816" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24560,7 +24560,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G817" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24586,7 +24586,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G818" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24612,7 +24612,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G819" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24638,7 +24638,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G820" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24664,7 +24664,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G821" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24690,7 +24690,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G822" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24716,7 +24716,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G823" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24742,7 +24742,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G824" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24768,7 +24768,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G825" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24794,7 +24794,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G826" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24820,7 +24820,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G827" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24846,7 +24846,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G828" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24872,7 +24872,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G829" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24898,7 +24898,7 @@
         <v>12</v>
       </c>
       <c r="G830" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24924,7 +24924,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G831" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24950,7 +24950,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G832" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24976,7 +24976,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G833" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25002,7 +25002,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G834" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25028,7 +25028,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G835" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25054,7 +25054,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G836" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25080,7 +25080,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G837" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25106,7 +25106,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G838" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25132,7 +25132,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G839" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25158,7 +25158,7 @@
         <v>11.75</v>
       </c>
       <c r="G840" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25184,7 +25184,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G841" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25210,7 +25210,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G842" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25236,7 +25236,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G843" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25262,7 +25262,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G844" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25288,7 +25288,7 @@
         <v>12</v>
       </c>
       <c r="G845" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25314,7 +25314,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G846" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25340,7 +25340,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G847" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25366,7 +25366,7 @@
         <v>12</v>
       </c>
       <c r="G848" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25392,7 +25392,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G849" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25418,7 +25418,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G850" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25444,7 +25444,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G851" t="s">
-        <v>416</v>
+        <v>476</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25652,7 +25652,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G859" t="s">
-        <v>416</v>
+        <v>476</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25756,7 +25756,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G863" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25834,7 +25834,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G866" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25886,7 +25886,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G868" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25912,7 +25912,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G869" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26354,7 +26354,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G886" t="s">
-        <v>416</v>
+        <v>476</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26406,7 +26406,7 @@
         <v>12</v>
       </c>
       <c r="G888" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26432,7 +26432,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G889" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26484,7 +26484,7 @@
         <v>12</v>
       </c>
       <c r="G891" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26510,7 +26510,7 @@
         <v>12</v>
       </c>
       <c r="G892" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26536,7 +26536,7 @@
         <v>12</v>
       </c>
       <c r="G893" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26562,7 +26562,7 @@
         <v>12</v>
       </c>
       <c r="G894" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26692,7 +26692,7 @@
         <v>12</v>
       </c>
       <c r="G899" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -27264,7 +27264,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G921" t="s">
-        <v>416</v>
+        <v>476</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27524,7 +27524,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G931" t="s">
-        <v>416</v>
+        <v>476</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27706,7 +27706,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G938" t="s">
-        <v>416</v>
+        <v>476</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27966,7 +27966,7 @@
         <v>12</v>
       </c>
       <c r="G948" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27992,7 +27992,7 @@
         <v>12</v>
       </c>
       <c r="G949" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -68014,7 +68014,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6493981481</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>11480</v>
@@ -68035,6 +68035,32 @@
         <v>991</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6493634259</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>8856</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>15.5500001907349</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>15.5500001907349</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>15.6499996185303</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>991</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BEC.MI.xlsx
+++ b/data/BEC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="992">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="991">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96833753585815</t>
+    <t xml:space="preserve">4.96833848953247</t>
   </si>
   <si>
     <t xml:space="preserve">BEC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96180868148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8704080581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87693691253662</t>
+    <t xml:space="preserve">4.9618091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87040758132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87693643569946</t>
   </si>
   <si>
     <t xml:space="preserve">4.92916631698608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77247714996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79859161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83450031280518</t>
+    <t xml:space="preserve">4.77247762680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79859209060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83449983596802</t>
   </si>
   <si>
     <t xml:space="preserve">4.73330545425415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79532814025879</t>
+    <t xml:space="preserve">4.79532766342163</t>
   </si>
   <si>
     <t xml:space="preserve">4.80512094497681</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">4.76594877243042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75942039489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60273122787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69739818572998</t>
+    <t xml:space="preserve">4.7594199180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60273170471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69739723205566</t>
   </si>
   <si>
     <t xml:space="preserve">4.69413280487061</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">4.63537454605103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44277858734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37422657012939</t>
+    <t xml:space="preserve">4.44277715682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37422704696655</t>
   </si>
   <si>
     <t xml:space="preserve">4.18489456176758</t>
@@ -107,31 +107,31 @@
     <t xml:space="preserve">4.08043575286865</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23385953903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40360593795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49174356460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53091526031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43298482894897</t>
+    <t xml:space="preserve">4.2338604927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40360546112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49174404144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53091621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43298530578613</t>
   </si>
   <si>
     <t xml:space="preserve">4.50480127334595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53744411468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42645597457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42319250106812</t>
+    <t xml:space="preserve">4.53744459152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42645645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42319202423096</t>
   </si>
   <si>
     <t xml:space="preserve">4.43951416015625</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">4.46562910079956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47868633270264</t>
+    <t xml:space="preserve">4.47868585586548</t>
   </si>
   <si>
     <t xml:space="preserve">4.60926008224487</t>
@@ -155,22 +155,22 @@
     <t xml:space="preserve">4.89652252197266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90958023071289</t>
+    <t xml:space="preserve">4.90958070755005</t>
   </si>
   <si>
     <t xml:space="preserve">4.93569421768188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91284418106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01403903961182</t>
+    <t xml:space="preserve">4.91284465789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01403951644897</t>
   </si>
   <si>
     <t xml:space="preserve">4.94222354888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03362464904785</t>
+    <t xml:space="preserve">5.03362512588501</t>
   </si>
   <si>
     <t xml:space="preserve">5.04015398025513</t>
@@ -179,19 +179,19 @@
     <t xml:space="preserve">5.09238386154175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94875144958496</t>
+    <t xml:space="preserve">4.94875240325928</t>
   </si>
   <si>
     <t xml:space="preserve">4.99445343017578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84429359436035</t>
+    <t xml:space="preserve">4.84429264068604</t>
   </si>
   <si>
     <t xml:space="preserve">5.0695333480835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09891223907471</t>
+    <t xml:space="preserve">5.09891271591187</t>
   </si>
   <si>
     <t xml:space="preserve">4.98792457580566</t>
@@ -200,16 +200,16 @@
     <t xml:space="preserve">5.0499472618103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04341793060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05973958969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98465967178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02709627151489</t>
+    <t xml:space="preserve">5.04341840744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05974054336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98466062545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02709674835205</t>
   </si>
   <si>
     <t xml:space="preserve">4.99973821640015</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">4.96212005615234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91766357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9450216293335</t>
+    <t xml:space="preserve">4.91766309738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94502115249634</t>
   </si>
   <si>
     <t xml:space="preserve">4.85610675811768</t>
   </si>
   <si>
-    <t xml:space="preserve">4.890305519104</t>
+    <t xml:space="preserve">4.89030456542969</t>
   </si>
   <si>
     <t xml:space="preserve">4.89714479446411</t>
@@ -245,67 +245,67 @@
     <t xml:space="preserve">4.98263931274414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92450284957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00657796859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88346529006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94844150543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95870065689087</t>
+    <t xml:space="preserve">4.9245023727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00657749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88346481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94844198226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95870113372803</t>
   </si>
   <si>
     <t xml:space="preserve">4.99289894104004</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86636590957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85268640518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93134212493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78771162033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78429126739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8253288269043</t>
+    <t xml:space="preserve">4.86636638641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8526873588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93134260177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78771114349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78429174423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82532835006714</t>
   </si>
   <si>
     <t xml:space="preserve">4.77403211593628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7227349281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67485857009888</t>
+    <t xml:space="preserve">4.72273540496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67485809326172</t>
   </si>
   <si>
     <t xml:space="preserve">4.75693321228027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56200456619263</t>
+    <t xml:space="preserve">4.56200504302979</t>
   </si>
   <si>
     <t xml:space="preserve">4.54148578643799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53122711181641</t>
+    <t xml:space="preserve">4.53122663497925</t>
   </si>
   <si>
     <t xml:space="preserve">4.6030421257019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63040065765381</t>
+    <t xml:space="preserve">4.63040113449097</t>
   </si>
   <si>
     <t xml:space="preserve">4.55516481399536</t>
@@ -314,118 +314,118 @@
     <t xml:space="preserve">4.58252334594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54832553863525</t>
+    <t xml:space="preserve">4.5483250617981</t>
   </si>
   <si>
     <t xml:space="preserve">4.45941066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53464651107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52780675888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52096700668335</t>
+    <t xml:space="preserve">4.53464603424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52780628204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52096748352051</t>
   </si>
   <si>
     <t xml:space="preserve">4.64408016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74325370788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73983287811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83558797836304</t>
+    <t xml:space="preserve">4.7432541847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73983430862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8355884552002</t>
   </si>
   <si>
     <t xml:space="preserve">4.92108345031738</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92792320251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98605966567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96553993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91424417495728</t>
+    <t xml:space="preserve">4.92792272567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98605918884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96554088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91424369812012</t>
   </si>
   <si>
     <t xml:space="preserve">4.97237968444824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96895933151245</t>
+    <t xml:space="preserve">4.96896028518677</t>
   </si>
   <si>
     <t xml:space="preserve">4.86978626251221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93818140029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88004541397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9518609046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87320613861084</t>
+    <t xml:space="preserve">4.93818187713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88004589080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95186042785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87320566177368</t>
   </si>
   <si>
     <t xml:space="preserve">4.86294651031494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76719188690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80139017105103</t>
+    <t xml:space="preserve">4.76719236373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80139064788818</t>
   </si>
   <si>
     <t xml:space="preserve">4.80822992324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76377248764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8424277305603</t>
+    <t xml:space="preserve">4.76377296447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84242820739746</t>
   </si>
   <si>
     <t xml:space="preserve">4.72957468032837</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84926700592041</t>
+    <t xml:space="preserve">4.84926748275757</t>
   </si>
   <si>
     <t xml:space="preserve">4.81164979934692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88688516616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02025651931763</t>
+    <t xml:space="preserve">4.88688564300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02025747299194</t>
   </si>
   <si>
     <t xml:space="preserve">5.08865356445312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10575246810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0647144317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04761505126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09549236297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17756795883179</t>
+    <t xml:space="preserve">5.10575199127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06471395492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04761552810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09549188613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17756748199463</t>
   </si>
   <si>
     <t xml:space="preserve">5.23228454589844</t>
@@ -437,37 +437,37 @@
     <t xml:space="preserve">5.13994979858398</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16388893127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21176528930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30751943588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3006796836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13311052322388</t>
+    <t xml:space="preserve">5.1638879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21176624298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30751991271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30068063735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13311004638672</t>
   </si>
   <si>
     <t xml:space="preserve">5.22544431686401</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16730785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19808673858643</t>
+    <t xml:space="preserve">5.16730833053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19808626174927</t>
   </si>
   <si>
     <t xml:space="preserve">5.29726028442383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47167015075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40327405929565</t>
+    <t xml:space="preserve">5.47166967391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4032735824585</t>
   </si>
   <si>
     <t xml:space="preserve">5.36565589904785</t>
@@ -479,22 +479,22 @@
     <t xml:space="preserve">5.46482992172241</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907625198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39643430709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25964260101318</t>
+    <t xml:space="preserve">5.36907529830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39643383026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25964307785034</t>
   </si>
   <si>
     <t xml:space="preserve">5.41353321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46141004562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43747138977051</t>
+    <t xml:space="preserve">5.46141052246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43747186660767</t>
   </si>
   <si>
     <t xml:space="preserve">5.45457077026367</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">5.46824979782104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47508955001831</t>
+    <t xml:space="preserve">5.47508907318115</t>
   </si>
   <si>
     <t xml:space="preserve">5.39985418319702</t>
@@ -512,22 +512,22 @@
     <t xml:space="preserve">5.41695308685303</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43063259124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45799112319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50586795806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52980661392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60846042633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68369770050049</t>
+    <t xml:space="preserve">5.43063163757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45799016952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50586843490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52980613708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60846185684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68369722366333</t>
   </si>
   <si>
     <t xml:space="preserve">5.73157405853271</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">5.9367618560791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94360113143921</t>
+    <t xml:space="preserve">5.94360160827637</t>
   </si>
   <si>
     <t xml:space="preserve">6.05645370483398</t>
@@ -548,61 +548,61 @@
     <t xml:space="preserve">5.94018220901489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04961442947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07355403900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02567672729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97437906265259</t>
+    <t xml:space="preserve">6.04961585998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07355308532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02567625045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97437858581543</t>
   </si>
   <si>
     <t xml:space="preserve">6.04277515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17272663116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39501428604126</t>
+    <t xml:space="preserve">6.17272806167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3950138092041</t>
   </si>
   <si>
     <t xml:space="preserve">6.37449502944946</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46682977676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32661867141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11117219924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89914512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00515651702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22402429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26506185531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39843273162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40527296066284</t>
+    <t xml:space="preserve">6.46683025360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32661771774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11117172241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8991436958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00515747070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2240252494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.265061378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39843463897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4052734375</t>
   </si>
   <si>
     <t xml:space="preserve">6.48050928115845</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41211223602295</t>
+    <t xml:space="preserve">6.41211271286011</t>
   </si>
   <si>
     <t xml:space="preserve">6.44973087310791</t>
@@ -611,82 +611,82 @@
     <t xml:space="preserve">6.43605136871338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52838611602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66859817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99689817428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94218158721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12001037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46882820129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66717720031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20066547393799</t>
+    <t xml:space="preserve">6.52838563919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66859769821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99689769744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94218111038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1200098991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46883010864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66717767715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20066452026367</t>
   </si>
   <si>
     <t xml:space="preserve">8.40585327148438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64523792266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27589988708496</t>
+    <t xml:space="preserve">8.64523887634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27590179443359</t>
   </si>
   <si>
     <t xml:space="preserve">8.35113620758057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28957939147949</t>
+    <t xml:space="preserve">8.28958034515381</t>
   </si>
   <si>
     <t xml:space="preserve">8.24170303344727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33745670318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33061790466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31693840026855</t>
+    <t xml:space="preserve">8.33745574951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3306188583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31693744659424</t>
   </si>
   <si>
     <t xml:space="preserve">8.26906108856201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22118473052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11859035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30325794219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48108768463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72047328948975</t>
+    <t xml:space="preserve">8.22118377685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11858940124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30325698852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48108863830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72047424316406</t>
   </si>
   <si>
     <t xml:space="preserve">8.7136344909668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79469013214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49782276153564</t>
+    <t xml:space="preserve">8.79469108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49782466888428</t>
   </si>
   <si>
     <t xml:space="preserve">8.52751064300537</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">8.31228160858154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43102931976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37165546417236</t>
+    <t xml:space="preserve">8.43102741241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37165451049805</t>
   </si>
   <si>
     <t xml:space="preserve">7.97830486297607</t>
@@ -719,82 +719,82 @@
     <t xml:space="preserve">8.21579933166504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64625835418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75758266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80211162567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69078731536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57946109771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66110038757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54977512359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5200891494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53493118286133</t>
+    <t xml:space="preserve">8.64625549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75758171081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8021125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69078636169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5794620513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66109943389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54977607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52008819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53493213653564</t>
   </si>
   <si>
     <t xml:space="preserve">8.60172653198242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4829797744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59430503845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46813583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14900493621826</t>
+    <t xml:space="preserve">8.48298072814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59430599212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46813678741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14900398254395</t>
   </si>
   <si>
     <t xml:space="preserve">8.31970310211182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12673950195312</t>
+    <t xml:space="preserve">8.12673854827881</t>
   </si>
   <si>
     <t xml:space="preserve">8.46071434020996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58688354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7056303024292</t>
+    <t xml:space="preserve">8.58688449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70562934875488</t>
   </si>
   <si>
     <t xml:space="preserve">8.84664154052734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69820976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7427396774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56461811065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43844985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40876483917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34938907623291</t>
+    <t xml:space="preserve">8.69820880889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74273777008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56461906433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43845081329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40876293182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34939002990723</t>
   </si>
   <si>
     <t xml:space="preserve">8.42360687255859</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">8.63141345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61656951904297</t>
+    <t xml:space="preserve">8.61657047271729</t>
   </si>
   <si>
     <t xml:space="preserve">8.63883495330811</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">8.66852188110352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77984714508057</t>
+    <t xml:space="preserve">8.77984619140625</t>
   </si>
   <si>
     <t xml:space="preserve">8.88375091552734</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">8.83922004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82437896728516</t>
+    <t xml:space="preserve">8.82437705993652</t>
   </si>
   <si>
     <t xml:space="preserve">8.68336486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60914897918701</t>
+    <t xml:space="preserve">8.60914707183838</t>
   </si>
   <si>
     <t xml:space="preserve">8.57204055786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49040126800537</t>
+    <t xml:space="preserve">8.49040031433105</t>
   </si>
   <si>
     <t xml:space="preserve">8.47555828094482</t>
@@ -845,22 +845,22 @@
     <t xml:space="preserve">8.78726863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71305274963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65367794036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62399291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75015926361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90601539611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89859294891357</t>
+    <t xml:space="preserve">8.71305179595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65367889404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62399101257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75016021728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90601444244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89859390258789</t>
   </si>
   <si>
     <t xml:space="preserve">8.94312381744385</t>
@@ -869,16 +869,16 @@
     <t xml:space="preserve">8.77242469787598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96538829803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87632942199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97281169891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09155750274658</t>
+    <t xml:space="preserve">8.96538925170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87632846832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97281074523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09155654907227</t>
   </si>
   <si>
     <t xml:space="preserve">9.2177267074585</t>
@@ -887,37 +887,37 @@
     <t xml:space="preserve">9.52201461791992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55170249938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56654644012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45522022247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47748470306396</t>
+    <t xml:space="preserve">9.55170345306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654453277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45522117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47748565673828</t>
   </si>
   <si>
     <t xml:space="preserve">9.53685855865479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35873699188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59623146057129</t>
+    <t xml:space="preserve">9.35873794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59623241424561</t>
   </si>
   <si>
     <t xml:space="preserve">9.64076137542725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90794372558594</t>
+    <t xml:space="preserve">9.90794277191162</t>
   </si>
   <si>
     <t xml:space="preserve">9.89309883117676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76693058013916</t>
+    <t xml:space="preserve">9.76692962646484</t>
   </si>
   <si>
     <t xml:space="preserve">9.72982215881348</t>
@@ -926,127 +926,127 @@
     <t xml:space="preserve">9.99700260162354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95247268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0563764572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64818477630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95989418029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82630443572998</t>
+    <t xml:space="preserve">9.95247173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0563774108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64818382263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95989322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82630348205566</t>
   </si>
   <si>
     <t xml:space="preserve">9.81146049499512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75208854675293</t>
+    <t xml:space="preserve">9.75208759307861</t>
   </si>
   <si>
     <t xml:space="preserve">9.85599040985107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86341190338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0415334701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0118455886841</t>
+    <t xml:space="preserve">9.86341285705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0415315628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0118465423584</t>
   </si>
   <si>
     <t xml:space="preserve">9.9450511932373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90052032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8317985534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97088479995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25290870666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16384696960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19353485107422</t>
+    <t xml:space="preserve">9.90051937103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83179950714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97088384628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25290775299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16384792327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1935338973999</t>
   </si>
   <si>
     <t xml:space="preserve">8.67594337463379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50524616241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02283573150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06736660003662</t>
+    <t xml:space="preserve">8.50524520874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02283668518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0673656463623</t>
   </si>
   <si>
     <t xml:space="preserve">7.98572826385498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7853422164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7630763053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70370388031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82987117767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64432907104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72596883773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04510021209717</t>
+    <t xml:space="preserve">7.78534126281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76307582855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70370292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82987213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64432954788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72596836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04510116577148</t>
   </si>
   <si>
     <t xml:space="preserve">8.14158248901367</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91893100738525</t>
+    <t xml:space="preserve">7.91893196105957</t>
   </si>
   <si>
     <t xml:space="preserve">8.08963108062744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11931610107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11189556121826</t>
+    <t xml:space="preserve">8.11931705474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11189746856689</t>
   </si>
   <si>
     <t xml:space="preserve">8.09705257415771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00057125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13416194915771</t>
+    <t xml:space="preserve">8.00057029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1341609954834</t>
   </si>
   <si>
     <t xml:space="preserve">8.28259372711182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20837688446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34196853637695</t>
+    <t xml:space="preserve">8.20837783813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34196758270264</t>
   </si>
   <si>
     <t xml:space="preserve">8.44587135314941</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">8.92085933685303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0247631072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32712554931641</t>
+    <t xml:space="preserve">9.02476215362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32712459564209</t>
   </si>
   <si>
     <t xml:space="preserve">8.26775169372559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71854782104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0302562713623</t>
+    <t xml:space="preserve">7.71854734420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03025722503662</t>
   </si>
   <si>
     <t xml:space="preserve">8.01541328430176</t>
@@ -1076,19 +1076,19 @@
     <t xml:space="preserve">8.10447406768799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17869186401367</t>
+    <t xml:space="preserve">8.17869091033936</t>
   </si>
   <si>
     <t xml:space="preserve">8.22322082519531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40133953094482</t>
+    <t xml:space="preserve">8.40134143829346</t>
   </si>
   <si>
     <t xml:space="preserve">9.0544490814209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93570232391357</t>
+    <t xml:space="preserve">8.93570327758789</t>
   </si>
   <si>
     <t xml:space="preserve">8.72789478302002</t>
@@ -1097,58 +1097,58 @@
     <t xml:space="preserve">8.89117240905762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00991916656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27710056304932</t>
+    <t xml:space="preserve">9.00991821289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.277099609375</t>
   </si>
   <si>
     <t xml:space="preserve">9.30678653717041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24741268157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35131645202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5294361114502</t>
+    <t xml:space="preserve">9.24741458892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35131549835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52943801879883</t>
   </si>
   <si>
     <t xml:space="preserve">9.47006416320801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39584636688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54427909851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87083435058594</t>
+    <t xml:space="preserve">9.39584732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54428005218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87083339691162</t>
   </si>
   <si>
     <t xml:space="preserve">9.60365390777588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0637979507446</t>
+    <t xml:space="preserve">10.063796043396</t>
   </si>
   <si>
     <t xml:space="preserve">9.87998390197754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54299259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55830860137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.726806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60426425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46640205383301</t>
+    <t xml:space="preserve">9.54299354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55831050872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72680568695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60426330566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46640300750732</t>
   </si>
   <si>
     <t xml:space="preserve">9.57362747192383</t>
@@ -1157,19 +1157,19 @@
     <t xml:space="preserve">9.6195821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6348991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68085193634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48172092437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43576812744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34386157989502</t>
+    <t xml:space="preserve">9.63489818572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68085384368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48172187805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43576717376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3438606262207</t>
   </si>
   <si>
     <t xml:space="preserve">9.31322479248047</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">9.08345794677734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59328937530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53201866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89964485168457</t>
+    <t xml:space="preserve">8.59328842163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53201770782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89964389801025</t>
   </si>
   <si>
     <t xml:space="preserve">8.96091556549072</t>
@@ -1196,13 +1196,13 @@
     <t xml:space="preserve">9.20600128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49703788757324</t>
+    <t xml:space="preserve">9.49703884124756</t>
   </si>
   <si>
     <t xml:space="preserve">9.51235675811768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52767562866211</t>
+    <t xml:space="preserve">9.52767372131348</t>
   </si>
   <si>
     <t xml:space="preserve">9.38981437683105</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">9.35917854309082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19068241119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86466503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58894729614258</t>
+    <t xml:space="preserve">9.19068145751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86466598510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58894538879395</t>
   </si>
   <si>
     <t xml:space="preserve">9.3285436630249</t>
@@ -1232,67 +1232,67 @@
     <t xml:space="preserve">9.25195407867432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11409282684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14472961425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26727199554443</t>
+    <t xml:space="preserve">9.11409378051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1447286605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26727294921875</t>
   </si>
   <si>
     <t xml:space="preserve">9.45108509063721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69616985321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65021705627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80773735046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06814098358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37449550628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03750610351562</t>
+    <t xml:space="preserve">9.69617080688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6502161026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80773830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06814002990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37449645996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03750419616699</t>
   </si>
   <si>
     <t xml:space="preserve">9.12941074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02218723297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91496276855469</t>
+    <t xml:space="preserve">9.02218532562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91496181488037</t>
   </si>
   <si>
     <t xml:space="preserve">8.94559860229492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17536354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00686836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95657348632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0331611633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91061973571777</t>
+    <t xml:space="preserve">9.17536449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00686931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95657253265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0331621170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91061878204346</t>
   </si>
   <si>
     <t xml:space="preserve">9.97189140319824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78807735443115</t>
+    <t xml:space="preserve">9.78807640075684</t>
   </si>
   <si>
     <t xml:space="preserve">9.75744152069092</t>
@@ -1316,37 +1316,37 @@
     <t xml:space="preserve">8.47074604034424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42479133605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01121139526367</t>
+    <t xml:space="preserve">8.42479228973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01121044158936</t>
   </si>
   <si>
     <t xml:space="preserve">8.225661277771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36352062225342</t>
+    <t xml:space="preserve">8.36352157592773</t>
   </si>
   <si>
     <t xml:space="preserve">8.65456008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77710342407227</t>
+    <t xml:space="preserve">8.77710151672363</t>
   </si>
   <si>
     <t xml:space="preserve">8.8383731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93027877807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62392330169678</t>
+    <t xml:space="preserve">8.93027973175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62392425537109</t>
   </si>
   <si>
     <t xml:space="preserve">8.71583080291748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50138092041016</t>
+    <t xml:space="preserve">8.50138187408447</t>
   </si>
   <si>
     <t xml:space="preserve">8.8230562210083</t>
@@ -1355,19 +1355,19 @@
     <t xml:space="preserve">8.60860633850098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57797145843506</t>
+    <t xml:space="preserve">8.57797050476074</t>
   </si>
   <si>
     <t xml:space="preserve">8.34820365905762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30224895477295</t>
+    <t xml:space="preserve">8.30224990844727</t>
   </si>
   <si>
     <t xml:space="preserve">8.3328857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37883758544922</t>
+    <t xml:space="preserve">8.37883853912354</t>
   </si>
   <si>
     <t xml:space="preserve">8.28693199157715</t>
@@ -1379,67 +1379,67 @@
     <t xml:space="preserve">8.39415740966797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13375377655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11843585968018</t>
+    <t xml:space="preserve">8.13375473022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11843681335449</t>
   </si>
   <si>
     <t xml:space="preserve">8.45542812347412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79241943359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85369110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70051383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66987609863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68519496917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54733371734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44011116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88432693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40513324737549</t>
+    <t xml:space="preserve">8.79242038726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85369205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70051288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66987705230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68519592285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54733467102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.440110206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88432502746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40513229370117</t>
   </si>
   <si>
     <t xml:space="preserve">9.92593669891357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80339527130127</t>
+    <t xml:space="preserve">9.80339431762695</t>
   </si>
   <si>
     <t xml:space="preserve">9.29790592193604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22897720336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07579803466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15238666534424</t>
+    <t xml:space="preserve">9.22897815704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0757999420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15238857269287</t>
   </si>
   <si>
     <t xml:space="preserve">8.99921035766602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59735012054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31742763519287</t>
+    <t xml:space="preserve">9.59734916687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31742572784424</t>
   </si>
   <si>
     <t xml:space="preserve">9.03750514984131</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">8.79757022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87754821777344</t>
+    <t xml:space="preserve">8.87754917144775</t>
   </si>
   <si>
     <t xml:space="preserve">8.83755970001221</t>
@@ -1457,13 +1457,13 @@
     <t xml:space="preserve">8.63761425018311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23745059967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27743911743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47738265991211</t>
+    <t xml:space="preserve">9.23744964599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27743721008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47738361358643</t>
   </si>
   <si>
     <t xml:space="preserve">9.3574161529541</t>
@@ -1472,13 +1472,13 @@
     <t xml:space="preserve">9.51737213134766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67732810974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63733768463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39740467071533</t>
+    <t xml:space="preserve">9.67732906341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63733959197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39740562438965</t>
   </si>
   <si>
     <t xml:space="preserve">9.19746112823486</t>
@@ -1490,22 +1490,22 @@
     <t xml:space="preserve">9.43739414215088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55736064910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11748123168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71759223937988</t>
+    <t xml:space="preserve">9.5573616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11748218536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7175931930542</t>
   </si>
   <si>
     <t xml:space="preserve">8.95752716064453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99751472473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.157470703125</t>
+    <t xml:space="preserve">8.99751567840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15747261047363</t>
   </si>
   <si>
     <t xml:space="preserve">8.91753768920898</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">10.1172065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91726016998291</t>
+    <t xml:space="preserve">9.91726207733154</t>
   </si>
   <si>
     <t xml:space="preserve">9.997239112854</t>
@@ -1538,82 +1538,82 @@
     <t xml:space="preserve">9.75730609893799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71731662750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79729557037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83728504180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1571969985962</t>
+    <t xml:space="preserve">9.71731758117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79729461669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83728408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1571950912476</t>
   </si>
   <si>
     <t xml:space="preserve">10.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2371740341187</t>
+    <t xml:space="preserve">10.2371730804443</t>
   </si>
   <si>
     <t xml:space="preserve">10.3971290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5570840835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4771060943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1971836090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5170955657959</t>
+    <t xml:space="preserve">10.5570850372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4771070480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1971845626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5170965194702</t>
   </si>
   <si>
     <t xml:space="preserve">10.9969635009766</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1169300079346</t>
+    <t xml:space="preserve">11.1169309616089</t>
   </si>
   <si>
     <t xml:space="preserve">11.3168754577637</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2368974685669</t>
+    <t xml:space="preserve">11.2368965148926</t>
   </si>
   <si>
     <t xml:space="preserve">11.3568639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.19690990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.837007522583</t>
+    <t xml:space="preserve">11.1969079971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8370084762573</t>
   </si>
   <si>
     <t xml:space="preserve">11.1569194793701</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0369520187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8769969940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9169864654541</t>
+    <t xml:space="preserve">11.0369529724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8769979476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9169855117798</t>
   </si>
   <si>
     <t xml:space="preserve">10.956974029541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7570295333862</t>
+    <t xml:space="preserve">10.7570285797119</t>
   </si>
   <si>
     <t xml:space="preserve">10.5970735549927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4371194839478</t>
+    <t xml:space="preserve">10.4371175765991</t>
   </si>
   <si>
     <t xml:space="preserve">11.2768869400024</t>
@@ -1622,34 +1622,34 @@
     <t xml:space="preserve">11.4368419647217</t>
   </si>
   <si>
-    <t xml:space="preserve">11.556809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.676775932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7170419692993</t>
+    <t xml:space="preserve">11.5568084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6767768859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.717041015625</t>
   </si>
   <si>
     <t xml:space="preserve">8.11775779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16602182388306</t>
+    <t xml:space="preserve">7.16602087020874</t>
   </si>
   <si>
     <t xml:space="preserve">7.88582229614258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46993684768677</t>
+    <t xml:space="preserve">7.46993780136108</t>
   </si>
   <si>
     <t xml:space="preserve">7.03805685043335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91009187698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39823293685913</t>
+    <t xml:space="preserve">6.91009330749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39823341369629</t>
   </si>
   <si>
     <t xml:space="preserve">6.20628643035889</t>
@@ -1661,28 +1661,28 @@
     <t xml:space="preserve">6.55818891525269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30998229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40595579147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32597732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11803483963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73414087295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9740743637085</t>
+    <t xml:space="preserve">7.30998182296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40595531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32597637176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11803388595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73414039611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97407531738281</t>
   </si>
   <si>
     <t xml:space="preserve">7.29398584365845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15002536773682</t>
+    <t xml:space="preserve">7.15002489089966</t>
   </si>
   <si>
     <t xml:space="preserve">6.86210489273071</t>
@@ -1691,64 +1691,64 @@
     <t xml:space="preserve">6.8141188621521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76613235473633</t>
+    <t xml:space="preserve">6.76613187789917</t>
   </si>
   <si>
     <t xml:space="preserve">6.94208335876465</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79812335968018</t>
+    <t xml:space="preserve">6.79812240600586</t>
   </si>
   <si>
     <t xml:space="preserve">6.92608833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78212690353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83011388778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92877912521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01067972183228</t>
+    <t xml:space="preserve">6.78212785720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83011436462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92877960205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01068019866943</t>
   </si>
   <si>
     <t xml:space="preserve">6.89601898193359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96153974533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73221826553345</t>
+    <t xml:space="preserve">6.96153879165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73221874237061</t>
   </si>
   <si>
     <t xml:space="preserve">6.74859762191772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05981969833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1253399848938</t>
+    <t xml:space="preserve">7.0598201751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12534046173096</t>
   </si>
   <si>
     <t xml:space="preserve">7.22362041473389</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5512228012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56760263442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0262451171875</t>
+    <t xml:space="preserve">7.55122232437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56760215759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02624607086182</t>
   </si>
   <si>
     <t xml:space="preserve">8.31289672851562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39479827880859</t>
+    <t xml:space="preserve">8.39479637145996</t>
   </si>
   <si>
     <t xml:space="preserve">8.72239875793457</t>
@@ -1757,34 +1757,34 @@
     <t xml:space="preserve">8.76334953308105</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88620185852051</t>
+    <t xml:space="preserve">8.88620090484619</t>
   </si>
   <si>
     <t xml:space="preserve">9.1728515625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41855335235596</t>
+    <t xml:space="preserve">9.41855430603027</t>
   </si>
   <si>
     <t xml:space="preserve">8.92714977264404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13190078735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96810054779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33665180206299</t>
+    <t xml:space="preserve">9.13190174102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96809959411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3366527557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.84524917602539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09095096588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21380138397217</t>
+    <t xml:space="preserve">9.09095191955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21380233764648</t>
   </si>
   <si>
     <t xml:space="preserve">9.25475215911865</t>
@@ -1799,58 +1799,58 @@
     <t xml:space="preserve">8.09176540374756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17366504669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1900463104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10814571380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15728569030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96072578430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87882423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71502351760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78054428100586</t>
+    <t xml:space="preserve">8.17366600036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19004726409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10814666748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15728664398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96072626113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87882375717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71502304077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7805438041687</t>
   </si>
   <si>
     <t xml:space="preserve">7.58398342132568</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51846218109131</t>
+    <t xml:space="preserve">7.51846265792847</t>
   </si>
   <si>
     <t xml:space="preserve">7.5348424911499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33828163146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4857029914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61674213409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69864320755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76416397094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73140287399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79692411422729</t>
+    <t xml:space="preserve">7.33828067779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48570251464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61674308776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69864225387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76416301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73140382766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79692459106445</t>
   </si>
   <si>
     <t xml:space="preserve">7.66588306427002</t>
@@ -1859,19 +1859,19 @@
     <t xml:space="preserve">7.63312244415283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64950275421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68226337432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82968378067017</t>
+    <t xml:space="preserve">7.64950323104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68226385116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82968473434448</t>
   </si>
   <si>
     <t xml:space="preserve">7.74778366088867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43656158447266</t>
+    <t xml:space="preserve">7.43656206130981</t>
   </si>
   <si>
     <t xml:space="preserve">7.6003623008728</t>
@@ -1883,28 +1883,28 @@
     <t xml:space="preserve">7.40380144119263</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24000120162964</t>
+    <t xml:space="preserve">7.2400016784668</t>
   </si>
   <si>
     <t xml:space="preserve">7.19086027145386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79773855209351</t>
+    <t xml:space="preserve">6.79773902893066</t>
   </si>
   <si>
     <t xml:space="preserve">6.68307733535767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56841802597046</t>
+    <t xml:space="preserve">6.5684175491333</t>
   </si>
   <si>
     <t xml:space="preserve">6.38823652267456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2244348526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48651695251465</t>
+    <t xml:space="preserve">6.22443532943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48651647567749</t>
   </si>
   <si>
     <t xml:space="preserve">6.42099618911743</t>
@@ -1916,10 +1916,10 @@
     <t xml:space="preserve">6.84687805175781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0434398651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92796516418457</t>
+    <t xml:space="preserve">7.04344034194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92796468734741</t>
   </si>
   <si>
     <t xml:space="preserve">8.5176477432251</t>
@@ -1928,16 +1928,16 @@
     <t xml:space="preserve">8.27194690704346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97710514068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84606409072876</t>
+    <t xml:space="preserve">7.97710418701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8460636138916</t>
   </si>
   <si>
     <t xml:space="preserve">8.12452507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59954929351807</t>
+    <t xml:space="preserve">8.59954833984375</t>
   </si>
   <si>
     <t xml:space="preserve">8.43574714660645</t>
@@ -1946,25 +1946,25 @@
     <t xml:space="preserve">8.55859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6814489364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47669887542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35384750366211</t>
+    <t xml:space="preserve">8.68144989013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47669792175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35384654998779</t>
   </si>
   <si>
     <t xml:space="preserve">8.23099613189697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04262447357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94434547424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86244440078735</t>
+    <t xml:space="preserve">8.04262542724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94434452056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86244487762451</t>
   </si>
   <si>
     <t xml:space="preserve">8.00986576080322</t>
@@ -1982,52 +1982,52 @@
     <t xml:space="preserve">10.1556568145752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86900520324707</t>
+    <t xml:space="preserve">9.86900615692139</t>
   </si>
   <si>
     <t xml:space="preserve">9.62330341339111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50045394897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37760257720947</t>
+    <t xml:space="preserve">9.50045299530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37760353088379</t>
   </si>
   <si>
     <t xml:space="preserve">9.58235359191895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70520496368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05000114440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54140377044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22513484954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18320274353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09933948516846</t>
+    <t xml:space="preserve">9.70520401000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05000019073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54140281677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22513580322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18320083618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09933853149414</t>
   </si>
   <si>
     <t xml:space="preserve">9.14126968383789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39286518096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30900001525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5605936050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43479633331299</t>
+    <t xml:space="preserve">9.39286422729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30900096893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56059455871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4347972869873</t>
   </si>
   <si>
     <t xml:space="preserve">9.35093212127686</t>
@@ -2042,13 +2042,13 @@
     <t xml:space="preserve">9.47672939300537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77025699615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60252666473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72832489013672</t>
+    <t xml:space="preserve">9.77025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6025276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7283239364624</t>
   </si>
   <si>
     <t xml:space="preserve">10.3153791427612</t>
@@ -2060,22 +2060,22 @@
     <t xml:space="preserve">10.2315139770508</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1057157516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3573112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2734460830688</t>
+    <t xml:space="preserve">10.1057167053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.357310295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2734451293945</t>
   </si>
   <si>
     <t xml:space="preserve">10.1476488113403</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0218505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85412120819092</t>
+    <t xml:space="preserve">10.0218515396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85412216186523</t>
   </si>
   <si>
     <t xml:space="preserve">9.81218910217285</t>
@@ -2090,10 +2090,10 @@
     <t xml:space="preserve">9.97991847991943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68639278411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05740451812744</t>
+    <t xml:space="preserve">9.68639183044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05740547180176</t>
   </si>
   <si>
     <t xml:space="preserve">8.97354030609131</t>
@@ -2102,34 +2102,34 @@
     <t xml:space="preserve">10.399242401123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5669727325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7766351699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7347040176392</t>
+    <t xml:space="preserve">10.5669736862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7766361236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7347030639648</t>
   </si>
   <si>
     <t xml:space="preserve">11.279824256897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3217573165894</t>
+    <t xml:space="preserve">11.321756362915</t>
   </si>
   <si>
     <t xml:space="preserve">10.9443655014038</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2378921508789</t>
+    <t xml:space="preserve">11.2378911972046</t>
   </si>
   <si>
     <t xml:space="preserve">11.1959600448608</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4056215286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1540279388428</t>
+    <t xml:space="preserve">11.4056224822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1540269851685</t>
   </si>
   <si>
     <t xml:space="preserve">11.783013343811</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">11.7410821914673</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0346078872681</t>
+    <t xml:space="preserve">12.0346088409424</t>
   </si>
   <si>
     <t xml:space="preserve">11.6152839660645</t>
@@ -2150,10 +2150,10 @@
     <t xml:space="preserve">11.1120939254761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9862966537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0701608657837</t>
+    <t xml:space="preserve">10.9862976074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0701627731323</t>
   </si>
   <si>
     <t xml:space="preserve">11.4894857406616</t>
@@ -2162,13 +2162,13 @@
     <t xml:space="preserve">11.3636894226074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6991491317749</t>
+    <t xml:space="preserve">11.6991481781006</t>
   </si>
   <si>
     <t xml:space="preserve">11.5733509063721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.531418800354</t>
+    <t xml:space="preserve">11.5314197540283</t>
   </si>
   <si>
     <t xml:space="preserve">11.0282297134399</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">10.4831075668335</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5250406265259</t>
+    <t xml:space="preserve">10.5250415802002</t>
   </si>
   <si>
     <t xml:space="preserve">10.608904838562</t>
@@ -2186,10 +2186,10 @@
     <t xml:space="preserve">10.818567276001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9024324417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4475545883179</t>
+    <t xml:space="preserve">10.9024314880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4475536346436</t>
   </si>
   <si>
     <t xml:space="preserve">11.1378631591797</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">11.6969060897827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4388875961304</t>
+    <t xml:space="preserve">11.4388866424561</t>
   </si>
   <si>
     <t xml:space="preserve">11.5248928070068</t>
@@ -2222,13 +2222,13 @@
     <t xml:space="preserve">11.5678958892822</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7399101257324</t>
+    <t xml:space="preserve">11.7399091720581</t>
   </si>
   <si>
     <t xml:space="preserve">11.2238702774048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0518560409546</t>
+    <t xml:space="preserve">11.0518569946289</t>
   </si>
   <si>
     <t xml:space="preserve">11.0088539123535</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">10.9658489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7508325576782</t>
+    <t xml:space="preserve">10.7508335113525</t>
   </si>
   <si>
     <t xml:space="preserve">10.8798427581787</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">10.6648254394531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9228467941284</t>
+    <t xml:space="preserve">10.9228458404541</t>
   </si>
   <si>
     <t xml:space="preserve">10.7078294754028</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">10.1487865447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97677326202393</t>
+    <t xml:space="preserve">9.97677230834961</t>
   </si>
   <si>
     <t xml:space="preserve">9.89076614379883</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">9.84776210784912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46073246002197</t>
+    <t xml:space="preserve">9.46073341369629</t>
   </si>
   <si>
     <t xml:space="preserve">9.54673957824707</t>
@@ -2288,10 +2288,10 @@
     <t xml:space="preserve">9.20271301269531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03070068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15970897674561</t>
+    <t xml:space="preserve">9.03069972991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15970993041992</t>
   </si>
   <si>
     <t xml:space="preserve">10.277795791626</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">9.93377017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80475902557373</t>
+    <t xml:space="preserve">9.80475997924805</t>
   </si>
   <si>
     <t xml:space="preserve">9.71875286102295</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">9.41772937774658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33172416687012</t>
+    <t xml:space="preserve">9.3317232131958</t>
   </si>
   <si>
     <t xml:space="preserve">9.37472534179688</t>
@@ -2345,10 +2345,10 @@
     <t xml:space="preserve">11.1808662414551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7938365936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3528785705566</t>
+    <t xml:space="preserve">10.7938356399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.352879524231</t>
   </si>
   <si>
     <t xml:space="preserve">11.4818897247314</t>
@@ -2360,10 +2360,10 @@
     <t xml:space="preserve">11.9549255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0409336090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8689193725586</t>
+    <t xml:space="preserve">12.0409326553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8689203262329</t>
   </si>
   <si>
     <t xml:space="preserve">11.7829122543335</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">11.9979295730591</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3419561386108</t>
+    <t xml:space="preserve">12.3419570922852</t>
   </si>
   <si>
     <t xml:space="preserve">12.4709663391113</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">12.2989530563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5139694213867</t>
+    <t xml:space="preserve">12.513970375061</t>
   </si>
   <si>
     <t xml:space="preserve">12.5569725036621</t>
@@ -2393,13 +2393,13 @@
     <t xml:space="preserve">12.2559490203857</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3849592208862</t>
+    <t xml:space="preserve">12.3849582672119</t>
   </si>
   <si>
     <t xml:space="preserve">12.5999755859375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6859827041626</t>
+    <t xml:space="preserve">12.6859817504883</t>
   </si>
   <si>
     <t xml:space="preserve">12.7719898223877</t>
@@ -2408,10 +2408,10 @@
     <t xml:space="preserve">12.7289867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9997711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.820463180542</t>
+    <t xml:space="preserve">12.9997701644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8204641342163</t>
   </si>
   <si>
     <t xml:space="preserve">12.9549436569214</t>
@@ -2423,28 +2423,28 @@
     <t xml:space="preserve">13.4480381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0894250869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2239036560059</t>
+    <t xml:space="preserve">13.0894241333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2239046096802</t>
   </si>
   <si>
     <t xml:space="preserve">13.3583841323853</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1342506408691</t>
+    <t xml:space="preserve">13.1342496871948</t>
   </si>
   <si>
     <t xml:space="preserve">13.0445976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1790781021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3135576248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2687311172485</t>
+    <t xml:space="preserve">13.1790771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3135585784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2687320709229</t>
   </si>
   <si>
     <t xml:space="preserve">12.8652906417847</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">13.7618265151978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7928428649902</t>
+    <t xml:space="preserve">14.7928419113159</t>
   </si>
   <si>
     <t xml:space="preserve">14.1652669906616</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">13.8963060379028</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4032106399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5825185775757</t>
+    <t xml:space="preserve">13.4032115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5825176239014</t>
   </si>
   <si>
     <t xml:space="preserve">13.492865562439</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">13.6721725463867</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9411334991455</t>
+    <t xml:space="preserve">13.9411325454712</t>
   </si>
   <si>
     <t xml:space="preserve">13.7169990539551</t>
@@ -2495,22 +2495,22 @@
     <t xml:space="preserve">14.3445739746094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9859609603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5238819122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2997465133667</t>
+    <t xml:space="preserve">13.9859600067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5238828659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.299747467041</t>
   </si>
   <si>
     <t xml:space="preserve">14.4342279434204</t>
   </si>
   <si>
-    <t xml:space="preserve">14.21009349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3894004821777</t>
+    <t xml:space="preserve">14.2100944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3893995285034</t>
   </si>
   <si>
     <t xml:space="preserve">14.6135339736938</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">15.0169763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1962833404541</t>
+    <t xml:space="preserve">15.1962842941284</t>
   </si>
   <si>
     <t xml:space="preserve">15.3307638168335</t>
@@ -2546,19 +2546,19 @@
     <t xml:space="preserve">15.4204187393188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3755893707275</t>
+    <t xml:space="preserve">15.3755912780762</t>
   </si>
   <si>
     <t xml:space="preserve">14.8376684188843</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8824968338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1514558792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7790327072144</t>
+    <t xml:space="preserve">14.882495880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1514568328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.77903175354</t>
   </si>
   <si>
     <t xml:space="preserve">17.0341815948486</t>
@@ -2570,22 +2570,22 @@
     <t xml:space="preserve">16.5859146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8686857223511</t>
+    <t xml:space="preserve">15.8686866760254</t>
   </si>
   <si>
     <t xml:space="preserve">16.0479907989502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7342052459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9583387374878</t>
+    <t xml:space="preserve">15.7342042922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9583377838135</t>
   </si>
   <si>
     <t xml:space="preserve">16.1376457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8100471496582</t>
+    <t xml:space="preserve">16.8100490570068</t>
   </si>
   <si>
     <t xml:space="preserve">16.7203941345215</t>
@@ -2594,13 +2594,13 @@
     <t xml:space="preserve">16.4066066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2721271514893</t>
+    <t xml:space="preserve">16.2721252441406</t>
   </si>
   <si>
     <t xml:space="preserve">16.0928211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9135131835938</t>
+    <t xml:space="preserve">15.9135122299194</t>
   </si>
   <si>
     <t xml:space="preserve">15.4652442932129</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">15.644552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8238582611084</t>
+    <t xml:space="preserve">15.8238592147827</t>
   </si>
   <si>
     <t xml:space="preserve">15.689377784729</t>
@@ -2685,9 +2685,6 @@
   </si>
   <si>
     <t xml:space="preserve">15.0579290390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1514568328857</t>
   </si>
   <si>
     <t xml:space="preserve">15.1982202529907</t>
@@ -59296,7 +59293,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2153" t="s">
-        <v>891</v>
+        <v>847</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59322,7 +59319,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2154" t="s">
-        <v>891</v>
+        <v>847</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59348,7 +59345,7 @@
         <v>16.25</v>
       </c>
       <c r="G2155" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59400,7 +59397,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2157" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59426,7 +59423,7 @@
         <v>15</v>
       </c>
       <c r="G2158" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59452,7 +59449,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2159" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59478,7 +59475,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2160" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59504,7 +59501,7 @@
         <v>15.25</v>
       </c>
       <c r="G2161" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59530,7 +59527,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2162" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59556,7 +59553,7 @@
         <v>15.25</v>
       </c>
       <c r="G2163" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59582,7 +59579,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2164" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59634,7 +59631,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2166" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59660,7 +59657,7 @@
         <v>16.25</v>
       </c>
       <c r="G2167" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59712,7 +59709,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2169" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59738,7 +59735,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2170" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59790,7 +59787,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59816,7 +59813,7 @@
         <v>16</v>
       </c>
       <c r="G2173" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59868,7 +59865,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2175" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59894,7 +59891,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2176" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59920,7 +59917,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2177" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59946,7 +59943,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2178" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59972,7 +59969,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2179" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -59998,7 +59995,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60024,7 +60021,7 @@
         <v>15.25</v>
       </c>
       <c r="G2181" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60050,7 +60047,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60076,7 +60073,7 @@
         <v>15.25</v>
       </c>
       <c r="G2183" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60102,7 +60099,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2184" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60128,7 +60125,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2185" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60154,7 +60151,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2186" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60180,7 +60177,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60206,7 +60203,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2188" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60232,7 +60229,7 @@
         <v>15</v>
       </c>
       <c r="G2189" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60258,7 +60255,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2190" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60284,7 +60281,7 @@
         <v>15</v>
       </c>
       <c r="G2191" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60310,7 +60307,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2192" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60336,7 +60333,7 @@
         <v>15</v>
       </c>
       <c r="G2193" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60362,7 +60359,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2194" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60388,7 +60385,7 @@
         <v>15</v>
       </c>
       <c r="G2195" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60414,7 +60411,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2196" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60440,7 +60437,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2197" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60466,7 +60463,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60492,7 +60489,7 @@
         <v>15</v>
       </c>
       <c r="G2199" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60518,7 +60515,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G2200" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60544,7 +60541,7 @@
         <v>15</v>
       </c>
       <c r="G2201" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60570,7 +60567,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60596,7 +60593,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2203" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60622,7 +60619,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2204" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60648,7 +60645,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60674,7 +60671,7 @@
         <v>14.5</v>
       </c>
       <c r="G2206" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60700,7 +60697,7 @@
         <v>14.5</v>
       </c>
       <c r="G2207" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60726,7 +60723,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60752,7 +60749,7 @@
         <v>14.5</v>
       </c>
       <c r="G2209" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60778,7 +60775,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60804,7 +60801,7 @@
         <v>14.5</v>
       </c>
       <c r="G2211" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60830,7 +60827,7 @@
         <v>14.5</v>
       </c>
       <c r="G2212" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60856,7 +60853,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60882,7 +60879,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2214" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60908,7 +60905,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2215" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60934,7 +60931,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2216" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60960,7 +60957,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2217" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -60986,7 +60983,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2218" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61012,7 +61009,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2219" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61038,7 +61035,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2220" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61064,7 +61061,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2221" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61090,7 +61087,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2222" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61116,7 +61113,7 @@
         <v>15</v>
       </c>
       <c r="G2223" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61142,7 +61139,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61168,7 +61165,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2225" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61194,7 +61191,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2226" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61220,7 +61217,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2227" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61246,7 +61243,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61272,7 +61269,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2229" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61298,7 +61295,7 @@
         <v>15.25</v>
       </c>
       <c r="G2230" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61324,7 +61321,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2231" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61350,7 +61347,7 @@
         <v>15.5</v>
       </c>
       <c r="G2232" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61376,7 +61373,7 @@
         <v>15.5</v>
       </c>
       <c r="G2233" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61402,7 +61399,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2234" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61428,7 +61425,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2235" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61454,7 +61451,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2236" t="s">
-        <v>891</v>
+        <v>847</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61480,7 +61477,7 @@
         <v>16</v>
       </c>
       <c r="G2237" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61506,7 +61503,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2238" t="s">
-        <v>891</v>
+        <v>847</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61532,7 +61529,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2239" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61558,7 +61555,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2240" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61662,7 +61659,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2244" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61688,7 +61685,7 @@
         <v>17.25</v>
       </c>
       <c r="G2245" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61740,7 +61737,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2247" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61818,7 +61815,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2250" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61844,7 +61841,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61870,7 +61867,7 @@
         <v>17.25</v>
       </c>
       <c r="G2252" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61896,7 +61893,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2253" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61922,7 +61919,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2254" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61948,7 +61945,7 @@
         <v>17.75</v>
       </c>
       <c r="G2255" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61974,7 +61971,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G2256" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62000,7 +61997,7 @@
         <v>18</v>
       </c>
       <c r="G2257" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62104,7 +62101,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2261" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62260,7 +62257,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2267" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62286,7 +62283,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2268" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62312,7 +62309,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2269" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62338,7 +62335,7 @@
         <v>15.5</v>
       </c>
       <c r="G2270" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62598,7 +62595,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2280" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62624,7 +62621,7 @@
         <v>16</v>
       </c>
       <c r="G2281" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62650,7 +62647,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62676,7 +62673,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2283" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62702,7 +62699,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2284" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62728,7 +62725,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2285" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62754,7 +62751,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62858,7 +62855,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62962,7 +62959,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2294" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63014,7 +63011,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2296" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63040,7 +63037,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2297" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63066,7 +63063,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2298" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63092,7 +63089,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63118,7 +63115,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63144,7 +63141,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63170,7 +63167,7 @@
         <v>16</v>
       </c>
       <c r="G2302" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63196,7 +63193,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2303" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63222,7 +63219,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2304" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63248,7 +63245,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63274,7 +63271,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2306" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63300,7 +63297,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2307" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63326,7 +63323,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2308" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63352,7 +63349,7 @@
         <v>15.75</v>
       </c>
       <c r="G2309" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63378,7 +63375,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2310" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63404,7 +63401,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2311" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63430,7 +63427,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63456,7 +63453,7 @@
         <v>16</v>
       </c>
       <c r="G2313" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63482,7 +63479,7 @@
         <v>16</v>
       </c>
       <c r="G2314" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63508,7 +63505,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2315" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63534,7 +63531,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2316" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63586,7 +63583,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>891</v>
+        <v>847</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63612,7 +63609,7 @@
         <v>16</v>
       </c>
       <c r="G2319" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63638,7 +63635,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2320" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63664,7 +63661,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2321" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63690,7 +63687,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2322" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63716,7 +63713,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2323" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63742,7 +63739,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2324" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63768,7 +63765,7 @@
         <v>16</v>
       </c>
       <c r="G2325" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63794,7 +63791,7 @@
         <v>16</v>
       </c>
       <c r="G2326" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63820,7 +63817,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2327" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63846,7 +63843,7 @@
         <v>16</v>
       </c>
       <c r="G2328" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63872,7 +63869,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2329" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63898,7 +63895,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2330" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63924,7 +63921,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2331" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63950,7 +63947,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63976,7 +63973,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64002,7 +63999,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2334" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64028,7 +64025,7 @@
         <v>15.75</v>
       </c>
       <c r="G2335" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64054,7 +64051,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2336" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64080,7 +64077,7 @@
         <v>15.75</v>
       </c>
       <c r="G2337" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64106,7 +64103,7 @@
         <v>15.25</v>
       </c>
       <c r="G2338" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64132,7 +64129,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2339" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64158,7 +64155,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2340" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64184,7 +64181,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2341" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64210,7 +64207,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64236,7 +64233,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64262,7 +64259,7 @@
         <v>15.5</v>
       </c>
       <c r="G2344" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64288,7 +64285,7 @@
         <v>15.5</v>
       </c>
       <c r="G2345" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64314,7 +64311,7 @@
         <v>15</v>
       </c>
       <c r="G2346" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64340,7 +64337,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64366,7 +64363,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64392,7 +64389,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2349" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64444,7 +64441,7 @@
         <v>16</v>
       </c>
       <c r="G2351" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64470,7 +64467,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64496,7 +64493,7 @@
         <v>15.75</v>
       </c>
       <c r="G2353" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64522,7 +64519,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64548,7 +64545,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2355" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64574,7 +64571,7 @@
         <v>15.25</v>
       </c>
       <c r="G2356" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64600,7 +64597,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2357" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64626,7 +64623,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64652,7 +64649,7 @@
         <v>14</v>
       </c>
       <c r="G2359" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64678,7 +64675,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2360" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64704,7 +64701,7 @@
         <v>15</v>
       </c>
       <c r="G2361" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64730,7 +64727,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2362" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64756,7 +64753,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2363" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64782,7 +64779,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2364" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64808,7 +64805,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64834,7 +64831,7 @@
         <v>14.5</v>
       </c>
       <c r="G2366" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64860,7 +64857,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2367" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64886,7 +64883,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2368" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64912,7 +64909,7 @@
         <v>15</v>
       </c>
       <c r="G2369" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64938,7 +64935,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2370" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64964,7 +64961,7 @@
         <v>15.25</v>
       </c>
       <c r="G2371" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64990,7 +64987,7 @@
         <v>15.25</v>
       </c>
       <c r="G2372" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65016,7 +65013,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2373" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65042,7 +65039,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2374" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65068,7 +65065,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2375" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65094,7 +65091,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2376" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65120,7 +65117,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65146,7 +65143,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2378" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65172,7 +65169,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2379" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65198,7 +65195,7 @@
         <v>15.25</v>
       </c>
       <c r="G2380" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65224,7 +65221,7 @@
         <v>15.25</v>
       </c>
       <c r="G2381" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65250,7 +65247,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2382" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65276,7 +65273,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2383" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65302,7 +65299,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65328,7 +65325,7 @@
         <v>16</v>
       </c>
       <c r="G2385" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65354,7 +65351,7 @@
         <v>16.25</v>
       </c>
       <c r="G2386" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65380,7 +65377,7 @@
         <v>16</v>
       </c>
       <c r="G2387" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65406,7 +65403,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2388" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65432,7 +65429,7 @@
         <v>16.5</v>
       </c>
       <c r="G2389" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65458,7 +65455,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2390" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65484,7 +65481,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2391" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65510,7 +65507,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2392" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65536,7 +65533,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2393" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65562,7 +65559,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2394" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65588,7 +65585,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2395" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65614,7 +65611,7 @@
         <v>16.75</v>
       </c>
       <c r="G2396" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65640,7 +65637,7 @@
         <v>16.5</v>
       </c>
       <c r="G2397" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65666,7 +65663,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2398" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65692,7 +65689,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2399" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65718,7 +65715,7 @@
         <v>16.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65744,7 +65741,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65770,7 +65767,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2402" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65796,7 +65793,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65822,7 +65819,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2404" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65848,7 +65845,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2405" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65874,7 +65871,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2406" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65900,7 +65897,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2407" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65926,7 +65923,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2408" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65952,7 +65949,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G2409" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65978,7 +65975,7 @@
         <v>16</v>
       </c>
       <c r="G2410" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66004,7 +66001,7 @@
         <v>15.75</v>
       </c>
       <c r="G2411" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66030,7 +66027,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2412" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66056,7 +66053,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2413" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66082,7 +66079,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2414" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66108,7 +66105,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2415" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66134,7 +66131,7 @@
         <v>16.25</v>
       </c>
       <c r="G2416" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66160,7 +66157,7 @@
         <v>16.75</v>
       </c>
       <c r="G2417" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66186,7 +66183,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2418" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66212,7 +66209,7 @@
         <v>16.25</v>
       </c>
       <c r="G2419" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66238,7 +66235,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2420" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66264,7 +66261,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2421" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66290,7 +66287,7 @@
         <v>16.25</v>
       </c>
       <c r="G2422" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66316,7 +66313,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2423" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66342,7 +66339,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2424" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66368,7 +66365,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2425" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66394,7 +66391,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2426" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66420,7 +66417,7 @@
         <v>16.25</v>
       </c>
       <c r="G2427" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66446,7 +66443,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2428" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66472,7 +66469,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66498,7 +66495,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2430" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66524,7 +66521,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2431" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66550,7 +66547,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66576,7 +66573,7 @@
         <v>16.5</v>
       </c>
       <c r="G2433" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66602,7 +66599,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2434" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66628,7 +66625,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2435" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66654,7 +66651,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2436" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66680,7 +66677,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2437" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66706,7 +66703,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2438" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66732,7 +66729,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2439" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66758,7 +66755,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2440" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66784,7 +66781,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66810,7 +66807,7 @@
         <v>16.75</v>
       </c>
       <c r="G2442" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66836,7 +66833,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66862,7 +66859,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2444" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66888,7 +66885,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2445" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66914,7 +66911,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2446" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66940,7 +66937,7 @@
         <v>18</v>
       </c>
       <c r="G2447" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66966,7 +66963,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2448" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66992,7 +66989,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67018,7 +67015,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2450" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67044,7 +67041,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2451" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67070,7 +67067,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2452" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67096,7 +67093,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2453" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67122,7 +67119,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2454" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67148,7 +67145,7 @@
         <v>21</v>
       </c>
       <c r="G2455" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67174,7 +67171,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G2456" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67200,7 +67197,7 @@
         <v>19.25</v>
       </c>
       <c r="G2457" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67226,7 +67223,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G2458" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67252,7 +67249,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G2459" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67278,7 +67275,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67304,7 +67301,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2461" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67330,7 +67327,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2462" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67356,7 +67353,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67382,7 +67379,7 @@
         <v>18.5</v>
       </c>
       <c r="G2464" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67408,7 +67405,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G2465" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67434,7 +67431,7 @@
         <v>19</v>
       </c>
       <c r="G2466" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67460,7 +67457,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2467" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67486,7 +67483,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2468" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67512,7 +67509,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2469" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67538,7 +67535,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2470" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67564,7 +67561,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2471" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67590,7 +67587,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2472" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67616,7 +67613,7 @@
         <v>16</v>
       </c>
       <c r="G2473" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67642,7 +67639,7 @@
         <v>16</v>
       </c>
       <c r="G2474" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67668,7 +67665,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2475" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67694,7 +67691,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67720,7 +67717,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67746,7 +67743,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67772,7 +67769,7 @@
         <v>16.25</v>
       </c>
       <c r="G2479" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67798,7 +67795,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67824,7 +67821,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2481" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67850,7 +67847,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67876,7 +67873,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67902,7 +67899,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2484" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67928,7 +67925,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2485" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67954,7 +67951,7 @@
         <v>16</v>
       </c>
       <c r="G2486" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67980,7 +67977,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2487" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68006,7 +68003,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2488" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68032,7 +68029,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68058,7 +68055,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2490" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68084,7 +68081,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2491" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68110,7 +68107,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2492" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68118,7 +68115,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6494560185</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>1507</v>
@@ -68127,7 +68124,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="D2493" t="n">
-        <v>15.3500003814697</v>
+        <v>15.3000001907349</v>
       </c>
       <c r="E2493" t="n">
         <v>15.3500003814697</v>
@@ -68136,9 +68133,35 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6493518519</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>3959</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>15.3000001907349</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>15.3500003814697</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>943</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BEC.MI.xlsx
+++ b/data/BEC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="993">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96833801269531</t>
+    <t xml:space="preserve">4.96833848953247</t>
   </si>
   <si>
     <t xml:space="preserve">BEC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9618091583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8704080581665</t>
+    <t xml:space="preserve">4.96180963516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87040758132935</t>
   </si>
   <si>
     <t xml:space="preserve">4.87693643569946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92916584014893</t>
+    <t xml:space="preserve">4.92916631698608</t>
   </si>
   <si>
     <t xml:space="preserve">4.77247762680054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79859256744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83450078964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73330593109131</t>
+    <t xml:space="preserve">4.79859161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83449983596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73330497741699</t>
   </si>
   <si>
     <t xml:space="preserve">4.79532766342163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80512046813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76594924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75942039489746</t>
+    <t xml:space="preserve">4.80512094497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76594829559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7594199180603</t>
   </si>
   <si>
     <t xml:space="preserve">4.60273122787476</t>
@@ -86,91 +86,91 @@
     <t xml:space="preserve">4.69739723205566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69413280487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63537406921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44277763366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37422704696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18489456176758</t>
+    <t xml:space="preserve">4.69413328170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63537502288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44277858734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37422657012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18489503860474</t>
   </si>
   <si>
     <t xml:space="preserve">4.07390689849854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08043527603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23386001586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40360546112061</t>
+    <t xml:space="preserve">4.08043622970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2338604927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40360593795776</t>
   </si>
   <si>
     <t xml:space="preserve">4.49174356460571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53091526031494</t>
+    <t xml:space="preserve">4.5309157371521</t>
   </si>
   <si>
     <t xml:space="preserve">4.43298530578613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50480079650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53744459152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42645692825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42319202423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43951368331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41666316986084</t>
+    <t xml:space="preserve">4.50480127334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53744411468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42645645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4231915473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43951463699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.416663646698</t>
   </si>
   <si>
     <t xml:space="preserve">4.44930696487427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46562957763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47868585586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60926055908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89652299880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90958023071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9356951713562</t>
+    <t xml:space="preserve">4.46562814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47868633270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60925960540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8965220451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90957975387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93569469451904</t>
   </si>
   <si>
     <t xml:space="preserve">4.91284418106079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01403903961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94222402572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03362560272217</t>
+    <t xml:space="preserve">5.01403951644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.942223072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">5.04015398025513</t>
@@ -179,25 +179,25 @@
     <t xml:space="preserve">5.09238386154175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94875192642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99445343017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84429407119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06953287124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09891223907471</t>
+    <t xml:space="preserve">4.94875144958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99445295333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84429264068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06953239440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09891176223755</t>
   </si>
   <si>
     <t xml:space="preserve">4.98792457580566</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04994678497314</t>
+    <t xml:space="preserve">5.0499472618103</t>
   </si>
   <si>
     <t xml:space="preserve">5.04341793060303</t>
@@ -209,34 +209,34 @@
     <t xml:space="preserve">4.98466014862061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02709579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9997386932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03393602371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9621205329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91766309738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9450216293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85610628128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89030456542969</t>
+    <t xml:space="preserve">5.02709722518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99973821640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03393650054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96212100982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91766357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94502210617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85610723495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.890305519104</t>
   </si>
   <si>
     <t xml:space="preserve">4.89714431762695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79455041885376</t>
+    <t xml:space="preserve">4.79455089569092</t>
   </si>
   <si>
     <t xml:space="preserve">4.82190895080566</t>
@@ -245,100 +245,100 @@
     <t xml:space="preserve">4.98263931274414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92450332641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0065770149231</t>
+    <t xml:space="preserve">4.92450284957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00657844543457</t>
   </si>
   <si>
     <t xml:space="preserve">4.88346529006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94844198226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95870113372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9928994178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86636590957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8526873588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93134260177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78771066665649</t>
+    <t xml:space="preserve">4.94844102859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95870065689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99289894104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86636638641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85268688201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93134212493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78771114349365</t>
   </si>
   <si>
     <t xml:space="preserve">4.78429126739502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82532930374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77403163909912</t>
+    <t xml:space="preserve">4.82532787322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77403116226196</t>
   </si>
   <si>
     <t xml:space="preserve">4.7227349281311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67485857009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75693225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56200504302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54148578643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53122663497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60304307937622</t>
+    <t xml:space="preserve">4.67485761642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75693273544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56200456619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54148626327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53122711181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60304164886475</t>
   </si>
   <si>
     <t xml:space="preserve">4.63040065765381</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5551643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58252382278442</t>
+    <t xml:space="preserve">4.55516481399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58252334594727</t>
   </si>
   <si>
     <t xml:space="preserve">4.54832553863525</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45941066741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53464603424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52780628204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52096796035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64407968521118</t>
+    <t xml:space="preserve">4.45941114425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53464698791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52780675888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52096748352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64407920837402</t>
   </si>
   <si>
     <t xml:space="preserve">4.74325323104858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73983383178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8355884552002</t>
+    <t xml:space="preserve">4.73983335494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83558797836304</t>
   </si>
   <si>
     <t xml:space="preserve">4.92108297348022</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">4.92792272567749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98605871200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96553993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91424369812012</t>
+    <t xml:space="preserve">4.98605918884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96554040908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91424322128296</t>
   </si>
   <si>
     <t xml:space="preserve">4.97237968444824</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">4.96896028518677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86978626251221</t>
+    <t xml:space="preserve">4.86978578567505</t>
   </si>
   <si>
     <t xml:space="preserve">4.93818187713623</t>
@@ -380,43 +380,43 @@
     <t xml:space="preserve">4.8629469871521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7671914100647</t>
+    <t xml:space="preserve">4.76719236373901</t>
   </si>
   <si>
     <t xml:space="preserve">4.80139017105103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80822992324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76377248764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8424277305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72957420349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84926748275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81164932250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88688564300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02025747299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08865261077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10575151443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06471490859985</t>
+    <t xml:space="preserve">4.80823040008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7637734413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84242820739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72957468032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84926700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81165027618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88688516616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02025699615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08865308761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10575103759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06471395492554</t>
   </si>
   <si>
     <t xml:space="preserve">5.04761552810669</t>
@@ -425,43 +425,43 @@
     <t xml:space="preserve">5.09549236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17756795883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23228454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12969064712524</t>
+    <t xml:space="preserve">5.17756700515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23228406906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12969017028809</t>
   </si>
   <si>
     <t xml:space="preserve">5.13994979858398</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16388893127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2117657661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30751943588257</t>
+    <t xml:space="preserve">5.16388845443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21176528930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30751991271973</t>
   </si>
   <si>
     <t xml:space="preserve">5.30068016052246</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13311052322388</t>
+    <t xml:space="preserve">5.13311004638672</t>
   </si>
   <si>
     <t xml:space="preserve">5.22544479370117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16730785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19808578491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29726028442383</t>
+    <t xml:space="preserve">5.16730833053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19808626174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29725980758667</t>
   </si>
   <si>
     <t xml:space="preserve">5.47167015075684</t>
@@ -470,25 +470,25 @@
     <t xml:space="preserve">5.40327405929565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36565589904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36223697662354</t>
+    <t xml:space="preserve">5.36565542221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36223649978638</t>
   </si>
   <si>
     <t xml:space="preserve">5.46482992172241</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907529830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39643478393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25964260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41353321075439</t>
+    <t xml:space="preserve">5.36907577514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39643430709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25964307785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41353368759155</t>
   </si>
   <si>
     <t xml:space="preserve">5.46141052246094</t>
@@ -506,34 +506,34 @@
     <t xml:space="preserve">5.47508955001831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39985418319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41695308685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43063163757324</t>
+    <t xml:space="preserve">5.39985370635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41695356369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4306321144104</t>
   </si>
   <si>
     <t xml:space="preserve">5.4579906463623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50586795806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52980661392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60846138000488</t>
+    <t xml:space="preserve">5.50586843490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52980613708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60846185684204</t>
   </si>
   <si>
     <t xml:space="preserve">5.68369770050049</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73157405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88204479217529</t>
+    <t xml:space="preserve">5.73157453536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88204574584961</t>
   </si>
   <si>
     <t xml:space="preserve">5.9367618560791</t>
@@ -542,58 +542,58 @@
     <t xml:space="preserve">5.94360160827637</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05645370483398</t>
+    <t xml:space="preserve">6.0564546585083</t>
   </si>
   <si>
     <t xml:space="preserve">5.94018220901489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04961538314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07355403900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02567672729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97437858581543</t>
+    <t xml:space="preserve">6.04961490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07355356216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02567625045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97437906265259</t>
   </si>
   <si>
     <t xml:space="preserve">6.04277515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17272806167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39501523971558</t>
+    <t xml:space="preserve">6.17272758483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39501428604126</t>
   </si>
   <si>
     <t xml:space="preserve">6.3744945526123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46682834625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32661819458008</t>
+    <t xml:space="preserve">6.46682977676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32661867141724</t>
   </si>
   <si>
     <t xml:space="preserve">6.11117124557495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89914417266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00515747070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2240252494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26506185531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39843368530273</t>
+    <t xml:space="preserve">5.8991436958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00515699386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22402477264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26506233215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39843320846558</t>
   </si>
   <si>
     <t xml:space="preserve">6.40527391433716</t>
@@ -602,43 +602,43 @@
     <t xml:space="preserve">6.48050975799561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41211318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44973039627075</t>
+    <t xml:space="preserve">6.41211366653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44973182678223</t>
   </si>
   <si>
     <t xml:space="preserve">6.43605184555054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52838563919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66859722137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99689722061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94217920303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1200098991394</t>
+    <t xml:space="preserve">6.52838611602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66859674453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99689817428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94218063354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12001085281372</t>
   </si>
   <si>
     <t xml:space="preserve">7.46882963180542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66717672348022</t>
+    <t xml:space="preserve">7.6671781539917</t>
   </si>
   <si>
     <t xml:space="preserve">8.20066356658936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40585231781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64523887634277</t>
+    <t xml:space="preserve">8.40585327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64523792266846</t>
   </si>
   <si>
     <t xml:space="preserve">8.27590084075928</t>
@@ -650,31 +650,31 @@
     <t xml:space="preserve">8.28957939147949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24170303344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33745574951172</t>
+    <t xml:space="preserve">8.24170398712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33745765686035</t>
   </si>
   <si>
     <t xml:space="preserve">8.33061790466309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31693744659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26906204223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22118473052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11858940124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30325984954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48108863830566</t>
+    <t xml:space="preserve">8.31693840026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2690601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22118377685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11859035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30325889587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48108768463135</t>
   </si>
   <si>
     <t xml:space="preserve">8.72047328948975</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">8.71363353729248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79469108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49782466888428</t>
+    <t xml:space="preserve">8.79469013214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49782371520996</t>
   </si>
   <si>
     <t xml:space="preserve">8.52750968933105</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">8.31228065490723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43102741241455</t>
+    <t xml:space="preserve">8.43102836608887</t>
   </si>
   <si>
     <t xml:space="preserve">8.37165451049805</t>
@@ -707,10 +707,10 @@
     <t xml:space="preserve">7.97830581665039</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88924598693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23806571960449</t>
+    <t xml:space="preserve">7.88924646377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23806476593018</t>
   </si>
   <si>
     <t xml:space="preserve">8.260329246521</t>
@@ -722,34 +722,34 @@
     <t xml:space="preserve">8.64625644683838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75758266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8021125793457</t>
+    <t xml:space="preserve">8.75758171081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80211162567139</t>
   </si>
   <si>
     <t xml:space="preserve">8.69078731536865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5794620513916</t>
+    <t xml:space="preserve">8.57946109771729</t>
   </si>
   <si>
     <t xml:space="preserve">8.66110038757324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54977512359619</t>
+    <t xml:space="preserve">8.54977607727051</t>
   </si>
   <si>
     <t xml:space="preserve">8.52008724212646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53493213653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60172653198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4829797744751</t>
+    <t xml:space="preserve">8.53493118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60172748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48298072814941</t>
   </si>
   <si>
     <t xml:space="preserve">8.59430599212646</t>
@@ -758,10 +758,10 @@
     <t xml:space="preserve">8.46813583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14900398254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3197021484375</t>
+    <t xml:space="preserve">8.14900302886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31970310211182</t>
   </si>
   <si>
     <t xml:space="preserve">8.12673950195312</t>
@@ -773,10 +773,10 @@
     <t xml:space="preserve">8.58688259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70563125610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84664344787598</t>
+    <t xml:space="preserve">8.70562934875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84664154052734</t>
   </si>
   <si>
     <t xml:space="preserve">8.69820880889893</t>
@@ -791,58 +791,58 @@
     <t xml:space="preserve">8.43845081329346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40876388549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34939002990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42360591888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54235458374023</t>
+    <t xml:space="preserve">8.40876293182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34939098358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42360687255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54235363006592</t>
   </si>
   <si>
     <t xml:space="preserve">8.63141345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6165714263916</t>
+    <t xml:space="preserve">8.61656951904297</t>
   </si>
   <si>
     <t xml:space="preserve">8.63883495330811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66852283477783</t>
+    <t xml:space="preserve">8.66852188110352</t>
   </si>
   <si>
     <t xml:space="preserve">8.77984714508057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88375186920166</t>
+    <t xml:space="preserve">8.88374996185303</t>
   </si>
   <si>
     <t xml:space="preserve">8.83922004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82437896728516</t>
+    <t xml:space="preserve">8.82437705993652</t>
   </si>
   <si>
     <t xml:space="preserve">8.68336486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60914707183838</t>
+    <t xml:space="preserve">8.60914993286133</t>
   </si>
   <si>
     <t xml:space="preserve">8.57204055786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49040031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47555923461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78726959228516</t>
+    <t xml:space="preserve">8.49040126800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47555828094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78726768493652</t>
   </si>
   <si>
     <t xml:space="preserve">8.71305179595947</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">8.65367889404297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62399101257324</t>
+    <t xml:space="preserve">8.62399196624756</t>
   </si>
   <si>
     <t xml:space="preserve">8.75016021728516</t>
@@ -860,19 +860,19 @@
     <t xml:space="preserve">8.90601634979248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89859294891357</t>
+    <t xml:space="preserve">8.89859390258789</t>
   </si>
   <si>
     <t xml:space="preserve">8.94312477111816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77242469787598</t>
+    <t xml:space="preserve">8.77242565155029</t>
   </si>
   <si>
     <t xml:space="preserve">8.96538925170898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87632942199707</t>
+    <t xml:space="preserve">8.87632846832275</t>
   </si>
   <si>
     <t xml:space="preserve">8.97281074523926</t>
@@ -881,16 +881,16 @@
     <t xml:space="preserve">9.0915584564209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21772480010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52201652526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55170249938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5665454864502</t>
+    <t xml:space="preserve">9.2177267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52201557159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55170154571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654644012451</t>
   </si>
   <si>
     <t xml:space="preserve">9.45522022247314</t>
@@ -899,34 +899,34 @@
     <t xml:space="preserve">9.47748565673828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53685855865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35873889923096</t>
+    <t xml:space="preserve">9.5368595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35873794555664</t>
   </si>
   <si>
     <t xml:space="preserve">9.59623241424561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64076137542725</t>
+    <t xml:space="preserve">9.64076042175293</t>
   </si>
   <si>
     <t xml:space="preserve">9.90794277191162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89309978485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76693058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72982311248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99700355529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95247268676758</t>
+    <t xml:space="preserve">9.89309883117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76692962646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72982215881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99700164794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95247173309326</t>
   </si>
   <si>
     <t xml:space="preserve">10.0563764572144</t>
@@ -938,55 +938,55 @@
     <t xml:space="preserve">9.95989418029785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82630443572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81146049499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75208568572998</t>
+    <t xml:space="preserve">9.82630348205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81146144866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75208759307861</t>
   </si>
   <si>
     <t xml:space="preserve">9.85599040985107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86341190338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0415315628052</t>
+    <t xml:space="preserve">9.86341285705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0415325164795</t>
   </si>
   <si>
     <t xml:space="preserve">10.0118455886841</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9450511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90052032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83179950714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97088479995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25290679931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16384792327881</t>
+    <t xml:space="preserve">9.94505023956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90051937103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83179759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97088527679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25290584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16384696960449</t>
   </si>
   <si>
     <t xml:space="preserve">8.1935338973999</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67594242095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50524616241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02283573150635</t>
+    <t xml:space="preserve">8.67594432830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50524520874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02283668518066</t>
   </si>
   <si>
     <t xml:space="preserve">8.0673656463623</t>
@@ -995,49 +995,49 @@
     <t xml:space="preserve">7.98572731018066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78534078598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76307678222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70370483398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82987308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6443305015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72596836090088</t>
+    <t xml:space="preserve">7.78534269332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76307725906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70370435714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8298716545105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64433097839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72596883773804</t>
   </si>
   <si>
     <t xml:space="preserve">8.04510116577148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14158248901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91893196105957</t>
+    <t xml:space="preserve">8.14158344268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91893291473389</t>
   </si>
   <si>
     <t xml:space="preserve">8.08963012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11931800842285</t>
+    <t xml:space="preserve">8.11931705474854</t>
   </si>
   <si>
     <t xml:space="preserve">8.11189556121826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0970516204834</t>
+    <t xml:space="preserve">8.09705257415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.00057029724121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1341609954834</t>
+    <t xml:space="preserve">8.13416194915771</t>
   </si>
   <si>
     <t xml:space="preserve">8.28259372711182</t>
@@ -1049,28 +1049,28 @@
     <t xml:space="preserve">8.34196853637695</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44587135314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92086029052734</t>
+    <t xml:space="preserve">8.44587230682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92085933685303</t>
   </si>
   <si>
     <t xml:space="preserve">9.02476215362549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32712554931641</t>
+    <t xml:space="preserve">8.32712459564209</t>
   </si>
   <si>
     <t xml:space="preserve">8.26775169372559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71854734420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03025817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01541328430176</t>
+    <t xml:space="preserve">7.71854639053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03025722503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01541519165039</t>
   </si>
   <si>
     <t xml:space="preserve">8.10447406768799</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">8.22322082519531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40134143829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05445003509521</t>
+    <t xml:space="preserve">8.40134239196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0544490814209</t>
   </si>
   <si>
     <t xml:space="preserve">8.93570327758789</t>
@@ -1094,28 +1094,28 @@
     <t xml:space="preserve">8.72789573669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8911714553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00991916656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27709865570068</t>
+    <t xml:space="preserve">8.89117240905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00992012023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27710056304932</t>
   </si>
   <si>
     <t xml:space="preserve">9.30678653717041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24741363525391</t>
+    <t xml:space="preserve">9.24741268157959</t>
   </si>
   <si>
     <t xml:space="preserve">9.35131645202637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52943706512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47006225585938</t>
+    <t xml:space="preserve">9.52943801879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47006320953369</t>
   </si>
   <si>
     <t xml:space="preserve">9.39584541320801</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">9.60365295410156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0637979507446</t>
+    <t xml:space="preserve">10.0637969970703</t>
   </si>
   <si>
     <t xml:space="preserve">9.87998390197754</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">9.55831050872803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72680473327637</t>
+    <t xml:space="preserve">9.72680568695068</t>
   </si>
   <si>
     <t xml:space="preserve">9.60426330566406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46640300750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57362747192383</t>
+    <t xml:space="preserve">9.46640396118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57362842559814</t>
   </si>
   <si>
     <t xml:space="preserve">9.6195821762085</t>
@@ -1163,19 +1163,19 @@
     <t xml:space="preserve">9.68085289001465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48172187805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43576622009277</t>
+    <t xml:space="preserve">9.48172092437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43576717376709</t>
   </si>
   <si>
     <t xml:space="preserve">9.3438606262207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31322383880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08345890045166</t>
+    <t xml:space="preserve">9.31322479248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08345794677734</t>
   </si>
   <si>
     <t xml:space="preserve">8.59328842163086</t>
@@ -1184,28 +1184,28 @@
     <t xml:space="preserve">8.53201770782471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89964389801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96091556549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28258991241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20600128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49703884124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51235485076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52767467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38981437683105</t>
+    <t xml:space="preserve">8.89964485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96091651916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28258895874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20600032806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49703788757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51235675811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52767372131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38981533050537</t>
   </si>
   <si>
     <t xml:space="preserve">9.35917949676514</t>
@@ -1214,19 +1214,19 @@
     <t xml:space="preserve">9.19068241119385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86466693878174</t>
+    <t xml:space="preserve">9.86466598510742</t>
   </si>
   <si>
     <t xml:space="preserve">9.58894538879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3285436630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42045021057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22131824493408</t>
+    <t xml:space="preserve">9.32854461669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42044925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22131729125977</t>
   </si>
   <si>
     <t xml:space="preserve">9.25195407867432</t>
@@ -1235,13 +1235,13 @@
     <t xml:space="preserve">9.11409282684326</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14472961425781</t>
+    <t xml:space="preserve">9.14473056793213</t>
   </si>
   <si>
     <t xml:space="preserve">9.26727199554443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45108604431152</t>
+    <t xml:space="preserve">9.45108509063721</t>
   </si>
   <si>
     <t xml:space="preserve">9.69616985321045</t>
@@ -1256,211 +1256,211 @@
     <t xml:space="preserve">9.06814098358154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37449645996094</t>
+    <t xml:space="preserve">9.37449550628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03750419616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12941265106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02218627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91496276855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94559860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17536449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00686836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95657253265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0331630706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91061878204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97189044952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78807544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75744152069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09877490997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86900997161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7464656829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73114776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51669883728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47074699401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42479133605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01121234893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.225661277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65456008911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77710151672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83837223052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93027973175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62392330169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71583271026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50138187408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82305526733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60860633850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57797050476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3482027053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30224990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33288478851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37883949279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28693294525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27161502838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39415740966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13375377655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11843776702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45542907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79241943359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85369110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70051288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66987705230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68519496917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54733371734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.440110206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88432788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40513229370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92593765258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80339622497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29790782928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22897815704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07579898834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15238857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9992094039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59735012054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31742668151855</t>
   </si>
   <si>
     <t xml:space="preserve">9.03750514984131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1294116973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02218627929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91496181488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94559955596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17536354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00686931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95657253265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0331611633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91061973571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97189140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78807830810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75744152069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09877490997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86900997161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74646759033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73114776611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51669883728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47074604034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42479228973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01121139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.225661277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65455913543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77710247039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8383731842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9302806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62392425537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71583080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50138092041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8230562210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60860633850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57796955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3482027053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30225086212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3328857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37883949279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28693103790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27161312103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39415645599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13375377655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11843681335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45542812347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79241943359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85369205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70051193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66987800598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68519496917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54733562469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.440110206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88432502746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40513324737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92593765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80339431762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29790687561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22897815704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07579898834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15238761901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99921035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59735012054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31742668151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03750419616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79757118225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87754917144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83756065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63761425018311</t>
+    <t xml:space="preserve">8.79757022857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87754821777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83755970001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63761520385742</t>
   </si>
   <si>
     <t xml:space="preserve">9.23745059967041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27743721008301</t>
+    <t xml:space="preserve">9.27743911743164</t>
   </si>
   <si>
     <t xml:space="preserve">9.47738361358643</t>
@@ -1472,52 +1472,52 @@
     <t xml:space="preserve">9.51737213134766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67732810974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63733959197998</t>
+    <t xml:space="preserve">9.67732906341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63733863830566</t>
   </si>
   <si>
     <t xml:space="preserve">9.39740562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19746112823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07749462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4373950958252</t>
+    <t xml:space="preserve">9.19746017456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07749366760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43739414215088</t>
   </si>
   <si>
     <t xml:space="preserve">9.55736064910889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11748218536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71759223937988</t>
+    <t xml:space="preserve">9.11748123168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7175931930542</t>
   </si>
   <si>
     <t xml:space="preserve">8.95752620697021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99751472473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15747261047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91753673553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7970190048218</t>
+    <t xml:space="preserve">8.99751567840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15747165679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91753768920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7970199584961</t>
   </si>
   <si>
     <t xml:space="preserve">10.3571405410767</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772180557251</t>
+    <t xml:space="preserve">10.0772171020508</t>
   </si>
   <si>
     <t xml:space="preserve">10.3171510696411</t>
@@ -1529,22 +1529,22 @@
     <t xml:space="preserve">9.91726207733154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.997239112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0372276306152</t>
+    <t xml:space="preserve">9.99724006652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0372295379639</t>
   </si>
   <si>
     <t xml:space="preserve">9.75730609893799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71731758117676</t>
+    <t xml:space="preserve">9.71731662750244</t>
   </si>
   <si>
     <t xml:space="preserve">9.79729557037354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83728504180908</t>
+    <t xml:space="preserve">9.83728408813477</t>
   </si>
   <si>
     <t xml:space="preserve">10.1571950912476</t>
@@ -1553,70 +1553,70 @@
     <t xml:space="preserve">10.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2371730804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3971300125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5570859909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4771070480347</t>
+    <t xml:space="preserve">10.2371740341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3971290588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5570850372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.477108001709</t>
   </si>
   <si>
     <t xml:space="preserve">10.1971845626831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170955657959</t>
+    <t xml:space="preserve">10.5170965194702</t>
   </si>
   <si>
     <t xml:space="preserve">10.9969635009766</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1169309616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3168745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2368965148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3568639755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1969079971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.837007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1569204330444</t>
+    <t xml:space="preserve">11.1169300079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3168754577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2368974685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3568630218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1969089508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8370065689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1569194793701</t>
   </si>
   <si>
     <t xml:space="preserve">11.0369539260864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8769969940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9169845581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.956974029541</t>
+    <t xml:space="preserve">10.8769979476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9169855117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9569749832153</t>
   </si>
   <si>
     <t xml:space="preserve">10.7570304870605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.597074508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4371175765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2768850326538</t>
+    <t xml:space="preserve">10.5970735549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4371194839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2768859863281</t>
   </si>
   <si>
     <t xml:space="preserve">11.4368419647217</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">11.5568084716797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6767768859863</t>
+    <t xml:space="preserve">11.676775932312</t>
   </si>
   <si>
     <t xml:space="preserve">10.717041015625</t>
@@ -1634,112 +1634,112 @@
     <t xml:space="preserve">8.11775779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16602182388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88582181930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46993827819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03805637359619</t>
+    <t xml:space="preserve">7.1660213470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88582229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46993684768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03805732727051</t>
   </si>
   <si>
     <t xml:space="preserve">6.9100923538208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39823293685913</t>
+    <t xml:space="preserve">6.39823389053345</t>
   </si>
   <si>
     <t xml:space="preserve">6.20628690719604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99834442138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55818939208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30998086929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40595531463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32597780227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11803388595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73414087295532</t>
+    <t xml:space="preserve">5.9983434677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55818891525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30998277664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40595483779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32597732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11803483963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73413991928101</t>
   </si>
   <si>
     <t xml:space="preserve">6.9740743637085</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29398584365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1500244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86210489273071</t>
+    <t xml:space="preserve">7.29398536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15002536773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86210536956787</t>
   </si>
   <si>
     <t xml:space="preserve">6.81411838531494</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76613187789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94208288192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79812240600586</t>
+    <t xml:space="preserve">6.76613235473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94208383560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79812288284302</t>
   </si>
   <si>
     <t xml:space="preserve">6.92608785629272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78212785720825</t>
+    <t xml:space="preserve">6.78212738037109</t>
   </si>
   <si>
     <t xml:space="preserve">6.83011436462402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92877960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01068019866943</t>
+    <t xml:space="preserve">6.92877912521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01067972183228</t>
   </si>
   <si>
     <t xml:space="preserve">6.89601898193359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96153879165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73221826553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74859762191772</t>
+    <t xml:space="preserve">6.96153926849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73221778869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74859809875488</t>
   </si>
   <si>
     <t xml:space="preserve">7.05981969833374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1253399848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22362089157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55122232437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56760311126709</t>
+    <t xml:space="preserve">7.12534046173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22362041473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55122327804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56760215759277</t>
   </si>
   <si>
     <t xml:space="preserve">8.0262451171875</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">8.31289672851562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39479732513428</t>
+    <t xml:space="preserve">8.39479827880859</t>
   </si>
   <si>
     <t xml:space="preserve">8.72239971160889</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">8.76334953308105</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88619995117188</t>
+    <t xml:space="preserve">8.88620090484619</t>
   </si>
   <si>
     <t xml:space="preserve">9.1728515625</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">9.41855335235596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92714977264404</t>
+    <t xml:space="preserve">8.92715072631836</t>
   </si>
   <si>
     <t xml:space="preserve">9.13190174102783</t>
@@ -1775,31 +1775,31 @@
     <t xml:space="preserve">8.96810054779053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33665180206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84524917602539</t>
+    <t xml:space="preserve">9.3366527557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84525012969971</t>
   </si>
   <si>
     <t xml:space="preserve">9.09095191955566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21380138397217</t>
+    <t xml:space="preserve">9.2138032913208</t>
   </si>
   <si>
     <t xml:space="preserve">9.25475311279297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00904941558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64050006866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09176635742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17366504669189</t>
+    <t xml:space="preserve">9.00905132293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64049911499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09176540374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17366600036621</t>
   </si>
   <si>
     <t xml:space="preserve">8.1900463104248</t>
@@ -1811,10 +1811,10 @@
     <t xml:space="preserve">8.15728569030762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96072483062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87882423400879</t>
+    <t xml:space="preserve">7.9607253074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87882328033447</t>
   </si>
   <si>
     <t xml:space="preserve">7.71502304077148</t>
@@ -1829,13 +1829,13 @@
     <t xml:space="preserve">7.51846265792847</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53484344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33828210830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48570203781128</t>
+    <t xml:space="preserve">7.5348424911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33828163146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48570251464844</t>
   </si>
   <si>
     <t xml:space="preserve">7.61674356460571</t>
@@ -1844,22 +1844,22 @@
     <t xml:space="preserve">7.69864320755005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76416349411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73140382766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79692363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66588306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63312196731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64950370788574</t>
+    <t xml:space="preserve">7.76416301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73140430450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79692411422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66588163375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63312292098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6495041847229</t>
   </si>
   <si>
     <t xml:space="preserve">7.68226289749146</t>
@@ -1868,31 +1868,31 @@
     <t xml:space="preserve">7.82968425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74778413772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43656206130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60036277770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.354660987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40380096435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24000072479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19086027145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79773855209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68307733535767</t>
+    <t xml:space="preserve">7.74778318405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43656158447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6003623008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35466146469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40380239486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24000120162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19086074829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79773807525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68307781219482</t>
   </si>
   <si>
     <t xml:space="preserve">6.56841707229614</t>
@@ -1904,19 +1904,19 @@
     <t xml:space="preserve">6.22443532943726</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48651647567749</t>
+    <t xml:space="preserve">6.48651695251465</t>
   </si>
   <si>
     <t xml:space="preserve">6.42099666595459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71583795547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84687852859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0434398651123</t>
+    <t xml:space="preserve">6.7158374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84687805175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04344034194946</t>
   </si>
   <si>
     <t xml:space="preserve">7.92796516418457</t>
@@ -1925,10 +1925,10 @@
     <t xml:space="preserve">8.5176477432251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27194595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97710418701172</t>
+    <t xml:space="preserve">8.27194786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97710466384888</t>
   </si>
   <si>
     <t xml:space="preserve">7.84606409072876</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">8.59954929351807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43574714660645</t>
+    <t xml:space="preserve">8.43574810028076</t>
   </si>
   <si>
     <t xml:space="preserve">8.55859851837158</t>
@@ -1952,31 +1952,31 @@
     <t xml:space="preserve">8.47669792175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35384559631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23099613189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04262638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94434499740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86244440078735</t>
+    <t xml:space="preserve">8.35384654998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23099803924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04262542724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94434452056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86244630813599</t>
   </si>
   <si>
     <t xml:space="preserve">8.00986480712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05900573730469</t>
+    <t xml:space="preserve">8.059006690979</t>
   </si>
   <si>
     <t xml:space="preserve">9.45950412750244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90995693206787</t>
+    <t xml:space="preserve">9.90995597839355</t>
   </si>
   <si>
     <t xml:space="preserve">10.1556568145752</t>
@@ -1988,10 +1988,10 @@
     <t xml:space="preserve">9.62330436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50045299530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37760257720947</t>
+    <t xml:space="preserve">9.50045394897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37760353088379</t>
   </si>
   <si>
     <t xml:space="preserve">9.58235454559326</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">9.70520496368408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05000114440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54140281677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22513484954834</t>
+    <t xml:space="preserve">9.0500020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54140472412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22513580322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.18320178985596</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">9.5605936050415</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4347972869873</t>
+    <t xml:space="preserve">9.43479824066162</t>
   </si>
   <si>
     <t xml:space="preserve">9.35093212127686</t>
@@ -2048,10 +2048,10 @@
     <t xml:space="preserve">9.6025276184082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72832584381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3153781890869</t>
+    <t xml:space="preserve">9.72832489013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3153791427612</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895809173584</t>
@@ -2063,16 +2063,16 @@
     <t xml:space="preserve">10.1057167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3573112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2734460830688</t>
+    <t xml:space="preserve">10.357310295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2734451293945</t>
   </si>
   <si>
     <t xml:space="preserve">10.1476488113403</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0218505859375</t>
+    <t xml:space="preserve">10.0218515396118</t>
   </si>
   <si>
     <t xml:space="preserve">9.85412120819092</t>
@@ -2099,16 +2099,16 @@
     <t xml:space="preserve">8.97354030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.399242401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5669736862183</t>
+    <t xml:space="preserve">10.3992443084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5669727325439</t>
   </si>
   <si>
     <t xml:space="preserve">10.7766351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7347030639648</t>
+    <t xml:space="preserve">10.7347021102905</t>
   </si>
   <si>
     <t xml:space="preserve">11.279824256897</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">10.9443655014038</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2378911972046</t>
+    <t xml:space="preserve">11.2378921508789</t>
   </si>
   <si>
     <t xml:space="preserve">11.1959600448608</t>
@@ -2129,25 +2129,25 @@
     <t xml:space="preserve">11.4056224822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1540279388428</t>
+    <t xml:space="preserve">11.1540269851685</t>
   </si>
   <si>
     <t xml:space="preserve">11.7830142974854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.741081237793</t>
+    <t xml:space="preserve">11.7410802841187</t>
   </si>
   <si>
     <t xml:space="preserve">12.0346088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6152830123901</t>
+    <t xml:space="preserve">11.6152839660645</t>
   </si>
   <si>
     <t xml:space="preserve">11.6572160720825</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1120948791504</t>
+    <t xml:space="preserve">11.1120939254761</t>
   </si>
   <si>
     <t xml:space="preserve">10.9862976074219</t>
@@ -2162,10 +2162,10 @@
     <t xml:space="preserve">11.3636894226074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6991481781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5733509063721</t>
+    <t xml:space="preserve">11.6991491317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5733528137207</t>
   </si>
   <si>
     <t xml:space="preserve">11.5314178466797</t>
@@ -2174,16 +2174,16 @@
     <t xml:space="preserve">11.0282297134399</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4831085205078</t>
+    <t xml:space="preserve">10.4831075668335</t>
   </si>
   <si>
     <t xml:space="preserve">10.5250406265259</t>
   </si>
   <si>
-    <t xml:space="preserve">10.608904838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.818567276001</t>
+    <t xml:space="preserve">10.6089057922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8185682296753</t>
   </si>
   <si>
     <t xml:space="preserve">10.9024324417114</t>
@@ -2192,13 +2192,13 @@
     <t xml:space="preserve">11.4475536346436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1378622055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.09485912323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3958835601807</t>
+    <t xml:space="preserve">11.1378631591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0948600769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3958826065063</t>
   </si>
   <si>
     <t xml:space="preserve">11.6539030075073</t>
@@ -2210,13 +2210,13 @@
     <t xml:space="preserve">11.6108989715576</t>
   </si>
   <si>
-    <t xml:space="preserve">11.696907043457</t>
+    <t xml:space="preserve">11.6969060897827</t>
   </si>
   <si>
     <t xml:space="preserve">11.4388866424561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5248918533325</t>
+    <t xml:space="preserve">11.5248928070068</t>
   </si>
   <si>
     <t xml:space="preserve">11.5678958892822</t>
@@ -2234,19 +2234,19 @@
     <t xml:space="preserve">11.0088529586792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8368406295776</t>
+    <t xml:space="preserve">10.8368396759033</t>
   </si>
   <si>
     <t xml:space="preserve">10.9658489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7508335113525</t>
+    <t xml:space="preserve">10.7508325576782</t>
   </si>
   <si>
     <t xml:space="preserve">10.8798427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6648254394531</t>
+    <t xml:space="preserve">10.6648263931274</t>
   </si>
   <si>
     <t xml:space="preserve">10.9228458404541</t>
@@ -2264,37 +2264,37 @@
     <t xml:space="preserve">10.1487865447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97677421569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89076614379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76175689697266</t>
+    <t xml:space="preserve">9.97677326202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89076709747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76175594329834</t>
   </si>
   <si>
     <t xml:space="preserve">9.84776306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46073246002197</t>
+    <t xml:space="preserve">9.46073341369629</t>
   </si>
   <si>
     <t xml:space="preserve">9.54673957824707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2457160949707</t>
+    <t xml:space="preserve">9.24571704864502</t>
   </si>
   <si>
     <t xml:space="preserve">9.20271301269531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03070068359375</t>
+    <t xml:space="preserve">9.03069972991943</t>
   </si>
   <si>
     <t xml:space="preserve">9.15970993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">10.277795791626</t>
+    <t xml:space="preserve">10.2777967453003</t>
   </si>
   <si>
     <t xml:space="preserve">9.67574977874756</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">9.63274574279785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6218233108521</t>
+    <t xml:space="preserve">10.6218223571777</t>
   </si>
   <si>
     <t xml:space="preserve">11.3098764419556</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">11.4818897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.169942855835</t>
+    <t xml:space="preserve">12.1699419021606</t>
   </si>
   <si>
     <t xml:space="preserve">11.9549255371094</t>
@@ -2363,22 +2363,22 @@
     <t xml:space="preserve">12.0409326553345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8689193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7829132080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9979286193848</t>
+    <t xml:space="preserve">11.8689203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7829122543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9979295730591</t>
   </si>
   <si>
     <t xml:space="preserve">12.3419570922852</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4709672927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2989530563354</t>
+    <t xml:space="preserve">12.4709663391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2989540100098</t>
   </si>
   <si>
     <t xml:space="preserve">12.513970375061</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">12.5569734573364</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6429796218872</t>
+    <t xml:space="preserve">12.6429786682129</t>
   </si>
   <si>
     <t xml:space="preserve">12.2559499740601</t>
@@ -2399,22 +2399,22 @@
     <t xml:space="preserve">12.5999755859375</t>
   </si>
   <si>
+    <t xml:space="preserve">12.6859827041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7719898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7289867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9997701644897</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.6859817504883</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7719888687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.728985786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9997711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6859827041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.820463180542</t>
+    <t xml:space="preserve">12.8204641342163</t>
   </si>
   <si>
     <t xml:space="preserve">12.9549436569214</t>
@@ -2426,28 +2426,28 @@
     <t xml:space="preserve">13.4480381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0894250869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2239036560059</t>
+    <t xml:space="preserve">13.0894241333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2239046096802</t>
   </si>
   <si>
     <t xml:space="preserve">13.3583841323853</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1342506408691</t>
+    <t xml:space="preserve">13.1342496871948</t>
   </si>
   <si>
     <t xml:space="preserve">13.0445976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1790781021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3135576248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2687311172485</t>
+    <t xml:space="preserve">13.1790771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3135585784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2687320709229</t>
   </si>
   <si>
     <t xml:space="preserve">12.8652906417847</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">13.7618265151978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7928428649902</t>
+    <t xml:space="preserve">14.7928419113159</t>
   </si>
   <si>
     <t xml:space="preserve">14.1652669906616</t>
@@ -2477,10 +2477,10 @@
     <t xml:space="preserve">13.8963060379028</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4032106399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5825185775757</t>
+    <t xml:space="preserve">13.4032115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5825176239014</t>
   </si>
   <si>
     <t xml:space="preserve">13.492865562439</t>
@@ -2489,7 +2489,7 @@
     <t xml:space="preserve">13.6721725463867</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9411334991455</t>
+    <t xml:space="preserve">13.9411325454712</t>
   </si>
   <si>
     <t xml:space="preserve">13.7169990539551</t>
@@ -2498,22 +2498,22 @@
     <t xml:space="preserve">14.3445739746094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9859609603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5238819122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2997465133667</t>
+    <t xml:space="preserve">13.9859600067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5238828659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.299747467041</t>
   </si>
   <si>
     <t xml:space="preserve">14.4342279434204</t>
   </si>
   <si>
-    <t xml:space="preserve">14.21009349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3894004821777</t>
+    <t xml:space="preserve">14.2100944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3893995285034</t>
   </si>
   <si>
     <t xml:space="preserve">14.6135339736938</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">15.0169763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1962833404541</t>
+    <t xml:space="preserve">15.1962842941284</t>
   </si>
   <si>
     <t xml:space="preserve">15.3307638168335</t>
@@ -2549,19 +2549,19 @@
     <t xml:space="preserve">15.4204187393188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3755893707275</t>
+    <t xml:space="preserve">15.3755912780762</t>
   </si>
   <si>
     <t xml:space="preserve">14.8376684188843</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8824968338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1514558792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7790327072144</t>
+    <t xml:space="preserve">14.882495880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1514568328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.77903175354</t>
   </si>
   <si>
     <t xml:space="preserve">17.0341815948486</t>
@@ -2573,22 +2573,22 @@
     <t xml:space="preserve">16.5859146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8686857223511</t>
+    <t xml:space="preserve">15.8686866760254</t>
   </si>
   <si>
     <t xml:space="preserve">16.0479907989502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7342052459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9583387374878</t>
+    <t xml:space="preserve">15.7342042922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9583377838135</t>
   </si>
   <si>
     <t xml:space="preserve">16.1376457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8100471496582</t>
+    <t xml:space="preserve">16.8100490570068</t>
   </si>
   <si>
     <t xml:space="preserve">16.7203941345215</t>
@@ -2597,13 +2597,13 @@
     <t xml:space="preserve">16.4066066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2721271514893</t>
+    <t xml:space="preserve">16.2721252441406</t>
   </si>
   <si>
     <t xml:space="preserve">16.0928211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9135131835938</t>
+    <t xml:space="preserve">15.9135122299194</t>
   </si>
   <si>
     <t xml:space="preserve">15.4652442932129</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">15.644552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8238582611084</t>
+    <t xml:space="preserve">15.8238592147827</t>
   </si>
   <si>
     <t xml:space="preserve">15.689377784729</t>
@@ -2688,9 +2688,6 @@
   </si>
   <si>
     <t xml:space="preserve">15.0579290390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1514568328857</t>
   </si>
   <si>
     <t xml:space="preserve">15.1982202529907</t>
@@ -59302,7 +59299,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2153" t="s">
-        <v>892</v>
+        <v>848</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59328,7 +59325,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2154" t="s">
-        <v>892</v>
+        <v>848</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59354,7 +59351,7 @@
         <v>16.25</v>
       </c>
       <c r="G2155" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59406,7 +59403,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2157" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59432,7 +59429,7 @@
         <v>15</v>
       </c>
       <c r="G2158" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59458,7 +59455,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2159" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59484,7 +59481,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2160" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59510,7 +59507,7 @@
         <v>15.25</v>
       </c>
       <c r="G2161" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59536,7 +59533,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2162" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59562,7 +59559,7 @@
         <v>15.25</v>
       </c>
       <c r="G2163" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59588,7 +59585,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2164" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59640,7 +59637,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2166" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59666,7 +59663,7 @@
         <v>16.25</v>
       </c>
       <c r="G2167" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59718,7 +59715,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2169" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59744,7 +59741,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2170" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59796,7 +59793,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59822,7 +59819,7 @@
         <v>16</v>
       </c>
       <c r="G2173" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59874,7 +59871,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2175" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59900,7 +59897,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2176" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59926,7 +59923,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2177" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59952,7 +59949,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2178" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59978,7 +59975,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2179" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60004,7 +60001,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60030,7 +60027,7 @@
         <v>15.25</v>
       </c>
       <c r="G2181" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60056,7 +60053,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60082,7 +60079,7 @@
         <v>15.25</v>
       </c>
       <c r="G2183" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60108,7 +60105,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2184" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60134,7 +60131,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2185" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60160,7 +60157,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2186" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60186,7 +60183,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60212,7 +60209,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2188" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60238,7 +60235,7 @@
         <v>15</v>
       </c>
       <c r="G2189" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60264,7 +60261,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2190" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60290,7 +60287,7 @@
         <v>15</v>
       </c>
       <c r="G2191" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60316,7 +60313,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2192" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60342,7 +60339,7 @@
         <v>15</v>
       </c>
       <c r="G2193" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60368,7 +60365,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2194" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60394,7 +60391,7 @@
         <v>15</v>
       </c>
       <c r="G2195" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60420,7 +60417,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2196" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60446,7 +60443,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2197" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60472,7 +60469,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60498,7 +60495,7 @@
         <v>15</v>
       </c>
       <c r="G2199" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60524,7 +60521,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G2200" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60550,7 +60547,7 @@
         <v>15</v>
       </c>
       <c r="G2201" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60576,7 +60573,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60602,7 +60599,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2203" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60628,7 +60625,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2204" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60654,7 +60651,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60680,7 +60677,7 @@
         <v>14.5</v>
       </c>
       <c r="G2206" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60706,7 +60703,7 @@
         <v>14.5</v>
       </c>
       <c r="G2207" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60732,7 +60729,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60758,7 +60755,7 @@
         <v>14.5</v>
       </c>
       <c r="G2209" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60784,7 +60781,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60810,7 +60807,7 @@
         <v>14.5</v>
       </c>
       <c r="G2211" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60836,7 +60833,7 @@
         <v>14.5</v>
       </c>
       <c r="G2212" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60862,7 +60859,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60888,7 +60885,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2214" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60914,7 +60911,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2215" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60940,7 +60937,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2216" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60966,7 +60963,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2217" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -60992,7 +60989,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2218" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61018,7 +61015,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2219" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61044,7 +61041,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2220" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61070,7 +61067,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2221" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61096,7 +61093,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2222" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61122,7 +61119,7 @@
         <v>15</v>
       </c>
       <c r="G2223" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61148,7 +61145,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61174,7 +61171,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2225" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61200,7 +61197,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2226" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61226,7 +61223,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2227" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61252,7 +61249,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61278,7 +61275,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2229" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61304,7 +61301,7 @@
         <v>15.25</v>
       </c>
       <c r="G2230" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61330,7 +61327,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2231" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61356,7 +61353,7 @@
         <v>15.5</v>
       </c>
       <c r="G2232" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61382,7 +61379,7 @@
         <v>15.5</v>
       </c>
       <c r="G2233" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61408,7 +61405,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2234" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61434,7 +61431,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2235" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61460,7 +61457,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2236" t="s">
-        <v>892</v>
+        <v>848</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61486,7 +61483,7 @@
         <v>16</v>
       </c>
       <c r="G2237" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61512,7 +61509,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2238" t="s">
-        <v>892</v>
+        <v>848</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61538,7 +61535,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2239" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61564,7 +61561,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2240" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61668,7 +61665,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2244" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61694,7 +61691,7 @@
         <v>17.25</v>
       </c>
       <c r="G2245" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61746,7 +61743,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2247" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61824,7 +61821,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2250" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61850,7 +61847,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61876,7 +61873,7 @@
         <v>17.25</v>
       </c>
       <c r="G2252" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61902,7 +61899,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2253" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61928,7 +61925,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2254" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61954,7 +61951,7 @@
         <v>17.75</v>
       </c>
       <c r="G2255" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61980,7 +61977,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G2256" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62006,7 +62003,7 @@
         <v>18</v>
       </c>
       <c r="G2257" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62110,7 +62107,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2261" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62266,7 +62263,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2267" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62292,7 +62289,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2268" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62318,7 +62315,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2269" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62344,7 +62341,7 @@
         <v>15.5</v>
       </c>
       <c r="G2270" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62604,7 +62601,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2280" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62630,7 +62627,7 @@
         <v>16</v>
       </c>
       <c r="G2281" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62656,7 +62653,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62682,7 +62679,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2283" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62708,7 +62705,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2284" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62734,7 +62731,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2285" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62760,7 +62757,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62864,7 +62861,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62968,7 +62965,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2294" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63020,7 +63017,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2296" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63046,7 +63043,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2297" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63072,7 +63069,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2298" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63098,7 +63095,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63124,7 +63121,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63150,7 +63147,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63176,7 +63173,7 @@
         <v>16</v>
       </c>
       <c r="G2302" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63202,7 +63199,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2303" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63228,7 +63225,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2304" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63254,7 +63251,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63280,7 +63277,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2306" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63306,7 +63303,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2307" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63332,7 +63329,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2308" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63358,7 +63355,7 @@
         <v>15.75</v>
       </c>
       <c r="G2309" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63384,7 +63381,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2310" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63410,7 +63407,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2311" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63436,7 +63433,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63462,7 +63459,7 @@
         <v>16</v>
       </c>
       <c r="G2313" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63488,7 +63485,7 @@
         <v>16</v>
       </c>
       <c r="G2314" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63514,7 +63511,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2315" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63540,7 +63537,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2316" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63592,7 +63589,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>892</v>
+        <v>848</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63618,7 +63615,7 @@
         <v>16</v>
       </c>
       <c r="G2319" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63644,7 +63641,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2320" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63670,7 +63667,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2321" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63696,7 +63693,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2322" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63722,7 +63719,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2323" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63748,7 +63745,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2324" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63774,7 +63771,7 @@
         <v>16</v>
       </c>
       <c r="G2325" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63800,7 +63797,7 @@
         <v>16</v>
       </c>
       <c r="G2326" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63826,7 +63823,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2327" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63852,7 +63849,7 @@
         <v>16</v>
       </c>
       <c r="G2328" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63878,7 +63875,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2329" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63904,7 +63901,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2330" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63930,7 +63927,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2331" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63956,7 +63953,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63982,7 +63979,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64008,7 +64005,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2334" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64034,7 +64031,7 @@
         <v>15.75</v>
       </c>
       <c r="G2335" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64060,7 +64057,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2336" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64086,7 +64083,7 @@
         <v>15.75</v>
       </c>
       <c r="G2337" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64112,7 +64109,7 @@
         <v>15.25</v>
       </c>
       <c r="G2338" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64138,7 +64135,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2339" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64164,7 +64161,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2340" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64190,7 +64187,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2341" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64216,7 +64213,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64242,7 +64239,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64268,7 +64265,7 @@
         <v>15.5</v>
       </c>
       <c r="G2344" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64294,7 +64291,7 @@
         <v>15.5</v>
       </c>
       <c r="G2345" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64320,7 +64317,7 @@
         <v>15</v>
       </c>
       <c r="G2346" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64346,7 +64343,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64372,7 +64369,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64398,7 +64395,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2349" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64450,7 +64447,7 @@
         <v>16</v>
       </c>
       <c r="G2351" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64476,7 +64473,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64502,7 +64499,7 @@
         <v>15.75</v>
       </c>
       <c r="G2353" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64528,7 +64525,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64554,7 +64551,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2355" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64580,7 +64577,7 @@
         <v>15.25</v>
       </c>
       <c r="G2356" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64606,7 +64603,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2357" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64632,7 +64629,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64658,7 +64655,7 @@
         <v>14</v>
       </c>
       <c r="G2359" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64684,7 +64681,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2360" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64710,7 +64707,7 @@
         <v>15</v>
       </c>
       <c r="G2361" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64736,7 +64733,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2362" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64762,7 +64759,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2363" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64788,7 +64785,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2364" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64814,7 +64811,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64840,7 +64837,7 @@
         <v>14.5</v>
       </c>
       <c r="G2366" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64866,7 +64863,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2367" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64892,7 +64889,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2368" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64918,7 +64915,7 @@
         <v>15</v>
       </c>
       <c r="G2369" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64944,7 +64941,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2370" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64970,7 +64967,7 @@
         <v>15.25</v>
       </c>
       <c r="G2371" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64996,7 +64993,7 @@
         <v>15.25</v>
       </c>
       <c r="G2372" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65022,7 +65019,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2373" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65048,7 +65045,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2374" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65074,7 +65071,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2375" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65100,7 +65097,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2376" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65126,7 +65123,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65152,7 +65149,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2378" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65178,7 +65175,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2379" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65204,7 +65201,7 @@
         <v>15.25</v>
       </c>
       <c r="G2380" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65230,7 +65227,7 @@
         <v>15.25</v>
       </c>
       <c r="G2381" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65256,7 +65253,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2382" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65282,7 +65279,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2383" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65308,7 +65305,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65334,7 +65331,7 @@
         <v>16</v>
       </c>
       <c r="G2385" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65360,7 +65357,7 @@
         <v>16.25</v>
       </c>
       <c r="G2386" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65386,7 +65383,7 @@
         <v>16</v>
       </c>
       <c r="G2387" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65412,7 +65409,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2388" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65438,7 +65435,7 @@
         <v>16.5</v>
       </c>
       <c r="G2389" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65464,7 +65461,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2390" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65490,7 +65487,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2391" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65516,7 +65513,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2392" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65542,7 +65539,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2393" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65568,7 +65565,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2394" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65594,7 +65591,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2395" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65620,7 +65617,7 @@
         <v>16.75</v>
       </c>
       <c r="G2396" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65646,7 +65643,7 @@
         <v>16.5</v>
       </c>
       <c r="G2397" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65672,7 +65669,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2398" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65698,7 +65695,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2399" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65724,7 +65721,7 @@
         <v>16.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65750,7 +65747,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65776,7 +65773,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2402" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65802,7 +65799,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65828,7 +65825,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2404" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65854,7 +65851,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2405" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65880,7 +65877,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2406" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65906,7 +65903,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2407" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65932,7 +65929,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2408" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65958,7 +65955,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G2409" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65984,7 +65981,7 @@
         <v>16</v>
       </c>
       <c r="G2410" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66010,7 +66007,7 @@
         <v>15.75</v>
       </c>
       <c r="G2411" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66036,7 +66033,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2412" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66062,7 +66059,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2413" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66088,7 +66085,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2414" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66114,7 +66111,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2415" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66140,7 +66137,7 @@
         <v>16.25</v>
       </c>
       <c r="G2416" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66166,7 +66163,7 @@
         <v>16.75</v>
       </c>
       <c r="G2417" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66192,7 +66189,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2418" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66218,7 +66215,7 @@
         <v>16.25</v>
       </c>
       <c r="G2419" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66244,7 +66241,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2420" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66270,7 +66267,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2421" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66296,7 +66293,7 @@
         <v>16.25</v>
       </c>
       <c r="G2422" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66322,7 +66319,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2423" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66348,7 +66345,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2424" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66374,7 +66371,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2425" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66400,7 +66397,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2426" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66426,7 +66423,7 @@
         <v>16.25</v>
       </c>
       <c r="G2427" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66452,7 +66449,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2428" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66478,7 +66475,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66504,7 +66501,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2430" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66530,7 +66527,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2431" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66556,7 +66553,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66582,7 +66579,7 @@
         <v>16.5</v>
       </c>
       <c r="G2433" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66608,7 +66605,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2434" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66634,7 +66631,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2435" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66660,7 +66657,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2436" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66686,7 +66683,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2437" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66712,7 +66709,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2438" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66738,7 +66735,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2439" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66764,7 +66761,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2440" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66790,7 +66787,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66816,7 +66813,7 @@
         <v>16.75</v>
       </c>
       <c r="G2442" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66842,7 +66839,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66868,7 +66865,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2444" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66894,7 +66891,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2445" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66920,7 +66917,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2446" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66946,7 +66943,7 @@
         <v>18</v>
       </c>
       <c r="G2447" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66972,7 +66969,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2448" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66998,7 +66995,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67024,7 +67021,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2450" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67050,7 +67047,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2451" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67076,7 +67073,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2452" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67102,7 +67099,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2453" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67128,7 +67125,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2454" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67154,7 +67151,7 @@
         <v>21</v>
       </c>
       <c r="G2455" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67180,7 +67177,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G2456" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67206,7 +67203,7 @@
         <v>19.25</v>
       </c>
       <c r="G2457" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67232,7 +67229,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G2458" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67258,7 +67255,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G2459" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67284,7 +67281,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67310,7 +67307,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2461" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67336,7 +67333,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2462" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67362,7 +67359,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67388,7 +67385,7 @@
         <v>18.5</v>
       </c>
       <c r="G2464" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67414,7 +67411,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G2465" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67440,7 +67437,7 @@
         <v>19</v>
       </c>
       <c r="G2466" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67466,7 +67463,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2467" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67492,7 +67489,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2468" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67518,7 +67515,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2469" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67544,7 +67541,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2470" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67570,7 +67567,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2471" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67596,7 +67593,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2472" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67622,7 +67619,7 @@
         <v>16</v>
       </c>
       <c r="G2473" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67648,7 +67645,7 @@
         <v>16</v>
       </c>
       <c r="G2474" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67674,7 +67671,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2475" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67700,7 +67697,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67726,7 +67723,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67752,7 +67749,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67778,7 +67775,7 @@
         <v>16.25</v>
       </c>
       <c r="G2479" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67804,7 +67801,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67830,7 +67827,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2481" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67856,7 +67853,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67882,7 +67879,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67908,7 +67905,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2484" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67934,7 +67931,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2485" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67960,7 +67957,7 @@
         <v>16</v>
       </c>
       <c r="G2486" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67986,7 +67983,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2487" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68012,7 +68009,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2488" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68038,7 +68035,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68064,7 +68061,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2490" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68090,7 +68087,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2491" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68116,7 +68113,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2492" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68142,7 +68139,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68168,7 +68165,7 @@
         <v>15.25</v>
       </c>
       <c r="G2494" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68194,7 +68191,7 @@
         <v>15.5</v>
       </c>
       <c r="G2495" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68202,7 +68199,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6493634259</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>3472</v>
@@ -68211,7 +68208,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="D2496" t="n">
-        <v>15.5</v>
+        <v>15.3999996185303</v>
       </c>
       <c r="E2496" t="n">
         <v>15.6000003814697</v>
@@ -68220,9 +68217,35 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2496" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6445949074</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>1544</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>15.5500001907349</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>15.4499998092651</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>15.5500001907349</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>992</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BEC.MI.xlsx
+++ b/data/BEC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="996">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96833848953247</t>
+    <t xml:space="preserve">4.96833801269531</t>
   </si>
   <si>
     <t xml:space="preserve">BEC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96180963516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8704080581665</t>
+    <t xml:space="preserve">4.9618091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87040853500366</t>
   </si>
   <si>
     <t xml:space="preserve">4.87693643569946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92916679382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77247667312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79859161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83450031280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73330593109131</t>
+    <t xml:space="preserve">4.92916584014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77247714996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79859256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83449983596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73330497741699</t>
   </si>
   <si>
     <t xml:space="preserve">4.79532766342163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80512094497681</t>
+    <t xml:space="preserve">4.80512142181396</t>
   </si>
   <si>
     <t xml:space="preserve">4.76594877243042</t>
@@ -89,10 +89,10 @@
     <t xml:space="preserve">4.69413280487061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63537406921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44277858734131</t>
+    <t xml:space="preserve">4.63537454605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44277811050415</t>
   </si>
   <si>
     <t xml:space="preserve">4.37422704696655</t>
@@ -101,70 +101,70 @@
     <t xml:space="preserve">4.18489456176758</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07390642166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08043575286865</t>
+    <t xml:space="preserve">4.07390689849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08043527603149</t>
   </si>
   <si>
     <t xml:space="preserve">4.23386001586914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40360593795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49174404144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5309157371521</t>
+    <t xml:space="preserve">4.40360546112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49174356460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53091621398926</t>
   </si>
   <si>
     <t xml:space="preserve">4.43298530578613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50480127334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5374436378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42645740509033</t>
+    <t xml:space="preserve">4.50480079650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53744411468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42645645141602</t>
   </si>
   <si>
     <t xml:space="preserve">4.42319202423096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43951368331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41666316986084</t>
+    <t xml:space="preserve">4.43951416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.416663646698</t>
   </si>
   <si>
     <t xml:space="preserve">4.44930696487427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4656286239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47868585586548</t>
+    <t xml:space="preserve">4.46562910079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47868633270264</t>
   </si>
   <si>
     <t xml:space="preserve">4.60926008224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8965220451355</t>
+    <t xml:space="preserve">4.89652299880981</t>
   </si>
   <si>
     <t xml:space="preserve">4.90957975387573</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93569469451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91284465789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01403999328613</t>
+    <t xml:space="preserve">4.93569564819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91284418106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01403951644897</t>
   </si>
   <si>
     <t xml:space="preserve">4.94222354888916</t>
@@ -176,19 +176,19 @@
     <t xml:space="preserve">5.04015350341797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09238433837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94875240325928</t>
+    <t xml:space="preserve">5.09238386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94875192642212</t>
   </si>
   <si>
     <t xml:space="preserve">4.99445295333862</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84429359436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06953287124634</t>
+    <t xml:space="preserve">4.84429311752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06953239440918</t>
   </si>
   <si>
     <t xml:space="preserve">5.09891223907471</t>
@@ -197,19 +197,19 @@
     <t xml:space="preserve">4.98792362213135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0499472618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04341840744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.059739112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98466014862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02709674835205</t>
+    <t xml:space="preserve">5.04994678497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04341793060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05973958969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98466062545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02709627151489</t>
   </si>
   <si>
     <t xml:space="preserve">4.99973821640015</t>
@@ -221,172 +221,172 @@
     <t xml:space="preserve">4.96212100982666</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91766357421875</t>
+    <t xml:space="preserve">4.91766309738159</t>
   </si>
   <si>
     <t xml:space="preserve">4.94502115249634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85610723495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.890305519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89714479446411</t>
+    <t xml:space="preserve">4.85610628128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89030504226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89714384078979</t>
   </si>
   <si>
     <t xml:space="preserve">4.79455089569092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82190942764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98263883590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92450284957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00657844543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88346576690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94844198226929</t>
+    <t xml:space="preserve">4.82190990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98263931274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9245023727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00657796859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88346529006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94844150543213</t>
   </si>
   <si>
     <t xml:space="preserve">4.95870065689087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99289846420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86636590957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85268688201904</t>
+    <t xml:space="preserve">4.9928994178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86636638641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85268640518188</t>
   </si>
   <si>
     <t xml:space="preserve">4.93134212493896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78771114349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78429174423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82532835006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77403163909912</t>
+    <t xml:space="preserve">4.78771066665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78429126739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82532930374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77403116226196</t>
   </si>
   <si>
     <t xml:space="preserve">4.7227349281311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67485857009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75693273544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56200504302979</t>
+    <t xml:space="preserve">4.67485809326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75693321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56200408935547</t>
   </si>
   <si>
     <t xml:space="preserve">4.54148578643799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53122711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60304260253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63040113449097</t>
+    <t xml:space="preserve">4.53122663497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60304164886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63040065765381</t>
   </si>
   <si>
     <t xml:space="preserve">4.55516529083252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58252334594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5483250617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45941066741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53464698791504</t>
+    <t xml:space="preserve">4.58252382278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54832553863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45941114425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53464603424072</t>
   </si>
   <si>
     <t xml:space="preserve">4.52780675888062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52096796035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64408016204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7432541847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73983383178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83558750152588</t>
+    <t xml:space="preserve">4.52096748352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64407968521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74325370788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73983430862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8355884552002</t>
   </si>
   <si>
     <t xml:space="preserve">4.92108345031738</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92792272567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98605871200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96554040908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91424369812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97237968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96895933151245</t>
+    <t xml:space="preserve">4.92792320251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98605966567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96554088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91424322128296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9723801612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96896028518677</t>
   </si>
   <si>
     <t xml:space="preserve">4.86978578567505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93818283081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88004541397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95186138153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87320566177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86294603347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76719236373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80138969421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80823040008545</t>
+    <t xml:space="preserve">4.93818140029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88004589080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9518609046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87320518493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86294746398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76719188690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80139017105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80822992324829</t>
   </si>
   <si>
     <t xml:space="preserve">4.76377296447754</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">4.84242820739746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72957420349121</t>
+    <t xml:space="preserve">4.72957468032837</t>
   </si>
   <si>
     <t xml:space="preserve">4.84926748275757</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">5.04761600494385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09549236297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17756795883179</t>
+    <t xml:space="preserve">5.09549188613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17756700515747</t>
   </si>
   <si>
     <t xml:space="preserve">5.23228406906128</t>
@@ -434,61 +434,61 @@
     <t xml:space="preserve">5.12969017028809</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13994979858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16388893127441</t>
+    <t xml:space="preserve">5.13994932174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16388845443726</t>
   </si>
   <si>
     <t xml:space="preserve">5.21176528930664</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30752038955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30068016052246</t>
+    <t xml:space="preserve">5.30751991271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30068063735962</t>
   </si>
   <si>
     <t xml:space="preserve">5.13311052322388</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22544479370117</t>
+    <t xml:space="preserve">5.22544431686401</t>
   </si>
   <si>
     <t xml:space="preserve">5.16730833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19808673858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29726028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47166919708252</t>
+    <t xml:space="preserve">5.19808626174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29725980758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47167062759399</t>
   </si>
   <si>
     <t xml:space="preserve">5.40327405929565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36565542221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36223649978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46483039855957</t>
+    <t xml:space="preserve">5.36565589904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36223697662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46482992172241</t>
   </si>
   <si>
     <t xml:space="preserve">5.36907529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39643430709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25964260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41353321075439</t>
+    <t xml:space="preserve">5.39643383026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25964212417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41353273391724</t>
   </si>
   <si>
     <t xml:space="preserve">5.46141052246094</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">5.43747186660767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45457124710083</t>
+    <t xml:space="preserve">5.45457077026367</t>
   </si>
   <si>
     <t xml:space="preserve">5.46824932098389</t>
@@ -509,58 +509,58 @@
     <t xml:space="preserve">5.39985418319702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41695308685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4306321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4579906463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50586795806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52980661392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60846090316772</t>
+    <t xml:space="preserve">5.41695261001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43063259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45799112319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50586843490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52980709075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60846185684204</t>
   </si>
   <si>
     <t xml:space="preserve">5.68369770050049</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73157405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88204574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93676328659058</t>
+    <t xml:space="preserve">5.73157358169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88204526901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9367618560791</t>
   </si>
   <si>
     <t xml:space="preserve">5.94360160827637</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05645322799683</t>
+    <t xml:space="preserve">6.0564546585083</t>
   </si>
   <si>
     <t xml:space="preserve">5.94018220901489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04961538314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07355403900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02567625045776</t>
+    <t xml:space="preserve">6.04961490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07355499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02567720413208</t>
   </si>
   <si>
     <t xml:space="preserve">5.97437906265259</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04277563095093</t>
+    <t xml:space="preserve">6.04277467727661</t>
   </si>
   <si>
     <t xml:space="preserve">6.17272806167603</t>
@@ -578,52 +578,52 @@
     <t xml:space="preserve">6.32661867141724</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11117124557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8991436958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00515747070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2240252494812</t>
+    <t xml:space="preserve">6.11117076873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89914417266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00515699386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22402572631836</t>
   </si>
   <si>
     <t xml:space="preserve">6.26506233215332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39843416213989</t>
+    <t xml:space="preserve">6.39843320846558</t>
   </si>
   <si>
     <t xml:space="preserve">6.4052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48050975799561</t>
+    <t xml:space="preserve">6.48050880432129</t>
   </si>
   <si>
     <t xml:space="preserve">6.41211271286011</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44973039627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43605089187622</t>
+    <t xml:space="preserve">6.44973087310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43605136871338</t>
   </si>
   <si>
     <t xml:space="preserve">6.52838611602783</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66859674453735</t>
+    <t xml:space="preserve">6.66859722137451</t>
   </si>
   <si>
     <t xml:space="preserve">6.99689722061157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94218063354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12001037597656</t>
+    <t xml:space="preserve">6.94218111038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1200098991394</t>
   </si>
   <si>
     <t xml:space="preserve">7.4688286781311</t>
@@ -632,31 +632,31 @@
     <t xml:space="preserve">7.66717672348022</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20066547393799</t>
+    <t xml:space="preserve">8.20066452026367</t>
   </si>
   <si>
     <t xml:space="preserve">8.40585327148438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64523887634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27590084075928</t>
+    <t xml:space="preserve">8.64523792266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27589988708496</t>
   </si>
   <si>
     <t xml:space="preserve">8.35113620758057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28958129882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24170112609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33745765686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33061790466309</t>
+    <t xml:space="preserve">8.28957939147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24170303344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33745670318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33061695098877</t>
   </si>
   <si>
     <t xml:space="preserve">8.31693744659424</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">8.26906108856201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22118282318115</t>
+    <t xml:space="preserve">8.22118473052979</t>
   </si>
   <si>
     <t xml:space="preserve">8.11859035491943</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">8.30325889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48108673095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72047328948975</t>
+    <t xml:space="preserve">8.48108863830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72047424316406</t>
   </si>
   <si>
     <t xml:space="preserve">8.7136344909668</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">8.79469108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49782371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52751159667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07478809356689</t>
+    <t xml:space="preserve">8.49782276153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52751064300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07478904724121</t>
   </si>
   <si>
     <t xml:space="preserve">8.31228065490723</t>
@@ -704,79 +704,79 @@
     <t xml:space="preserve">8.37165451049805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97830629348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88924646377563</t>
+    <t xml:space="preserve">7.97830581665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88924694061279</t>
   </si>
   <si>
     <t xml:space="preserve">8.23806476593018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26032829284668</t>
+    <t xml:space="preserve">8.26033020019531</t>
   </si>
   <si>
     <t xml:space="preserve">8.21579933166504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64625549316406</t>
+    <t xml:space="preserve">8.6462574005127</t>
   </si>
   <si>
     <t xml:space="preserve">8.75758266448975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80211353302002</t>
+    <t xml:space="preserve">8.80211162567139</t>
   </si>
   <si>
     <t xml:space="preserve">8.69078731536865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5794620513916</t>
+    <t xml:space="preserve">8.57946109771729</t>
   </si>
   <si>
     <t xml:space="preserve">8.66110038757324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54977607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5200891494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53493213653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60172653198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48298072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59430408477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46813678741455</t>
+    <t xml:space="preserve">8.54977416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52008724212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53493118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60172748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4829797744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59430503845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46813583374023</t>
   </si>
   <si>
     <t xml:space="preserve">8.14900398254395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3197021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12673950195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46071529388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58688259124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7056303024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72047424316406</t>
+    <t xml:space="preserve">8.31970310211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12673854827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46071434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58688354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70563125610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72047233581543</t>
   </si>
   <si>
     <t xml:space="preserve">8.84664249420166</t>
@@ -785,13 +785,13 @@
     <t xml:space="preserve">8.69820880889893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74273872375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56461811065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43845176696777</t>
+    <t xml:space="preserve">8.7427396774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56461906433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43844985961914</t>
   </si>
   <si>
     <t xml:space="preserve">8.40876293182373</t>
@@ -806,112 +806,112 @@
     <t xml:space="preserve">8.54235363006592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63141250610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61656951904297</t>
+    <t xml:space="preserve">8.63141345977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61657047271729</t>
   </si>
   <si>
     <t xml:space="preserve">8.63883495330811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66852188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77984619140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88374996185303</t>
+    <t xml:space="preserve">8.6685209274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77984714508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88375186920166</t>
   </si>
   <si>
     <t xml:space="preserve">8.83922004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82437801361084</t>
+    <t xml:space="preserve">8.82437705993652</t>
   </si>
   <si>
     <t xml:space="preserve">8.68336486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60914993286133</t>
+    <t xml:space="preserve">8.6091480255127</t>
   </si>
   <si>
     <t xml:space="preserve">8.57204055786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49040126800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47555732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78726863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71305179595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65367794036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62399005889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75016117095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90601539611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89859294891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94312381744385</t>
+    <t xml:space="preserve">8.49040031433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47555828094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78726959228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71305274963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65367889404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62399101257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75016021728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90601634979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89859390258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94312477111816</t>
   </si>
   <si>
     <t xml:space="preserve">8.77242565155029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96538925170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87632751464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97281169891357</t>
+    <t xml:space="preserve">8.9653902053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87632846832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97281074523926</t>
   </si>
   <si>
     <t xml:space="preserve">9.09155750274658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2177267074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52201652526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55170249938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5665454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45521926879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47748470306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53685855865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35873889923096</t>
+    <t xml:space="preserve">9.21772575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52201557159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55170345306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654644012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45522022247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4774866104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53685760498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35873699188232</t>
   </si>
   <si>
     <t xml:space="preserve">9.59623241424561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64076137542725</t>
+    <t xml:space="preserve">9.64076232910156</t>
   </si>
   <si>
     <t xml:space="preserve">9.90794372558594</t>
@@ -920,22 +920,22 @@
     <t xml:space="preserve">9.89309883117676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76693153381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72982120513916</t>
+    <t xml:space="preserve">9.76693058013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72982215881348</t>
   </si>
   <si>
     <t xml:space="preserve">9.99700355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95247077941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0563764572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64818382263184</t>
+    <t xml:space="preserve">9.95247268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.05637550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64818286895752</t>
   </si>
   <si>
     <t xml:space="preserve">9.95989418029785</t>
@@ -944,28 +944,28 @@
     <t xml:space="preserve">9.82630443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81146144866943</t>
+    <t xml:space="preserve">9.81146049499512</t>
   </si>
   <si>
     <t xml:space="preserve">9.7520866394043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85599136352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86341190338135</t>
+    <t xml:space="preserve">9.85599040985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86341094970703</t>
   </si>
   <si>
     <t xml:space="preserve">10.0415325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0118446350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94505023956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90052127838135</t>
+    <t xml:space="preserve">10.0118455886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9450511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90051937103271</t>
   </si>
   <si>
     <t xml:space="preserve">8.83179950714111</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">7.97088384628296</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25290775299072</t>
+    <t xml:space="preserve">8.25290679931641</t>
   </si>
   <si>
     <t xml:space="preserve">8.16384792327881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19353580474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67594432830811</t>
+    <t xml:space="preserve">8.19353485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67594337463379</t>
   </si>
   <si>
     <t xml:space="preserve">8.50524520874023</t>
@@ -992,46 +992,46 @@
     <t xml:space="preserve">8.02283573150635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06736469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98572826385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78534078598022</t>
+    <t xml:space="preserve">8.0673656463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98572731018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78534269332886</t>
   </si>
   <si>
     <t xml:space="preserve">7.76307678222656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70370388031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8298716545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6443305015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72596883773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04510021209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14158344268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91893339157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08963012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11931705474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11189556121826</t>
+    <t xml:space="preserve">7.70370483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82987308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64432954788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72596836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04510116577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14158248901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91893291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08963108062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11931800842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11189651489258</t>
   </si>
   <si>
     <t xml:space="preserve">8.0970516204834</t>
@@ -1040,13 +1040,13 @@
     <t xml:space="preserve">8.00057029724121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13416194915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28259468078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20837783813477</t>
+    <t xml:space="preserve">8.1341609954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28259372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20837879180908</t>
   </si>
   <si>
     <t xml:space="preserve">8.34196758270264</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">8.44587230682373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92085838317871</t>
+    <t xml:space="preserve">8.92085933685303</t>
   </si>
   <si>
     <t xml:space="preserve">9.02476215362549</t>
@@ -1064,25 +1064,25 @@
     <t xml:space="preserve">8.32712459564209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26775169372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71854686737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03025722503662</t>
+    <t xml:space="preserve">8.26775074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71854591369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03025817871094</t>
   </si>
   <si>
     <t xml:space="preserve">8.01541423797607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10447406768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17869186401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22322177886963</t>
+    <t xml:space="preserve">8.10447311401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17869091033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22322082519531</t>
   </si>
   <si>
     <t xml:space="preserve">8.40134143829346</t>
@@ -1091,46 +1091,46 @@
     <t xml:space="preserve">9.05445003509521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93570137023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72789478302002</t>
+    <t xml:space="preserve">8.93570327758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72789573669434</t>
   </si>
   <si>
     <t xml:space="preserve">8.8911714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00992012023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27710056304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30678653717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24741363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35131645202637</t>
+    <t xml:space="preserve">9.00991916656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.277099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30678558349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24741268157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35131549835205</t>
   </si>
   <si>
     <t xml:space="preserve">9.52943706512451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47006320953369</t>
+    <t xml:space="preserve">9.47006416320801</t>
   </si>
   <si>
     <t xml:space="preserve">9.39584541320801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54428005218506</t>
+    <t xml:space="preserve">9.54427909851074</t>
   </si>
   <si>
     <t xml:space="preserve">9.87083339691162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60365390777588</t>
+    <t xml:space="preserve">9.60365295410156</t>
   </si>
   <si>
     <t xml:space="preserve">10.0637979507446</t>
@@ -1139,70 +1139,70 @@
     <t xml:space="preserve">9.87998390197754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54299259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55830955505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.726806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60426330566406</t>
+    <t xml:space="preserve">9.54299163818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55831050872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72680568695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60426425933838</t>
   </si>
   <si>
     <t xml:space="preserve">9.46640300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57362842559814</t>
+    <t xml:space="preserve">9.57362747192383</t>
   </si>
   <si>
     <t xml:space="preserve">9.61958122253418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63489818572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68085193634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48171997070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43576717376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34386157989502</t>
+    <t xml:space="preserve">9.6348991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68085289001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48172187805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43576812744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3438606262207</t>
   </si>
   <si>
     <t xml:space="preserve">9.31322479248047</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08345699310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59328842163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53201770782471</t>
+    <t xml:space="preserve">9.08345794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59328746795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53201675415039</t>
   </si>
   <si>
     <t xml:space="preserve">8.89964485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96091556549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28258895874023</t>
+    <t xml:space="preserve">8.96091461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28258991241455</t>
   </si>
   <si>
     <t xml:space="preserve">9.20600032806396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49703693389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51235580444336</t>
+    <t xml:space="preserve">9.49703788757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51235675811768</t>
   </si>
   <si>
     <t xml:space="preserve">9.52767372131348</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">9.38981437683105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35918045043945</t>
+    <t xml:space="preserve">9.35917949676514</t>
   </si>
   <si>
     <t xml:space="preserve">9.19068241119385</t>
@@ -1220,13 +1220,13 @@
     <t xml:space="preserve">9.86466693878174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58894538879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3285436630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42045021057129</t>
+    <t xml:space="preserve">9.58894634246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32854270935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42044830322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.22131824493408</t>
@@ -1238,22 +1238,22 @@
     <t xml:space="preserve">9.11409378051758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14472961425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26727199554443</t>
+    <t xml:space="preserve">9.14473056793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26727104187012</t>
   </si>
   <si>
     <t xml:space="preserve">9.45108509063721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69616889953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65021705627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80773830413818</t>
+    <t xml:space="preserve">9.69616985321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6502161026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80773735046387</t>
   </si>
   <si>
     <t xml:space="preserve">9.06814002990723</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">9.1294116973877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02218627929688</t>
+    <t xml:space="preserve">9.02218723297119</t>
   </si>
   <si>
     <t xml:space="preserve">8.91496276855469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94559764862061</t>
+    <t xml:space="preserve">8.94559860229492</t>
   </si>
   <si>
     <t xml:space="preserve">9.17536544799805</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">9.00686836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95657348632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0331630706787</t>
+    <t xml:space="preserve">9.95657157897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0331621170044</t>
   </si>
   <si>
     <t xml:space="preserve">9.91061973571777</t>
@@ -1295,19 +1295,19 @@
     <t xml:space="preserve">9.97189140319824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78807735443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75744247436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09877586364746</t>
+    <t xml:space="preserve">9.78807640075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7574405670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09877681732178</t>
   </si>
   <si>
     <t xml:space="preserve">8.86900997161865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74646759033203</t>
+    <t xml:space="preserve">8.7464656829834</t>
   </si>
   <si>
     <t xml:space="preserve">8.73114776611328</t>
@@ -1316,16 +1316,16 @@
     <t xml:space="preserve">8.51669883728027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47074699401855</t>
+    <t xml:space="preserve">8.47074604034424</t>
   </si>
   <si>
     <t xml:space="preserve">8.42479228973389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01121139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22566032409668</t>
+    <t xml:space="preserve">8.01121234893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.225661277771</t>
   </si>
   <si>
     <t xml:space="preserve">8.36352062225342</t>
@@ -1334,52 +1334,52 @@
     <t xml:space="preserve">8.65456008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77710342407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8383731842041</t>
+    <t xml:space="preserve">8.77710247039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83837223052979</t>
   </si>
   <si>
     <t xml:space="preserve">8.9302806854248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62392425537109</t>
+    <t xml:space="preserve">8.62392330169678</t>
   </si>
   <si>
     <t xml:space="preserve">8.7158317565918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50138282775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8230562210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60860538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57797050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34820365905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30224895477295</t>
+    <t xml:space="preserve">8.50138092041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82305431365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60860633850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57796955108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3482027053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30224990844727</t>
   </si>
   <si>
     <t xml:space="preserve">8.3328857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37883949279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28693199157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27161502838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39415645599365</t>
+    <t xml:space="preserve">8.37883853912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28693103790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27161407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39415740966797</t>
   </si>
   <si>
     <t xml:space="preserve">8.13375473022461</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">8.45542907714844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79241943359375</t>
+    <t xml:space="preserve">8.79241847991943</t>
   </si>
   <si>
     <t xml:space="preserve">8.85369110107422</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">8.70051288604736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66987800598145</t>
+    <t xml:space="preserve">8.66987705230713</t>
   </si>
   <si>
     <t xml:space="preserve">8.68519592285156</t>
@@ -1409,43 +1409,43 @@
     <t xml:space="preserve">8.54733467102051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44011116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88432788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40513229370117</t>
+    <t xml:space="preserve">8.440110206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88432693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40513324737549</t>
   </si>
   <si>
     <t xml:space="preserve">9.92593669891357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80339527130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29790782928467</t>
+    <t xml:space="preserve">9.80339336395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29790687561035</t>
   </si>
   <si>
     <t xml:space="preserve">9.22897720336914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0757999420166</t>
+    <t xml:space="preserve">9.07579898834229</t>
   </si>
   <si>
     <t xml:space="preserve">9.15238761901855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99920845031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59734916687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31742668151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79757022857666</t>
+    <t xml:space="preserve">8.9992094039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59735012054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31742763519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79757118225098</t>
   </si>
   <si>
     <t xml:space="preserve">8.87755012512207</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">8.83755970001221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63761520385742</t>
+    <t xml:space="preserve">8.63761425018311</t>
   </si>
   <si>
     <t xml:space="preserve">9.23744964599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27743911743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47738361358643</t>
+    <t xml:space="preserve">9.27743816375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47738265991211</t>
   </si>
   <si>
     <t xml:space="preserve">9.3574161529541</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">9.51737213134766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67732810974121</t>
+    <t xml:space="preserve">9.67732715606689</t>
   </si>
   <si>
     <t xml:space="preserve">9.63733959197998</t>
@@ -1484,13 +1484,13 @@
     <t xml:space="preserve">9.19746112823486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07749366760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43739604949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55735969543457</t>
+    <t xml:space="preserve">9.07749462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4373950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55736064910889</t>
   </si>
   <si>
     <t xml:space="preserve">9.11748218536377</t>
@@ -1499,37 +1499,37 @@
     <t xml:space="preserve">8.71759223937988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95752716064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99751663208008</t>
+    <t xml:space="preserve">8.95752620697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99751567840576</t>
   </si>
   <si>
     <t xml:space="preserve">9.15747261047363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91753768920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7970190048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3571395874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0772171020508</t>
+    <t xml:space="preserve">8.91753673553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7970180511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3571405410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0772180557251</t>
   </si>
   <si>
     <t xml:space="preserve">10.3171510696411</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1172046661377</t>
+    <t xml:space="preserve">10.1172075271606</t>
   </si>
   <si>
     <t xml:space="preserve">9.91726207733154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99724006652832</t>
+    <t xml:space="preserve">9.997239112854</t>
   </si>
   <si>
     <t xml:space="preserve">10.0372285842896</t>
@@ -1538,13 +1538,13 @@
     <t xml:space="preserve">9.75730609893799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71731758117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7972936630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83728313446045</t>
+    <t xml:space="preserve">9.71731853485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79729461669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83728408813477</t>
   </si>
   <si>
     <t xml:space="preserve">10.1571960449219</t>
@@ -1553,37 +1553,37 @@
     <t xml:space="preserve">10.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2371740341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3971300125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5570840835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4771089553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1971855163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5170965194702</t>
+    <t xml:space="preserve">10.2371730804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3971290588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5570850372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.477108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1971845626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5170946121216</t>
   </si>
   <si>
     <t xml:space="preserve">10.9969635009766</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1169290542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3168745040894</t>
+    <t xml:space="preserve">11.1169300079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3168754577637</t>
   </si>
   <si>
     <t xml:space="preserve">11.2368974685669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3568639755249</t>
+    <t xml:space="preserve">11.3568649291992</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969079971313</t>
@@ -1598,10 +1598,10 @@
     <t xml:space="preserve">11.0369529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8769969940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9169855117798</t>
+    <t xml:space="preserve">10.8769979476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9169845581055</t>
   </si>
   <si>
     <t xml:space="preserve">10.956974029541</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">10.4371185302734</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2768869400024</t>
+    <t xml:space="preserve">11.2768859863281</t>
   </si>
   <si>
     <t xml:space="preserve">11.436842918396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.556809425354</t>
+    <t xml:space="preserve">11.5568075180054</t>
   </si>
   <si>
     <t xml:space="preserve">11.6767768859863</t>
@@ -1634,16 +1634,16 @@
     <t xml:space="preserve">8.11775779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1660213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88582277297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46993827819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03805685043335</t>
+    <t xml:space="preserve">7.16602230072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88582181930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46993732452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03805732727051</t>
   </si>
   <si>
     <t xml:space="preserve">6.9100923538208</t>
@@ -1652,22 +1652,22 @@
     <t xml:space="preserve">6.39823293685913</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20628643035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9983434677124</t>
+    <t xml:space="preserve">6.20628690719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99834442138672</t>
   </si>
   <si>
     <t xml:space="preserve">6.55818891525269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30998134613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40595483779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32597684860229</t>
+    <t xml:space="preserve">7.30998182296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40595531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32597732543945</t>
   </si>
   <si>
     <t xml:space="preserve">7.11803436279297</t>
@@ -1676,16 +1676,16 @@
     <t xml:space="preserve">6.73414039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97407484054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29398536682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15002584457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86210489273071</t>
+    <t xml:space="preserve">6.9740743637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29398584365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15002536773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86210536956787</t>
   </si>
   <si>
     <t xml:space="preserve">6.8141188621521</t>
@@ -1694,31 +1694,31 @@
     <t xml:space="preserve">6.76613187789917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94208335876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79812240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92608690261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78212785720825</t>
+    <t xml:space="preserve">6.94208288192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79812288284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92608785629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78212738037109</t>
   </si>
   <si>
     <t xml:space="preserve">6.83011436462402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92877864837646</t>
+    <t xml:space="preserve">6.92877960205078</t>
   </si>
   <si>
     <t xml:space="preserve">7.01067972183228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89601898193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96153926849365</t>
+    <t xml:space="preserve">6.89601945877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96153879165649</t>
   </si>
   <si>
     <t xml:space="preserve">6.73221778869629</t>
@@ -1727,28 +1727,28 @@
     <t xml:space="preserve">6.74859762191772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05981922149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12533950805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22362041473389</t>
+    <t xml:space="preserve">7.05981969833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1253399848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22361993789673</t>
   </si>
   <si>
     <t xml:space="preserve">7.55122327804565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56760311126709</t>
+    <t xml:space="preserve">7.56760215759277</t>
   </si>
   <si>
     <t xml:space="preserve">8.0262451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31289577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39479732513428</t>
+    <t xml:space="preserve">8.31289768218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39479827880859</t>
   </si>
   <si>
     <t xml:space="preserve">8.72239875793457</t>
@@ -1757,10 +1757,10 @@
     <t xml:space="preserve">8.76334953308105</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88620090484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17285060882568</t>
+    <t xml:space="preserve">8.88619995117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1728515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.41855239868164</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">9.13190174102783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96809959411621</t>
+    <t xml:space="preserve">8.96810054779053</t>
   </si>
   <si>
     <t xml:space="preserve">9.33665180206299</t>
@@ -1784,43 +1784,43 @@
     <t xml:space="preserve">9.09095191955566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21380233764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25475120544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00905132293701</t>
+    <t xml:space="preserve">9.21380138397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25475311279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00904941558838</t>
   </si>
   <si>
     <t xml:space="preserve">8.64049911499023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09176635742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17366600036621</t>
+    <t xml:space="preserve">8.09176540374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17366409301758</t>
   </si>
   <si>
     <t xml:space="preserve">8.1900463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10814476013184</t>
+    <t xml:space="preserve">8.10814571380615</t>
   </si>
   <si>
     <t xml:space="preserve">8.15728664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96072578430176</t>
+    <t xml:space="preserve">7.96072483062744</t>
   </si>
   <si>
     <t xml:space="preserve">7.87882423400879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71502351760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7805438041687</t>
+    <t xml:space="preserve">7.71502304077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78054428100586</t>
   </si>
   <si>
     <t xml:space="preserve">7.58398294448853</t>
@@ -1829,40 +1829,40 @@
     <t xml:space="preserve">7.51846265792847</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53484296798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33828163146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48570251464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61674404144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69864416122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76416492462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73140335083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79692411422729</t>
+    <t xml:space="preserve">7.5348424911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33828210830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48570203781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61674356460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69864320755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76416349411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73140382766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79692363739014</t>
   </si>
   <si>
     <t xml:space="preserve">7.66588306427002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63312292098999</t>
+    <t xml:space="preserve">7.63312196731567</t>
   </si>
   <si>
     <t xml:space="preserve">7.64950370788574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68226289749146</t>
+    <t xml:space="preserve">7.68226337432861</t>
   </si>
   <si>
     <t xml:space="preserve">7.82968425750732</t>
@@ -1871,37 +1871,37 @@
     <t xml:space="preserve">7.74778366088867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43656253814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6003623008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35466194152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40380191802979</t>
+    <t xml:space="preserve">7.43656206130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60036277770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.354660987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40380096435547</t>
   </si>
   <si>
     <t xml:space="preserve">7.24000072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19085931777954</t>
+    <t xml:space="preserve">7.19086027145386</t>
   </si>
   <si>
     <t xml:space="preserve">6.79773855209351</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68307733535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5684175491333</t>
+    <t xml:space="preserve">6.68307781219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56841707229614</t>
   </si>
   <si>
     <t xml:space="preserve">6.38823652267456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2244348526001</t>
+    <t xml:space="preserve">6.22443532943726</t>
   </si>
   <si>
     <t xml:space="preserve">6.48651647567749</t>
@@ -1910,13 +1910,13 @@
     <t xml:space="preserve">6.42099618911743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71583795547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84687852859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04344034194946</t>
+    <t xml:space="preserve">6.7158374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84687805175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04344081878662</t>
   </si>
   <si>
     <t xml:space="preserve">7.92796516418457</t>
@@ -1925,70 +1925,70 @@
     <t xml:space="preserve">8.51764678955078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27194786071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97710514068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84606456756592</t>
+    <t xml:space="preserve">8.27194690704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97710418701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84606409072876</t>
   </si>
   <si>
     <t xml:space="preserve">8.12452602386475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59954833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43574810028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5585994720459</t>
+    <t xml:space="preserve">8.59954929351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43574714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55859851837158</t>
   </si>
   <si>
     <t xml:space="preserve">8.6814489364624</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47669792175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35384750366211</t>
+    <t xml:space="preserve">8.47669887542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35384559631348</t>
   </si>
   <si>
     <t xml:space="preserve">8.23099613189697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04262447357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94434452056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86244487762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00986480712891</t>
+    <t xml:space="preserve">8.04262638092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94434499740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86244440078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00986385345459</t>
   </si>
   <si>
     <t xml:space="preserve">8.05900573730469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45950317382812</t>
+    <t xml:space="preserve">9.45950412750244</t>
   </si>
   <si>
     <t xml:space="preserve">9.90995693206787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1556577682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86900615692139</t>
+    <t xml:space="preserve">10.1556558609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86900520324707</t>
   </si>
   <si>
     <t xml:space="preserve">9.62330436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50045490264893</t>
+    <t xml:space="preserve">9.50045394897461</t>
   </si>
   <si>
     <t xml:space="preserve">9.37760257720947</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">9.58235454559326</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70520496368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05000114440918</t>
+    <t xml:space="preserve">9.70520401000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0500020980835</t>
   </si>
   <si>
     <t xml:space="preserve">9.54140281677246</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">9.18320178985596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09933853149414</t>
+    <t xml:space="preserve">9.09933757781982</t>
   </si>
   <si>
     <t xml:space="preserve">9.14126968383789</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">9.30900001525879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56059455871582</t>
+    <t xml:space="preserve">9.5605936050415</t>
   </si>
   <si>
     <t xml:space="preserve">9.4347972869873</t>
@@ -2036,19 +2036,19 @@
     <t xml:space="preserve">9.64445972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51866340637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47673034667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60252666473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7283239364624</t>
+    <t xml:space="preserve">9.51866245269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47672939300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77025699615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6025276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72832584381104</t>
   </si>
   <si>
     <t xml:space="preserve">10.3153781890869</t>
@@ -2060,13 +2060,13 @@
     <t xml:space="preserve">10.2315130233765</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1057157516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.357310295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2734451293945</t>
+    <t xml:space="preserve">10.1057167053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3573112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2734460830688</t>
   </si>
   <si>
     <t xml:space="preserve">10.1476488113403</t>
@@ -2078,19 +2078,19 @@
     <t xml:space="preserve">9.85412120819092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81218814849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89605331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26706695556641</t>
+    <t xml:space="preserve">9.81218910217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8960542678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26706790924072</t>
   </si>
   <si>
     <t xml:space="preserve">9.97991847991943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68639183044434</t>
+    <t xml:space="preserve">9.68639278411865</t>
   </si>
   <si>
     <t xml:space="preserve">9.05740547180176</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">8.97354030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3992443084717</t>
+    <t xml:space="preserve">10.399242401123</t>
   </si>
   <si>
     <t xml:space="preserve">10.5669736862183</t>
@@ -2114,10 +2114,10 @@
     <t xml:space="preserve">11.279824256897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3217573165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9443664550781</t>
+    <t xml:space="preserve">11.321756362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9443655014038</t>
   </si>
   <si>
     <t xml:space="preserve">11.2378911972046</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">11.4056224822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1540269851685</t>
+    <t xml:space="preserve">11.1540279388428</t>
   </si>
   <si>
     <t xml:space="preserve">11.7830142974854</t>
@@ -2138,10 +2138,10 @@
     <t xml:space="preserve">11.741081237793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0346078872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6152839660645</t>
+    <t xml:space="preserve">12.0346088409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6152830123901</t>
   </si>
   <si>
     <t xml:space="preserve">11.6572160720825</t>
@@ -2150,13 +2150,13 @@
     <t xml:space="preserve">11.1120948791504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9862985610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0701627731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4894857406616</t>
+    <t xml:space="preserve">10.9862976074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.070161819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4894866943359</t>
   </si>
   <si>
     <t xml:space="preserve">11.3636894226074</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">11.5733509063721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.531418800354</t>
+    <t xml:space="preserve">11.5314178466797</t>
   </si>
   <si>
     <t xml:space="preserve">11.0282297134399</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">10.4831085205078</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5250415802002</t>
+    <t xml:space="preserve">10.5250406265259</t>
   </si>
   <si>
     <t xml:space="preserve">10.608904838562</t>
@@ -2186,13 +2186,13 @@
     <t xml:space="preserve">10.818567276001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9024333953857</t>
+    <t xml:space="preserve">10.9024324417114</t>
   </si>
   <si>
     <t xml:space="preserve">11.4475536346436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1378631591797</t>
+    <t xml:space="preserve">11.1378622055054</t>
   </si>
   <si>
     <t xml:space="preserve">11.09485912323</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">11.6539030075073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8259162902832</t>
+    <t xml:space="preserve">11.8259153366089</t>
   </si>
   <si>
     <t xml:space="preserve">11.6108989715576</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">11.4388866424561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5248928070068</t>
+    <t xml:space="preserve">11.5248918533325</t>
   </si>
   <si>
     <t xml:space="preserve">11.5678958892822</t>
@@ -2240,16 +2240,16 @@
     <t xml:space="preserve">10.9658489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7508325576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8798418045044</t>
+    <t xml:space="preserve">10.7508335113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8798427581787</t>
   </si>
   <si>
     <t xml:space="preserve">10.6648254394531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9228467941284</t>
+    <t xml:space="preserve">10.9228458404541</t>
   </si>
   <si>
     <t xml:space="preserve">10.7078294754028</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">10.1487865447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97677326202393</t>
+    <t xml:space="preserve">9.97677421569824</t>
   </si>
   <si>
     <t xml:space="preserve">9.89076614379883</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">9.76175689697266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84776210784912</t>
+    <t xml:space="preserve">9.84776306152344</t>
   </si>
   <si>
     <t xml:space="preserve">9.46073246002197</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">9.03070068359375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15970897674561</t>
+    <t xml:space="preserve">9.15970993041992</t>
   </si>
   <si>
     <t xml:space="preserve">10.277795791626</t>
@@ -2318,19 +2318,19 @@
     <t xml:space="preserve">9.58974266052246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41772937774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3317232131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37472629547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.503737449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63274669647217</t>
+    <t xml:space="preserve">9.41772842407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33172225952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37472534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50373649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63274574279785</t>
   </si>
   <si>
     <t xml:space="preserve">10.6218233108521</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">10.7938365936279</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3528785705566</t>
+    <t xml:space="preserve">11.352879524231</t>
   </si>
   <si>
     <t xml:space="preserve">11.4818897247314</t>
@@ -2360,7 +2360,7 @@
     <t xml:space="preserve">11.9549255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0409336090088</t>
+    <t xml:space="preserve">12.0409326553345</t>
   </si>
   <si>
     <t xml:space="preserve">11.8689193725586</t>
@@ -2372,16 +2372,16 @@
     <t xml:space="preserve">11.9979286193848</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3419561386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4709663391113</t>
+    <t xml:space="preserve">12.3419570922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4709672927856</t>
   </si>
   <si>
     <t xml:space="preserve">12.2989530563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5139694213867</t>
+    <t xml:space="preserve">12.513970375061</t>
   </si>
   <si>
     <t xml:space="preserve">12.5569734573364</t>
@@ -2390,27 +2390,30 @@
     <t xml:space="preserve">12.6429796218872</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2559490203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3849582672119</t>
+    <t xml:space="preserve">12.2559499740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3849592208862</t>
   </si>
   <si>
     <t xml:space="preserve">12.5999755859375</t>
   </si>
   <si>
+    <t xml:space="preserve">12.6859817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7719888687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.728985786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9997711181641</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.6859827041626</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7719898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7289867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9997711181641</t>
-  </si>
-  <si>
     <t xml:space="preserve">12.820463180542</t>
   </si>
   <si>
@@ -2994,6 +2997,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.4499998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1999998092651</t>
   </si>
 </sst>
 </file>
@@ -51970,7 +51976,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1871" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51996,7 +52002,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52022,7 +52028,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1873" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52074,7 +52080,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1875" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -52100,7 +52106,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1876" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -52126,7 +52132,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1877" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52152,7 +52158,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -52204,7 +52210,7 @@
         <v>15</v>
       </c>
       <c r="G1880" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52256,7 +52262,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1882" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52282,7 +52288,7 @@
         <v>14.75</v>
       </c>
       <c r="G1883" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52308,7 +52314,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52334,7 +52340,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1885" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52360,7 +52366,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52386,7 +52392,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1887" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52412,7 +52418,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1888" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52438,7 +52444,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1889" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52464,7 +52470,7 @@
         <v>15</v>
       </c>
       <c r="G1890" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52490,7 +52496,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52516,7 +52522,7 @@
         <v>14.75</v>
       </c>
       <c r="G1892" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52542,7 +52548,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1893" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52568,7 +52574,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52594,7 +52600,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1895" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52620,7 +52626,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52646,7 +52652,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1897" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52672,7 +52678,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1898" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52698,7 +52704,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1899" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52724,7 +52730,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1900" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52750,7 +52756,7 @@
         <v>14.75</v>
       </c>
       <c r="G1901" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52776,7 +52782,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1902" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52802,7 +52808,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52828,7 +52834,7 @@
         <v>14.75</v>
       </c>
       <c r="G1904" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52854,7 +52860,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1905" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52880,7 +52886,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1906" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52906,7 +52912,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52932,7 +52938,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52958,7 +52964,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1909" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52984,7 +52990,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1910" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53010,7 +53016,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1911" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53036,7 +53042,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1912" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -53062,7 +53068,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1913" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53088,7 +53094,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1914" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53114,7 +53120,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53192,7 +53198,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1918" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53244,7 +53250,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1920" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53270,7 +53276,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1921" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53296,7 +53302,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53322,7 +53328,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1923" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53348,7 +53354,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1924" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53374,7 +53380,7 @@
         <v>14.75</v>
       </c>
       <c r="G1925" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53400,7 +53406,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1926" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53426,7 +53432,7 @@
         <v>14.75</v>
       </c>
       <c r="G1927" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53452,7 +53458,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1928" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53478,7 +53484,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1929" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53504,7 +53510,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1930" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53530,7 +53536,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1931" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53556,7 +53562,7 @@
         <v>15.75</v>
       </c>
       <c r="G1932" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53582,7 +53588,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53608,7 +53614,7 @@
         <v>15.75</v>
       </c>
       <c r="G1934" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53634,7 +53640,7 @@
         <v>16.5</v>
       </c>
       <c r="G1935" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53660,7 +53666,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1936" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53686,7 +53692,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53712,7 +53718,7 @@
         <v>15.5</v>
       </c>
       <c r="G1938" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53738,7 +53744,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1939" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53764,7 +53770,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1940" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53790,7 +53796,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53816,7 +53822,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1942" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53842,7 +53848,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1943" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53868,7 +53874,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1944" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53894,7 +53900,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1945" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53920,7 +53926,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1946" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53946,7 +53952,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1947" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53972,7 +53978,7 @@
         <v>15.75</v>
       </c>
       <c r="G1948" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53998,7 +54004,7 @@
         <v>15.5</v>
       </c>
       <c r="G1949" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54024,7 +54030,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54050,7 +54056,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1951" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54076,7 +54082,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1952" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54102,7 +54108,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1953" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54128,7 +54134,7 @@
         <v>15.25</v>
       </c>
       <c r="G1954" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54154,7 +54160,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1955" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54180,7 +54186,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1956" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54206,7 +54212,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1957" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54232,7 +54238,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1958" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54258,7 +54264,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54284,7 +54290,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1960" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54310,7 +54316,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1961" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54336,7 +54342,7 @@
         <v>15.5</v>
       </c>
       <c r="G1962" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54362,7 +54368,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1963" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54388,7 +54394,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54414,7 +54420,7 @@
         <v>16</v>
       </c>
       <c r="G1965" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54440,7 +54446,7 @@
         <v>16</v>
       </c>
       <c r="G1966" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -54466,7 +54472,7 @@
         <v>15.75</v>
       </c>
       <c r="G1967" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54492,7 +54498,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1968" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54518,7 +54524,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1969" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54544,7 +54550,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1970" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54570,7 +54576,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1971" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54596,7 +54602,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1972" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54622,7 +54628,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1973" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54648,7 +54654,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1974" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54674,7 +54680,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1975" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54700,7 +54706,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1976" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54726,7 +54732,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54752,7 +54758,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1978" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54778,7 +54784,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1979" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54804,7 +54810,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1980" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54830,7 +54836,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1981" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54856,7 +54862,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54882,7 +54888,7 @@
         <v>16</v>
       </c>
       <c r="G1983" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54908,7 +54914,7 @@
         <v>16.5</v>
       </c>
       <c r="G1984" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54934,7 +54940,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1985" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54960,7 +54966,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1986" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54986,7 +54992,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1987" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55012,7 +55018,7 @@
         <v>15.75</v>
       </c>
       <c r="G1988" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55038,7 +55044,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1989" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55064,7 +55070,7 @@
         <v>15.75</v>
       </c>
       <c r="G1990" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55090,7 +55096,7 @@
         <v>15.75</v>
       </c>
       <c r="G1991" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55116,7 +55122,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1992" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55142,7 +55148,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1993" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55168,7 +55174,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1994" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55194,7 +55200,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1995" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55220,7 +55226,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1996" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55246,7 +55252,7 @@
         <v>15.75</v>
       </c>
       <c r="G1997" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55272,7 +55278,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1998" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55298,7 +55304,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1999" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55324,7 +55330,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2000" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55350,7 +55356,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2001" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55376,7 +55382,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2002" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55402,7 +55408,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55428,7 +55434,7 @@
         <v>16</v>
       </c>
       <c r="G2004" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55454,7 +55460,7 @@
         <v>16</v>
       </c>
       <c r="G2005" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55480,7 +55486,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2006" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55506,7 +55512,7 @@
         <v>16</v>
       </c>
       <c r="G2007" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55532,7 +55538,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2008" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55558,7 +55564,7 @@
         <v>16</v>
       </c>
       <c r="G2009" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55584,7 +55590,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2010" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55610,7 +55616,7 @@
         <v>16</v>
       </c>
       <c r="G2011" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55636,7 +55642,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55662,7 +55668,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2013" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55688,7 +55694,7 @@
         <v>16</v>
       </c>
       <c r="G2014" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55714,7 +55720,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55740,7 +55746,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2016" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55766,7 +55772,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55792,7 +55798,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2018" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55818,7 +55824,7 @@
         <v>15.75</v>
       </c>
       <c r="G2019" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55844,7 +55850,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2020" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55870,7 +55876,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2021" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55896,7 +55902,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2022" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55922,7 +55928,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2023" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55948,7 +55954,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2024" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55974,7 +55980,7 @@
         <v>16.75</v>
       </c>
       <c r="G2025" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56000,7 +56006,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2026" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56026,7 +56032,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2027" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56052,7 +56058,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56078,7 +56084,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2029" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56104,7 +56110,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2030" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56130,7 +56136,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2031" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56156,7 +56162,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2032" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56182,7 +56188,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2033" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56208,7 +56214,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2034" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56234,7 +56240,7 @@
         <v>19</v>
       </c>
       <c r="G2035" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56260,7 +56266,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G2036" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56286,7 +56292,7 @@
         <v>18.5</v>
       </c>
       <c r="G2037" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56312,7 +56318,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2038" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56338,7 +56344,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2039" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56364,7 +56370,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2040" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56390,7 +56396,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2041" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56416,7 +56422,7 @@
         <v>18</v>
       </c>
       <c r="G2042" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56442,7 +56448,7 @@
         <v>18.5</v>
       </c>
       <c r="G2043" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56468,7 +56474,7 @@
         <v>18.75</v>
       </c>
       <c r="G2044" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56494,7 +56500,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2045" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56520,7 +56526,7 @@
         <v>18.5</v>
       </c>
       <c r="G2046" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56546,7 +56552,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2047" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56572,7 +56578,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G2048" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56598,7 +56604,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2049" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56624,7 +56630,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2050" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56650,7 +56656,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2051" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56676,7 +56682,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2052" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56702,7 +56708,7 @@
         <v>17.75</v>
       </c>
       <c r="G2053" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56728,7 +56734,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2054" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56754,7 +56760,7 @@
         <v>17.25</v>
       </c>
       <c r="G2055" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56780,7 +56786,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2056" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56806,7 +56812,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2057" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56832,7 +56838,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2058" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56858,7 +56864,7 @@
         <v>16.25</v>
       </c>
       <c r="G2059" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56884,7 +56890,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2060" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56910,7 +56916,7 @@
         <v>16.5</v>
       </c>
       <c r="G2061" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56936,7 +56942,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2062" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56962,7 +56968,7 @@
         <v>16.5</v>
       </c>
       <c r="G2063" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56988,7 +56994,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2064" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57014,7 +57020,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2065" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57040,7 +57046,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2066" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57066,7 +57072,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2067" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57092,7 +57098,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2068" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57118,7 +57124,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2069" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57144,7 +57150,7 @@
         <v>16.75</v>
       </c>
       <c r="G2070" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57170,7 +57176,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2071" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57196,7 +57202,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2072" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57222,7 +57228,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2073" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57248,7 +57254,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2074" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57274,7 +57280,7 @@
         <v>17</v>
       </c>
       <c r="G2075" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57300,7 +57306,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2076" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57326,7 +57332,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2077" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -57352,7 +57358,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2078" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -57378,7 +57384,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57404,7 +57410,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2080" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57430,7 +57436,7 @@
         <v>17.75</v>
       </c>
       <c r="G2081" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57456,7 +57462,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G2082" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57482,7 +57488,7 @@
         <v>17.5</v>
       </c>
       <c r="G2083" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57508,7 +57514,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2084" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57534,7 +57540,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2085" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57560,7 +57566,7 @@
         <v>17.5</v>
       </c>
       <c r="G2086" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57586,7 +57592,7 @@
         <v>17</v>
       </c>
       <c r="G2087" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57612,7 +57618,7 @@
         <v>17</v>
       </c>
       <c r="G2088" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57638,7 +57644,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2089" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57664,7 +57670,7 @@
         <v>17.75</v>
       </c>
       <c r="G2090" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57690,7 +57696,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2091" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57716,7 +57722,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2092" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57742,7 +57748,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2093" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57768,7 +57774,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2094" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57794,7 +57800,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2095" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57820,7 +57826,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2096" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -57846,7 +57852,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2097" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57872,7 +57878,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57898,7 +57904,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2099" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57924,7 +57930,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2100" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57950,7 +57956,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2101" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57976,7 +57982,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2102" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58002,7 +58008,7 @@
         <v>17</v>
       </c>
       <c r="G2103" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58028,7 +58034,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2104" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58054,7 +58060,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2105" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58080,7 +58086,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2106" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58106,7 +58112,7 @@
         <v>17.5</v>
       </c>
       <c r="G2107" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -58132,7 +58138,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2108" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58158,7 +58164,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2109" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -58184,7 +58190,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2110" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58210,7 +58216,7 @@
         <v>17</v>
       </c>
       <c r="G2111" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58236,7 +58242,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2112" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58262,7 +58268,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2113" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58288,7 +58294,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2114" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58314,7 +58320,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2115" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58340,7 +58346,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2116" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58366,7 +58372,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2117" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -58392,7 +58398,7 @@
         <v>17</v>
       </c>
       <c r="G2118" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58418,7 +58424,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2119" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58444,7 +58450,7 @@
         <v>17</v>
       </c>
       <c r="G2120" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58470,7 +58476,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2121" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58496,7 +58502,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2122" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58522,7 +58528,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2123" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58548,7 +58554,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2124" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58574,7 +58580,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2125" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58600,7 +58606,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2126" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58626,7 +58632,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2127" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58652,7 +58658,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2128" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58678,7 +58684,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2129" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58704,7 +58710,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2130" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58730,7 +58736,7 @@
         <v>16.5</v>
       </c>
       <c r="G2131" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58756,7 +58762,7 @@
         <v>16.5</v>
       </c>
       <c r="G2132" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58782,7 +58788,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2133" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58808,7 +58814,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2134" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58834,7 +58840,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2135" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58860,7 +58866,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2136" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58886,7 +58892,7 @@
         <v>17</v>
       </c>
       <c r="G2137" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58912,7 +58918,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2138" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58938,7 +58944,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2139" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58964,7 +58970,7 @@
         <v>16.5</v>
       </c>
       <c r="G2140" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -58990,7 +58996,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2141" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59016,7 +59022,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2142" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59042,7 +59048,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2143" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59068,7 +59074,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2144" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59094,7 +59100,7 @@
         <v>16.75</v>
       </c>
       <c r="G2145" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59120,7 +59126,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2146" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59146,7 +59152,7 @@
         <v>16.75</v>
       </c>
       <c r="G2147" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59172,7 +59178,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2148" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59198,7 +59204,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2149" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59224,7 +59230,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2150" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59250,7 +59256,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2151" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59276,7 +59282,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2152" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59302,7 +59308,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2153" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59328,7 +59334,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2154" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59354,7 +59360,7 @@
         <v>16.25</v>
       </c>
       <c r="G2155" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59380,7 +59386,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2156" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59406,7 +59412,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2157" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59432,7 +59438,7 @@
         <v>15</v>
       </c>
       <c r="G2158" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59458,7 +59464,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2159" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59484,7 +59490,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2160" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59510,7 +59516,7 @@
         <v>15.25</v>
       </c>
       <c r="G2161" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59536,7 +59542,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2162" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59562,7 +59568,7 @@
         <v>15.25</v>
       </c>
       <c r="G2163" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59588,7 +59594,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2164" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59614,7 +59620,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2165" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59640,7 +59646,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2166" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59666,7 +59672,7 @@
         <v>16.25</v>
       </c>
       <c r="G2167" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59692,7 +59698,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2168" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59718,7 +59724,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2169" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59744,7 +59750,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2170" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59770,7 +59776,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2171" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59796,7 +59802,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59822,7 +59828,7 @@
         <v>16</v>
       </c>
       <c r="G2173" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59848,7 +59854,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2174" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -59874,7 +59880,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2175" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59900,7 +59906,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2176" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59926,7 +59932,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2177" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59952,7 +59958,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2178" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59978,7 +59984,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2179" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60004,7 +60010,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60030,7 +60036,7 @@
         <v>15.25</v>
       </c>
       <c r="G2181" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60056,7 +60062,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60082,7 +60088,7 @@
         <v>15.25</v>
       </c>
       <c r="G2183" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60108,7 +60114,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2184" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60134,7 +60140,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2185" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60160,7 +60166,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2186" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60186,7 +60192,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60212,7 +60218,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2188" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60238,7 +60244,7 @@
         <v>15</v>
       </c>
       <c r="G2189" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60264,7 +60270,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2190" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60290,7 +60296,7 @@
         <v>15</v>
       </c>
       <c r="G2191" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60316,7 +60322,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2192" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60342,7 +60348,7 @@
         <v>15</v>
       </c>
       <c r="G2193" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60368,7 +60374,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2194" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60394,7 +60400,7 @@
         <v>15</v>
       </c>
       <c r="G2195" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60420,7 +60426,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2196" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60446,7 +60452,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2197" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60472,7 +60478,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60498,7 +60504,7 @@
         <v>15</v>
       </c>
       <c r="G2199" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60524,7 +60530,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G2200" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60550,7 +60556,7 @@
         <v>15</v>
       </c>
       <c r="G2201" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60576,7 +60582,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60602,7 +60608,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2203" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60628,7 +60634,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2204" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60654,7 +60660,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60680,7 +60686,7 @@
         <v>14.5</v>
       </c>
       <c r="G2206" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60706,7 +60712,7 @@
         <v>14.5</v>
       </c>
       <c r="G2207" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60732,7 +60738,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60758,7 +60764,7 @@
         <v>14.5</v>
       </c>
       <c r="G2209" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60784,7 +60790,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60810,7 +60816,7 @@
         <v>14.5</v>
       </c>
       <c r="G2211" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60836,7 +60842,7 @@
         <v>14.5</v>
       </c>
       <c r="G2212" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60862,7 +60868,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60888,7 +60894,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2214" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60914,7 +60920,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2215" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60940,7 +60946,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2216" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60966,7 +60972,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2217" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -60992,7 +60998,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2218" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61018,7 +61024,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2219" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61044,7 +61050,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2220" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61070,7 +61076,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2221" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61096,7 +61102,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2222" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61122,7 +61128,7 @@
         <v>15</v>
       </c>
       <c r="G2223" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61148,7 +61154,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61174,7 +61180,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2225" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61200,7 +61206,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2226" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61226,7 +61232,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2227" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61252,7 +61258,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61278,7 +61284,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2229" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61304,7 +61310,7 @@
         <v>15.25</v>
       </c>
       <c r="G2230" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61330,7 +61336,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2231" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61356,7 +61362,7 @@
         <v>15.5</v>
       </c>
       <c r="G2232" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61382,7 +61388,7 @@
         <v>15.5</v>
       </c>
       <c r="G2233" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61408,7 +61414,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2234" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61434,7 +61440,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2235" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61460,7 +61466,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2236" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61486,7 +61492,7 @@
         <v>16</v>
       </c>
       <c r="G2237" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61512,7 +61518,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2238" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61538,7 +61544,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2239" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61564,7 +61570,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2240" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61590,7 +61596,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2241" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61616,7 +61622,7 @@
         <v>16.5</v>
       </c>
       <c r="G2242" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61642,7 +61648,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2243" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61668,7 +61674,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2244" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61694,7 +61700,7 @@
         <v>17.25</v>
       </c>
       <c r="G2245" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61720,7 +61726,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2246" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61746,7 +61752,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2247" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61772,7 +61778,7 @@
         <v>17</v>
       </c>
       <c r="G2248" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61798,7 +61804,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2249" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61824,7 +61830,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2250" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61850,7 +61856,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61876,7 +61882,7 @@
         <v>17.25</v>
       </c>
       <c r="G2252" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61902,7 +61908,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2253" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61928,7 +61934,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2254" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61954,7 +61960,7 @@
         <v>17.75</v>
       </c>
       <c r="G2255" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61980,7 +61986,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G2256" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62006,7 +62012,7 @@
         <v>18</v>
       </c>
       <c r="G2257" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62032,7 +62038,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2258" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62058,7 +62064,7 @@
         <v>17</v>
       </c>
       <c r="G2259" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62084,7 +62090,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2260" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62110,7 +62116,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2261" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62136,7 +62142,7 @@
         <v>16.5</v>
       </c>
       <c r="G2262" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62162,7 +62168,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2263" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62188,7 +62194,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2264" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62214,7 +62220,7 @@
         <v>16.5</v>
       </c>
       <c r="G2265" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62240,7 +62246,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2266" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62266,7 +62272,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2267" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62292,7 +62298,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2268" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62318,7 +62324,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2269" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62344,7 +62350,7 @@
         <v>15.5</v>
       </c>
       <c r="G2270" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62370,7 +62376,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2271" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62396,7 +62402,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2272" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62422,7 +62428,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2273" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62448,7 +62454,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2274" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62474,7 +62480,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2275" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62500,7 +62506,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2276" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62526,7 +62532,7 @@
         <v>17</v>
       </c>
       <c r="G2277" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62552,7 +62558,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2278" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62578,7 +62584,7 @@
         <v>16.5</v>
       </c>
       <c r="G2279" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62604,7 +62610,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2280" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62630,7 +62636,7 @@
         <v>16</v>
       </c>
       <c r="G2281" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62656,7 +62662,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62682,7 +62688,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2283" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62708,7 +62714,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2284" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62734,7 +62740,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2285" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62760,7 +62766,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62786,7 +62792,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2287" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62812,7 +62818,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2288" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62838,7 +62844,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2289" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62864,7 +62870,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62890,7 +62896,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2291" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62916,7 +62922,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2292" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62942,7 +62948,7 @@
         <v>16.5</v>
       </c>
       <c r="G2293" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62968,7 +62974,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2294" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62994,7 +63000,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2295" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63020,7 +63026,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2296" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63046,7 +63052,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2297" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63072,7 +63078,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2298" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63098,7 +63104,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63124,7 +63130,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63150,7 +63156,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63176,7 +63182,7 @@
         <v>16</v>
       </c>
       <c r="G2302" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63202,7 +63208,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2303" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63228,7 +63234,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2304" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63254,7 +63260,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63280,7 +63286,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2306" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63306,7 +63312,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2307" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63332,7 +63338,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2308" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63358,7 +63364,7 @@
         <v>15.75</v>
       </c>
       <c r="G2309" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63384,7 +63390,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2310" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63410,7 +63416,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2311" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63436,7 +63442,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63462,7 +63468,7 @@
         <v>16</v>
       </c>
       <c r="G2313" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63488,7 +63494,7 @@
         <v>16</v>
       </c>
       <c r="G2314" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63514,7 +63520,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2315" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63540,7 +63546,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2316" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63566,7 +63572,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2317" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63592,7 +63598,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63618,7 +63624,7 @@
         <v>16</v>
       </c>
       <c r="G2319" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63644,7 +63650,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2320" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63670,7 +63676,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2321" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63696,7 +63702,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2322" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63722,7 +63728,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2323" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63748,7 +63754,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2324" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63774,7 +63780,7 @@
         <v>16</v>
       </c>
       <c r="G2325" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63800,7 +63806,7 @@
         <v>16</v>
       </c>
       <c r="G2326" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63826,7 +63832,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2327" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63852,7 +63858,7 @@
         <v>16</v>
       </c>
       <c r="G2328" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63878,7 +63884,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2329" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63904,7 +63910,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2330" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63930,7 +63936,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2331" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63956,7 +63962,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63982,7 +63988,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64008,7 +64014,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2334" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64034,7 +64040,7 @@
         <v>15.75</v>
       </c>
       <c r="G2335" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64060,7 +64066,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2336" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64086,7 +64092,7 @@
         <v>15.75</v>
       </c>
       <c r="G2337" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64112,7 +64118,7 @@
         <v>15.25</v>
       </c>
       <c r="G2338" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64138,7 +64144,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2339" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64164,7 +64170,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2340" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64190,7 +64196,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2341" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64216,7 +64222,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64242,7 +64248,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64268,7 +64274,7 @@
         <v>15.5</v>
       </c>
       <c r="G2344" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64294,7 +64300,7 @@
         <v>15.5</v>
       </c>
       <c r="G2345" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64320,7 +64326,7 @@
         <v>15</v>
       </c>
       <c r="G2346" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64346,7 +64352,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64372,7 +64378,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64398,7 +64404,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2349" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64424,7 +64430,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2350" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64450,7 +64456,7 @@
         <v>16</v>
       </c>
       <c r="G2351" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64476,7 +64482,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64502,7 +64508,7 @@
         <v>15.75</v>
       </c>
       <c r="G2353" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64528,7 +64534,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64554,7 +64560,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2355" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64580,7 +64586,7 @@
         <v>15.25</v>
       </c>
       <c r="G2356" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64606,7 +64612,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2357" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64632,7 +64638,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64658,7 +64664,7 @@
         <v>14</v>
       </c>
       <c r="G2359" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64684,7 +64690,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2360" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64710,7 +64716,7 @@
         <v>15</v>
       </c>
       <c r="G2361" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64736,7 +64742,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2362" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64762,7 +64768,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2363" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64788,7 +64794,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2364" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64814,7 +64820,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64840,7 +64846,7 @@
         <v>14.5</v>
       </c>
       <c r="G2366" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64866,7 +64872,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2367" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64892,7 +64898,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2368" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64918,7 +64924,7 @@
         <v>15</v>
       </c>
       <c r="G2369" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64944,7 +64950,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2370" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64970,7 +64976,7 @@
         <v>15.25</v>
       </c>
       <c r="G2371" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64996,7 +65002,7 @@
         <v>15.25</v>
       </c>
       <c r="G2372" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65022,7 +65028,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2373" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65048,7 +65054,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2374" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65074,7 +65080,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2375" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65100,7 +65106,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2376" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65126,7 +65132,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65152,7 +65158,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2378" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65178,7 +65184,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2379" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65204,7 +65210,7 @@
         <v>15.25</v>
       </c>
       <c r="G2380" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65230,7 +65236,7 @@
         <v>15.25</v>
       </c>
       <c r="G2381" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65256,7 +65262,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2382" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65282,7 +65288,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2383" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65308,7 +65314,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65334,7 +65340,7 @@
         <v>16</v>
       </c>
       <c r="G2385" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65360,7 +65366,7 @@
         <v>16.25</v>
       </c>
       <c r="G2386" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65386,7 +65392,7 @@
         <v>16</v>
       </c>
       <c r="G2387" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65412,7 +65418,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2388" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65438,7 +65444,7 @@
         <v>16.5</v>
       </c>
       <c r="G2389" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65464,7 +65470,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2390" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65490,7 +65496,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2391" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65516,7 +65522,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2392" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65542,7 +65548,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2393" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65568,7 +65574,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2394" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65594,7 +65600,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2395" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65620,7 +65626,7 @@
         <v>16.75</v>
       </c>
       <c r="G2396" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65646,7 +65652,7 @@
         <v>16.5</v>
       </c>
       <c r="G2397" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65672,7 +65678,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2398" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65698,7 +65704,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2399" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65724,7 +65730,7 @@
         <v>16.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65750,7 +65756,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65776,7 +65782,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2402" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65802,7 +65808,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65828,7 +65834,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2404" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65854,7 +65860,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2405" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65880,7 +65886,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2406" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65906,7 +65912,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2407" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65932,7 +65938,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2408" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65958,7 +65964,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G2409" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65984,7 +65990,7 @@
         <v>16</v>
       </c>
       <c r="G2410" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66010,7 +66016,7 @@
         <v>15.75</v>
       </c>
       <c r="G2411" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66036,7 +66042,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2412" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66062,7 +66068,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2413" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66088,7 +66094,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2414" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66114,7 +66120,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2415" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66140,7 +66146,7 @@
         <v>16.25</v>
       </c>
       <c r="G2416" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66166,7 +66172,7 @@
         <v>16.75</v>
       </c>
       <c r="G2417" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66192,7 +66198,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2418" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66218,7 +66224,7 @@
         <v>16.25</v>
       </c>
       <c r="G2419" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66244,7 +66250,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2420" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66270,7 +66276,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2421" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66296,7 +66302,7 @@
         <v>16.25</v>
       </c>
       <c r="G2422" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66322,7 +66328,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2423" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66348,7 +66354,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2424" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66374,7 +66380,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2425" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66400,7 +66406,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2426" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66426,7 +66432,7 @@
         <v>16.25</v>
       </c>
       <c r="G2427" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66452,7 +66458,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2428" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66478,7 +66484,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66504,7 +66510,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2430" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66530,7 +66536,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2431" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66556,7 +66562,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66582,7 +66588,7 @@
         <v>16.5</v>
       </c>
       <c r="G2433" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66608,7 +66614,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2434" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66634,7 +66640,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2435" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66660,7 +66666,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2436" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66686,7 +66692,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2437" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66712,7 +66718,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2438" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66738,7 +66744,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2439" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66764,7 +66770,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2440" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66790,7 +66796,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66816,7 +66822,7 @@
         <v>16.75</v>
       </c>
       <c r="G2442" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66842,7 +66848,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66868,7 +66874,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2444" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66894,7 +66900,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2445" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66920,7 +66926,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2446" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66946,7 +66952,7 @@
         <v>18</v>
       </c>
       <c r="G2447" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66972,7 +66978,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2448" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66998,7 +67004,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67024,7 +67030,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2450" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67050,7 +67056,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2451" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67076,7 +67082,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2452" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67102,7 +67108,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2453" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67128,7 +67134,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2454" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67154,7 +67160,7 @@
         <v>21</v>
       </c>
       <c r="G2455" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67180,7 +67186,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G2456" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67206,7 +67212,7 @@
         <v>19.25</v>
       </c>
       <c r="G2457" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67232,7 +67238,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G2458" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67258,7 +67264,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G2459" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67284,7 +67290,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67310,7 +67316,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2461" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67336,7 +67342,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2462" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67362,7 +67368,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67388,7 +67394,7 @@
         <v>18.5</v>
       </c>
       <c r="G2464" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67414,7 +67420,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G2465" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67440,7 +67446,7 @@
         <v>19</v>
       </c>
       <c r="G2466" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67466,7 +67472,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2467" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67492,7 +67498,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2468" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67518,7 +67524,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2469" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67544,7 +67550,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2470" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67570,7 +67576,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2471" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67596,7 +67602,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2472" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67622,7 +67628,7 @@
         <v>16</v>
       </c>
       <c r="G2473" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67648,7 +67654,7 @@
         <v>16</v>
       </c>
       <c r="G2474" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67674,7 +67680,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2475" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67700,7 +67706,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67726,7 +67732,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67752,7 +67758,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67778,7 +67784,7 @@
         <v>16.25</v>
       </c>
       <c r="G2479" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67804,7 +67810,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67830,7 +67836,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2481" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67856,7 +67862,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67882,7 +67888,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67908,7 +67914,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2484" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67934,7 +67940,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2485" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67960,7 +67966,7 @@
         <v>16</v>
       </c>
       <c r="G2486" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67986,7 +67992,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2487" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68012,7 +68018,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2488" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68038,7 +68044,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68064,7 +68070,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2490" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68090,7 +68096,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2491" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68116,7 +68122,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2492" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68142,7 +68148,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68168,7 +68174,7 @@
         <v>15.25</v>
       </c>
       <c r="G2494" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68194,7 +68200,7 @@
         <v>15.5</v>
       </c>
       <c r="G2495" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68220,7 +68226,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2496" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68246,7 +68252,7 @@
         <v>15.5</v>
       </c>
       <c r="G2497" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68272,7 +68278,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2498" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68298,7 +68304,7 @@
         <v>15.25</v>
       </c>
       <c r="G2499" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -68324,7 +68330,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2500" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -68332,7 +68338,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6911574074</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>7137</v>
@@ -68350,9 +68356,35 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2501" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6910069444</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>2414</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>15.3000001907349</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>15.0500001907349</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>15.3000001907349</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>15.1999998092651</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>995</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BEC.MI.xlsx
+++ b/data/BEC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="997">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96833801269531</t>
+    <t xml:space="preserve">4.96833848953247</t>
   </si>
   <si>
     <t xml:space="preserve">BEC.MI</t>
@@ -50,64 +50,64 @@
     <t xml:space="preserve">4.87040758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87693643569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92916631698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77247714996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79859209060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83450031280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73330593109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79532766342163</t>
+    <t xml:space="preserve">4.87693691253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92916536331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77247762680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79859161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83449983596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73330450057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79532814025879</t>
   </si>
   <si>
     <t xml:space="preserve">4.80512094497681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76594924926758</t>
+    <t xml:space="preserve">4.76594829559326</t>
   </si>
   <si>
     <t xml:space="preserve">4.75942039489746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60273265838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69739723205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69413280487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63537454605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44277763366699</t>
+    <t xml:space="preserve">4.60273122787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69739818572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69413328170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63537406921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44277811050415</t>
   </si>
   <si>
     <t xml:space="preserve">4.37422657012939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18489408493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07390642166138</t>
+    <t xml:space="preserve">4.18489503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07390737533569</t>
   </si>
   <si>
     <t xml:space="preserve">4.08043575286865</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23386001586914</t>
+    <t xml:space="preserve">4.2338604927063</t>
   </si>
   <si>
     <t xml:space="preserve">4.40360593795776</t>
@@ -116,46 +116,46 @@
     <t xml:space="preserve">4.49174356460571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53091621398926</t>
+    <t xml:space="preserve">4.5309157371521</t>
   </si>
   <si>
     <t xml:space="preserve">4.43298530578613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50480127334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53744459152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42645692825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42319250106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43951416015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41666316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44930696487427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4656286239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47868537902832</t>
+    <t xml:space="preserve">4.50480079650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53744411468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42645645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42319202423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43951368331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.416663646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44930744171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46562910079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47868633270264</t>
   </si>
   <si>
     <t xml:space="preserve">4.60926008224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8965220451355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90957975387573</t>
+    <t xml:space="preserve">4.89652252197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90958023071289</t>
   </si>
   <si>
     <t xml:space="preserve">4.93569469451904</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">5.09238338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94875144958496</t>
+    <t xml:space="preserve">4.94875192642212</t>
   </si>
   <si>
     <t xml:space="preserve">4.99445295333862</t>
@@ -188,16 +188,16 @@
     <t xml:space="preserve">4.84429311752319</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06953382492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09891223907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98792409896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04994678497314</t>
+    <t xml:space="preserve">5.0695333480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09891319274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98792457580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04994773864746</t>
   </si>
   <si>
     <t xml:space="preserve">5.04341840744019</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">4.98466014862061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02709627151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99973773956299</t>
+    <t xml:space="preserve">5.02709579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99973821640015</t>
   </si>
   <si>
     <t xml:space="preserve">5.03393602371216</t>
@@ -224,46 +224,46 @@
     <t xml:space="preserve">4.91766357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94502067565918</t>
+    <t xml:space="preserve">4.9450216293335</t>
   </si>
   <si>
     <t xml:space="preserve">4.85610628128052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89030504226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89714479446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79455184936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82190895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98264026641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92450332641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00657844543457</t>
+    <t xml:space="preserve">4.89030456542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89714431762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79455089569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82190942764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9826397895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92450284957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00657796859741</t>
   </si>
   <si>
     <t xml:space="preserve">4.88346529006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94844150543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95870113372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99289846420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86636590957642</t>
+    <t xml:space="preserve">4.94844102859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95870018005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99289894104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86636638641357</t>
   </si>
   <si>
     <t xml:space="preserve">4.8526873588562</t>
@@ -275,28 +275,28 @@
     <t xml:space="preserve">4.78771114349365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78429079055786</t>
+    <t xml:space="preserve">4.78429174423218</t>
   </si>
   <si>
     <t xml:space="preserve">4.8253288269043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77403163909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72273540496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67485809326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75693225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56200504302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54148626327515</t>
+    <t xml:space="preserve">4.77403211593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7227349281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67485761642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75693321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56200408935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54148530960083</t>
   </si>
   <si>
     <t xml:space="preserve">4.53122615814209</t>
@@ -305,34 +305,34 @@
     <t xml:space="preserve">4.6030421257019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63040113449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55516529083252</t>
+    <t xml:space="preserve">4.63040065765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5551643371582</t>
   </si>
   <si>
     <t xml:space="preserve">4.58252334594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54832601547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45941114425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53464698791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52780675888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52096748352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64407920837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74325323104858</t>
+    <t xml:space="preserve">4.54832553863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45941066741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53464603424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5278058052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52096652984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64407968521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7432541847229</t>
   </si>
   <si>
     <t xml:space="preserve">4.73983383178711</t>
@@ -341,22 +341,22 @@
     <t xml:space="preserve">4.8355884552002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92108249664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92792177200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98605871200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96554088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91424226760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97237968444824</t>
+    <t xml:space="preserve">4.92108297348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92792224884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98605966567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96554040908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91424322128296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9723801612854</t>
   </si>
   <si>
     <t xml:space="preserve">4.96896028518677</t>
@@ -368,43 +368,43 @@
     <t xml:space="preserve">4.93818187713623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88004493713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9518609046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87320566177368</t>
+    <t xml:space="preserve">4.88004589080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95186138153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87320613861084</t>
   </si>
   <si>
     <t xml:space="preserve">4.86294651031494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76719236373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80139017105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80822992324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7637734413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84242820739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72957468032837</t>
+    <t xml:space="preserve">4.76719188690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80139064788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80823040008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76377296447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8424277305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72957420349121</t>
   </si>
   <si>
     <t xml:space="preserve">4.84926748275757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81164932250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8868842124939</t>
+    <t xml:space="preserve">4.81164979934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88688516616821</t>
   </si>
   <si>
     <t xml:space="preserve">5.02025651931763</t>
@@ -413,19 +413,19 @@
     <t xml:space="preserve">5.08865308761597</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10575199127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06471490859985</t>
+    <t xml:space="preserve">5.10575246810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0647144317627</t>
   </si>
   <si>
     <t xml:space="preserve">5.04761552810669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09549283981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17756795883179</t>
+    <t xml:space="preserve">5.09549188613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17756843566895</t>
   </si>
   <si>
     <t xml:space="preserve">5.23228454589844</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">5.12969064712524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13994979858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16388893127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21176481246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30752038955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30068063735962</t>
+    <t xml:space="preserve">5.13994932174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16388845443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21176528930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30751943588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30068016052246</t>
   </si>
   <si>
     <t xml:space="preserve">5.13311004638672</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">5.22544479370117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16730833053589</t>
+    <t xml:space="preserve">5.16730785369873</t>
   </si>
   <si>
     <t xml:space="preserve">5.19808626174927</t>
@@ -464,37 +464,37 @@
     <t xml:space="preserve">5.29726028442383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47167015075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40327405929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36565637588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36223602294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46482992172241</t>
+    <t xml:space="preserve">5.47166967391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4032735824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36565589904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36223697662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46483087539673</t>
   </si>
   <si>
     <t xml:space="preserve">5.36907577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39643383026123</t>
+    <t xml:space="preserve">5.39643430709839</t>
   </si>
   <si>
     <t xml:space="preserve">5.25964307785034</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41353368759155</t>
+    <t xml:space="preserve">5.41353321075439</t>
   </si>
   <si>
     <t xml:space="preserve">5.46141052246094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43747234344482</t>
+    <t xml:space="preserve">5.43747138977051</t>
   </si>
   <si>
     <t xml:space="preserve">5.45457077026367</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">5.46824979782104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47508907318115</t>
+    <t xml:space="preserve">5.47508955001831</t>
   </si>
   <si>
     <t xml:space="preserve">5.39985370635986</t>
@@ -512,25 +512,25 @@
     <t xml:space="preserve">5.41695308685303</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43063259124756</t>
+    <t xml:space="preserve">5.4306321144104</t>
   </si>
   <si>
     <t xml:space="preserve">5.45799112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50586795806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52980613708496</t>
+    <t xml:space="preserve">5.50586748123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52980709075928</t>
   </si>
   <si>
     <t xml:space="preserve">5.60846090316772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68369674682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73157453536987</t>
+    <t xml:space="preserve">5.68369770050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73157405853271</t>
   </si>
   <si>
     <t xml:space="preserve">5.88204526901245</t>
@@ -542,34 +542,34 @@
     <t xml:space="preserve">5.94360113143921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0564546585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94018173217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04961585998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07355260848999</t>
+    <t xml:space="preserve">6.05645370483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94018220901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04961538314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07355308532715</t>
   </si>
   <si>
     <t xml:space="preserve">6.02567720413208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97437906265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04277515411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17272663116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39501428604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37449502944946</t>
+    <t xml:space="preserve">5.97437953948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04277610778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17272710800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39501476287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3744945526123</t>
   </si>
   <si>
     <t xml:space="preserve">6.46683025360107</t>
@@ -584,58 +584,58 @@
     <t xml:space="preserve">5.8991436958313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00515699386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22402381896973</t>
+    <t xml:space="preserve">6.00515747070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22402429580688</t>
   </si>
   <si>
     <t xml:space="preserve">6.26506233215332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39843416213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48050832748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41211366653442</t>
+    <t xml:space="preserve">6.39843368530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40527391433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48050975799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41211318969727</t>
   </si>
   <si>
     <t xml:space="preserve">6.44973039627075</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43605136871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52838563919067</t>
+    <t xml:space="preserve">6.4360523223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52838611602783</t>
   </si>
   <si>
     <t xml:space="preserve">6.66859865188599</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99689674377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94218063354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12001085281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46882915496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6671781539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2006664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40585327148438</t>
+    <t xml:space="preserve">6.99689769744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94218111038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1200098991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46882963180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66717720031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20066452026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40585231781006</t>
   </si>
   <si>
     <t xml:space="preserve">8.64523792266846</t>
@@ -647,76 +647,76 @@
     <t xml:space="preserve">8.35113620758057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28958034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24170398712158</t>
+    <t xml:space="preserve">8.28957939147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24170303344727</t>
   </si>
   <si>
     <t xml:space="preserve">8.33745670318604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33061790466309</t>
+    <t xml:space="preserve">8.3306188583374</t>
   </si>
   <si>
     <t xml:space="preserve">8.31693840026855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26906108856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22118377685547</t>
+    <t xml:space="preserve">8.26906204223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22118186950684</t>
   </si>
   <si>
     <t xml:space="preserve">8.11858940124512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30325984954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48108768463135</t>
+    <t xml:space="preserve">8.30325889587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48108863830566</t>
   </si>
   <si>
     <t xml:space="preserve">8.72047424316406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7136344909668</t>
+    <t xml:space="preserve">8.71363353729248</t>
   </si>
   <si>
     <t xml:space="preserve">8.79469108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49782371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52750968933105</t>
+    <t xml:space="preserve">8.49782276153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52751064300537</t>
   </si>
   <si>
     <t xml:space="preserve">8.07478904724121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31228160858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43102741241455</t>
+    <t xml:space="preserve">8.31228065490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43102836608887</t>
   </si>
   <si>
     <t xml:space="preserve">8.37165546417236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97830533981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88924598693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23806476593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26033020019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21579933166504</t>
+    <t xml:space="preserve">7.97830629348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88924551010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23806571960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.260329246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21580028533936</t>
   </si>
   <si>
     <t xml:space="preserve">8.64625644683838</t>
@@ -728,13 +728,13 @@
     <t xml:space="preserve">8.80211162567139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69078731536865</t>
+    <t xml:space="preserve">8.69078826904297</t>
   </si>
   <si>
     <t xml:space="preserve">8.5794620513916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66110134124756</t>
+    <t xml:space="preserve">8.66110038757324</t>
   </si>
   <si>
     <t xml:space="preserve">8.54977512359619</t>
@@ -746,28 +746,28 @@
     <t xml:space="preserve">8.53493118286133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60172748565674</t>
+    <t xml:space="preserve">8.60172653198242</t>
   </si>
   <si>
     <t xml:space="preserve">8.4829797744751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59430503845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46813583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14900207519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31970405578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12673759460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46071434020996</t>
+    <t xml:space="preserve">8.59430694580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46813678741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14900493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31970310211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12673950195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46071529388428</t>
   </si>
   <si>
     <t xml:space="preserve">8.58688354492188</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">8.7056303024292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84664154052734</t>
+    <t xml:space="preserve">8.84664249420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.69820880889893</t>
@@ -785,82 +785,82 @@
     <t xml:space="preserve">8.74273777008057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56461811065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43844890594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40876197814941</t>
+    <t xml:space="preserve">8.56461906433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43845081329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40876293182373</t>
   </si>
   <si>
     <t xml:space="preserve">8.34939002990723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42360591888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54235458374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63141441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61657047271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63883590698242</t>
+    <t xml:space="preserve">8.42360782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54235172271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63141250610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61656951904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63883495330811</t>
   </si>
   <si>
     <t xml:space="preserve">8.66852283477783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77984809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88374996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83922100067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82437705993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6091480255127</t>
+    <t xml:space="preserve">8.77984714508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88375186920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83922004699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82437801361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68336582183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60914897918701</t>
   </si>
   <si>
     <t xml:space="preserve">8.57203960418701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49040222167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47555828094482</t>
+    <t xml:space="preserve">8.49040126800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47555732727051</t>
   </si>
   <si>
     <t xml:space="preserve">8.78726863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71305084228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65367698669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62399101257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75016117095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90601444244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89859485626221</t>
+    <t xml:space="preserve">8.71305179595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65367889404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62399196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75016021728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90601634979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89859390258789</t>
   </si>
   <si>
     <t xml:space="preserve">8.94312477111816</t>
@@ -872,28 +872,28 @@
     <t xml:space="preserve">8.96538925170898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87632942199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97281074523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09155750274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21772766113281</t>
+    <t xml:space="preserve">8.87632846832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97281265258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09155654907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2177267074585</t>
   </si>
   <si>
     <t xml:space="preserve">9.52201557159424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55170154571533</t>
+    <t xml:space="preserve">9.55170059204102</t>
   </si>
   <si>
     <t xml:space="preserve">9.5665454864502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45522022247314</t>
+    <t xml:space="preserve">9.45521926879883</t>
   </si>
   <si>
     <t xml:space="preserve">9.47748565673828</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">9.53685855865479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35873889923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59623336791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64076328277588</t>
+    <t xml:space="preserve">9.35873699188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59623146057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64076137542725</t>
   </si>
   <si>
     <t xml:space="preserve">9.90794277191162</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">9.89309883117676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76693058013916</t>
+    <t xml:space="preserve">9.76693153381348</t>
   </si>
   <si>
     <t xml:space="preserve">9.72982025146484</t>
@@ -932,73 +932,73 @@
     <t xml:space="preserve">10.0563764572144</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64818286895752</t>
+    <t xml:space="preserve">9.64818382263184</t>
   </si>
   <si>
     <t xml:space="preserve">9.95989418029785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82630348205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81146049499512</t>
+    <t xml:space="preserve">9.82630252838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8114595413208</t>
   </si>
   <si>
     <t xml:space="preserve">9.75208759307861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85599136352539</t>
+    <t xml:space="preserve">9.85598945617676</t>
   </si>
   <si>
     <t xml:space="preserve">9.86341285705566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0415325164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0118455886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9450511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90052127838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83179759979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97088432312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25290870666504</t>
+    <t xml:space="preserve">10.0415334701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0118465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94505023956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90051937103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8317985534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97088384628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25290679931641</t>
   </si>
   <si>
     <t xml:space="preserve">8.16384792327881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1935338973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67594242095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50524425506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02283668518066</t>
+    <t xml:space="preserve">8.19353485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67594337463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50524520874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02283573150635</t>
   </si>
   <si>
     <t xml:space="preserve">8.0673656463623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98572683334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78534078598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76307582855225</t>
+    <t xml:space="preserve">7.98572826385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78534317016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76307725906372</t>
   </si>
   <si>
     <t xml:space="preserve">7.7037034034729</t>
@@ -1007,10 +1007,10 @@
     <t xml:space="preserve">7.82987213134766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64433002471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72596788406372</t>
+    <t xml:space="preserve">7.64433097839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72596836090088</t>
   </si>
   <si>
     <t xml:space="preserve">8.04510116577148</t>
@@ -1019,19 +1019,19 @@
     <t xml:space="preserve">8.14158344268799</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91893291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08963012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11931705474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11189746856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09705257415771</t>
+    <t xml:space="preserve">7.9189338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08963108062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11931800842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11189556121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0970516204834</t>
   </si>
   <si>
     <t xml:space="preserve">8.00057029724121</t>
@@ -1040,49 +1040,49 @@
     <t xml:space="preserve">8.13416194915771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28259563446045</t>
+    <t xml:space="preserve">8.28259468078613</t>
   </si>
   <si>
     <t xml:space="preserve">8.20837688446045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34196853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44587135314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92085933685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02476215362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32712459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26775169372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71854686737061</t>
+    <t xml:space="preserve">8.34196758270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4458703994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92085742950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0247631072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32712554931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26775074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71854734420776</t>
   </si>
   <si>
     <t xml:space="preserve">8.03025722503662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01541423797607</t>
+    <t xml:space="preserve">8.01541519165039</t>
   </si>
   <si>
     <t xml:space="preserve">8.1044750213623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17869186401367</t>
+    <t xml:space="preserve">8.17868995666504</t>
   </si>
   <si>
     <t xml:space="preserve">8.22322082519531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40134143829346</t>
+    <t xml:space="preserve">8.40134048461914</t>
   </si>
   <si>
     <t xml:space="preserve">9.0544490814209</t>
@@ -1091,25 +1091,25 @@
     <t xml:space="preserve">8.93570232391357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72789669036865</t>
+    <t xml:space="preserve">8.72789573669434</t>
   </si>
   <si>
     <t xml:space="preserve">8.8911714553833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00992012023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27710056304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30678558349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24741268157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35131645202637</t>
+    <t xml:space="preserve">9.00991916656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.277099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30678653717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24741363525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35131549835205</t>
   </si>
   <si>
     <t xml:space="preserve">9.5294361114502</t>
@@ -1127,10 +1127,10 @@
     <t xml:space="preserve">9.87083435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60365295410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0637989044189</t>
+    <t xml:space="preserve">9.60365390777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0637979507446</t>
   </si>
   <si>
     <t xml:space="preserve">9.87998390197754</t>
@@ -1139,22 +1139,22 @@
     <t xml:space="preserve">9.54299163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55831050872803</t>
+    <t xml:space="preserve">9.55830955505371</t>
   </si>
   <si>
     <t xml:space="preserve">9.72680568695068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60426235198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46640396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57362842559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6195821762085</t>
+    <t xml:space="preserve">9.60426330566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46640300750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57362747192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61958122253418</t>
   </si>
   <si>
     <t xml:space="preserve">9.63489818572998</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">9.68085289001465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48172187805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43576717376709</t>
+    <t xml:space="preserve">9.48172092437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43576812744141</t>
   </si>
   <si>
     <t xml:space="preserve">9.3438606262207</t>
@@ -1184,10 +1184,10 @@
     <t xml:space="preserve">8.53201770782471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89964389801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96091556549072</t>
+    <t xml:space="preserve">8.89964485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96091651916504</t>
   </si>
   <si>
     <t xml:space="preserve">9.28258991241455</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">9.20600128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49703884124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51235771179199</t>
+    <t xml:space="preserve">9.49703693389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51235675811768</t>
   </si>
   <si>
     <t xml:space="preserve">9.52767467498779</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">9.35917949676514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19068145751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86466503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58894634246826</t>
+    <t xml:space="preserve">9.19068336486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86466598510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58894729614258</t>
   </si>
   <si>
     <t xml:space="preserve">9.32854461669922</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">9.11409282684326</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14472770690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26727390289307</t>
+    <t xml:space="preserve">9.1447286605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26727294921875</t>
   </si>
   <si>
     <t xml:space="preserve">9.45108604431152</t>
@@ -1247,25 +1247,25 @@
     <t xml:space="preserve">9.69616985321045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65021705627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80773735046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06814002990723</t>
+    <t xml:space="preserve">9.65021800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80773639678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">9.37449645996094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03750514984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12941074371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02218627929688</t>
+    <t xml:space="preserve">9.03750610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1294116973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02218723297119</t>
   </si>
   <si>
     <t xml:space="preserve">8.91496276855469</t>
@@ -1277,13 +1277,13 @@
     <t xml:space="preserve">9.17536354064941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00687026977539</t>
+    <t xml:space="preserve">9.00686931610107</t>
   </si>
   <si>
     <t xml:space="preserve">9.95657253265381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0331630706787</t>
+    <t xml:space="preserve">10.0331611633301</t>
   </si>
   <si>
     <t xml:space="preserve">9.91061878204346</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">9.78807640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75744152069092</t>
+    <t xml:space="preserve">9.75744247436523</t>
   </si>
   <si>
     <t xml:space="preserve">9.09877586364746</t>
@@ -1304,28 +1304,28 @@
     <t xml:space="preserve">8.86900901794434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74646663665771</t>
+    <t xml:space="preserve">8.7464656829834</t>
   </si>
   <si>
     <t xml:space="preserve">8.73114776611328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51669979095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47074508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42479228973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01121044158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.225661277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36352157592773</t>
+    <t xml:space="preserve">8.51669883728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47074699401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42479133605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01121139526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22566223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36352062225342</t>
   </si>
   <si>
     <t xml:space="preserve">8.65456008911133</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">8.77710151672363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8383731842041</t>
+    <t xml:space="preserve">8.83837413787842</t>
   </si>
   <si>
     <t xml:space="preserve">8.93027877807617</t>
@@ -1352,43 +1352,43 @@
     <t xml:space="preserve">8.82305526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60860633850098</t>
+    <t xml:space="preserve">8.60860538482666</t>
   </si>
   <si>
     <t xml:space="preserve">8.57797050476074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3482027053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30224990844727</t>
+    <t xml:space="preserve">8.34820365905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30224895477295</t>
   </si>
   <si>
     <t xml:space="preserve">8.33288669586182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37883853912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28693199157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27161407470703</t>
+    <t xml:space="preserve">8.37883758544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28693103790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27161502838135</t>
   </si>
   <si>
     <t xml:space="preserve">8.39415740966797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13375473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11843681335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4554271697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79242038726807</t>
+    <t xml:space="preserve">8.13375377655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11843776702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45542812347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79241943359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.85369110107422</t>
@@ -1403,31 +1403,31 @@
     <t xml:space="preserve">8.68519592285156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54733562469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44011116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88432598114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40513229370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92593669891357</t>
+    <t xml:space="preserve">8.54733467102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.440110206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88432693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40513324737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92593574523926</t>
   </si>
   <si>
     <t xml:space="preserve">9.80339527130127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29790782928467</t>
+    <t xml:space="preserve">9.29790687561035</t>
   </si>
   <si>
     <t xml:space="preserve">9.22897815704346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0757999420166</t>
+    <t xml:space="preserve">9.07579898834229</t>
   </si>
   <si>
     <t xml:space="preserve">9.15238761901855</t>
@@ -1436,16 +1436,16 @@
     <t xml:space="preserve">8.99921035766602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59734916687012</t>
+    <t xml:space="preserve">9.59735107421875</t>
   </si>
   <si>
     <t xml:space="preserve">9.31742668151855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79757022857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87754917144775</t>
+    <t xml:space="preserve">8.79757118225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87754821777344</t>
   </si>
   <si>
     <t xml:space="preserve">8.83756065368652</t>
@@ -1454,37 +1454,37 @@
     <t xml:space="preserve">8.63761520385742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23744869232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27743816375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47738361358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3574161529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51737117767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67733001708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63733959197998</t>
+    <t xml:space="preserve">9.23744964599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27743911743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47738265991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35741710662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51737213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67732906341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63733863830566</t>
   </si>
   <si>
     <t xml:space="preserve">9.39740562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19746017456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07749366760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4373950958252</t>
+    <t xml:space="preserve">9.19745922088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07749557495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43739414215088</t>
   </si>
   <si>
     <t xml:space="preserve">9.55736064910889</t>
@@ -1502,28 +1502,28 @@
     <t xml:space="preserve">8.99751567840576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15747165679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9175386428833</t>
+    <t xml:space="preserve">9.157470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91753768920898</t>
   </si>
   <si>
     <t xml:space="preserve">10.7970190048218</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3571395874023</t>
+    <t xml:space="preserve">10.3571405410767</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3171510696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.117205619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91726207733154</t>
+    <t xml:space="preserve">10.3171520233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1172065734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91726016998291</t>
   </si>
   <si>
     <t xml:space="preserve">9.99724006652832</t>
@@ -1532,13 +1532,13 @@
     <t xml:space="preserve">10.0372295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75730609893799</t>
+    <t xml:space="preserve">9.75730514526367</t>
   </si>
   <si>
     <t xml:space="preserve">9.71731758117676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79729461669922</t>
+    <t xml:space="preserve">9.79729557037354</t>
   </si>
   <si>
     <t xml:space="preserve">9.83728313446045</t>
@@ -1559,22 +1559,22 @@
     <t xml:space="preserve">10.5570850372314</t>
   </si>
   <si>
-    <t xml:space="preserve">10.477108001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1971855163574</t>
+    <t xml:space="preserve">10.4771070480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1971836090088</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170955657959</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9969644546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1169290542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3168754577637</t>
+    <t xml:space="preserve">10.9969635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1169300079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.316876411438</t>
   </si>
   <si>
     <t xml:space="preserve">11.2368974685669</t>
@@ -1583,22 +1583,22 @@
     <t xml:space="preserve">11.3568639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969089508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8370084762573</t>
+    <t xml:space="preserve">11.1969079971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.837007522583</t>
   </si>
   <si>
     <t xml:space="preserve">11.1569185256958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0369520187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8769969940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9169855117798</t>
+    <t xml:space="preserve">11.0369529724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8769989013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9169845581055</t>
   </si>
   <si>
     <t xml:space="preserve">10.9569749832153</t>
@@ -1607,37 +1607,37 @@
     <t xml:space="preserve">10.7570295333862</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5970735549927</t>
+    <t xml:space="preserve">10.597074508667</t>
   </si>
   <si>
     <t xml:space="preserve">10.4371185302734</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2768869400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.436842918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.556809425354</t>
+    <t xml:space="preserve">11.2768859863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4368419647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5568084716797</t>
   </si>
   <si>
     <t xml:space="preserve">11.6767768859863</t>
   </si>
   <si>
-    <t xml:space="preserve">10.717041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11775779724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1660213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88582277297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46993827819824</t>
+    <t xml:space="preserve">10.7170400619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11775684356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16602087020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88582229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46993780136108</t>
   </si>
   <si>
     <t xml:space="preserve">7.03805732727051</t>
@@ -1649,25 +1649,25 @@
     <t xml:space="preserve">6.39823341369629</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20628690719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99834394454956</t>
+    <t xml:space="preserve">6.20628643035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9983434677124</t>
   </si>
   <si>
     <t xml:space="preserve">6.55818843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30998134613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40595579147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32597732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11803436279297</t>
+    <t xml:space="preserve">7.30998277664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40595483779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32597684860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11803531646729</t>
   </si>
   <si>
     <t xml:space="preserve">6.73414087295532</t>
@@ -1676,34 +1676,34 @@
     <t xml:space="preserve">6.9740743637085</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29398536682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15002584457397</t>
+    <t xml:space="preserve">7.29398632049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15002536773682</t>
   </si>
   <si>
     <t xml:space="preserve">6.86210536956787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81411933898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76613235473633</t>
+    <t xml:space="preserve">6.8141188621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76613187789917</t>
   </si>
   <si>
     <t xml:space="preserve">6.94208335876465</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79812288284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92608690261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78212738037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83011436462402</t>
+    <t xml:space="preserve">6.79812335968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92608737945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78212690353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83011388778687</t>
   </si>
   <si>
     <t xml:space="preserve">6.92877912521362</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">6.89601898193359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96153974533081</t>
+    <t xml:space="preserve">6.96153926849365</t>
   </si>
   <si>
     <t xml:space="preserve">6.73221826553345</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">6.74859809875488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05981922149658</t>
+    <t xml:space="preserve">7.05981969833374</t>
   </si>
   <si>
     <t xml:space="preserve">7.1253399848938</t>
@@ -1736,37 +1736,37 @@
     <t xml:space="preserve">7.55122327804565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56760215759277</t>
+    <t xml:space="preserve">7.56760168075562</t>
   </si>
   <si>
     <t xml:space="preserve">8.0262451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31289577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39479732513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72239875793457</t>
+    <t xml:space="preserve">8.31289672851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39479827880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72239971160889</t>
   </si>
   <si>
     <t xml:space="preserve">8.76334953308105</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88620090484619</t>
+    <t xml:space="preserve">8.88619995117188</t>
   </si>
   <si>
     <t xml:space="preserve">9.1728515625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41855239868164</t>
+    <t xml:space="preserve">9.41855335235596</t>
   </si>
   <si>
     <t xml:space="preserve">8.92714977264404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13190174102783</t>
+    <t xml:space="preserve">9.13190078735352</t>
   </si>
   <si>
     <t xml:space="preserve">8.96809959411621</t>
@@ -1775,10 +1775,10 @@
     <t xml:space="preserve">9.33665180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84525108337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09095191955566</t>
+    <t xml:space="preserve">8.84525012969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09095096588135</t>
   </si>
   <si>
     <t xml:space="preserve">9.21380233764648</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">9.25475215911865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00905132293701</t>
+    <t xml:space="preserve">9.0090503692627</t>
   </si>
   <si>
     <t xml:space="preserve">8.64049911499023</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">8.17366504669189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1900463104248</t>
+    <t xml:space="preserve">8.19004535675049</t>
   </si>
   <si>
     <t xml:space="preserve">8.10814476013184</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">8.15728569030762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96072483062744</t>
+    <t xml:space="preserve">7.96072578430176</t>
   </si>
   <si>
     <t xml:space="preserve">7.87882423400879</t>
@@ -1817,34 +1817,34 @@
     <t xml:space="preserve">7.71502351760864</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7805438041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58398294448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51846361160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53484201431274</t>
+    <t xml:space="preserve">7.78054428100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58398342132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51846265792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5348424911499</t>
   </si>
   <si>
     <t xml:space="preserve">7.33828163146973</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48570251464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61674308776855</t>
+    <t xml:space="preserve">7.48570203781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6167426109314</t>
   </si>
   <si>
     <t xml:space="preserve">7.69864320755005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76416397094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73140335083008</t>
+    <t xml:space="preserve">7.76416301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73140382766724</t>
   </si>
   <si>
     <t xml:space="preserve">7.79692411422729</t>
@@ -1853,13 +1853,13 @@
     <t xml:space="preserve">7.66588306427002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63312292098999</t>
+    <t xml:space="preserve">7.63312244415283</t>
   </si>
   <si>
     <t xml:space="preserve">7.64950370788574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68226289749146</t>
+    <t xml:space="preserve">7.68226337432861</t>
   </si>
   <si>
     <t xml:space="preserve">7.82968378067017</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">7.74778270721436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43656158447266</t>
+    <t xml:space="preserve">7.4365611076355</t>
   </si>
   <si>
     <t xml:space="preserve">7.6003623008728</t>
@@ -1877,19 +1877,19 @@
     <t xml:space="preserve">7.354660987854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40380191802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24000024795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19086027145386</t>
+    <t xml:space="preserve">7.40380144119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24000120162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19086074829102</t>
   </si>
   <si>
     <t xml:space="preserve">6.79773902893066</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68307781219482</t>
+    <t xml:space="preserve">6.68307733535767</t>
   </si>
   <si>
     <t xml:space="preserve">6.5684175491333</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">6.2244348526001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48651647567749</t>
+    <t xml:space="preserve">6.48651695251465</t>
   </si>
   <si>
     <t xml:space="preserve">6.42099618911743</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">7.92796516418457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51764678955078</t>
+    <t xml:space="preserve">8.5176477432251</t>
   </si>
   <si>
     <t xml:space="preserve">8.27194690704346</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">7.97710514068604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84606456756592</t>
+    <t xml:space="preserve">7.84606409072876</t>
   </si>
   <si>
     <t xml:space="preserve">8.12452602386475</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">8.59954929351807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43574714660645</t>
+    <t xml:space="preserve">8.43574810028076</t>
   </si>
   <si>
     <t xml:space="preserve">8.55859851837158</t>
@@ -1946,34 +1946,34 @@
     <t xml:space="preserve">8.68144989013672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47669792175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35384654998779</t>
+    <t xml:space="preserve">8.47669887542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35384750366211</t>
   </si>
   <si>
     <t xml:space="preserve">8.23099613189697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04262351989746</t>
+    <t xml:space="preserve">8.04262542724609</t>
   </si>
   <si>
     <t xml:space="preserve">7.94434452056885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86244487762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00986385345459</t>
+    <t xml:space="preserve">7.86244535446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00986480712891</t>
   </si>
   <si>
     <t xml:space="preserve">8.05900573730469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45950317382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90995693206787</t>
+    <t xml:space="preserve">9.45950412750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90995597839355</t>
   </si>
   <si>
     <t xml:space="preserve">10.1556568145752</t>
@@ -1982,16 +1982,16 @@
     <t xml:space="preserve">9.86900615692139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62330436706543</t>
+    <t xml:space="preserve">9.62330341339111</t>
   </si>
   <si>
     <t xml:space="preserve">9.50045490264893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37760257720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58235454559326</t>
+    <t xml:space="preserve">9.37760353088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58235359191895</t>
   </si>
   <si>
     <t xml:space="preserve">9.70520496368408</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">9.05000114440918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54140281677246</t>
+    <t xml:space="preserve">9.54140377044678</t>
   </si>
   <si>
     <t xml:space="preserve">9.22513484954834</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">9.18320178985596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09933853149414</t>
+    <t xml:space="preserve">9.09933757781982</t>
   </si>
   <si>
     <t xml:space="preserve">9.14126968383789</t>
@@ -2030,25 +2030,25 @@
     <t xml:space="preserve">9.35093212127686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64445877075195</t>
+    <t xml:space="preserve">9.64445972442627</t>
   </si>
   <si>
     <t xml:space="preserve">9.51866245269775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47673034667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60252666473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72832489013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3153772354126</t>
+    <t xml:space="preserve">9.47672939300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77025699615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6025276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72832584381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3153781890869</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895809173584</t>
@@ -2060,10 +2060,10 @@
     <t xml:space="preserve">10.1057167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.357310295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2734451293945</t>
+    <t xml:space="preserve">10.3573112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2734460830688</t>
   </si>
   <si>
     <t xml:space="preserve">10.1476488113403</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">9.81218910217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89605331420898</t>
+    <t xml:space="preserve">9.8960542678833</t>
   </si>
   <si>
     <t xml:space="preserve">9.26706790924072</t>
@@ -2087,19 +2087,19 @@
     <t xml:space="preserve">9.97991847991943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68639183044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05740642547607</t>
+    <t xml:space="preserve">9.68639278411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05740547180176</t>
   </si>
   <si>
     <t xml:space="preserve">8.97354030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3992433547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5669746398926</t>
+    <t xml:space="preserve">10.399242401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5669736862183</t>
   </si>
   <si>
     <t xml:space="preserve">10.7766351699829</t>
@@ -2111,10 +2111,10 @@
     <t xml:space="preserve">11.279824256897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3217573165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9443664550781</t>
+    <t xml:space="preserve">11.321756362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9443655014038</t>
   </si>
   <si>
     <t xml:space="preserve">11.2378911972046</t>
@@ -2126,19 +2126,19 @@
     <t xml:space="preserve">11.4056224822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1540269851685</t>
+    <t xml:space="preserve">11.1540279388428</t>
   </si>
   <si>
     <t xml:space="preserve">11.7830142974854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7410802841187</t>
+    <t xml:space="preserve">11.741081237793</t>
   </si>
   <si>
     <t xml:space="preserve">12.0346088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6152839660645</t>
+    <t xml:space="preserve">11.6152830123901</t>
   </si>
   <si>
     <t xml:space="preserve">11.6572160720825</t>
@@ -2162,34 +2162,34 @@
     <t xml:space="preserve">11.6991481781006</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5733518600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.531418800354</t>
+    <t xml:space="preserve">11.5733509063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5314178466797</t>
   </si>
   <si>
     <t xml:space="preserve">11.0282297134399</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4831094741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5250415802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6089057922363</t>
+    <t xml:space="preserve">10.4831085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5250406265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.608904838562</t>
   </si>
   <si>
     <t xml:space="preserve">10.818567276001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9024333953857</t>
+    <t xml:space="preserve">10.9024324417114</t>
   </si>
   <si>
     <t xml:space="preserve">11.4475536346436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1378631591797</t>
+    <t xml:space="preserve">11.1378622055054</t>
   </si>
   <si>
     <t xml:space="preserve">11.09485912323</t>
@@ -2201,7 +2201,7 @@
     <t xml:space="preserve">11.6539030075073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8259162902832</t>
+    <t xml:space="preserve">11.8259153366089</t>
   </si>
   <si>
     <t xml:space="preserve">11.6108989715576</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">11.4388866424561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5248928070068</t>
+    <t xml:space="preserve">11.5248918533325</t>
   </si>
   <si>
     <t xml:space="preserve">11.5678958892822</t>
@@ -2237,16 +2237,16 @@
     <t xml:space="preserve">10.9658489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7508325576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8798418045044</t>
+    <t xml:space="preserve">10.7508335113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8798427581787</t>
   </si>
   <si>
     <t xml:space="preserve">10.6648254394531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9228467941284</t>
+    <t xml:space="preserve">10.9228458404541</t>
   </si>
   <si>
     <t xml:space="preserve">10.7078294754028</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">10.1487865447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97677326202393</t>
+    <t xml:space="preserve">9.97677421569824</t>
   </si>
   <si>
     <t xml:space="preserve">9.89076614379883</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">9.76175689697266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84776210784912</t>
+    <t xml:space="preserve">9.84776306152344</t>
   </si>
   <si>
     <t xml:space="preserve">9.46073246002197</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">9.03070068359375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15970897674561</t>
+    <t xml:space="preserve">9.15970993041992</t>
   </si>
   <si>
     <t xml:space="preserve">10.277795791626</t>
@@ -2315,19 +2315,19 @@
     <t xml:space="preserve">9.58974266052246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41772937774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3317232131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37472629547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.503737449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63274669647217</t>
+    <t xml:space="preserve">9.41772842407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33172225952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37472534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50373649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63274574279785</t>
   </si>
   <si>
     <t xml:space="preserve">10.6218233108521</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">10.7938365936279</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3528785705566</t>
+    <t xml:space="preserve">11.352879524231</t>
   </si>
   <si>
     <t xml:space="preserve">11.4818897247314</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">11.9549255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0409336090088</t>
+    <t xml:space="preserve">12.0409326553345</t>
   </si>
   <si>
     <t xml:space="preserve">11.8689193725586</t>
@@ -2369,16 +2369,16 @@
     <t xml:space="preserve">11.9979286193848</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3419561386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4709663391113</t>
+    <t xml:space="preserve">12.3419570922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4709672927856</t>
   </si>
   <si>
     <t xml:space="preserve">12.2989530563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5139694213867</t>
+    <t xml:space="preserve">12.513970375061</t>
   </si>
   <si>
     <t xml:space="preserve">12.5569734573364</t>
@@ -2387,27 +2387,30 @@
     <t xml:space="preserve">12.6429796218872</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2559490203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3849582672119</t>
+    <t xml:space="preserve">12.2559499740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3849592208862</t>
   </si>
   <si>
     <t xml:space="preserve">12.5999755859375</t>
   </si>
   <si>
+    <t xml:space="preserve">12.6859817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7719888687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.728985786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9997711181641</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.6859827041626</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7719898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7289867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9997711181641</t>
-  </si>
-  <si>
     <t xml:space="preserve">12.820463180542</t>
   </si>
   <si>
@@ -2997,6 +3000,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.0500001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8999996185303</t>
   </si>
 </sst>
 </file>
@@ -51973,7 +51979,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1871" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51999,7 +52005,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52025,7 +52031,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1873" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52077,7 +52083,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1875" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -52103,7 +52109,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1876" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -52129,7 +52135,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1877" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52155,7 +52161,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -52207,7 +52213,7 @@
         <v>15</v>
       </c>
       <c r="G1880" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52259,7 +52265,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1882" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52285,7 +52291,7 @@
         <v>14.75</v>
       </c>
       <c r="G1883" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52311,7 +52317,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52337,7 +52343,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1885" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52363,7 +52369,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52389,7 +52395,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1887" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52415,7 +52421,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1888" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52441,7 +52447,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1889" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52467,7 +52473,7 @@
         <v>15</v>
       </c>
       <c r="G1890" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52493,7 +52499,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52519,7 +52525,7 @@
         <v>14.75</v>
       </c>
       <c r="G1892" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52545,7 +52551,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1893" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52571,7 +52577,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52597,7 +52603,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1895" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52623,7 +52629,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52649,7 +52655,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1897" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52675,7 +52681,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1898" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52701,7 +52707,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1899" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52727,7 +52733,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1900" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52753,7 +52759,7 @@
         <v>14.75</v>
       </c>
       <c r="G1901" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52779,7 +52785,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1902" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52805,7 +52811,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52831,7 +52837,7 @@
         <v>14.75</v>
       </c>
       <c r="G1904" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52857,7 +52863,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1905" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52883,7 +52889,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1906" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52909,7 +52915,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52935,7 +52941,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52961,7 +52967,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1909" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52987,7 +52993,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1910" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53013,7 +53019,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1911" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53039,7 +53045,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1912" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -53065,7 +53071,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1913" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53091,7 +53097,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1914" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53117,7 +53123,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53195,7 +53201,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1918" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53247,7 +53253,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1920" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53273,7 +53279,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1921" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53299,7 +53305,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53325,7 +53331,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1923" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53351,7 +53357,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1924" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53377,7 +53383,7 @@
         <v>14.75</v>
       </c>
       <c r="G1925" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53403,7 +53409,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1926" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53429,7 +53435,7 @@
         <v>14.75</v>
       </c>
       <c r="G1927" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53455,7 +53461,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1928" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53481,7 +53487,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1929" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53507,7 +53513,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1930" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53533,7 +53539,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1931" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53559,7 +53565,7 @@
         <v>15.75</v>
       </c>
       <c r="G1932" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53585,7 +53591,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53611,7 +53617,7 @@
         <v>15.75</v>
       </c>
       <c r="G1934" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53637,7 +53643,7 @@
         <v>16.5</v>
       </c>
       <c r="G1935" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53663,7 +53669,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1936" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53689,7 +53695,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53715,7 +53721,7 @@
         <v>15.5</v>
       </c>
       <c r="G1938" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53741,7 +53747,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1939" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53767,7 +53773,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1940" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53793,7 +53799,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53819,7 +53825,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1942" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53845,7 +53851,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1943" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53871,7 +53877,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1944" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53897,7 +53903,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1945" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53923,7 +53929,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1946" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53949,7 +53955,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1947" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53975,7 +53981,7 @@
         <v>15.75</v>
       </c>
       <c r="G1948" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54001,7 +54007,7 @@
         <v>15.5</v>
       </c>
       <c r="G1949" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54027,7 +54033,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54053,7 +54059,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1951" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54079,7 +54085,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1952" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54105,7 +54111,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1953" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54131,7 +54137,7 @@
         <v>15.25</v>
       </c>
       <c r="G1954" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54157,7 +54163,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1955" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54183,7 +54189,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1956" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54209,7 +54215,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1957" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54235,7 +54241,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1958" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54261,7 +54267,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54287,7 +54293,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1960" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54313,7 +54319,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1961" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54339,7 +54345,7 @@
         <v>15.5</v>
       </c>
       <c r="G1962" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54365,7 +54371,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1963" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54391,7 +54397,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54417,7 +54423,7 @@
         <v>16</v>
       </c>
       <c r="G1965" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54443,7 +54449,7 @@
         <v>16</v>
       </c>
       <c r="G1966" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -54469,7 +54475,7 @@
         <v>15.75</v>
       </c>
       <c r="G1967" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54495,7 +54501,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1968" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54521,7 +54527,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1969" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54547,7 +54553,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1970" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54573,7 +54579,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1971" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54599,7 +54605,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1972" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54625,7 +54631,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1973" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54651,7 +54657,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1974" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54677,7 +54683,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1975" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54703,7 +54709,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1976" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54729,7 +54735,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54755,7 +54761,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1978" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54781,7 +54787,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1979" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54807,7 +54813,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1980" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54833,7 +54839,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1981" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54859,7 +54865,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54885,7 +54891,7 @@
         <v>16</v>
       </c>
       <c r="G1983" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54911,7 +54917,7 @@
         <v>16.5</v>
       </c>
       <c r="G1984" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54937,7 +54943,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1985" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54963,7 +54969,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1986" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54989,7 +54995,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1987" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55015,7 +55021,7 @@
         <v>15.75</v>
       </c>
       <c r="G1988" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55041,7 +55047,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1989" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55067,7 +55073,7 @@
         <v>15.75</v>
       </c>
       <c r="G1990" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55093,7 +55099,7 @@
         <v>15.75</v>
       </c>
       <c r="G1991" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55119,7 +55125,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1992" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55145,7 +55151,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1993" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55171,7 +55177,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1994" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55197,7 +55203,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1995" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55223,7 +55229,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1996" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55249,7 +55255,7 @@
         <v>15.75</v>
       </c>
       <c r="G1997" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55275,7 +55281,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1998" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55301,7 +55307,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1999" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55327,7 +55333,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2000" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55353,7 +55359,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2001" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55379,7 +55385,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2002" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55405,7 +55411,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55431,7 +55437,7 @@
         <v>16</v>
       </c>
       <c r="G2004" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55457,7 +55463,7 @@
         <v>16</v>
       </c>
       <c r="G2005" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55483,7 +55489,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2006" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55509,7 +55515,7 @@
         <v>16</v>
       </c>
       <c r="G2007" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55535,7 +55541,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2008" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55561,7 +55567,7 @@
         <v>16</v>
       </c>
       <c r="G2009" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55587,7 +55593,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2010" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55613,7 +55619,7 @@
         <v>16</v>
       </c>
       <c r="G2011" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55639,7 +55645,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55665,7 +55671,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2013" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55691,7 +55697,7 @@
         <v>16</v>
       </c>
       <c r="G2014" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55717,7 +55723,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55743,7 +55749,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2016" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55769,7 +55775,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55795,7 +55801,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2018" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55821,7 +55827,7 @@
         <v>15.75</v>
       </c>
       <c r="G2019" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55847,7 +55853,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2020" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55873,7 +55879,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2021" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55899,7 +55905,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2022" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55925,7 +55931,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2023" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55951,7 +55957,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2024" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55977,7 +55983,7 @@
         <v>16.75</v>
       </c>
       <c r="G2025" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56003,7 +56009,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2026" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56029,7 +56035,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2027" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56055,7 +56061,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56081,7 +56087,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2029" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56107,7 +56113,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2030" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56133,7 +56139,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2031" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56159,7 +56165,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2032" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56185,7 +56191,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2033" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56211,7 +56217,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2034" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56237,7 +56243,7 @@
         <v>19</v>
       </c>
       <c r="G2035" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56263,7 +56269,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G2036" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56289,7 +56295,7 @@
         <v>18.5</v>
       </c>
       <c r="G2037" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56315,7 +56321,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2038" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56341,7 +56347,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2039" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56367,7 +56373,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2040" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56393,7 +56399,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2041" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56419,7 +56425,7 @@
         <v>18</v>
       </c>
       <c r="G2042" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56445,7 +56451,7 @@
         <v>18.5</v>
       </c>
       <c r="G2043" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56471,7 +56477,7 @@
         <v>18.75</v>
       </c>
       <c r="G2044" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56497,7 +56503,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2045" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56523,7 +56529,7 @@
         <v>18.5</v>
       </c>
       <c r="G2046" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56549,7 +56555,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2047" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56575,7 +56581,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G2048" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56601,7 +56607,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2049" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56627,7 +56633,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2050" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56653,7 +56659,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2051" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56679,7 +56685,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2052" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56705,7 +56711,7 @@
         <v>17.75</v>
       </c>
       <c r="G2053" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56731,7 +56737,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2054" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56757,7 +56763,7 @@
         <v>17.25</v>
       </c>
       <c r="G2055" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56783,7 +56789,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2056" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56809,7 +56815,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2057" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56835,7 +56841,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2058" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56861,7 +56867,7 @@
         <v>16.25</v>
       </c>
       <c r="G2059" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56887,7 +56893,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2060" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56913,7 +56919,7 @@
         <v>16.5</v>
       </c>
       <c r="G2061" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56939,7 +56945,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2062" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56965,7 +56971,7 @@
         <v>16.5</v>
       </c>
       <c r="G2063" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56991,7 +56997,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2064" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57017,7 +57023,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2065" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57043,7 +57049,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2066" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57069,7 +57075,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2067" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57095,7 +57101,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2068" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57121,7 +57127,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2069" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57147,7 +57153,7 @@
         <v>16.75</v>
       </c>
       <c r="G2070" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57173,7 +57179,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2071" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57199,7 +57205,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2072" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57225,7 +57231,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2073" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57251,7 +57257,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2074" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57277,7 +57283,7 @@
         <v>17</v>
       </c>
       <c r="G2075" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57303,7 +57309,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2076" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57329,7 +57335,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2077" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -57355,7 +57361,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2078" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -57381,7 +57387,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57407,7 +57413,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2080" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57433,7 +57439,7 @@
         <v>17.75</v>
       </c>
       <c r="G2081" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57459,7 +57465,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G2082" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57485,7 +57491,7 @@
         <v>17.5</v>
       </c>
       <c r="G2083" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57511,7 +57517,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2084" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57537,7 +57543,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2085" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57563,7 +57569,7 @@
         <v>17.5</v>
       </c>
       <c r="G2086" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57589,7 +57595,7 @@
         <v>17</v>
       </c>
       <c r="G2087" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57615,7 +57621,7 @@
         <v>17</v>
       </c>
       <c r="G2088" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57641,7 +57647,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2089" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57667,7 +57673,7 @@
         <v>17.75</v>
       </c>
       <c r="G2090" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57693,7 +57699,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2091" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57719,7 +57725,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2092" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57745,7 +57751,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2093" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57771,7 +57777,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2094" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57797,7 +57803,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2095" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57823,7 +57829,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2096" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -57849,7 +57855,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2097" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57875,7 +57881,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57901,7 +57907,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2099" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57927,7 +57933,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2100" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57953,7 +57959,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2101" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57979,7 +57985,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2102" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58005,7 +58011,7 @@
         <v>17</v>
       </c>
       <c r="G2103" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58031,7 +58037,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2104" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58057,7 +58063,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2105" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58083,7 +58089,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2106" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58109,7 +58115,7 @@
         <v>17.5</v>
       </c>
       <c r="G2107" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -58135,7 +58141,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2108" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58161,7 +58167,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2109" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -58187,7 +58193,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2110" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58213,7 +58219,7 @@
         <v>17</v>
       </c>
       <c r="G2111" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58239,7 +58245,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2112" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58265,7 +58271,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2113" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58291,7 +58297,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2114" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58317,7 +58323,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2115" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58343,7 +58349,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2116" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58369,7 +58375,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2117" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -58395,7 +58401,7 @@
         <v>17</v>
       </c>
       <c r="G2118" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58421,7 +58427,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2119" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58447,7 +58453,7 @@
         <v>17</v>
       </c>
       <c r="G2120" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58473,7 +58479,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2121" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58499,7 +58505,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2122" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58525,7 +58531,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2123" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58551,7 +58557,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2124" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58577,7 +58583,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2125" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58603,7 +58609,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2126" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58629,7 +58635,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2127" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58655,7 +58661,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2128" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58681,7 +58687,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2129" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58707,7 +58713,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2130" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58733,7 +58739,7 @@
         <v>16.5</v>
       </c>
       <c r="G2131" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58759,7 +58765,7 @@
         <v>16.5</v>
       </c>
       <c r="G2132" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58785,7 +58791,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2133" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58811,7 +58817,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2134" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58837,7 +58843,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2135" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58863,7 +58869,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2136" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58889,7 +58895,7 @@
         <v>17</v>
       </c>
       <c r="G2137" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58915,7 +58921,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2138" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58941,7 +58947,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2139" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58967,7 +58973,7 @@
         <v>16.5</v>
       </c>
       <c r="G2140" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -58993,7 +58999,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2141" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59019,7 +59025,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2142" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59045,7 +59051,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2143" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59071,7 +59077,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2144" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59097,7 +59103,7 @@
         <v>16.75</v>
       </c>
       <c r="G2145" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59123,7 +59129,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2146" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59149,7 +59155,7 @@
         <v>16.75</v>
       </c>
       <c r="G2147" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59175,7 +59181,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2148" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59201,7 +59207,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2149" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59227,7 +59233,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2150" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59253,7 +59259,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2151" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59279,7 +59285,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2152" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59305,7 +59311,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2153" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59331,7 +59337,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2154" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59357,7 +59363,7 @@
         <v>16.25</v>
       </c>
       <c r="G2155" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59383,7 +59389,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2156" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59409,7 +59415,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2157" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59435,7 +59441,7 @@
         <v>15</v>
       </c>
       <c r="G2158" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59461,7 +59467,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2159" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59487,7 +59493,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2160" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59513,7 +59519,7 @@
         <v>15.25</v>
       </c>
       <c r="G2161" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59539,7 +59545,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2162" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59565,7 +59571,7 @@
         <v>15.25</v>
       </c>
       <c r="G2163" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59591,7 +59597,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2164" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59617,7 +59623,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2165" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59643,7 +59649,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2166" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59669,7 +59675,7 @@
         <v>16.25</v>
       </c>
       <c r="G2167" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59695,7 +59701,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2168" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59721,7 +59727,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2169" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59747,7 +59753,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2170" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59773,7 +59779,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2171" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59799,7 +59805,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59825,7 +59831,7 @@
         <v>16</v>
       </c>
       <c r="G2173" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59851,7 +59857,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2174" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -59877,7 +59883,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2175" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59903,7 +59909,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2176" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59929,7 +59935,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2177" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59955,7 +59961,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2178" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59981,7 +59987,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2179" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60007,7 +60013,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60033,7 +60039,7 @@
         <v>15.25</v>
       </c>
       <c r="G2181" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60059,7 +60065,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60085,7 +60091,7 @@
         <v>15.25</v>
       </c>
       <c r="G2183" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60111,7 +60117,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2184" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60137,7 +60143,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2185" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60163,7 +60169,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2186" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60189,7 +60195,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60215,7 +60221,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2188" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60241,7 +60247,7 @@
         <v>15</v>
       </c>
       <c r="G2189" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60267,7 +60273,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2190" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60293,7 +60299,7 @@
         <v>15</v>
       </c>
       <c r="G2191" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60319,7 +60325,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2192" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60345,7 +60351,7 @@
         <v>15</v>
       </c>
       <c r="G2193" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60371,7 +60377,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2194" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60397,7 +60403,7 @@
         <v>15</v>
       </c>
       <c r="G2195" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60423,7 +60429,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2196" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60449,7 +60455,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2197" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60475,7 +60481,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60501,7 +60507,7 @@
         <v>15</v>
       </c>
       <c r="G2199" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60527,7 +60533,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G2200" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60553,7 +60559,7 @@
         <v>15</v>
       </c>
       <c r="G2201" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60579,7 +60585,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60605,7 +60611,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2203" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60631,7 +60637,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2204" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60657,7 +60663,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60683,7 +60689,7 @@
         <v>14.5</v>
       </c>
       <c r="G2206" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60709,7 +60715,7 @@
         <v>14.5</v>
       </c>
       <c r="G2207" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60735,7 +60741,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60761,7 +60767,7 @@
         <v>14.5</v>
       </c>
       <c r="G2209" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60787,7 +60793,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60813,7 +60819,7 @@
         <v>14.5</v>
       </c>
       <c r="G2211" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60839,7 +60845,7 @@
         <v>14.5</v>
       </c>
       <c r="G2212" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60865,7 +60871,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60891,7 +60897,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2214" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60917,7 +60923,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2215" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60943,7 +60949,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2216" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60969,7 +60975,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2217" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -60995,7 +61001,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2218" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61021,7 +61027,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2219" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61047,7 +61053,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2220" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61073,7 +61079,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2221" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61099,7 +61105,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2222" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61125,7 +61131,7 @@
         <v>15</v>
       </c>
       <c r="G2223" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61151,7 +61157,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61177,7 +61183,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2225" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61203,7 +61209,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2226" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61229,7 +61235,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2227" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61255,7 +61261,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61281,7 +61287,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2229" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61307,7 +61313,7 @@
         <v>15.25</v>
       </c>
       <c r="G2230" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61333,7 +61339,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2231" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61359,7 +61365,7 @@
         <v>15.5</v>
       </c>
       <c r="G2232" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61385,7 +61391,7 @@
         <v>15.5</v>
       </c>
       <c r="G2233" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61411,7 +61417,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2234" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61437,7 +61443,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2235" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61463,7 +61469,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2236" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61489,7 +61495,7 @@
         <v>16</v>
       </c>
       <c r="G2237" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61515,7 +61521,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2238" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61541,7 +61547,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2239" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61567,7 +61573,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2240" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61593,7 +61599,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2241" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61619,7 +61625,7 @@
         <v>16.5</v>
       </c>
       <c r="G2242" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61645,7 +61651,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2243" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61671,7 +61677,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2244" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61697,7 +61703,7 @@
         <v>17.25</v>
       </c>
       <c r="G2245" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61723,7 +61729,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2246" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61749,7 +61755,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2247" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61775,7 +61781,7 @@
         <v>17</v>
       </c>
       <c r="G2248" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61801,7 +61807,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2249" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61827,7 +61833,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2250" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61853,7 +61859,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61879,7 +61885,7 @@
         <v>17.25</v>
       </c>
       <c r="G2252" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61905,7 +61911,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2253" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61931,7 +61937,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2254" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61957,7 +61963,7 @@
         <v>17.75</v>
       </c>
       <c r="G2255" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61983,7 +61989,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G2256" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62009,7 +62015,7 @@
         <v>18</v>
       </c>
       <c r="G2257" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62035,7 +62041,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2258" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62061,7 +62067,7 @@
         <v>17</v>
       </c>
       <c r="G2259" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62087,7 +62093,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2260" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62113,7 +62119,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2261" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62139,7 +62145,7 @@
         <v>16.5</v>
       </c>
       <c r="G2262" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62165,7 +62171,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2263" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62191,7 +62197,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2264" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62217,7 +62223,7 @@
         <v>16.5</v>
       </c>
       <c r="G2265" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62243,7 +62249,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2266" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62269,7 +62275,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2267" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62295,7 +62301,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2268" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62321,7 +62327,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2269" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62347,7 +62353,7 @@
         <v>15.5</v>
       </c>
       <c r="G2270" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62373,7 +62379,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2271" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62399,7 +62405,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2272" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62425,7 +62431,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2273" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62451,7 +62457,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2274" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62477,7 +62483,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2275" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62503,7 +62509,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2276" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62529,7 +62535,7 @@
         <v>17</v>
       </c>
       <c r="G2277" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62555,7 +62561,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2278" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62581,7 +62587,7 @@
         <v>16.5</v>
       </c>
       <c r="G2279" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62607,7 +62613,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2280" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62633,7 +62639,7 @@
         <v>16</v>
       </c>
       <c r="G2281" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62659,7 +62665,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62685,7 +62691,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2283" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62711,7 +62717,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2284" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62737,7 +62743,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2285" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62763,7 +62769,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62789,7 +62795,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2287" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62815,7 +62821,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2288" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62841,7 +62847,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2289" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62867,7 +62873,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62893,7 +62899,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2291" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62919,7 +62925,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2292" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62945,7 +62951,7 @@
         <v>16.5</v>
       </c>
       <c r="G2293" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62971,7 +62977,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2294" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62997,7 +63003,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2295" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63023,7 +63029,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2296" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63049,7 +63055,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2297" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63075,7 +63081,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2298" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63101,7 +63107,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63127,7 +63133,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63153,7 +63159,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63179,7 +63185,7 @@
         <v>16</v>
       </c>
       <c r="G2302" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63205,7 +63211,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2303" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63231,7 +63237,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2304" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63257,7 +63263,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63283,7 +63289,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2306" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63309,7 +63315,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2307" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63335,7 +63341,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2308" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63361,7 +63367,7 @@
         <v>15.75</v>
       </c>
       <c r="G2309" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63387,7 +63393,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2310" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63413,7 +63419,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2311" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63439,7 +63445,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63465,7 +63471,7 @@
         <v>16</v>
       </c>
       <c r="G2313" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63491,7 +63497,7 @@
         <v>16</v>
       </c>
       <c r="G2314" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63517,7 +63523,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2315" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63543,7 +63549,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2316" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63569,7 +63575,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2317" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63595,7 +63601,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63621,7 +63627,7 @@
         <v>16</v>
       </c>
       <c r="G2319" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63647,7 +63653,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2320" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63673,7 +63679,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2321" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63699,7 +63705,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2322" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63725,7 +63731,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2323" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63751,7 +63757,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2324" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63777,7 +63783,7 @@
         <v>16</v>
       </c>
       <c r="G2325" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63803,7 +63809,7 @@
         <v>16</v>
       </c>
       <c r="G2326" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63829,7 +63835,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2327" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63855,7 +63861,7 @@
         <v>16</v>
       </c>
       <c r="G2328" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63881,7 +63887,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2329" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63907,7 +63913,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2330" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63933,7 +63939,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2331" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63959,7 +63965,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63985,7 +63991,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64011,7 +64017,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2334" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64037,7 +64043,7 @@
         <v>15.75</v>
       </c>
       <c r="G2335" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64063,7 +64069,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2336" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64089,7 +64095,7 @@
         <v>15.75</v>
       </c>
       <c r="G2337" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64115,7 +64121,7 @@
         <v>15.25</v>
       </c>
       <c r="G2338" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64141,7 +64147,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2339" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64167,7 +64173,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2340" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64193,7 +64199,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2341" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64219,7 +64225,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64245,7 +64251,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64271,7 +64277,7 @@
         <v>15.5</v>
       </c>
       <c r="G2344" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64297,7 +64303,7 @@
         <v>15.5</v>
       </c>
       <c r="G2345" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64323,7 +64329,7 @@
         <v>15</v>
       </c>
       <c r="G2346" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64349,7 +64355,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64375,7 +64381,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64401,7 +64407,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2349" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64427,7 +64433,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2350" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64453,7 +64459,7 @@
         <v>16</v>
       </c>
       <c r="G2351" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64479,7 +64485,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64505,7 +64511,7 @@
         <v>15.75</v>
       </c>
       <c r="G2353" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64531,7 +64537,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64557,7 +64563,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2355" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64583,7 +64589,7 @@
         <v>15.25</v>
       </c>
       <c r="G2356" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64609,7 +64615,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2357" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64635,7 +64641,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64661,7 +64667,7 @@
         <v>14</v>
       </c>
       <c r="G2359" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64687,7 +64693,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2360" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64713,7 +64719,7 @@
         <v>15</v>
       </c>
       <c r="G2361" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64739,7 +64745,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2362" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64765,7 +64771,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2363" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64791,7 +64797,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2364" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64817,7 +64823,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64843,7 +64849,7 @@
         <v>14.5</v>
       </c>
       <c r="G2366" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64869,7 +64875,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2367" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64895,7 +64901,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2368" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64921,7 +64927,7 @@
         <v>15</v>
       </c>
       <c r="G2369" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64947,7 +64953,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2370" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64973,7 +64979,7 @@
         <v>15.25</v>
       </c>
       <c r="G2371" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64999,7 +65005,7 @@
         <v>15.25</v>
       </c>
       <c r="G2372" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65025,7 +65031,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2373" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65051,7 +65057,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2374" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65077,7 +65083,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2375" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65103,7 +65109,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2376" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65129,7 +65135,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65155,7 +65161,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2378" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65181,7 +65187,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2379" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65207,7 +65213,7 @@
         <v>15.25</v>
       </c>
       <c r="G2380" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65233,7 +65239,7 @@
         <v>15.25</v>
       </c>
       <c r="G2381" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65259,7 +65265,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2382" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65285,7 +65291,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2383" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65311,7 +65317,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65337,7 +65343,7 @@
         <v>16</v>
       </c>
       <c r="G2385" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65363,7 +65369,7 @@
         <v>16.25</v>
       </c>
       <c r="G2386" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65389,7 +65395,7 @@
         <v>16</v>
       </c>
       <c r="G2387" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65415,7 +65421,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2388" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65441,7 +65447,7 @@
         <v>16.5</v>
       </c>
       <c r="G2389" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65467,7 +65473,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2390" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65493,7 +65499,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2391" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65519,7 +65525,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2392" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65545,7 +65551,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2393" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65571,7 +65577,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2394" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65597,7 +65603,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2395" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65623,7 +65629,7 @@
         <v>16.75</v>
       </c>
       <c r="G2396" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65649,7 +65655,7 @@
         <v>16.5</v>
       </c>
       <c r="G2397" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65675,7 +65681,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2398" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65701,7 +65707,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2399" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65727,7 +65733,7 @@
         <v>16.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65753,7 +65759,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65779,7 +65785,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2402" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65805,7 +65811,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65831,7 +65837,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2404" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65857,7 +65863,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2405" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65883,7 +65889,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2406" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65909,7 +65915,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2407" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65935,7 +65941,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2408" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65961,7 +65967,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G2409" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65987,7 +65993,7 @@
         <v>16</v>
       </c>
       <c r="G2410" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66013,7 +66019,7 @@
         <v>15.75</v>
       </c>
       <c r="G2411" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66039,7 +66045,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2412" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66065,7 +66071,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2413" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66091,7 +66097,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2414" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66117,7 +66123,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2415" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66143,7 +66149,7 @@
         <v>16.25</v>
       </c>
       <c r="G2416" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66169,7 +66175,7 @@
         <v>16.75</v>
       </c>
       <c r="G2417" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66195,7 +66201,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2418" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66221,7 +66227,7 @@
         <v>16.25</v>
       </c>
       <c r="G2419" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66247,7 +66253,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2420" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66273,7 +66279,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2421" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66299,7 +66305,7 @@
         <v>16.25</v>
       </c>
       <c r="G2422" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66325,7 +66331,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2423" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66351,7 +66357,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2424" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66377,7 +66383,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2425" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66403,7 +66409,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2426" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66429,7 +66435,7 @@
         <v>16.25</v>
       </c>
       <c r="G2427" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66455,7 +66461,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2428" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66481,7 +66487,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66507,7 +66513,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2430" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66533,7 +66539,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2431" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66559,7 +66565,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66585,7 +66591,7 @@
         <v>16.5</v>
       </c>
       <c r="G2433" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66611,7 +66617,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2434" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66637,7 +66643,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2435" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66663,7 +66669,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2436" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66689,7 +66695,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2437" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66715,7 +66721,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2438" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66741,7 +66747,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2439" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66767,7 +66773,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2440" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66793,7 +66799,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66819,7 +66825,7 @@
         <v>16.75</v>
       </c>
       <c r="G2442" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66845,7 +66851,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66871,7 +66877,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2444" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66897,7 +66903,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2445" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66923,7 +66929,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2446" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66949,7 +66955,7 @@
         <v>18</v>
       </c>
       <c r="G2447" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66975,7 +66981,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2448" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67001,7 +67007,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67027,7 +67033,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2450" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67053,7 +67059,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2451" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67079,7 +67085,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2452" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67105,7 +67111,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2453" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67131,7 +67137,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2454" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67157,7 +67163,7 @@
         <v>21</v>
       </c>
       <c r="G2455" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67183,7 +67189,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G2456" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67209,7 +67215,7 @@
         <v>19.25</v>
       </c>
       <c r="G2457" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67235,7 +67241,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G2458" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67261,7 +67267,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G2459" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67287,7 +67293,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67313,7 +67319,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2461" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67339,7 +67345,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2462" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67365,7 +67371,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67391,7 +67397,7 @@
         <v>18.5</v>
       </c>
       <c r="G2464" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67417,7 +67423,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G2465" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67443,7 +67449,7 @@
         <v>19</v>
       </c>
       <c r="G2466" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67469,7 +67475,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2467" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67495,7 +67501,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2468" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67521,7 +67527,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2469" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67547,7 +67553,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2470" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67573,7 +67579,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2471" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67599,7 +67605,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2472" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67625,7 +67631,7 @@
         <v>16</v>
       </c>
       <c r="G2473" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67651,7 +67657,7 @@
         <v>16</v>
       </c>
       <c r="G2474" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67677,7 +67683,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2475" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67703,7 +67709,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67729,7 +67735,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67755,7 +67761,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67781,7 +67787,7 @@
         <v>16.25</v>
       </c>
       <c r="G2479" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67807,7 +67813,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67833,7 +67839,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2481" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67859,7 +67865,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67885,7 +67891,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67911,7 +67917,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2484" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67937,7 +67943,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2485" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67963,7 +67969,7 @@
         <v>16</v>
       </c>
       <c r="G2486" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67989,7 +67995,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2487" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68015,7 +68021,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2488" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68041,7 +68047,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68067,7 +68073,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2490" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68093,7 +68099,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2491" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68119,7 +68125,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2492" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68145,7 +68151,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68171,7 +68177,7 @@
         <v>15.25</v>
       </c>
       <c r="G2494" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68197,7 +68203,7 @@
         <v>15.5</v>
       </c>
       <c r="G2495" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68223,7 +68229,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2496" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68249,7 +68255,7 @@
         <v>15.5</v>
       </c>
       <c r="G2497" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68275,7 +68281,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2498" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68301,7 +68307,7 @@
         <v>15.25</v>
       </c>
       <c r="G2499" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -68327,7 +68333,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2500" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -68353,7 +68359,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2501" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -68379,7 +68385,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2502" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68405,7 +68411,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2503" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68431,7 +68437,7 @@
         <v>15.25</v>
       </c>
       <c r="G2504" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -68457,7 +68463,7 @@
         <v>15.25</v>
       </c>
       <c r="G2505" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -68483,7 +68489,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2506" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68509,7 +68515,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2507" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68517,7 +68523,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6912731481</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>4935</v>
@@ -68535,9 +68541,35 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2508" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6910069444</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>9256</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>15.1999998092651</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>14.8500003814697</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>15.1999998092651</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>996</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BEC.MI.xlsx
+++ b/data/BEC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="995">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,16 +44,16 @@
     <t xml:space="preserve">BEC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9618091583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87040758132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87693691253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92916536331177</t>
+    <t xml:space="preserve">4.96180963516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8704080581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8769359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92916584014893</t>
   </si>
   <si>
     <t xml:space="preserve">4.77247762680054</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">4.83449983596802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73330450057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79532814025879</t>
+    <t xml:space="preserve">4.73330545425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79532718658447</t>
   </si>
   <si>
     <t xml:space="preserve">4.80512094497681</t>
@@ -80,16 +80,16 @@
     <t xml:space="preserve">4.75942039489746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60273122787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69739818572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69413328170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63537406921387</t>
+    <t xml:space="preserve">4.60273170471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69739770889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69413280487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63537454605103</t>
   </si>
   <si>
     <t xml:space="preserve">4.44277811050415</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">4.37422657012939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18489503860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07390737533569</t>
+    <t xml:space="preserve">4.18489408493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07390642166138</t>
   </si>
   <si>
     <t xml:space="preserve">4.08043575286865</t>
@@ -116,40 +116,40 @@
     <t xml:space="preserve">4.49174356460571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5309157371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43298530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50480079650879</t>
+    <t xml:space="preserve">4.53091621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43298578262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50480127334595</t>
   </si>
   <si>
     <t xml:space="preserve">4.53744411468506</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42645645141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42319202423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43951368331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.416663646698</t>
+    <t xml:space="preserve">4.42645597457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4231915473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43951416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41666316986084</t>
   </si>
   <si>
     <t xml:space="preserve">4.44930744171143</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46562910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47868633270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60926008224487</t>
+    <t xml:space="preserve">4.4656286239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47868585586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60926055908203</t>
   </si>
   <si>
     <t xml:space="preserve">4.89652252197266</t>
@@ -158,13 +158,13 @@
     <t xml:space="preserve">4.90958023071289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93569469451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91284465789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01403951644897</t>
+    <t xml:space="preserve">4.93569564819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91284513473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01403903961182</t>
   </si>
   <si>
     <t xml:space="preserve">4.94222402572632</t>
@@ -173,142 +173,142 @@
     <t xml:space="preserve">5.03362512588501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04015398025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09238338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94875192642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99445295333862</t>
+    <t xml:space="preserve">5.04015350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09238290786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94875240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99445343017578</t>
   </si>
   <si>
     <t xml:space="preserve">4.84429311752319</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0695333480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09891319274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98792457580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04994773864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04341840744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05973958969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98466014862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02709579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99973821640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03393602371216</t>
+    <t xml:space="preserve">5.06953287124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09891271591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98792362213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0499472618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04341793060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05974006652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98465967178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02709627151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9997386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03393650054932</t>
   </si>
   <si>
     <t xml:space="preserve">4.9621205329895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91766357421875</t>
+    <t xml:space="preserve">4.91766309738159</t>
   </si>
   <si>
     <t xml:space="preserve">4.9450216293335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85610628128052</t>
+    <t xml:space="preserve">4.85610675811768</t>
   </si>
   <si>
     <t xml:space="preserve">4.89030456542969</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89714431762695</t>
+    <t xml:space="preserve">4.89714479446411</t>
   </si>
   <si>
     <t xml:space="preserve">4.79455089569092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82190942764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9826397895813</t>
+    <t xml:space="preserve">4.82190895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98263883590698</t>
   </si>
   <si>
     <t xml:space="preserve">4.92450284957886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00657796859741</t>
+    <t xml:space="preserve">5.00657844543457</t>
   </si>
   <si>
     <t xml:space="preserve">4.88346529006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94844102859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95870018005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99289894104004</t>
+    <t xml:space="preserve">4.94844198226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95870113372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99289846420288</t>
   </si>
   <si>
     <t xml:space="preserve">4.86636638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8526873588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93134212493896</t>
+    <t xml:space="preserve">4.85268640518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93134260177612</t>
   </si>
   <si>
     <t xml:space="preserve">4.78771114349365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78429174423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8253288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77403211593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7227349281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67485761642456</t>
+    <t xml:space="preserve">4.78429126739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82532835006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77403163909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72273540496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67485809326172</t>
   </si>
   <si>
     <t xml:space="preserve">4.75693321228027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56200408935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54148530960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53122615814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6030421257019</t>
+    <t xml:space="preserve">4.56200456619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54148578643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53122663497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60304260253906</t>
   </si>
   <si>
     <t xml:space="preserve">4.63040065765381</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5551643371582</t>
+    <t xml:space="preserve">4.55516481399536</t>
   </si>
   <si>
     <t xml:space="preserve">4.58252334594727</t>
@@ -320,22 +320,22 @@
     <t xml:space="preserve">4.45941066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53464603424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5278058052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52096652984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64407968521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7432541847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73983383178711</t>
+    <t xml:space="preserve">4.53464651107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52780675888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52096700668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6440806388855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74325370788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73983335494995</t>
   </si>
   <si>
     <t xml:space="preserve">4.8355884552002</t>
@@ -344,34 +344,34 @@
     <t xml:space="preserve">4.92108297348022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92792224884033</t>
+    <t xml:space="preserve">4.92792272567749</t>
   </si>
   <si>
     <t xml:space="preserve">4.98605966567993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96554040908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91424322128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9723801612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96896028518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86978578567505</t>
+    <t xml:space="preserve">4.96553993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91424369812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97237968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96895980834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86978626251221</t>
   </si>
   <si>
     <t xml:space="preserve">4.93818187713623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88004589080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95186138153076</t>
+    <t xml:space="preserve">4.88004541397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9518609046936</t>
   </si>
   <si>
     <t xml:space="preserve">4.87320613861084</t>
@@ -380,10 +380,10 @@
     <t xml:space="preserve">4.86294651031494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76719188690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80139064788818</t>
+    <t xml:space="preserve">4.76719236373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80138969421387</t>
   </si>
   <si>
     <t xml:space="preserve">4.80823040008545</t>
@@ -395,19 +395,19 @@
     <t xml:space="preserve">4.8424277305603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72957420349121</t>
+    <t xml:space="preserve">4.72957372665405</t>
   </si>
   <si>
     <t xml:space="preserve">4.84926748275757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81164979934692</t>
+    <t xml:space="preserve">4.81164932250977</t>
   </si>
   <si>
     <t xml:space="preserve">4.88688516616821</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02025651931763</t>
+    <t xml:space="preserve">5.02025747299194</t>
   </si>
   <si>
     <t xml:space="preserve">5.08865308761597</t>
@@ -416,28 +416,28 @@
     <t xml:space="preserve">5.10575246810913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0647144317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04761552810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09549188613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17756843566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23228454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12969064712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13994932174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16388845443726</t>
+    <t xml:space="preserve">5.06471490859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04761600494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09549236297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17756795883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23228406906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12969017028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13994979858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1638879776001</t>
   </si>
   <si>
     <t xml:space="preserve">5.21176528930664</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">5.30751943588257</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30068016052246</t>
+    <t xml:space="preserve">5.30068063735962</t>
   </si>
   <si>
     <t xml:space="preserve">5.13311004638672</t>
@@ -458,25 +458,25 @@
     <t xml:space="preserve">5.16730785369873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19808626174927</t>
+    <t xml:space="preserve">5.19808673858643</t>
   </si>
   <si>
     <t xml:space="preserve">5.29726028442383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47166967391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4032735824585</t>
+    <t xml:space="preserve">5.47167015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40327405929565</t>
   </si>
   <si>
     <t xml:space="preserve">5.36565589904785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36223697662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46483087539673</t>
+    <t xml:space="preserve">5.36223649978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46482992172241</t>
   </si>
   <si>
     <t xml:space="preserve">5.36907577514648</t>
@@ -485,13 +485,13 @@
     <t xml:space="preserve">5.39643430709839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25964307785034</t>
+    <t xml:space="preserve">5.25964260101318</t>
   </si>
   <si>
     <t xml:space="preserve">5.41353321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46141052246094</t>
+    <t xml:space="preserve">5.4614109992981</t>
   </si>
   <si>
     <t xml:space="preserve">5.43747138977051</t>
@@ -506,25 +506,25 @@
     <t xml:space="preserve">5.47508955001831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39985370635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41695308685303</t>
+    <t xml:space="preserve">5.39985418319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41695356369019</t>
   </si>
   <si>
     <t xml:space="preserve">5.4306321144104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45799112319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50586748123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52980709075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60846090316772</t>
+    <t xml:space="preserve">5.4579906463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50586795806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52980661392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60846138000488</t>
   </si>
   <si>
     <t xml:space="preserve">5.68369770050049</t>
@@ -533,40 +533,40 @@
     <t xml:space="preserve">5.73157405853271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88204526901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93676233291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94360113143921</t>
+    <t xml:space="preserve">5.88204479217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9367618560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94360160827637</t>
   </si>
   <si>
     <t xml:space="preserve">6.05645370483398</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94018220901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04961538314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07355308532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02567720413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97437953948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04277610778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17272710800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39501476287842</t>
+    <t xml:space="preserve">5.94018173217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04961490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07355403900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02567768096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97437906265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04277467727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17272663116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39501428604126</t>
   </si>
   <si>
     <t xml:space="preserve">6.3744945526123</t>
@@ -575,10 +575,10 @@
     <t xml:space="preserve">6.46683025360107</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32661819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11117172241211</t>
+    <t xml:space="preserve">6.32661867141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11117076873779</t>
   </si>
   <si>
     <t xml:space="preserve">5.8991436958313</t>
@@ -587,46 +587,46 @@
     <t xml:space="preserve">6.00515747070312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22402429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26506233215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39843368530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40527391433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48050975799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41211318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44973039627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4360523223877</t>
+    <t xml:space="preserve">6.2240252494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26506185531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39843320846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40527248382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48050928115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41211366653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44973134994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43605089187622</t>
   </si>
   <si>
     <t xml:space="preserve">6.52838611602783</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66859865188599</t>
+    <t xml:space="preserve">6.66859769821167</t>
   </si>
   <si>
     <t xml:space="preserve">6.99689769744873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94218111038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1200098991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46882963180542</t>
+    <t xml:space="preserve">6.94218063354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12001085281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4688286781311</t>
   </si>
   <si>
     <t xml:space="preserve">7.66717720031738</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">8.20066452026367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40585231781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64523792266846</t>
+    <t xml:space="preserve">8.40585327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64523887634277</t>
   </si>
   <si>
     <t xml:space="preserve">8.27590084075928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35113620758057</t>
+    <t xml:space="preserve">8.35113525390625</t>
   </si>
   <si>
     <t xml:space="preserve">8.28957939147949</t>
@@ -653,70 +653,70 @@
     <t xml:space="preserve">8.24170303344727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33745670318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3306188583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31693840026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26906204223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22118186950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11858940124512</t>
+    <t xml:space="preserve">8.33745765686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33061599731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31693744659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26906108856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22118377685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11859035491943</t>
   </si>
   <si>
     <t xml:space="preserve">8.30325889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48108863830566</t>
+    <t xml:space="preserve">8.48108768463135</t>
   </si>
   <si>
     <t xml:space="preserve">8.72047424316406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71363353729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79469108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49782276153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52751064300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07478904724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31228065490723</t>
+    <t xml:space="preserve">8.71363258361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79469013214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49782371520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52750968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07478713989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31228160858154</t>
   </si>
   <si>
     <t xml:space="preserve">8.43102836608887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37165546417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97830629348755</t>
+    <t xml:space="preserve">8.37165355682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97830533981323</t>
   </si>
   <si>
     <t xml:space="preserve">7.88924551010132</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23806571960449</t>
+    <t xml:space="preserve">8.23806476593018</t>
   </si>
   <si>
     <t xml:space="preserve">8.260329246521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21580028533936</t>
+    <t xml:space="preserve">8.21580123901367</t>
   </si>
   <si>
     <t xml:space="preserve">8.64625644683838</t>
@@ -725,43 +725,43 @@
     <t xml:space="preserve">8.75758266448975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80211162567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69078826904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5794620513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66110038757324</t>
+    <t xml:space="preserve">8.8021125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69078731536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57946109771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66110134124756</t>
   </si>
   <si>
     <t xml:space="preserve">8.54977512359619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5200891494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53493118286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60172653198242</t>
+    <t xml:space="preserve">8.52008819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53493213653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60172843933105</t>
   </si>
   <si>
     <t xml:space="preserve">8.4829797744751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59430694580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46813678741455</t>
+    <t xml:space="preserve">8.59430503845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46813583374023</t>
   </si>
   <si>
     <t xml:space="preserve">8.14900493621826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31970310211182</t>
+    <t xml:space="preserve">8.3197021484375</t>
   </si>
   <si>
     <t xml:space="preserve">8.12673950195312</t>
@@ -776,16 +776,16 @@
     <t xml:space="preserve">8.7056303024292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84664249420166</t>
+    <t xml:space="preserve">8.84664344787598</t>
   </si>
   <si>
     <t xml:space="preserve">8.69820880889893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74273777008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56461906433105</t>
+    <t xml:space="preserve">8.74273872375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56461811065674</t>
   </si>
   <si>
     <t xml:space="preserve">8.43845081329346</t>
@@ -797,28 +797,28 @@
     <t xml:space="preserve">8.34939002990723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42360782623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54235172271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63141250610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61656951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63883495330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66852283477783</t>
+    <t xml:space="preserve">8.42360591888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54235458374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63141345977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61657047271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63883590698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66852188110352</t>
   </si>
   <si>
     <t xml:space="preserve">8.77984714508057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88375186920166</t>
+    <t xml:space="preserve">8.88374996185303</t>
   </si>
   <si>
     <t xml:space="preserve">8.83922004699707</t>
@@ -830,19 +830,19 @@
     <t xml:space="preserve">8.68336582183838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60914897918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57203960418701</t>
+    <t xml:space="preserve">8.6091480255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57204055786133</t>
   </si>
   <si>
     <t xml:space="preserve">8.49040126800537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47555732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78726863861084</t>
+    <t xml:space="preserve">8.47555923461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78726959228516</t>
   </si>
   <si>
     <t xml:space="preserve">8.71305179595947</t>
@@ -857,40 +857,40 @@
     <t xml:space="preserve">8.75016021728516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90601634979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89859390258789</t>
+    <t xml:space="preserve">8.9060173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89859294891357</t>
   </si>
   <si>
     <t xml:space="preserve">8.94312477111816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77242469787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96538925170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87632846832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97281265258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09155654907227</t>
+    <t xml:space="preserve">8.77242374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96538829803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87632942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97281169891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0915584564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.2177267074585</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52201557159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55170059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5665454864502</t>
+    <t xml:space="preserve">9.52201461791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55170249938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654644012451</t>
   </si>
   <si>
     <t xml:space="preserve">9.45521926879883</t>
@@ -899,97 +899,97 @@
     <t xml:space="preserve">9.47748565673828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53685855865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35873699188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59623146057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64076137542725</t>
+    <t xml:space="preserve">9.5368595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35873889923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59623241424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64076042175293</t>
   </si>
   <si>
     <t xml:space="preserve">9.90794277191162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89309883117676</t>
+    <t xml:space="preserve">9.89309978485107</t>
   </si>
   <si>
     <t xml:space="preserve">9.76693153381348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72982025146484</t>
+    <t xml:space="preserve">9.72982215881348</t>
   </si>
   <si>
     <t xml:space="preserve">9.99700260162354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95247268676758</t>
+    <t xml:space="preserve">9.95247364044189</t>
   </si>
   <si>
     <t xml:space="preserve">10.0563764572144</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64818382263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95989418029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82630252838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8114595413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75208759307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85598945617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86341285705566</t>
+    <t xml:space="preserve">9.64818477630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95989322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82630348205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81146144866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7520866394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85599136352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86341190338135</t>
   </si>
   <si>
     <t xml:space="preserve">10.0415334701538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0118465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94505023956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90051937103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8317985534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97088384628296</t>
+    <t xml:space="preserve">10.0118455886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94504928588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90052032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83179759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97088479995728</t>
   </si>
   <si>
     <t xml:space="preserve">8.25290679931641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16384792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19353485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67594337463379</t>
+    <t xml:space="preserve">8.16384696960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1935338973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67594242095947</t>
   </si>
   <si>
     <t xml:space="preserve">8.50524520874023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02283573150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0673656463623</t>
+    <t xml:space="preserve">8.02283668518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06736469268799</t>
   </si>
   <si>
     <t xml:space="preserve">7.98572826385498</t>
@@ -998,46 +998,46 @@
     <t xml:space="preserve">7.78534317016602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76307725906372</t>
+    <t xml:space="preserve">7.76307678222656</t>
   </si>
   <si>
     <t xml:space="preserve">7.7037034034729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82987213134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64433097839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72596836090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04510116577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14158344268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9189338684082</t>
+    <t xml:space="preserve">7.82987117767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64432907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72596883773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04510021209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14158248901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91893196105957</t>
   </si>
   <si>
     <t xml:space="preserve">8.08963108062744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11931800842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11189556121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0970516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00057029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13416194915771</t>
+    <t xml:space="preserve">8.11931705474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11189651489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09705257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00056934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1341609954834</t>
   </si>
   <si>
     <t xml:space="preserve">8.28259468078613</t>
@@ -1046,61 +1046,61 @@
     <t xml:space="preserve">8.20837688446045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34196758270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4458703994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92085742950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0247631072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32712554931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26775074005127</t>
+    <t xml:space="preserve">8.34196853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44587135314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92086029052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02476119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32712459564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26775169372559</t>
   </si>
   <si>
     <t xml:space="preserve">7.71854734420776</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03025722503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01541519165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1044750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17868995666504</t>
+    <t xml:space="preserve">8.03025817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01541423797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10447406768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17869091033936</t>
   </si>
   <si>
     <t xml:space="preserve">8.22322082519531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40134048461914</t>
+    <t xml:space="preserve">8.40134239196777</t>
   </si>
   <si>
     <t xml:space="preserve">9.0544490814209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93570232391357</t>
+    <t xml:space="preserve">8.93570137023926</t>
   </si>
   <si>
     <t xml:space="preserve">8.72789573669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8911714553833</t>
+    <t xml:space="preserve">8.89117240905762</t>
   </si>
   <si>
     <t xml:space="preserve">9.00991916656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.277099609375</t>
+    <t xml:space="preserve">9.27710056304932</t>
   </si>
   <si>
     <t xml:space="preserve">9.30678653717041</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">9.24741363525391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35131549835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5294361114502</t>
+    <t xml:space="preserve">9.35131740570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52943706512451</t>
   </si>
   <si>
     <t xml:space="preserve">9.47006416320801</t>
@@ -1124,19 +1124,19 @@
     <t xml:space="preserve">9.54428005218506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87083435058594</t>
+    <t xml:space="preserve">9.87083530426025</t>
   </si>
   <si>
     <t xml:space="preserve">9.60365390777588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0637979507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87998390197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54299163818359</t>
+    <t xml:space="preserve">10.0637969970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87998294830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54299259185791</t>
   </si>
   <si>
     <t xml:space="preserve">9.55830955505371</t>
@@ -1145,13 +1145,13 @@
     <t xml:space="preserve">9.72680568695068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60426330566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46640300750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57362747192383</t>
+    <t xml:space="preserve">9.60426425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46640396118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57362842559814</t>
   </si>
   <si>
     <t xml:space="preserve">9.61958122253418</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">9.48172092437744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43576812744141</t>
+    <t xml:space="preserve">9.43576717376709</t>
   </si>
   <si>
     <t xml:space="preserve">9.3438606262207</t>
@@ -1181,46 +1181,46 @@
     <t xml:space="preserve">8.59328842163086</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53201770782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89964485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96091651916504</t>
+    <t xml:space="preserve">8.53201675415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89964389801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96091556549072</t>
   </si>
   <si>
     <t xml:space="preserve">9.28258991241455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20600128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49703693389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51235675811768</t>
+    <t xml:space="preserve">9.20600032806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49703788757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51235771179199</t>
   </si>
   <si>
     <t xml:space="preserve">9.52767467498779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38981437683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35917949676514</t>
+    <t xml:space="preserve">9.38981342315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35917854309082</t>
   </si>
   <si>
     <t xml:space="preserve">9.19068336486816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86466598510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58894729614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32854461669922</t>
+    <t xml:space="preserve">9.86466503143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58894538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3285436630249</t>
   </si>
   <si>
     <t xml:space="preserve">9.42044925689697</t>
@@ -1229,34 +1229,34 @@
     <t xml:space="preserve">9.22131824493408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25195407867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11409282684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1447286605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26727294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45108604431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69616985321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65021800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80773639678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06813907623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37449645996094</t>
+    <t xml:space="preserve">9.251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11409187316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14472961425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26727199554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45108509063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69616889953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65021705627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80773830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06814002990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37449550628662</t>
   </si>
   <si>
     <t xml:space="preserve">9.03750610351562</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">9.02218723297119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91496276855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94559860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17536354064941</t>
+    <t xml:space="preserve">8.91496181488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94559764862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17536449432373</t>
   </si>
   <si>
     <t xml:space="preserve">9.00686931610107</t>
@@ -1283,28 +1283,28 @@
     <t xml:space="preserve">9.95657253265381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0331611633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91061878204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97189140319824</t>
+    <t xml:space="preserve">10.0331630706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91061973571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97189235687256</t>
   </si>
   <si>
     <t xml:space="preserve">9.78807640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75744247436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09877586364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86900901794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7464656829834</t>
+    <t xml:space="preserve">9.7574405670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09877490997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86900806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74646663665771</t>
   </si>
   <si>
     <t xml:space="preserve">8.73114776611328</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">8.51669883728027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47074699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42479133605957</t>
+    <t xml:space="preserve">8.47074508666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42479228973389</t>
   </si>
   <si>
     <t xml:space="preserve">8.01121139526367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22566223144531</t>
+    <t xml:space="preserve">8.225661277771</t>
   </si>
   <si>
     <t xml:space="preserve">8.36352062225342</t>
@@ -1331,28 +1331,28 @@
     <t xml:space="preserve">8.65456008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77710151672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83837413787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93027877807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62392425537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71583080291748</t>
+    <t xml:space="preserve">8.77710247039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8383731842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9302806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62392330169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7158317565918</t>
   </si>
   <si>
     <t xml:space="preserve">8.50138187408447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82305526733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60860538482666</t>
+    <t xml:space="preserve">8.8230562210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60860633850098</t>
   </si>
   <si>
     <t xml:space="preserve">8.57797050476074</t>
@@ -1361,28 +1361,28 @@
     <t xml:space="preserve">8.34820365905762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30224895477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33288669586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37883758544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28693103790283</t>
+    <t xml:space="preserve">8.30224990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3328857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37883853912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28693294525146</t>
   </si>
   <si>
     <t xml:space="preserve">8.27161502838135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39415740966797</t>
+    <t xml:space="preserve">8.39415550231934</t>
   </si>
   <si>
     <t xml:space="preserve">8.13375377655029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11843776702881</t>
+    <t xml:space="preserve">8.11843681335449</t>
   </si>
   <si>
     <t xml:space="preserve">8.45542812347412</t>
@@ -1400,58 +1400,58 @@
     <t xml:space="preserve">8.66987705230713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68519592285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54733467102051</t>
+    <t xml:space="preserve">8.68519496917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54733657836914</t>
   </si>
   <si>
     <t xml:space="preserve">8.440110206604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88432693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40513324737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92593574523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80339527130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29790687561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22897815704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07579898834229</t>
+    <t xml:space="preserve">8.88432788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40513229370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92593669891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80339622497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29790782928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22897720336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0757999420166</t>
   </si>
   <si>
     <t xml:space="preserve">9.15238761901855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99921035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59735107421875</t>
+    <t xml:space="preserve">8.9992094039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59734916687012</t>
   </si>
   <si>
     <t xml:space="preserve">9.31742668151855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79757118225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87754821777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83756065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63761520385742</t>
+    <t xml:space="preserve">8.79757022857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87754917144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83755970001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63761425018311</t>
   </si>
   <si>
     <t xml:space="preserve">9.23744964599609</t>
@@ -1460,49 +1460,49 @@
     <t xml:space="preserve">9.27743911743164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47738265991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35741710662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51737213134766</t>
+    <t xml:space="preserve">9.47738361358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3574161529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51737117767334</t>
   </si>
   <si>
     <t xml:space="preserve">9.67732906341553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63733863830566</t>
+    <t xml:space="preserve">9.63733959197998</t>
   </si>
   <si>
     <t xml:space="preserve">9.39740562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19745922088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07749557495117</t>
+    <t xml:space="preserve">9.19746112823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07749271392822</t>
   </si>
   <si>
     <t xml:space="preserve">9.43739414215088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55736064910889</t>
+    <t xml:space="preserve">9.5573616027832</t>
   </si>
   <si>
     <t xml:space="preserve">9.11748218536377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71759223937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95752716064453</t>
+    <t xml:space="preserve">8.7175931930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95752620697021</t>
   </si>
   <si>
     <t xml:space="preserve">8.99751567840576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.157470703125</t>
+    <t xml:space="preserve">9.15747165679932</t>
   </si>
   <si>
     <t xml:space="preserve">8.91753768920898</t>
@@ -1514,22 +1514,22 @@
     <t xml:space="preserve">10.3571405410767</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772180557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3171520233154</t>
+    <t xml:space="preserve">10.0772171020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3171510696411</t>
   </si>
   <si>
     <t xml:space="preserve">10.1172065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91726016998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99724006652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0372295379639</t>
+    <t xml:space="preserve">9.91726112365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99724102020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0372285842896</t>
   </si>
   <si>
     <t xml:space="preserve">9.75730514526367</t>
@@ -1538,19 +1538,19 @@
     <t xml:space="preserve">9.71731758117676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79729557037354</t>
+    <t xml:space="preserve">9.79729461669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.83728313446045</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1571950912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2771625518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2371740341187</t>
+    <t xml:space="preserve">10.1571960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2771615982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2371730804443</t>
   </si>
   <si>
     <t xml:space="preserve">10.3971290588379</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">10.4771070480347</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1971836090088</t>
+    <t xml:space="preserve">10.1971845626831</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170955657959</t>
@@ -1574,34 +1574,34 @@
     <t xml:space="preserve">11.1169300079346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.316876411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2368974685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3568639755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1969079971313</t>
+    <t xml:space="preserve">11.3168754577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2368965148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3568649291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1969089508057</t>
   </si>
   <si>
     <t xml:space="preserve">10.837007522583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1569185256958</t>
+    <t xml:space="preserve">11.1569194793701</t>
   </si>
   <si>
     <t xml:space="preserve">11.0369529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8769989013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9169845581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9569749832153</t>
+    <t xml:space="preserve">10.8769979476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9169855117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.956974029541</t>
   </si>
   <si>
     <t xml:space="preserve">10.7570295333862</t>
@@ -1616,73 +1616,73 @@
     <t xml:space="preserve">11.2768859863281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4368419647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5568084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6767768859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7170400619507</t>
+    <t xml:space="preserve">11.436842918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.556809425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.676775932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.717041015625</t>
   </si>
   <si>
     <t xml:space="preserve">8.11775684356689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16602087020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88582229614258</t>
+    <t xml:space="preserve">7.16602182388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88582324981689</t>
   </si>
   <si>
     <t xml:space="preserve">7.46993780136108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03805732727051</t>
+    <t xml:space="preserve">7.03805589675903</t>
   </si>
   <si>
     <t xml:space="preserve">6.9100923538208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39823341369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20628643035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9983434677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55818843841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30998277664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40595483779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32597684860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11803531646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73414087295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9740743637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29398632049561</t>
+    <t xml:space="preserve">6.39823293685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20628690719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99834394454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55818939208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30998182296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40595436096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32597732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11803436279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73414039611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97407484054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29398584365845</t>
   </si>
   <si>
     <t xml:space="preserve">7.15002536773682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86210536956787</t>
+    <t xml:space="preserve">6.86210489273071</t>
   </si>
   <si>
     <t xml:space="preserve">6.8141188621521</t>
@@ -1691,16 +1691,16 @@
     <t xml:space="preserve">6.76613187789917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94208335876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79812335968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92608737945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78212690353394</t>
+    <t xml:space="preserve">6.94208383560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79812240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92608785629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78212785720825</t>
   </si>
   <si>
     <t xml:space="preserve">6.83011388778687</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">6.96153926849365</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73221826553345</t>
+    <t xml:space="preserve">6.73221778869629</t>
   </si>
   <si>
     <t xml:space="preserve">6.74859809875488</t>
@@ -1727,7 +1727,7 @@
     <t xml:space="preserve">7.05981969833374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1253399848938</t>
+    <t xml:space="preserve">7.12534046173096</t>
   </si>
   <si>
     <t xml:space="preserve">7.22362041473389</t>
@@ -1736,25 +1736,25 @@
     <t xml:space="preserve">7.55122327804565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56760168075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0262451171875</t>
+    <t xml:space="preserve">7.56760263442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02624607086182</t>
   </si>
   <si>
     <t xml:space="preserve">8.31289672851562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39479827880859</t>
+    <t xml:space="preserve">8.39479732513428</t>
   </si>
   <si>
     <t xml:space="preserve">8.72239971160889</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76334953308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88619995117188</t>
+    <t xml:space="preserve">8.76334857940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88620185852051</t>
   </si>
   <si>
     <t xml:space="preserve">9.1728515625</t>
@@ -1763,61 +1763,61 @@
     <t xml:space="preserve">9.41855335235596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92714977264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13190078735352</t>
+    <t xml:space="preserve">8.92715072631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13190174102783</t>
   </si>
   <si>
     <t xml:space="preserve">8.96809959411621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33665180206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84525012969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09095096588135</t>
+    <t xml:space="preserve">9.3366527557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84524917602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09095191955566</t>
   </si>
   <si>
     <t xml:space="preserve">9.21380233764648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25475215911865</t>
+    <t xml:space="preserve">9.25475120544434</t>
   </si>
   <si>
     <t xml:space="preserve">9.0090503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64049911499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09176540374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17366504669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19004535675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10814476013184</t>
+    <t xml:space="preserve">8.64049816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09176445007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17366600036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19004726409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10814571380615</t>
   </si>
   <si>
     <t xml:space="preserve">8.15728569030762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96072578430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87882423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71502351760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78054428100586</t>
+    <t xml:space="preserve">7.96072626113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87882375717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7150239944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78054475784302</t>
   </si>
   <si>
     <t xml:space="preserve">7.58398342132568</t>
@@ -1832,64 +1832,64 @@
     <t xml:space="preserve">7.33828163146973</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48570203781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6167426109314</t>
+    <t xml:space="preserve">7.48570251464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61674308776855</t>
   </si>
   <si>
     <t xml:space="preserve">7.69864320755005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76416301727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73140382766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79692411422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66588306427002</t>
+    <t xml:space="preserve">7.76416397094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73140287399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79692363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6658821105957</t>
   </si>
   <si>
     <t xml:space="preserve">7.63312244415283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64950370788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68226337432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82968378067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74778270721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4365611076355</t>
+    <t xml:space="preserve">7.6495041847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68226385116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82968473434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74778366088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43656206130981</t>
   </si>
   <si>
     <t xml:space="preserve">7.6003623008728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.354660987854</t>
+    <t xml:space="preserve">7.35466194152832</t>
   </si>
   <si>
     <t xml:space="preserve">7.40380144119263</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24000120162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19086074829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79773902893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68307733535767</t>
+    <t xml:space="preserve">7.24000072479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1908597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79773855209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68307781219482</t>
   </si>
   <si>
     <t xml:space="preserve">6.5684175491333</t>
@@ -1901,10 +1901,10 @@
     <t xml:space="preserve">6.2244348526001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48651695251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42099618911743</t>
+    <t xml:space="preserve">6.48651647567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42099666595459</t>
   </si>
   <si>
     <t xml:space="preserve">6.71583795547485</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">7.04344034194946</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92796516418457</t>
+    <t xml:space="preserve">7.92796468734741</t>
   </si>
   <si>
     <t xml:space="preserve">8.5176477432251</t>
@@ -1928,19 +1928,19 @@
     <t xml:space="preserve">7.97710514068604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84606409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12452602386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59954929351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43574810028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55859851837158</t>
+    <t xml:space="preserve">7.8460636138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12452507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59954833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43574714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55859756469727</t>
   </si>
   <si>
     <t xml:space="preserve">8.68144989013672</t>
@@ -1949,28 +1949,28 @@
     <t xml:space="preserve">8.47669887542725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35384750366211</t>
+    <t xml:space="preserve">8.35384654998779</t>
   </si>
   <si>
     <t xml:space="preserve">8.23099613189697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04262542724609</t>
+    <t xml:space="preserve">8.04262447357178</t>
   </si>
   <si>
     <t xml:space="preserve">7.94434452056885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86244535446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00986480712891</t>
+    <t xml:space="preserve">7.86244440078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00986576080322</t>
   </si>
   <si>
     <t xml:space="preserve">8.05900573730469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45950412750244</t>
+    <t xml:space="preserve">9.45950317382812</t>
   </si>
   <si>
     <t xml:space="preserve">9.90995597839355</t>
@@ -1982,34 +1982,34 @@
     <t xml:space="preserve">9.86900615692139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62330341339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50045490264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37760353088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58235359191895</t>
+    <t xml:space="preserve">9.62330436706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50045299530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37760257720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58235454559326</t>
   </si>
   <si>
     <t xml:space="preserve">9.70520496368408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05000114440918</t>
+    <t xml:space="preserve">9.05000019073486</t>
   </si>
   <si>
     <t xml:space="preserve">9.54140377044678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22513484954834</t>
+    <t xml:space="preserve">9.22513580322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.18320178985596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09933757781982</t>
+    <t xml:space="preserve">9.09933853149414</t>
   </si>
   <si>
     <t xml:space="preserve">9.14126968383789</t>
@@ -2021,13 +2021,13 @@
     <t xml:space="preserve">9.30900001525879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5605936050415</t>
+    <t xml:space="preserve">9.56059455871582</t>
   </si>
   <si>
     <t xml:space="preserve">9.4347972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35093212127686</t>
+    <t xml:space="preserve">9.35093307495117</t>
   </si>
   <si>
     <t xml:space="preserve">9.64445972442627</t>
@@ -2039,31 +2039,31 @@
     <t xml:space="preserve">9.47672939300537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77025699615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6025276184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72832584381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3153781890869</t>
+    <t xml:space="preserve">9.77025604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60252666473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7283239364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3153791427612</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895809173584</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2315130233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1057167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3573112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2734460830688</t>
+    <t xml:space="preserve">10.2315139770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1057157516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.357310295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2734451293945</t>
   </si>
   <si>
     <t xml:space="preserve">10.1476488113403</t>
@@ -2078,16 +2078,16 @@
     <t xml:space="preserve">9.81218910217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8960542678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26706790924072</t>
+    <t xml:space="preserve">9.89605522155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26706886291504</t>
   </si>
   <si>
     <t xml:space="preserve">9.97991847991943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68639278411865</t>
+    <t xml:space="preserve">9.68639183044434</t>
   </si>
   <si>
     <t xml:space="preserve">9.05740547180176</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">10.5669736862183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7766351699829</t>
+    <t xml:space="preserve">10.7766361236572</t>
   </si>
   <si>
     <t xml:space="preserve">10.7347030639648</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">11.321756362915</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9443655014038</t>
+    <t xml:space="preserve">10.9443645477295</t>
   </si>
   <si>
     <t xml:space="preserve">11.2378911972046</t>
@@ -2129,28 +2129,28 @@
     <t xml:space="preserve">11.1540279388428</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7830142974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.741081237793</t>
+    <t xml:space="preserve">11.783013343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7410821914673</t>
   </si>
   <si>
     <t xml:space="preserve">12.0346088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6152830123901</t>
+    <t xml:space="preserve">11.6152839660645</t>
   </si>
   <si>
     <t xml:space="preserve">11.6572160720825</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1120948791504</t>
+    <t xml:space="preserve">11.1120939254761</t>
   </si>
   <si>
     <t xml:space="preserve">10.9862976074219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.070161819458</t>
+    <t xml:space="preserve">11.0701627731323</t>
   </si>
   <si>
     <t xml:space="preserve">11.4894866943359</t>
@@ -2159,13 +2159,13 @@
     <t xml:space="preserve">11.3636894226074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6991481781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5733509063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5314178466797</t>
+    <t xml:space="preserve">11.6991491317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5733518600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.531418800354</t>
   </si>
   <si>
     <t xml:space="preserve">11.0282297134399</t>
@@ -2189,31 +2189,31 @@
     <t xml:space="preserve">11.4475536346436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1378622055054</t>
+    <t xml:space="preserve">11.1378631591797</t>
   </si>
   <si>
     <t xml:space="preserve">11.09485912323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3958835601807</t>
+    <t xml:space="preserve">11.3958826065063</t>
   </si>
   <si>
     <t xml:space="preserve">11.6539030075073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8259153366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6108989715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.696907043457</t>
+    <t xml:space="preserve">11.8259162902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6108999252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6969060897827</t>
   </si>
   <si>
     <t xml:space="preserve">11.4388866424561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5248918533325</t>
+    <t xml:space="preserve">11.5248928070068</t>
   </si>
   <si>
     <t xml:space="preserve">11.5678958892822</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">11.2238702774048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0518560409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0088529586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8368406295776</t>
+    <t xml:space="preserve">11.0518569946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0088539123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8368396759033</t>
   </si>
   <si>
     <t xml:space="preserve">10.9658489227295</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">10.1487865447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97677421569824</t>
+    <t xml:space="preserve">9.97677230834961</t>
   </si>
   <si>
     <t xml:space="preserve">9.89076614379883</t>
@@ -2270,10 +2270,10 @@
     <t xml:space="preserve">9.76175689697266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84776306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46073246002197</t>
+    <t xml:space="preserve">9.84776210784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46073341369629</t>
   </si>
   <si>
     <t xml:space="preserve">9.54673957824707</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">9.20271301269531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03070068359375</t>
+    <t xml:space="preserve">9.03069972991943</t>
   </si>
   <si>
     <t xml:space="preserve">9.15970993041992</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">10.277795791626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67574977874756</t>
+    <t xml:space="preserve">9.67574882507324</t>
   </si>
   <si>
     <t xml:space="preserve">10.0197763442993</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">9.93377017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80475902557373</t>
+    <t xml:space="preserve">9.80475997924805</t>
   </si>
   <si>
     <t xml:space="preserve">9.71875286102295</t>
@@ -2315,10 +2315,10 @@
     <t xml:space="preserve">9.58974266052246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41772842407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33172225952148</t>
+    <t xml:space="preserve">9.41772937774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3317232131958</t>
   </si>
   <si>
     <t xml:space="preserve">9.37472534179688</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">9.50373649597168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63274574279785</t>
+    <t xml:space="preserve">9.63274669647217</t>
   </si>
   <si>
     <t xml:space="preserve">10.6218233108521</t>
@@ -2336,13 +2336,13 @@
     <t xml:space="preserve">11.3098764419556</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2668733596802</t>
+    <t xml:space="preserve">11.2668724060059</t>
   </si>
   <si>
     <t xml:space="preserve">11.1808662414551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7938365936279</t>
+    <t xml:space="preserve">10.7938356399536</t>
   </si>
   <si>
     <t xml:space="preserve">11.352879524231</t>
@@ -2360,19 +2360,19 @@
     <t xml:space="preserve">12.0409326553345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8689193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7829132080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9979286193848</t>
+    <t xml:space="preserve">11.8689203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7829122543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9979295730591</t>
   </si>
   <si>
     <t xml:space="preserve">12.3419570922852</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4709672927856</t>
+    <t xml:space="preserve">12.4709663391113</t>
   </si>
   <si>
     <t xml:space="preserve">12.2989530563354</t>
@@ -2381,16 +2381,16 @@
     <t xml:space="preserve">12.513970375061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5569734573364</t>
+    <t xml:space="preserve">12.5569725036621</t>
   </si>
   <si>
     <t xml:space="preserve">12.6429796218872</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2559499740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3849592208862</t>
+    <t xml:space="preserve">12.2559490203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3849582672119</t>
   </si>
   <si>
     <t xml:space="preserve">12.5999755859375</t>
@@ -2399,19 +2399,16 @@
     <t xml:space="preserve">12.6859817504883</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7719888687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.728985786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9997711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6859827041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.820463180542</t>
+    <t xml:space="preserve">12.7719898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7289867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9997701644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8204641342163</t>
   </si>
   <si>
     <t xml:space="preserve">12.9549436569214</t>
@@ -2423,28 +2420,28 @@
     <t xml:space="preserve">13.4480381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0894250869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2239036560059</t>
+    <t xml:space="preserve">13.0894241333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2239046096802</t>
   </si>
   <si>
     <t xml:space="preserve">13.3583841323853</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1342506408691</t>
+    <t xml:space="preserve">13.1342496871948</t>
   </si>
   <si>
     <t xml:space="preserve">13.0445976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1790781021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3135576248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2687311172485</t>
+    <t xml:space="preserve">13.1790771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3135585784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2687320709229</t>
   </si>
   <si>
     <t xml:space="preserve">12.8652906417847</t>
@@ -2462,7 +2459,7 @@
     <t xml:space="preserve">13.7618265151978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7928428649902</t>
+    <t xml:space="preserve">14.7928419113159</t>
   </si>
   <si>
     <t xml:space="preserve">14.1652669906616</t>
@@ -2474,10 +2471,10 @@
     <t xml:space="preserve">13.8963060379028</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4032106399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5825185775757</t>
+    <t xml:space="preserve">13.4032115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5825176239014</t>
   </si>
   <si>
     <t xml:space="preserve">13.492865562439</t>
@@ -2486,7 +2483,7 @@
     <t xml:space="preserve">13.6721725463867</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9411334991455</t>
+    <t xml:space="preserve">13.9411325454712</t>
   </si>
   <si>
     <t xml:space="preserve">13.7169990539551</t>
@@ -2495,22 +2492,22 @@
     <t xml:space="preserve">14.3445739746094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9859609603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5238819122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2997465133667</t>
+    <t xml:space="preserve">13.9859600067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5238828659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.299747467041</t>
   </si>
   <si>
     <t xml:space="preserve">14.4342279434204</t>
   </si>
   <si>
-    <t xml:space="preserve">14.21009349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3894004821777</t>
+    <t xml:space="preserve">14.2100944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3893995285034</t>
   </si>
   <si>
     <t xml:space="preserve">14.6135339736938</t>
@@ -2537,7 +2534,7 @@
     <t xml:space="preserve">15.0169763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1962833404541</t>
+    <t xml:space="preserve">15.1962842941284</t>
   </si>
   <si>
     <t xml:space="preserve">15.3307638168335</t>
@@ -2546,19 +2543,19 @@
     <t xml:space="preserve">15.4204187393188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3755893707275</t>
+    <t xml:space="preserve">15.3755912780762</t>
   </si>
   <si>
     <t xml:space="preserve">14.8376684188843</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8824968338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1514558792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7790327072144</t>
+    <t xml:space="preserve">14.882495880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1514568328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.77903175354</t>
   </si>
   <si>
     <t xml:space="preserve">17.0341815948486</t>
@@ -2570,22 +2567,22 @@
     <t xml:space="preserve">16.5859146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8686857223511</t>
+    <t xml:space="preserve">15.8686866760254</t>
   </si>
   <si>
     <t xml:space="preserve">16.0479907989502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7342052459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9583387374878</t>
+    <t xml:space="preserve">15.7342042922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9583377838135</t>
   </si>
   <si>
     <t xml:space="preserve">16.1376457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8100471496582</t>
+    <t xml:space="preserve">16.8100490570068</t>
   </si>
   <si>
     <t xml:space="preserve">16.7203941345215</t>
@@ -2594,13 +2591,13 @@
     <t xml:space="preserve">16.4066066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2721271514893</t>
+    <t xml:space="preserve">16.2721252441406</t>
   </si>
   <si>
     <t xml:space="preserve">16.0928211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9135131835938</t>
+    <t xml:space="preserve">15.9135122299194</t>
   </si>
   <si>
     <t xml:space="preserve">15.4652442932129</t>
@@ -2630,7 +2627,7 @@
     <t xml:space="preserve">15.644552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8238582611084</t>
+    <t xml:space="preserve">15.8238592147827</t>
   </si>
   <si>
     <t xml:space="preserve">15.689377784729</t>
@@ -2685,9 +2682,6 @@
   </si>
   <si>
     <t xml:space="preserve">15.0579290390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1514568328857</t>
   </si>
   <si>
     <t xml:space="preserve">15.1982202529907</t>
@@ -51979,7 +51973,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1871" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -52005,7 +51999,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52031,7 +52025,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1873" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52083,7 +52077,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1875" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -52109,7 +52103,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1876" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -52135,7 +52129,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1877" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52161,7 +52155,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -52213,7 +52207,7 @@
         <v>15</v>
       </c>
       <c r="G1880" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52265,7 +52259,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1882" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52291,7 +52285,7 @@
         <v>14.75</v>
       </c>
       <c r="G1883" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52317,7 +52311,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52343,7 +52337,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1885" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52369,7 +52363,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52395,7 +52389,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1887" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52421,7 +52415,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1888" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52447,7 +52441,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1889" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52473,7 +52467,7 @@
         <v>15</v>
       </c>
       <c r="G1890" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52499,7 +52493,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52525,7 +52519,7 @@
         <v>14.75</v>
       </c>
       <c r="G1892" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52551,7 +52545,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1893" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52577,7 +52571,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52603,7 +52597,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1895" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52629,7 +52623,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52655,7 +52649,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1897" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52681,7 +52675,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1898" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52707,7 +52701,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1899" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52733,7 +52727,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1900" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52759,7 +52753,7 @@
         <v>14.75</v>
       </c>
       <c r="G1901" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52785,7 +52779,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1902" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52811,7 +52805,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52837,7 +52831,7 @@
         <v>14.75</v>
       </c>
       <c r="G1904" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52863,7 +52857,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1905" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52889,7 +52883,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1906" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52915,7 +52909,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52941,7 +52935,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52967,7 +52961,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1909" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52993,7 +52987,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1910" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53019,7 +53013,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1911" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53045,7 +53039,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1912" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -53071,7 +53065,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1913" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53097,7 +53091,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1914" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53123,7 +53117,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53201,7 +53195,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1918" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53253,7 +53247,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1920" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53279,7 +53273,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1921" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53305,7 +53299,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53331,7 +53325,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1923" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53357,7 +53351,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1924" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53383,7 +53377,7 @@
         <v>14.75</v>
       </c>
       <c r="G1925" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53409,7 +53403,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1926" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53435,7 +53429,7 @@
         <v>14.75</v>
       </c>
       <c r="G1927" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53461,7 +53455,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1928" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53487,7 +53481,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1929" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53513,7 +53507,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1930" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53539,7 +53533,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1931" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53565,7 +53559,7 @@
         <v>15.75</v>
       </c>
       <c r="G1932" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53591,7 +53585,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53617,7 +53611,7 @@
         <v>15.75</v>
       </c>
       <c r="G1934" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53643,7 +53637,7 @@
         <v>16.5</v>
       </c>
       <c r="G1935" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53669,7 +53663,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1936" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53695,7 +53689,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53721,7 +53715,7 @@
         <v>15.5</v>
       </c>
       <c r="G1938" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53747,7 +53741,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1939" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53773,7 +53767,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1940" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53799,7 +53793,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53825,7 +53819,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1942" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53851,7 +53845,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1943" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53877,7 +53871,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1944" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53903,7 +53897,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1945" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53929,7 +53923,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1946" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53955,7 +53949,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1947" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53981,7 +53975,7 @@
         <v>15.75</v>
       </c>
       <c r="G1948" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54007,7 +54001,7 @@
         <v>15.5</v>
       </c>
       <c r="G1949" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54033,7 +54027,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54059,7 +54053,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1951" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54085,7 +54079,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1952" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54111,7 +54105,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1953" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54137,7 +54131,7 @@
         <v>15.25</v>
       </c>
       <c r="G1954" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54163,7 +54157,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1955" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54189,7 +54183,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1956" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54215,7 +54209,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1957" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54241,7 +54235,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1958" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54267,7 +54261,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54293,7 +54287,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1960" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54319,7 +54313,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1961" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54345,7 +54339,7 @@
         <v>15.5</v>
       </c>
       <c r="G1962" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54371,7 +54365,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1963" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54397,7 +54391,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54423,7 +54417,7 @@
         <v>16</v>
       </c>
       <c r="G1965" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54449,7 +54443,7 @@
         <v>16</v>
       </c>
       <c r="G1966" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -54475,7 +54469,7 @@
         <v>15.75</v>
       </c>
       <c r="G1967" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54501,7 +54495,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1968" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54527,7 +54521,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1969" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54553,7 +54547,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1970" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54579,7 +54573,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1971" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54605,7 +54599,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1972" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54631,7 +54625,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1973" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54657,7 +54651,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1974" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54683,7 +54677,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1975" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54709,7 +54703,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1976" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54735,7 +54729,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54761,7 +54755,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1978" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54787,7 +54781,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1979" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54813,7 +54807,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1980" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54839,7 +54833,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1981" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54865,7 +54859,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54891,7 +54885,7 @@
         <v>16</v>
       </c>
       <c r="G1983" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54917,7 +54911,7 @@
         <v>16.5</v>
       </c>
       <c r="G1984" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54943,7 +54937,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1985" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54969,7 +54963,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1986" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54995,7 +54989,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1987" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55021,7 +55015,7 @@
         <v>15.75</v>
       </c>
       <c r="G1988" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55047,7 +55041,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1989" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55073,7 +55067,7 @@
         <v>15.75</v>
       </c>
       <c r="G1990" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55099,7 +55093,7 @@
         <v>15.75</v>
       </c>
       <c r="G1991" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55125,7 +55119,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1992" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55151,7 +55145,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1993" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55177,7 +55171,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1994" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55203,7 +55197,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1995" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55229,7 +55223,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1996" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55255,7 +55249,7 @@
         <v>15.75</v>
       </c>
       <c r="G1997" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55281,7 +55275,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1998" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55307,7 +55301,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1999" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55333,7 +55327,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2000" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55359,7 +55353,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2001" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55385,7 +55379,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2002" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55411,7 +55405,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55437,7 +55431,7 @@
         <v>16</v>
       </c>
       <c r="G2004" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55463,7 +55457,7 @@
         <v>16</v>
       </c>
       <c r="G2005" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55489,7 +55483,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2006" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55515,7 +55509,7 @@
         <v>16</v>
       </c>
       <c r="G2007" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55541,7 +55535,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2008" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55567,7 +55561,7 @@
         <v>16</v>
       </c>
       <c r="G2009" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55593,7 +55587,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2010" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55619,7 +55613,7 @@
         <v>16</v>
       </c>
       <c r="G2011" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55645,7 +55639,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55671,7 +55665,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2013" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55697,7 +55691,7 @@
         <v>16</v>
       </c>
       <c r="G2014" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55723,7 +55717,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55749,7 +55743,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2016" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55775,7 +55769,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55801,7 +55795,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2018" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55827,7 +55821,7 @@
         <v>15.75</v>
       </c>
       <c r="G2019" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55853,7 +55847,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2020" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55879,7 +55873,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2021" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55905,7 +55899,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2022" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55931,7 +55925,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2023" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55957,7 +55951,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2024" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55983,7 +55977,7 @@
         <v>16.75</v>
       </c>
       <c r="G2025" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56009,7 +56003,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2026" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56035,7 +56029,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2027" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56061,7 +56055,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56087,7 +56081,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2029" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56113,7 +56107,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2030" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56139,7 +56133,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2031" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56165,7 +56159,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2032" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56191,7 +56185,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2033" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56217,7 +56211,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2034" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56243,7 +56237,7 @@
         <v>19</v>
       </c>
       <c r="G2035" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56269,7 +56263,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G2036" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56295,7 +56289,7 @@
         <v>18.5</v>
       </c>
       <c r="G2037" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56321,7 +56315,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2038" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56347,7 +56341,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2039" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56373,7 +56367,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2040" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56399,7 +56393,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2041" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56425,7 +56419,7 @@
         <v>18</v>
       </c>
       <c r="G2042" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56451,7 +56445,7 @@
         <v>18.5</v>
       </c>
       <c r="G2043" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56477,7 +56471,7 @@
         <v>18.75</v>
       </c>
       <c r="G2044" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56503,7 +56497,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2045" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56529,7 +56523,7 @@
         <v>18.5</v>
       </c>
       <c r="G2046" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56555,7 +56549,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2047" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56581,7 +56575,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G2048" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56607,7 +56601,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2049" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56633,7 +56627,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2050" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56659,7 +56653,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2051" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56685,7 +56679,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2052" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56711,7 +56705,7 @@
         <v>17.75</v>
       </c>
       <c r="G2053" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56737,7 +56731,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2054" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56763,7 +56757,7 @@
         <v>17.25</v>
       </c>
       <c r="G2055" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56789,7 +56783,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2056" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56815,7 +56809,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2057" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56841,7 +56835,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2058" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56867,7 +56861,7 @@
         <v>16.25</v>
       </c>
       <c r="G2059" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56893,7 +56887,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2060" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56919,7 +56913,7 @@
         <v>16.5</v>
       </c>
       <c r="G2061" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56945,7 +56939,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2062" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56971,7 +56965,7 @@
         <v>16.5</v>
       </c>
       <c r="G2063" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56997,7 +56991,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2064" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57023,7 +57017,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2065" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57049,7 +57043,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2066" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57075,7 +57069,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2067" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57101,7 +57095,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2068" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57127,7 +57121,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2069" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57153,7 +57147,7 @@
         <v>16.75</v>
       </c>
       <c r="G2070" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57179,7 +57173,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2071" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57205,7 +57199,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2072" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57231,7 +57225,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2073" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57257,7 +57251,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2074" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57283,7 +57277,7 @@
         <v>17</v>
       </c>
       <c r="G2075" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57309,7 +57303,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2076" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57335,7 +57329,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2077" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -57361,7 +57355,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2078" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -57387,7 +57381,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57413,7 +57407,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2080" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57439,7 +57433,7 @@
         <v>17.75</v>
       </c>
       <c r="G2081" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57465,7 +57459,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G2082" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57491,7 +57485,7 @@
         <v>17.5</v>
       </c>
       <c r="G2083" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57517,7 +57511,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2084" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57543,7 +57537,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2085" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57569,7 +57563,7 @@
         <v>17.5</v>
       </c>
       <c r="G2086" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57595,7 +57589,7 @@
         <v>17</v>
       </c>
       <c r="G2087" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57621,7 +57615,7 @@
         <v>17</v>
       </c>
       <c r="G2088" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57647,7 +57641,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2089" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57673,7 +57667,7 @@
         <v>17.75</v>
       </c>
       <c r="G2090" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57699,7 +57693,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2091" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57725,7 +57719,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2092" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57751,7 +57745,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2093" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57777,7 +57771,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2094" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57803,7 +57797,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2095" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57829,7 +57823,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2096" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -57855,7 +57849,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2097" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57881,7 +57875,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57907,7 +57901,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2099" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57933,7 +57927,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2100" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57959,7 +57953,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2101" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57985,7 +57979,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2102" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58011,7 +58005,7 @@
         <v>17</v>
       </c>
       <c r="G2103" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58037,7 +58031,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2104" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58063,7 +58057,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2105" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58089,7 +58083,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2106" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58115,7 +58109,7 @@
         <v>17.5</v>
       </c>
       <c r="G2107" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -58141,7 +58135,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2108" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58167,7 +58161,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2109" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -58193,7 +58187,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2110" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58219,7 +58213,7 @@
         <v>17</v>
       </c>
       <c r="G2111" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58245,7 +58239,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2112" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58271,7 +58265,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2113" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58297,7 +58291,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2114" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58323,7 +58317,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2115" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58349,7 +58343,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2116" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58375,7 +58369,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2117" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -58401,7 +58395,7 @@
         <v>17</v>
       </c>
       <c r="G2118" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58427,7 +58421,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2119" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58453,7 +58447,7 @@
         <v>17</v>
       </c>
       <c r="G2120" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58479,7 +58473,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2121" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58505,7 +58499,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2122" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58531,7 +58525,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2123" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58557,7 +58551,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2124" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58583,7 +58577,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2125" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58609,7 +58603,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2126" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58635,7 +58629,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2127" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58661,7 +58655,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2128" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58687,7 +58681,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2129" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58713,7 +58707,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2130" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58739,7 +58733,7 @@
         <v>16.5</v>
       </c>
       <c r="G2131" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58765,7 +58759,7 @@
         <v>16.5</v>
       </c>
       <c r="G2132" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58791,7 +58785,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2133" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58817,7 +58811,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2134" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58843,7 +58837,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2135" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58869,7 +58863,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2136" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58895,7 +58889,7 @@
         <v>17</v>
       </c>
       <c r="G2137" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58921,7 +58915,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2138" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58947,7 +58941,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2139" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58973,7 +58967,7 @@
         <v>16.5</v>
       </c>
       <c r="G2140" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -58999,7 +58993,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2141" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59025,7 +59019,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2142" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59051,7 +59045,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2143" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59077,7 +59071,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2144" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59103,7 +59097,7 @@
         <v>16.75</v>
       </c>
       <c r="G2145" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59129,7 +59123,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2146" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59155,7 +59149,7 @@
         <v>16.75</v>
       </c>
       <c r="G2147" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59181,7 +59175,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2148" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59207,7 +59201,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2149" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59233,7 +59227,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2150" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59259,7 +59253,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2151" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59285,7 +59279,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2152" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59311,7 +59305,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2153" t="s">
-        <v>891</v>
+        <v>846</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59337,7 +59331,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2154" t="s">
-        <v>891</v>
+        <v>846</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59363,7 +59357,7 @@
         <v>16.25</v>
       </c>
       <c r="G2155" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59389,7 +59383,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2156" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59415,7 +59409,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2157" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59441,7 +59435,7 @@
         <v>15</v>
       </c>
       <c r="G2158" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59467,7 +59461,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2159" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59493,7 +59487,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2160" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59519,7 +59513,7 @@
         <v>15.25</v>
       </c>
       <c r="G2161" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59545,7 +59539,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2162" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59571,7 +59565,7 @@
         <v>15.25</v>
       </c>
       <c r="G2163" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59597,7 +59591,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2164" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59623,7 +59617,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2165" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59649,7 +59643,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2166" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59675,7 +59669,7 @@
         <v>16.25</v>
       </c>
       <c r="G2167" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59701,7 +59695,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2168" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59727,7 +59721,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2169" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59753,7 +59747,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2170" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59779,7 +59773,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2171" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59805,7 +59799,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59831,7 +59825,7 @@
         <v>16</v>
       </c>
       <c r="G2173" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59857,7 +59851,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2174" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -59883,7 +59877,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2175" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59909,7 +59903,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2176" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59935,7 +59929,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2177" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59961,7 +59955,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2178" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59987,7 +59981,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2179" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60013,7 +60007,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60039,7 +60033,7 @@
         <v>15.25</v>
       </c>
       <c r="G2181" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60065,7 +60059,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60091,7 +60085,7 @@
         <v>15.25</v>
       </c>
       <c r="G2183" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60117,7 +60111,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2184" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60143,7 +60137,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2185" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60169,7 +60163,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2186" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60195,7 +60189,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60221,7 +60215,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2188" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60247,7 +60241,7 @@
         <v>15</v>
       </c>
       <c r="G2189" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60273,7 +60267,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2190" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60299,7 +60293,7 @@
         <v>15</v>
       </c>
       <c r="G2191" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60325,7 +60319,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2192" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60351,7 +60345,7 @@
         <v>15</v>
       </c>
       <c r="G2193" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60377,7 +60371,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2194" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60403,7 +60397,7 @@
         <v>15</v>
       </c>
       <c r="G2195" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60429,7 +60423,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2196" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60455,7 +60449,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2197" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60481,7 +60475,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60507,7 +60501,7 @@
         <v>15</v>
       </c>
       <c r="G2199" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60533,7 +60527,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G2200" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60559,7 +60553,7 @@
         <v>15</v>
       </c>
       <c r="G2201" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60585,7 +60579,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60611,7 +60605,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2203" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60637,7 +60631,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2204" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60663,7 +60657,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60689,7 +60683,7 @@
         <v>14.5</v>
       </c>
       <c r="G2206" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60715,7 +60709,7 @@
         <v>14.5</v>
       </c>
       <c r="G2207" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60741,7 +60735,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60767,7 +60761,7 @@
         <v>14.5</v>
       </c>
       <c r="G2209" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60793,7 +60787,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60819,7 +60813,7 @@
         <v>14.5</v>
       </c>
       <c r="G2211" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60845,7 +60839,7 @@
         <v>14.5</v>
       </c>
       <c r="G2212" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60871,7 +60865,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60897,7 +60891,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2214" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60923,7 +60917,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2215" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60949,7 +60943,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2216" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60975,7 +60969,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2217" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61001,7 +60995,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2218" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61027,7 +61021,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2219" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61053,7 +61047,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2220" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61079,7 +61073,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2221" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61105,7 +61099,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2222" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61131,7 +61125,7 @@
         <v>15</v>
       </c>
       <c r="G2223" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61157,7 +61151,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61183,7 +61177,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2225" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61209,7 +61203,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2226" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61235,7 +61229,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2227" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61261,7 +61255,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61287,7 +61281,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2229" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61313,7 +61307,7 @@
         <v>15.25</v>
       </c>
       <c r="G2230" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61339,7 +61333,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2231" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61365,7 +61359,7 @@
         <v>15.5</v>
       </c>
       <c r="G2232" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61391,7 +61385,7 @@
         <v>15.5</v>
       </c>
       <c r="G2233" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61417,7 +61411,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2234" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61443,7 +61437,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2235" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61469,7 +61463,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2236" t="s">
-        <v>891</v>
+        <v>846</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61495,7 +61489,7 @@
         <v>16</v>
       </c>
       <c r="G2237" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61521,7 +61515,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2238" t="s">
-        <v>891</v>
+        <v>846</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61547,7 +61541,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2239" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61573,7 +61567,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2240" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61599,7 +61593,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2241" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61625,7 +61619,7 @@
         <v>16.5</v>
       </c>
       <c r="G2242" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61651,7 +61645,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2243" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61677,7 +61671,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2244" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61703,7 +61697,7 @@
         <v>17.25</v>
       </c>
       <c r="G2245" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61729,7 +61723,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2246" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61755,7 +61749,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2247" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61781,7 +61775,7 @@
         <v>17</v>
       </c>
       <c r="G2248" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61807,7 +61801,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2249" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61833,7 +61827,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2250" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61859,7 +61853,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61885,7 +61879,7 @@
         <v>17.25</v>
       </c>
       <c r="G2252" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61911,7 +61905,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2253" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61937,7 +61931,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2254" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61963,7 +61957,7 @@
         <v>17.75</v>
       </c>
       <c r="G2255" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61989,7 +61983,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G2256" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62015,7 +62009,7 @@
         <v>18</v>
       </c>
       <c r="G2257" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62041,7 +62035,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2258" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62067,7 +62061,7 @@
         <v>17</v>
       </c>
       <c r="G2259" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62093,7 +62087,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2260" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62119,7 +62113,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2261" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62145,7 +62139,7 @@
         <v>16.5</v>
       </c>
       <c r="G2262" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62171,7 +62165,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2263" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62197,7 +62191,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2264" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62223,7 +62217,7 @@
         <v>16.5</v>
       </c>
       <c r="G2265" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62249,7 +62243,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2266" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62275,7 +62269,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2267" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62301,7 +62295,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2268" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62327,7 +62321,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2269" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62353,7 +62347,7 @@
         <v>15.5</v>
       </c>
       <c r="G2270" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62379,7 +62373,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2271" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62405,7 +62399,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2272" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62431,7 +62425,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2273" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62457,7 +62451,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2274" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62483,7 +62477,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2275" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62509,7 +62503,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2276" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62535,7 +62529,7 @@
         <v>17</v>
       </c>
       <c r="G2277" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62561,7 +62555,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2278" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62587,7 +62581,7 @@
         <v>16.5</v>
       </c>
       <c r="G2279" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62613,7 +62607,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2280" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62639,7 +62633,7 @@
         <v>16</v>
       </c>
       <c r="G2281" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62665,7 +62659,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62691,7 +62685,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2283" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62717,7 +62711,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2284" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62743,7 +62737,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2285" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62769,7 +62763,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62795,7 +62789,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2287" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62821,7 +62815,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2288" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62847,7 +62841,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2289" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62873,7 +62867,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62899,7 +62893,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2291" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62925,7 +62919,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2292" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62951,7 +62945,7 @@
         <v>16.5</v>
       </c>
       <c r="G2293" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62977,7 +62971,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2294" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63003,7 +62997,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2295" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63029,7 +63023,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2296" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63055,7 +63049,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2297" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63081,7 +63075,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2298" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63107,7 +63101,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63133,7 +63127,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63159,7 +63153,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63185,7 +63179,7 @@
         <v>16</v>
       </c>
       <c r="G2302" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63211,7 +63205,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2303" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63237,7 +63231,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2304" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63263,7 +63257,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63289,7 +63283,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2306" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63315,7 +63309,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2307" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63341,7 +63335,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2308" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63367,7 +63361,7 @@
         <v>15.75</v>
       </c>
       <c r="G2309" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63393,7 +63387,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2310" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63419,7 +63413,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2311" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63445,7 +63439,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63471,7 +63465,7 @@
         <v>16</v>
       </c>
       <c r="G2313" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63497,7 +63491,7 @@
         <v>16</v>
       </c>
       <c r="G2314" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63523,7 +63517,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2315" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63549,7 +63543,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2316" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63575,7 +63569,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2317" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63601,7 +63595,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>891</v>
+        <v>846</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63627,7 +63621,7 @@
         <v>16</v>
       </c>
       <c r="G2319" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63653,7 +63647,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2320" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63679,7 +63673,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2321" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63705,7 +63699,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2322" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63731,7 +63725,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2323" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63757,7 +63751,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2324" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63783,7 +63777,7 @@
         <v>16</v>
       </c>
       <c r="G2325" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63809,7 +63803,7 @@
         <v>16</v>
       </c>
       <c r="G2326" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63835,7 +63829,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2327" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63861,7 +63855,7 @@
         <v>16</v>
       </c>
       <c r="G2328" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63887,7 +63881,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2329" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63913,7 +63907,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2330" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63939,7 +63933,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2331" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63965,7 +63959,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63991,7 +63985,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64017,7 +64011,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2334" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64043,7 +64037,7 @@
         <v>15.75</v>
       </c>
       <c r="G2335" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64069,7 +64063,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2336" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64095,7 +64089,7 @@
         <v>15.75</v>
       </c>
       <c r="G2337" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64121,7 +64115,7 @@
         <v>15.25</v>
       </c>
       <c r="G2338" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64147,7 +64141,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2339" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64173,7 +64167,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2340" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64199,7 +64193,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2341" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64225,7 +64219,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64251,7 +64245,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64277,7 +64271,7 @@
         <v>15.5</v>
       </c>
       <c r="G2344" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64303,7 +64297,7 @@
         <v>15.5</v>
       </c>
       <c r="G2345" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64329,7 +64323,7 @@
         <v>15</v>
       </c>
       <c r="G2346" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64355,7 +64349,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64381,7 +64375,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64407,7 +64401,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2349" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64433,7 +64427,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2350" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64459,7 +64453,7 @@
         <v>16</v>
       </c>
       <c r="G2351" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64485,7 +64479,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64511,7 +64505,7 @@
         <v>15.75</v>
       </c>
       <c r="G2353" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64537,7 +64531,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64563,7 +64557,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2355" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64589,7 +64583,7 @@
         <v>15.25</v>
       </c>
       <c r="G2356" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64615,7 +64609,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2357" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64641,7 +64635,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64667,7 +64661,7 @@
         <v>14</v>
       </c>
       <c r="G2359" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64693,7 +64687,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2360" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64719,7 +64713,7 @@
         <v>15</v>
       </c>
       <c r="G2361" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64745,7 +64739,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2362" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64771,7 +64765,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2363" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64797,7 +64791,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2364" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64823,7 +64817,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64849,7 +64843,7 @@
         <v>14.5</v>
       </c>
       <c r="G2366" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64875,7 +64869,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2367" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64901,7 +64895,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2368" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64927,7 +64921,7 @@
         <v>15</v>
       </c>
       <c r="G2369" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64953,7 +64947,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2370" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64979,7 +64973,7 @@
         <v>15.25</v>
       </c>
       <c r="G2371" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65005,7 +64999,7 @@
         <v>15.25</v>
       </c>
       <c r="G2372" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65031,7 +65025,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2373" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65057,7 +65051,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2374" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65083,7 +65077,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2375" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65109,7 +65103,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2376" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65135,7 +65129,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65161,7 +65155,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2378" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65187,7 +65181,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2379" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65213,7 +65207,7 @@
         <v>15.25</v>
       </c>
       <c r="G2380" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65239,7 +65233,7 @@
         <v>15.25</v>
       </c>
       <c r="G2381" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65265,7 +65259,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2382" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65291,7 +65285,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2383" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65317,7 +65311,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65343,7 +65337,7 @@
         <v>16</v>
       </c>
       <c r="G2385" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65369,7 +65363,7 @@
         <v>16.25</v>
       </c>
       <c r="G2386" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65395,7 +65389,7 @@
         <v>16</v>
       </c>
       <c r="G2387" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65421,7 +65415,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2388" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65447,7 +65441,7 @@
         <v>16.5</v>
       </c>
       <c r="G2389" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65473,7 +65467,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2390" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65499,7 +65493,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2391" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65525,7 +65519,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2392" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65551,7 +65545,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2393" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65577,7 +65571,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2394" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65603,7 +65597,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2395" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65629,7 +65623,7 @@
         <v>16.75</v>
       </c>
       <c r="G2396" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65655,7 +65649,7 @@
         <v>16.5</v>
       </c>
       <c r="G2397" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65681,7 +65675,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2398" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65707,7 +65701,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2399" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65733,7 +65727,7 @@
         <v>16.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65759,7 +65753,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65785,7 +65779,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2402" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65811,7 +65805,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65837,7 +65831,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2404" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65863,7 +65857,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2405" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65889,7 +65883,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2406" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65915,7 +65909,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2407" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65941,7 +65935,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2408" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65967,7 +65961,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G2409" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65993,7 +65987,7 @@
         <v>16</v>
       </c>
       <c r="G2410" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66019,7 +66013,7 @@
         <v>15.75</v>
       </c>
       <c r="G2411" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66045,7 +66039,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2412" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66071,7 +66065,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2413" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66097,7 +66091,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2414" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66123,7 +66117,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2415" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66149,7 +66143,7 @@
         <v>16.25</v>
       </c>
       <c r="G2416" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66175,7 +66169,7 @@
         <v>16.75</v>
       </c>
       <c r="G2417" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66201,7 +66195,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2418" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66227,7 +66221,7 @@
         <v>16.25</v>
       </c>
       <c r="G2419" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66253,7 +66247,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2420" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66279,7 +66273,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2421" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66305,7 +66299,7 @@
         <v>16.25</v>
       </c>
       <c r="G2422" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66331,7 +66325,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2423" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66357,7 +66351,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2424" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66383,7 +66377,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2425" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66409,7 +66403,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2426" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66435,7 +66429,7 @@
         <v>16.25</v>
       </c>
       <c r="G2427" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66461,7 +66455,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2428" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66487,7 +66481,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66513,7 +66507,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2430" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66539,7 +66533,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2431" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66565,7 +66559,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66591,7 +66585,7 @@
         <v>16.5</v>
       </c>
       <c r="G2433" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66617,7 +66611,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2434" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66643,7 +66637,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2435" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66669,7 +66663,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2436" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66695,7 +66689,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2437" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66721,7 +66715,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2438" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66747,7 +66741,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2439" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66773,7 +66767,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2440" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66799,7 +66793,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66825,7 +66819,7 @@
         <v>16.75</v>
       </c>
       <c r="G2442" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66851,7 +66845,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66877,7 +66871,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2444" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66903,7 +66897,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2445" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66929,7 +66923,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2446" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66955,7 +66949,7 @@
         <v>18</v>
       </c>
       <c r="G2447" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66981,7 +66975,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2448" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67007,7 +67001,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67033,7 +67027,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2450" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67059,7 +67053,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2451" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67085,7 +67079,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2452" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67111,7 +67105,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2453" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67137,7 +67131,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2454" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67163,7 +67157,7 @@
         <v>21</v>
       </c>
       <c r="G2455" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67189,7 +67183,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G2456" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67215,7 +67209,7 @@
         <v>19.25</v>
       </c>
       <c r="G2457" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67241,7 +67235,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G2458" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67267,7 +67261,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G2459" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67293,7 +67287,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67319,7 +67313,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2461" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67345,7 +67339,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2462" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67371,7 +67365,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67397,7 +67391,7 @@
         <v>18.5</v>
       </c>
       <c r="G2464" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67423,7 +67417,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G2465" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67449,7 +67443,7 @@
         <v>19</v>
       </c>
       <c r="G2466" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67475,7 +67469,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2467" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67501,7 +67495,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2468" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67527,7 +67521,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2469" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67553,7 +67547,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2470" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67579,7 +67573,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2471" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67605,7 +67599,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2472" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67631,7 +67625,7 @@
         <v>16</v>
       </c>
       <c r="G2473" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67657,7 +67651,7 @@
         <v>16</v>
       </c>
       <c r="G2474" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67683,7 +67677,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2475" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67709,7 +67703,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67735,7 +67729,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67761,7 +67755,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67787,7 +67781,7 @@
         <v>16.25</v>
       </c>
       <c r="G2479" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67813,7 +67807,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67839,7 +67833,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2481" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67865,7 +67859,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67891,7 +67885,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67917,7 +67911,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2484" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67943,7 +67937,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2485" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67969,7 +67963,7 @@
         <v>16</v>
       </c>
       <c r="G2486" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67995,7 +67989,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2487" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68021,7 +68015,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2488" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68047,7 +68041,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68073,7 +68067,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2490" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68099,7 +68093,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2491" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68125,7 +68119,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2492" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68151,7 +68145,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68177,7 +68171,7 @@
         <v>15.25</v>
       </c>
       <c r="G2494" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68203,7 +68197,7 @@
         <v>15.5</v>
       </c>
       <c r="G2495" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68229,7 +68223,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2496" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68255,7 +68249,7 @@
         <v>15.5</v>
       </c>
       <c r="G2497" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68281,7 +68275,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2498" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68307,7 +68301,7 @@
         <v>15.25</v>
       </c>
       <c r="G2499" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -68333,7 +68327,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2500" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -68359,7 +68353,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2501" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -68385,7 +68379,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2502" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68411,7 +68405,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2503" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68437,7 +68431,7 @@
         <v>15.25</v>
       </c>
       <c r="G2504" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -68463,7 +68457,7 @@
         <v>15.25</v>
       </c>
       <c r="G2505" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -68489,7 +68483,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2506" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68515,7 +68509,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2507" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68541,7 +68535,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2508" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68549,7 +68543,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6910069444</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>9256</v>
@@ -68567,9 +68561,35 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2509" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6913078704</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>40452</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>15.9499998092651</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>15.1000003814697</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>15.1000003814697</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>15.5500001907349</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>959</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BEC.MI.xlsx
+++ b/data/BEC.MI.xlsx
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96833848953247</t>
+    <t xml:space="preserve">4.96833801269531</t>
   </si>
   <si>
     <t xml:space="preserve">BEC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96180963516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87040758132935</t>
+    <t xml:space="preserve">4.9618091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8704080581665</t>
   </si>
   <si>
     <t xml:space="preserve">4.87693643569946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92916631698608</t>
+    <t xml:space="preserve">4.92916584014893</t>
   </si>
   <si>
     <t xml:space="preserve">4.77247714996338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79859161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83450031280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73330545425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79532766342163</t>
+    <t xml:space="preserve">4.79859209060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83449983596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73330497741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79532718658447</t>
   </si>
   <si>
     <t xml:space="preserve">4.80512094497681</t>
@@ -77,61 +77,61 @@
     <t xml:space="preserve">4.76594924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7594199180603</t>
+    <t xml:space="preserve">4.75942039489746</t>
   </si>
   <si>
     <t xml:space="preserve">4.60273170471191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69739770889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69413232803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63537406921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44277811050415</t>
+    <t xml:space="preserve">4.69739723205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69413328170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63537502288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44277763366699</t>
   </si>
   <si>
     <t xml:space="preserve">4.37422704696655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18489503860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07390737533569</t>
+    <t xml:space="preserve">4.18489456176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07390689849854</t>
   </si>
   <si>
     <t xml:space="preserve">4.08043527603149</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23385953903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40360641479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49174356460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53091621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43298435211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50480127334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53744411468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42645597457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42319250106812</t>
+    <t xml:space="preserve">4.23386001586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40360593795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49174404144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53091669082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43298482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50480031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53744459152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42645692825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42319202423096</t>
   </si>
   <si>
     <t xml:space="preserve">4.43951416015625</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">4.41666316986084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44930648803711</t>
+    <t xml:space="preserve">4.44930696487427</t>
   </si>
   <si>
     <t xml:space="preserve">4.46562814712524</t>
@@ -155,37 +155,37 @@
     <t xml:space="preserve">4.89652252197266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90958023071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93569421768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91284465789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01403856277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94222402572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03362560272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04015350341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09238338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94875240325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99445295333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84429359436035</t>
+    <t xml:space="preserve">4.90957975387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93569469451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91284418106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01403903961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94222354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03362512588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04015445709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09238386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94875192642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99445343017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84429264068604</t>
   </si>
   <si>
     <t xml:space="preserve">5.0695333480835</t>
@@ -197,22 +197,22 @@
     <t xml:space="preserve">4.98792457580566</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04994678497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04341840744019</t>
+    <t xml:space="preserve">5.04994773864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04341888427734</t>
   </si>
   <si>
     <t xml:space="preserve">5.05974006652832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98466014862061</t>
+    <t xml:space="preserve">4.98466062545776</t>
   </si>
   <si>
     <t xml:space="preserve">5.02709627151489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9997386932373</t>
+    <t xml:space="preserve">4.99973821640015</t>
   </si>
   <si>
     <t xml:space="preserve">5.03393650054932</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">4.9621205329895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91766309738159</t>
+    <t xml:space="preserve">4.91766262054443</t>
   </si>
   <si>
     <t xml:space="preserve">4.9450216293335</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">4.89030504226685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89714431762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79455089569092</t>
+    <t xml:space="preserve">4.89714479446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79455041885376</t>
   </si>
   <si>
     <t xml:space="preserve">4.82190942764282</t>
@@ -245,25 +245,25 @@
     <t xml:space="preserve">4.98263883590698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9245023727417</t>
+    <t xml:space="preserve">4.92450189590454</t>
   </si>
   <si>
     <t xml:space="preserve">5.00657796859741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88346481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94844198226929</t>
+    <t xml:space="preserve">4.88346529006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94844150543213</t>
   </si>
   <si>
     <t xml:space="preserve">4.95870113372803</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99289846420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86636543273926</t>
+    <t xml:space="preserve">4.99289894104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86636638641357</t>
   </si>
   <si>
     <t xml:space="preserve">4.8526873588562</t>
@@ -275,103 +275,103 @@
     <t xml:space="preserve">4.78771114349365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78429079055786</t>
+    <t xml:space="preserve">4.78429126739502</t>
   </si>
   <si>
     <t xml:space="preserve">4.82532835006714</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77403211593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7227349281311</t>
+    <t xml:space="preserve">4.77403163909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72273540496826</t>
   </si>
   <si>
     <t xml:space="preserve">4.67485809326172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75693273544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56200456619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54148578643799</t>
+    <t xml:space="preserve">4.75693321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56200504302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54148626327515</t>
   </si>
   <si>
     <t xml:space="preserve">4.53122663497925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60304260253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63040113449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55516529083252</t>
+    <t xml:space="preserve">4.6030421257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63040065765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55516481399536</t>
   </si>
   <si>
     <t xml:space="preserve">4.58252334594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54832553863525</t>
+    <t xml:space="preserve">4.54832601547241</t>
   </si>
   <si>
     <t xml:space="preserve">4.45941066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53464698791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52780675888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52096652984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64407968521118</t>
+    <t xml:space="preserve">4.53464651107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52780628204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52096700668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64408016204834</t>
   </si>
   <si>
     <t xml:space="preserve">4.74325370788574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73983430862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83558797836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92108345031738</t>
+    <t xml:space="preserve">4.73983383178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8355884552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92108297348022</t>
   </si>
   <si>
     <t xml:space="preserve">4.92792272567749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98605918884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96554040908813</t>
+    <t xml:space="preserve">4.98605966567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96553993225098</t>
   </si>
   <si>
     <t xml:space="preserve">4.91424322128296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97237968444824</t>
+    <t xml:space="preserve">4.97237920761108</t>
   </si>
   <si>
     <t xml:space="preserve">4.96896028518677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86978673934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93818187713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88004589080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95186138153076</t>
+    <t xml:space="preserve">4.86978578567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93818235397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88004541397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9518609046936</t>
   </si>
   <si>
     <t xml:space="preserve">4.87320566177368</t>
@@ -383,115 +383,115 @@
     <t xml:space="preserve">4.76719236373901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80139017105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80822992324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76377248764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8424277305603</t>
+    <t xml:space="preserve">4.80138969421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80822944641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76377201080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84242820739746</t>
   </si>
   <si>
     <t xml:space="preserve">4.72957468032837</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84926700592041</t>
+    <t xml:space="preserve">4.84926748275757</t>
   </si>
   <si>
     <t xml:space="preserve">4.81164979934692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88688516616821</t>
+    <t xml:space="preserve">4.88688564300537</t>
   </si>
   <si>
     <t xml:space="preserve">5.02025747299194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08865308761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10575199127197</t>
+    <t xml:space="preserve">5.08865261077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10575151443481</t>
   </si>
   <si>
     <t xml:space="preserve">5.0647144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04761552810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09549188613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17756795883179</t>
+    <t xml:space="preserve">5.04761600494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09549236297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17756700515747</t>
   </si>
   <si>
     <t xml:space="preserve">5.23228454589844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12969064712524</t>
+    <t xml:space="preserve">5.1296911239624</t>
   </si>
   <si>
     <t xml:space="preserve">5.13995027542114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16388893127441</t>
+    <t xml:space="preserve">5.1638879776001</t>
   </si>
   <si>
     <t xml:space="preserve">5.21176528930664</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30751991271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3006796836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13311052322388</t>
+    <t xml:space="preserve">5.30751943588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30068063735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13311004638672</t>
   </si>
   <si>
     <t xml:space="preserve">5.22544479370117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16730880737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19808673858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29726028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47166919708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4032735824585</t>
+    <t xml:space="preserve">5.16730785369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19808578491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29725980758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47167015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40327405929565</t>
   </si>
   <si>
     <t xml:space="preserve">5.36565589904785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36223697662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46483087539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36907577514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39643430709839</t>
+    <t xml:space="preserve">5.36223649978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46482992172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36907529830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39643383026123</t>
   </si>
   <si>
     <t xml:space="preserve">5.25964260101318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41353273391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4614109992981</t>
+    <t xml:space="preserve">5.41353368759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46141052246094</t>
   </si>
   <si>
     <t xml:space="preserve">5.43747186660767</t>
@@ -506,19 +506,19 @@
     <t xml:space="preserve">5.47508955001831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39985418319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41695356369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4306321144104</t>
+    <t xml:space="preserve">5.39985370635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41695308685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43063259124756</t>
   </si>
   <si>
     <t xml:space="preserve">5.4579906463623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50586843490601</t>
+    <t xml:space="preserve">5.50586795806885</t>
   </si>
   <si>
     <t xml:space="preserve">5.52980613708496</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">5.60846185684204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68369674682617</t>
+    <t xml:space="preserve">5.68369770050049</t>
   </si>
   <si>
     <t xml:space="preserve">5.73157405853271</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">5.88204574584961</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9367618560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94360113143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05645370483398</t>
+    <t xml:space="preserve">5.93676137924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94360065460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05645418167114</t>
   </si>
   <si>
     <t xml:space="preserve">5.94018220901489</t>
@@ -551,109 +551,109 @@
     <t xml:space="preserve">6.04961538314819</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07355308532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02567672729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97437906265259</t>
+    <t xml:space="preserve">6.07355356216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02567625045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97437858581543</t>
   </si>
   <si>
     <t xml:space="preserve">6.04277515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17272710800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39501428604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37449502944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46682977676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32661914825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11117219924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89914417266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00515699386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2240252494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.265061378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39843368530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4052734375</t>
+    <t xml:space="preserve">6.17272663116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39501476287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37449550628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46683025360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32661867141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11117172241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89914464950562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00515747070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22402429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26506233215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39843463897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40527391433716</t>
   </si>
   <si>
     <t xml:space="preserve">6.48050880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41211366653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44973039627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43605184555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52838611602783</t>
+    <t xml:space="preserve">6.41211271286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44973087310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43605136871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52838659286499</t>
   </si>
   <si>
     <t xml:space="preserve">6.66859817504883</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99689722061157</t>
+    <t xml:space="preserve">6.99689769744873</t>
   </si>
   <si>
     <t xml:space="preserve">6.94218111038208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1200098991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46882915496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66717672348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20066356658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40585327148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64523887634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27590179443359</t>
+    <t xml:space="preserve">7.12001037597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46883010864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66717767715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20066452026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40585231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64523792266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27590274810791</t>
   </si>
   <si>
     <t xml:space="preserve">8.35113620758057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28958034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24170207977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33745765686035</t>
+    <t xml:space="preserve">8.28957939147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24170303344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33745670318604</t>
   </si>
   <si>
     <t xml:space="preserve">8.33061695098877</t>
@@ -668,124 +668,124 @@
     <t xml:space="preserve">8.22118377685547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11859130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30325889587402</t>
+    <t xml:space="preserve">8.11859035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30325794219971</t>
   </si>
   <si>
     <t xml:space="preserve">8.48108768463135</t>
   </si>
   <si>
+    <t xml:space="preserve">8.72047424316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71363353729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79469108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49782371520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52751064300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07478809356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31228065490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43102836608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37165451049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97830486297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88924551010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23806381225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.260329246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21579933166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6462574005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75758266448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8021125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69078636169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57946109771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66110038757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54977512359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52008724212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53493213653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60172557830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48298072814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59430599212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46813678741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14900302886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31970405578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12673854827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46071434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58688354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70562934875488</t>
+  </si>
+  <si>
     <t xml:space="preserve">8.72047328948975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7136344909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79469013214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49782371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52751064300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07478713989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31228160858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43102741241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37165546417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97830581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88924551010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23806571960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.260329246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21579933166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64625549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75758266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80211353302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69078636169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57946109771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66110038757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54977607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52008819580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53493118286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60172653198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48298072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59430599212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46813583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14900302886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3197021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12673854827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46071434020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58688259124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70562934875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72047424316406</t>
-  </si>
-  <si>
     <t xml:space="preserve">8.84664249420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.69820880889893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74273872375488</t>
+    <t xml:space="preserve">8.7427396774292</t>
   </si>
   <si>
     <t xml:space="preserve">8.56461811065674</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">8.63883495330811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66852283477783</t>
+    <t xml:space="preserve">8.66852188110352</t>
   </si>
   <si>
     <t xml:space="preserve">8.77984714508057</t>
@@ -833,43 +833,43 @@
     <t xml:space="preserve">8.68336486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6091480255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57204055786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49040126800537</t>
+    <t xml:space="preserve">8.60914897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57204151153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49040031433105</t>
   </si>
   <si>
     <t xml:space="preserve">8.47555828094482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78726863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71305084228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65367889404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62399291992188</t>
+    <t xml:space="preserve">8.78726959228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71305179595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65367794036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62399196624756</t>
   </si>
   <si>
     <t xml:space="preserve">8.75016021728516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90601634979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89859199523926</t>
+    <t xml:space="preserve">8.90601539611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89859390258789</t>
   </si>
   <si>
     <t xml:space="preserve">8.94312381744385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77242469787598</t>
+    <t xml:space="preserve">8.77242565155029</t>
   </si>
   <si>
     <t xml:space="preserve">8.96538829803467</t>
@@ -878,40 +878,40 @@
     <t xml:space="preserve">8.87632846832275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97281074523926</t>
+    <t xml:space="preserve">8.97281169891357</t>
   </si>
   <si>
     <t xml:space="preserve">9.09155750274658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21772575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52201461791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55170249938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56654357910156</t>
+    <t xml:space="preserve">9.21772766113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52201557159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55170154571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654453277588</t>
   </si>
   <si>
     <t xml:space="preserve">9.45522022247314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47748565673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5368595123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35873699188232</t>
+    <t xml:space="preserve">9.47748470306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53685855865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35873794555664</t>
   </si>
   <si>
     <t xml:space="preserve">9.59623241424561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64076137542725</t>
+    <t xml:space="preserve">9.64076328277588</t>
   </si>
   <si>
     <t xml:space="preserve">9.90794277191162</t>
@@ -926,49 +926,49 @@
     <t xml:space="preserve">9.72982311248779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99700164794922</t>
+    <t xml:space="preserve">9.99700355529785</t>
   </si>
   <si>
     <t xml:space="preserve">9.95247173309326</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0563764572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64818382263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95989322662354</t>
+    <t xml:space="preserve">10.0563774108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64818477630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95989418029785</t>
   </si>
   <si>
     <t xml:space="preserve">9.82630348205566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8114595413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75208568572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85599040985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86341285705566</t>
+    <t xml:space="preserve">9.81146049499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75208759307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85599136352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86341190338135</t>
   </si>
   <si>
     <t xml:space="preserve">10.0415325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0118465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94505023956299</t>
+    <t xml:space="preserve">10.0118455886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9450511932373</t>
   </si>
   <si>
     <t xml:space="preserve">9.90052032470703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8317985534668</t>
+    <t xml:space="preserve">8.83179950714111</t>
   </si>
   <si>
     <t xml:space="preserve">7.97088384628296</t>
@@ -977,37 +977,37 @@
     <t xml:space="preserve">8.25290679931641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16384887695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19353294372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67594432830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50524425506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02283573150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0673656463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98572826385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78534126281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76307678222656</t>
+    <t xml:space="preserve">8.16384792327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1935338973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67594337463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50524520874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02283668518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06736469268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9857292175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7853422164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76307582855225</t>
   </si>
   <si>
     <t xml:space="preserve">7.70370388031006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82987213134766</t>
+    <t xml:space="preserve">7.82987117767334</t>
   </si>
   <si>
     <t xml:space="preserve">7.64432954788208</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">8.04510116577148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14158248901367</t>
+    <t xml:space="preserve">8.14158344268799</t>
   </si>
   <si>
     <t xml:space="preserve">7.91893291473389</t>
@@ -1028,10 +1028,10 @@
     <t xml:space="preserve">8.08963108062744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11931800842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11189746856689</t>
+    <t xml:space="preserve">8.11931705474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11189651489258</t>
   </si>
   <si>
     <t xml:space="preserve">8.09705352783203</t>
@@ -1043,16 +1043,16 @@
     <t xml:space="preserve">8.1341609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28259372711182</t>
+    <t xml:space="preserve">8.2825927734375</t>
   </si>
   <si>
     <t xml:space="preserve">8.20837783813477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34196853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44587135314941</t>
+    <t xml:space="preserve">8.34196758270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44587230682373</t>
   </si>
   <si>
     <t xml:space="preserve">8.92085933685303</t>
@@ -1061,10 +1061,10 @@
     <t xml:space="preserve">9.02476215362549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32712459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2677526473999</t>
+    <t xml:space="preserve">8.32712554931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26775169372559</t>
   </si>
   <si>
     <t xml:space="preserve">7.71854734420776</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">8.03025722503662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01541328430176</t>
+    <t xml:space="preserve">8.01541423797607</t>
   </si>
   <si>
     <t xml:space="preserve">8.10447406768799</t>
@@ -1082,58 +1082,58 @@
     <t xml:space="preserve">8.17869186401367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22322177886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40134143829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05445003509521</t>
+    <t xml:space="preserve">8.22322082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40134048461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05444812774658</t>
   </si>
   <si>
     <t xml:space="preserve">8.93570232391357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72789573669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8911714553833</t>
+    <t xml:space="preserve">8.7278938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89117240905762</t>
   </si>
   <si>
     <t xml:space="preserve">9.00991916656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27710056304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30678653717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24741268157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35131549835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52943801879883</t>
+    <t xml:space="preserve">9.277099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30678749084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24741363525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35131645202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5294361114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.47006416320801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39584541320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54427909851074</t>
+    <t xml:space="preserve">9.39584636688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54428005218506</t>
   </si>
   <si>
     <t xml:space="preserve">9.87083435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60365295410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.063796043396</t>
+    <t xml:space="preserve">9.60365390777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0637979507446</t>
   </si>
   <si>
     <t xml:space="preserve">9.87998390197754</t>
@@ -1145,40 +1145,40 @@
     <t xml:space="preserve">9.55830955505371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72680473327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60426330566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46640300750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57362842559814</t>
+    <t xml:space="preserve">9.726806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60426425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46640396118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57362747192383</t>
   </si>
   <si>
     <t xml:space="preserve">9.6195821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63489818572998</t>
+    <t xml:space="preserve">9.63490009307861</t>
   </si>
   <si>
     <t xml:space="preserve">9.68085289001465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48172092437744</t>
+    <t xml:space="preserve">9.48172187805176</t>
   </si>
   <si>
     <t xml:space="preserve">9.43576717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34386157989502</t>
+    <t xml:space="preserve">9.34385967254639</t>
   </si>
   <si>
     <t xml:space="preserve">9.31322479248047</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08345890045166</t>
+    <t xml:space="preserve">9.08345794677734</t>
   </si>
   <si>
     <t xml:space="preserve">8.59328937530518</t>
@@ -1193,25 +1193,25 @@
     <t xml:space="preserve">8.96091556549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28258991241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2060022354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49703979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51235675811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52767467498779</t>
+    <t xml:space="preserve">9.28258895874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20600128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49703788757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51235771179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52767562866211</t>
   </si>
   <si>
     <t xml:space="preserve">9.38981437683105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35917949676514</t>
+    <t xml:space="preserve">9.35918045043945</t>
   </si>
   <si>
     <t xml:space="preserve">9.19068241119385</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">9.86466503143311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58894443511963</t>
+    <t xml:space="preserve">9.58894634246826</t>
   </si>
   <si>
     <t xml:space="preserve">9.32854270935059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42045116424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22132015228271</t>
+    <t xml:space="preserve">9.42044925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22131824493408</t>
   </si>
   <si>
     <t xml:space="preserve">9.25195407867432</t>
@@ -1238,19 +1238,19 @@
     <t xml:space="preserve">9.11409378051758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14472961425781</t>
+    <t xml:space="preserve">9.1447286605835</t>
   </si>
   <si>
     <t xml:space="preserve">9.26727294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45108604431152</t>
+    <t xml:space="preserve">9.45108509063721</t>
   </si>
   <si>
     <t xml:space="preserve">9.69616985321045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6502161026001</t>
+    <t xml:space="preserve">9.65021705627441</t>
   </si>
   <si>
     <t xml:space="preserve">8.80773830413818</t>
@@ -1259,37 +1259,37 @@
     <t xml:space="preserve">9.06814098358154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37449645996094</t>
+    <t xml:space="preserve">9.37449550628662</t>
   </si>
   <si>
     <t xml:space="preserve">9.03750514984131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12941074371338</t>
+    <t xml:space="preserve">9.1294116973877</t>
   </si>
   <si>
     <t xml:space="preserve">9.02218723297119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91496276855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94559955596924</t>
+    <t xml:space="preserve">8.91496181488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94559860229492</t>
   </si>
   <si>
     <t xml:space="preserve">9.17536449432373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00687026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95657253265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0331621170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91061782836914</t>
+    <t xml:space="preserve">9.00686836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95657348632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0331630706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91061878204346</t>
   </si>
   <si>
     <t xml:space="preserve">9.97189140319824</t>
@@ -1301,34 +1301,34 @@
     <t xml:space="preserve">9.7574405670166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09877681732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86900997161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74646854400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7311487197876</t>
+    <t xml:space="preserve">9.09877586364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86900901794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74646663665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73114776611328</t>
   </si>
   <si>
     <t xml:space="preserve">8.51669883728027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47074699401855</t>
+    <t xml:space="preserve">8.47074604034424</t>
   </si>
   <si>
     <t xml:space="preserve">8.42479228973389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01121139526367</t>
+    <t xml:space="preserve">8.01121044158936</t>
   </si>
   <si>
     <t xml:space="preserve">8.225661277771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36352062225342</t>
+    <t xml:space="preserve">8.36352157592773</t>
   </si>
   <si>
     <t xml:space="preserve">8.65455913543701</t>
@@ -1340,37 +1340,37 @@
     <t xml:space="preserve">8.8383731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93027973175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62392330169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71583080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50138187408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8230562210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60860729217529</t>
+    <t xml:space="preserve">8.93027877807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62392425537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7158317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50138092041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82305526733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60860633850098</t>
   </si>
   <si>
     <t xml:space="preserve">8.57796955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3482027053833</t>
+    <t xml:space="preserve">8.34820365905762</t>
   </si>
   <si>
     <t xml:space="preserve">8.30224990844727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33288669586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37883949279785</t>
+    <t xml:space="preserve">8.3328857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37883853912354</t>
   </si>
   <si>
     <t xml:space="preserve">8.28693199157715</t>
@@ -1382,67 +1382,67 @@
     <t xml:space="preserve">8.39415740966797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13375473022461</t>
+    <t xml:space="preserve">8.13375377655029</t>
   </si>
   <si>
     <t xml:space="preserve">8.11843681335449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45542812347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79242038726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85369205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70051193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66987895965576</t>
+    <t xml:space="preserve">8.4554271697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79241943359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85369110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70051383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66987609863281</t>
   </si>
   <si>
     <t xml:space="preserve">8.68519592285156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54733562469482</t>
+    <t xml:space="preserve">8.54733371734619</t>
   </si>
   <si>
     <t xml:space="preserve">8.44011116027832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88432598114014</t>
+    <t xml:space="preserve">8.88432693481445</t>
   </si>
   <si>
     <t xml:space="preserve">9.40513229370117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92593765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80339527130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29790782928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22897815704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07580089569092</t>
+    <t xml:space="preserve">9.92593860626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80339431762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29790687561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22897720336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0757999420166</t>
   </si>
   <si>
     <t xml:space="preserve">9.15238761901855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99921131134033</t>
+    <t xml:space="preserve">8.9992094039917</t>
   </si>
   <si>
     <t xml:space="preserve">9.59735012054443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31742668151855</t>
+    <t xml:space="preserve">9.31742763519287</t>
   </si>
   <si>
     <t xml:space="preserve">9.03750419616699</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">8.79757022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87754917144775</t>
+    <t xml:space="preserve">8.87754821777344</t>
   </si>
   <si>
     <t xml:space="preserve">8.83756065368652</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">8.63761520385742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23744964599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27743816375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47738456726074</t>
+    <t xml:space="preserve">9.23745059967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27743911743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47738361358643</t>
   </si>
   <si>
     <t xml:space="preserve">9.3574161529541</t>
@@ -1478,16 +1478,16 @@
     <t xml:space="preserve">9.67732906341553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63733959197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39740657806396</t>
+    <t xml:space="preserve">9.63733863830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39740467071533</t>
   </si>
   <si>
     <t xml:space="preserve">9.19746112823486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07749366760254</t>
+    <t xml:space="preserve">9.07749462127686</t>
   </si>
   <si>
     <t xml:space="preserve">9.4373950958252</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">9.55736064910889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11748313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71759223937988</t>
+    <t xml:space="preserve">9.11748218536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7175931930542</t>
   </si>
   <si>
     <t xml:space="preserve">8.95752620697021</t>
@@ -1511,70 +1511,70 @@
     <t xml:space="preserve">9.15747165679932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91753768920898</t>
+    <t xml:space="preserve">8.91753673553467</t>
   </si>
   <si>
     <t xml:space="preserve">10.7970190048218</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3571395874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0772171020508</t>
+    <t xml:space="preserve">10.357141494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0772180557251</t>
   </si>
   <si>
     <t xml:space="preserve">10.3171510696411</t>
   </si>
   <si>
-    <t xml:space="preserve">10.117205619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91726303100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99724006652832</t>
+    <t xml:space="preserve">10.1172046661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91726112365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.997239112854</t>
   </si>
   <si>
     <t xml:space="preserve">10.0372285842896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7573070526123</t>
+    <t xml:space="preserve">9.75730514526367</t>
   </si>
   <si>
     <t xml:space="preserve">9.71731662750244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79729461669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83728504180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1571941375732</t>
+    <t xml:space="preserve">9.79729557037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83728313446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1571960449219</t>
   </si>
   <si>
     <t xml:space="preserve">10.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2371740341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3971290588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5570850372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4771070480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1971845626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5170974731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9969644546509</t>
+    <t xml:space="preserve">10.2371730804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3971300125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5570840835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.477108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1971836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5170965194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9969635009766</t>
   </si>
   <si>
     <t xml:space="preserve">11.1169300079346</t>
@@ -1589,73 +1589,73 @@
     <t xml:space="preserve">11.3568639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.196907043457</t>
+    <t xml:space="preserve">11.1969089508057</t>
   </si>
   <si>
     <t xml:space="preserve">10.8370084762573</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1569204330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0369529724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8769969940186</t>
+    <t xml:space="preserve">11.1569185256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0369520187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8769979476929</t>
   </si>
   <si>
     <t xml:space="preserve">10.9169855117798</t>
   </si>
   <si>
-    <t xml:space="preserve">10.956974029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7570304870605</t>
+    <t xml:space="preserve">10.9569749832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7570295333862</t>
   </si>
   <si>
     <t xml:space="preserve">10.597074508667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4371175765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2768859863281</t>
+    <t xml:space="preserve">10.4371194839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2768869400024</t>
   </si>
   <si>
     <t xml:space="preserve">11.4368419647217</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5568084716797</t>
+    <t xml:space="preserve">11.556809425354</t>
   </si>
   <si>
     <t xml:space="preserve">11.6767768859863</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7170400619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11775684356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1660213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88582181930542</t>
+    <t xml:space="preserve">10.717041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11775875091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16602182388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88582229614258</t>
   </si>
   <si>
     <t xml:space="preserve">7.46993827819824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03805685043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91009283065796</t>
+    <t xml:space="preserve">7.03805732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9100923538208</t>
   </si>
   <si>
     <t xml:space="preserve">6.39823341369629</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20628690719604</t>
+    <t xml:space="preserve">6.20628643035889</t>
   </si>
   <si>
     <t xml:space="preserve">5.99834394454956</t>
@@ -1667,13 +1667,13 @@
     <t xml:space="preserve">7.30998134613037</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40595579147339</t>
+    <t xml:space="preserve">7.40595483779907</t>
   </si>
   <si>
     <t xml:space="preserve">7.32597732543945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11803436279297</t>
+    <t xml:space="preserve">7.11803483963013</t>
   </si>
   <si>
     <t xml:space="preserve">6.73414087295532</t>
@@ -1682,40 +1682,40 @@
     <t xml:space="preserve">6.9740743637085</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29398536682129</t>
+    <t xml:space="preserve">7.29398632049561</t>
   </si>
   <si>
     <t xml:space="preserve">7.15002489089966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86210489273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81411933898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76613235473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94208383560181</t>
+    <t xml:space="preserve">6.86210536956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8141188621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76613187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94208335876465</t>
   </si>
   <si>
     <t xml:space="preserve">6.79812288284302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92608785629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78212785720825</t>
+    <t xml:space="preserve">6.92608690261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78212738037109</t>
   </si>
   <si>
     <t xml:space="preserve">6.83011436462402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92877960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01068067550659</t>
+    <t xml:space="preserve">6.92877912521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01067972183228</t>
   </si>
   <si>
     <t xml:space="preserve">6.89601898193359</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">6.96153926849365</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73221874237061</t>
+    <t xml:space="preserve">6.73221826553345</t>
   </si>
   <si>
     <t xml:space="preserve">6.74859809875488</t>
@@ -1736,22 +1736,22 @@
     <t xml:space="preserve">7.1253399848938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22362089157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55122232437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56760311126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0262451171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31289577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39479637145996</t>
+    <t xml:space="preserve">7.22362041473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5512228012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56760168075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02624607086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31289672851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39479827880859</t>
   </si>
   <si>
     <t xml:space="preserve">8.72239875793457</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">8.76334953308105</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88619995117188</t>
+    <t xml:space="preserve">8.88620090484619</t>
   </si>
   <si>
     <t xml:space="preserve">9.1728515625</t>
@@ -1769,22 +1769,22 @@
     <t xml:space="preserve">9.41855335235596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92714977264404</t>
+    <t xml:space="preserve">8.92715072631836</t>
   </si>
   <si>
     <t xml:space="preserve">9.13190078735352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96809959411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3366527557373</t>
+    <t xml:space="preserve">8.96810054779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33665180206299</t>
   </si>
   <si>
     <t xml:space="preserve">8.84525012969971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09095191955566</t>
+    <t xml:space="preserve">9.09095096588135</t>
   </si>
   <si>
     <t xml:space="preserve">9.21380233764648</t>
@@ -1793,22 +1793,22 @@
     <t xml:space="preserve">9.25475215911865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00905132293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64049911499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09176635742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17366600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1900463104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10814476013184</t>
+    <t xml:space="preserve">9.0090503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64049816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09176540374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17366409301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19004535675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10814571380615</t>
   </si>
   <si>
     <t xml:space="preserve">8.15728569030762</t>
@@ -1823,34 +1823,34 @@
     <t xml:space="preserve">7.71502351760864</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7805438041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58398294448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51846265792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53484296798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33828115463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48570156097412</t>
+    <t xml:space="preserve">7.78054332733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58398246765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51846313476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5348424911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33828163146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48570203781128</t>
   </si>
   <si>
     <t xml:space="preserve">7.61674308776855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69864320755005</t>
+    <t xml:space="preserve">7.69864225387573</t>
   </si>
   <si>
     <t xml:space="preserve">7.76416397094727</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73140335083008</t>
+    <t xml:space="preserve">7.73140382766724</t>
   </si>
   <si>
     <t xml:space="preserve">7.79692411422729</t>
@@ -1859,13 +1859,13 @@
     <t xml:space="preserve">7.66588306427002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63312196731567</t>
+    <t xml:space="preserve">7.63312339782715</t>
   </si>
   <si>
     <t xml:space="preserve">7.64950370788574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6822624206543</t>
+    <t xml:space="preserve">7.68226337432861</t>
   </si>
   <si>
     <t xml:space="preserve">7.82968378067017</t>
@@ -1880,28 +1880,28 @@
     <t xml:space="preserve">7.6003623008728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.354660987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40380096435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24000072479248</t>
+    <t xml:space="preserve">7.35466051101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40380144119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24000120162964</t>
   </si>
   <si>
     <t xml:space="preserve">7.19086027145386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79773902893066</t>
+    <t xml:space="preserve">6.79773855209351</t>
   </si>
   <si>
     <t xml:space="preserve">6.68307733535767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5684175491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3882360458374</t>
+    <t xml:space="preserve">6.56841802597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38823652267456</t>
   </si>
   <si>
     <t xml:space="preserve">6.2244348526001</t>
@@ -1913,13 +1913,13 @@
     <t xml:space="preserve">6.42099618911743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71583843231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84687852859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0434398651123</t>
+    <t xml:space="preserve">6.71583795547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84687805175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04344081878662</t>
   </si>
   <si>
     <t xml:space="preserve">7.92796516418457</t>
@@ -1934,7 +1934,7 @@
     <t xml:space="preserve">7.97710514068604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84606456756592</t>
+    <t xml:space="preserve">7.84606409072876</t>
   </si>
   <si>
     <t xml:space="preserve">8.12452602386475</t>
@@ -1946,28 +1946,28 @@
     <t xml:space="preserve">8.43574714660645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55859851837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68144989013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47669792175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35384654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23099517822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04262542724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94434452056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86244487762451</t>
+    <t xml:space="preserve">8.55859756469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6814489364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47669887542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35384750366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23099613189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04262447357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94434547424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86244535446167</t>
   </si>
   <si>
     <t xml:space="preserve">8.00986480712891</t>
@@ -1976,19 +1976,19 @@
     <t xml:space="preserve">8.05900573730469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45950317382812</t>
+    <t xml:space="preserve">9.45950412750244</t>
   </si>
   <si>
     <t xml:space="preserve">9.90995693206787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1556577682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86900615692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62330436706543</t>
+    <t xml:space="preserve">10.1556568145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86900520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62330341339111</t>
   </si>
   <si>
     <t xml:space="preserve">9.50045394897461</t>
@@ -1997,31 +1997,31 @@
     <t xml:space="preserve">9.37760257720947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58235454559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7052059173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05000114440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54140281677246</t>
+    <t xml:space="preserve">9.58235359191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70520496368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0500020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54140377044678</t>
   </si>
   <si>
     <t xml:space="preserve">9.22513484954834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18320178985596</t>
+    <t xml:space="preserve">9.18320274353027</t>
   </si>
   <si>
     <t xml:space="preserve">9.09933853149414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14126968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39286422729492</t>
+    <t xml:space="preserve">9.14127063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39286518096924</t>
   </si>
   <si>
     <t xml:space="preserve">9.30900001525879</t>
@@ -2036,16 +2036,16 @@
     <t xml:space="preserve">9.35093212127686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64445877075195</t>
+    <t xml:space="preserve">9.64445972442627</t>
   </si>
   <si>
     <t xml:space="preserve">9.51866245269775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47673034667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77025604248047</t>
+    <t xml:space="preserve">9.47672939300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77025699615479</t>
   </si>
   <si>
     <t xml:space="preserve">9.60252666473389</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">9.72832489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3153772354126</t>
+    <t xml:space="preserve">10.3153781890869</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895809173584</t>
@@ -2063,16 +2063,16 @@
     <t xml:space="preserve">10.2315130233765</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1057167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.357310295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2734451293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1476488113403</t>
+    <t xml:space="preserve">10.1057157516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3573112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2734470367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1476497650146</t>
   </si>
   <si>
     <t xml:space="preserve">10.0218505859375</t>
@@ -2084,28 +2084,28 @@
     <t xml:space="preserve">9.81218910217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89605331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26706790924072</t>
+    <t xml:space="preserve">9.8960542678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26706886291504</t>
   </si>
   <si>
     <t xml:space="preserve">9.97991847991943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68639183044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05740642547607</t>
+    <t xml:space="preserve">9.68639278411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05740547180176</t>
   </si>
   <si>
     <t xml:space="preserve">8.97354030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3992433547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5669746398926</t>
+    <t xml:space="preserve">10.399242401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5669736862183</t>
   </si>
   <si>
     <t xml:space="preserve">10.7766351699829</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">11.279824256897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3217573165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9443664550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2378911972046</t>
+    <t xml:space="preserve">11.321756362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9443655014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2378921508789</t>
   </si>
   <si>
     <t xml:space="preserve">11.1959600448608</t>
@@ -2132,16 +2132,16 @@
     <t xml:space="preserve">11.4056224822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1540269851685</t>
+    <t xml:space="preserve">11.1540279388428</t>
   </si>
   <si>
     <t xml:space="preserve">11.7830142974854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7410802841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0346088409424</t>
+    <t xml:space="preserve">11.7410821914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0346078872681</t>
   </si>
   <si>
     <t xml:space="preserve">11.6152839660645</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">10.9862976074219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.070161819458</t>
+    <t xml:space="preserve">11.0701608657837</t>
   </si>
   <si>
     <t xml:space="preserve">11.4894866943359</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">11.6991481781006</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5733518600464</t>
+    <t xml:space="preserve">11.5733509063721</t>
   </si>
   <si>
     <t xml:space="preserve">11.531418800354</t>
@@ -2177,19 +2177,19 @@
     <t xml:space="preserve">11.0282297134399</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4831094741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5250415802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6089057922363</t>
+    <t xml:space="preserve">10.4831075668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5250406265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6089038848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.818567276001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9024333953857</t>
+    <t xml:space="preserve">10.9024324417114</t>
   </si>
   <si>
     <t xml:space="preserve">11.4475536346436</t>
@@ -68685,7 +68685,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6909722222</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>6287</v>
@@ -68706,6 +68706,32 @@
         <v>997</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6912268518</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>2554</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>14.8500003814697</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>14.6999998092651</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>944</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BEC.MI.xlsx
+++ b/data/BEC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="999">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96833801269531</t>
+    <t xml:space="preserve">4.96833896636963</t>
   </si>
   <si>
     <t xml:space="preserve">BEC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96180963516235</t>
+    <t xml:space="preserve">4.96181058883667</t>
   </si>
   <si>
     <t xml:space="preserve">4.8704080581665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87693643569946</t>
+    <t xml:space="preserve">4.87693691253662</t>
   </si>
   <si>
     <t xml:space="preserve">4.92916631698608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77247714996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79859256744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83450031280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73330545425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79532718658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80512094497681</t>
+    <t xml:space="preserve">4.77247667312622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79859161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83449983596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73330450057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79532766342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80512046813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.76594877243042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75942039489746</t>
+    <t xml:space="preserve">4.75941896438599</t>
   </si>
   <si>
     <t xml:space="preserve">4.60273122787476</t>
@@ -95,31 +95,31 @@
     <t xml:space="preserve">4.44277811050415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37422657012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18489360809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07390689849854</t>
+    <t xml:space="preserve">4.37422609329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18489456176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07390737533569</t>
   </si>
   <si>
     <t xml:space="preserve">4.08043527603149</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2338604927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40360593795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49174308776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53091526031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43298482894897</t>
+    <t xml:space="preserve">4.23386001586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40360546112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49174404144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5309157371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43298530578613</t>
   </si>
   <si>
     <t xml:space="preserve">4.50480079650879</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">4.53744411468506</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42645692825317</t>
+    <t xml:space="preserve">4.42645645141602</t>
   </si>
   <si>
     <t xml:space="preserve">4.42319202423096</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">4.41666316986084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44930696487427</t>
+    <t xml:space="preserve">4.44930744171143</t>
   </si>
   <si>
     <t xml:space="preserve">4.46562910079956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47868680953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60925960540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89652347564697</t>
+    <t xml:space="preserve">4.47868633270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60926055908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89652299880981</t>
   </si>
   <si>
     <t xml:space="preserve">4.90958023071289</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">4.9356951713562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91284465789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01403903961182</t>
+    <t xml:space="preserve">4.91284370422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0140380859375</t>
   </si>
   <si>
     <t xml:space="preserve">4.94222354888916</t>
@@ -173,31 +173,31 @@
     <t xml:space="preserve">5.03362560272217</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04015350341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09238386154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94875192642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99445343017578</t>
+    <t xml:space="preserve">5.04015398025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09238290786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94875240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99445295333862</t>
   </si>
   <si>
     <t xml:space="preserve">4.84429311752319</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06953191757202</t>
+    <t xml:space="preserve">5.0695333480835</t>
   </si>
   <si>
     <t xml:space="preserve">5.09891223907471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98792362213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04994678497314</t>
+    <t xml:space="preserve">4.98792457580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04994630813599</t>
   </si>
   <si>
     <t xml:space="preserve">5.04341793060303</t>
@@ -206,22 +206,22 @@
     <t xml:space="preserve">5.05974006652832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98465967178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02709579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99973821640015</t>
+    <t xml:space="preserve">4.98466014862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02709627151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99973773956299</t>
   </si>
   <si>
     <t xml:space="preserve">5.03393602371216</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9621205329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91766309738159</t>
+    <t xml:space="preserve">4.96212100982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91766357421875</t>
   </si>
   <si>
     <t xml:space="preserve">4.9450216293335</t>
@@ -245,37 +245,37 @@
     <t xml:space="preserve">4.98263931274414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92450284957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00657796859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88346481323242</t>
+    <t xml:space="preserve">4.92450332641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00657749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88346529006958</t>
   </si>
   <si>
     <t xml:space="preserve">4.94844150543213</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95870065689087</t>
+    <t xml:space="preserve">4.95870018005371</t>
   </si>
   <si>
     <t xml:space="preserve">4.99289894104004</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86636686325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8526873588562</t>
+    <t xml:space="preserve">4.86636734008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85268688201904</t>
   </si>
   <si>
     <t xml:space="preserve">4.93134260177612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78771066665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78429126739502</t>
+    <t xml:space="preserve">4.78771114349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78429079055786</t>
   </si>
   <si>
     <t xml:space="preserve">4.8253288269043</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">4.67485809326172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75693321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56200504302979</t>
+    <t xml:space="preserve">4.75693273544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56200551986694</t>
   </si>
   <si>
     <t xml:space="preserve">4.54148578643799</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">4.53122663497925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6030421257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63040018081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55516529083252</t>
+    <t xml:space="preserve">4.60304260253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63040065765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55516481399536</t>
   </si>
   <si>
     <t xml:space="preserve">4.58252286911011</t>
@@ -317,118 +317,118 @@
     <t xml:space="preserve">4.54832553863525</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45941162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53464651107788</t>
+    <t xml:space="preserve">4.45941114425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53464698791504</t>
   </si>
   <si>
     <t xml:space="preserve">4.52780628204346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52096796035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64407968521118</t>
+    <t xml:space="preserve">4.52096748352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64408016204834</t>
   </si>
   <si>
     <t xml:space="preserve">4.74325323104858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73983383178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8355884552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92108249664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92792320251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98605918884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96554040908813</t>
+    <t xml:space="preserve">4.73983335494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83558893203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92108297348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92792224884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98605823516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96554088592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.91424322128296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9723801612854</t>
+    <t xml:space="preserve">4.97237968444824</t>
   </si>
   <si>
     <t xml:space="preserve">4.96896028518677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86978673934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93818140029907</t>
+    <t xml:space="preserve">4.86978626251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93818187713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.88004541397095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95186138153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87320613861084</t>
+    <t xml:space="preserve">4.9518609046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87320566177368</t>
   </si>
   <si>
     <t xml:space="preserve">4.86294651031494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76719236373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80139064788818</t>
+    <t xml:space="preserve">4.76719188690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80139017105103</t>
   </si>
   <si>
     <t xml:space="preserve">4.80822992324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76377248764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84242820739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72957468032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84926748275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81164979934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88688516616821</t>
+    <t xml:space="preserve">4.76377201080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8424277305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72957515716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84926700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81164932250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88688564300537</t>
   </si>
   <si>
     <t xml:space="preserve">5.02025699615479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08865308761597</t>
+    <t xml:space="preserve">5.08865261077881</t>
   </si>
   <si>
     <t xml:space="preserve">5.10575199127197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06471490859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04761552810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09549188613892</t>
+    <t xml:space="preserve">5.06471395492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04761505126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09549236297607</t>
   </si>
   <si>
     <t xml:space="preserve">5.17756748199463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23228454589844</t>
+    <t xml:space="preserve">5.23228406906128</t>
   </si>
   <si>
     <t xml:space="preserve">5.12969064712524</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">5.13994932174683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16388893127441</t>
+    <t xml:space="preserve">5.16388845443726</t>
   </si>
   <si>
     <t xml:space="preserve">5.21176528930664</t>
@@ -449,187 +449,187 @@
     <t xml:space="preserve">5.30068016052246</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13311100006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22544384002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16730833053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19808578491211</t>
+    <t xml:space="preserve">5.13311052322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22544479370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16730880737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19808721542358</t>
   </si>
   <si>
     <t xml:space="preserve">5.29726028442383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47167015075684</t>
+    <t xml:space="preserve">5.47166967391968</t>
   </si>
   <si>
     <t xml:space="preserve">5.40327405929565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36565637588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36223697662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46482992172241</t>
+    <t xml:space="preserve">5.36565589904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36223602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46483039855957</t>
   </si>
   <si>
     <t xml:space="preserve">5.36907577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39643383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25964212417603</t>
+    <t xml:space="preserve">5.39643430709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25964260101318</t>
   </si>
   <si>
     <t xml:space="preserve">5.41353321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46141004562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43747186660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45457029342651</t>
+    <t xml:space="preserve">5.4614109992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43747138977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45457124710083</t>
   </si>
   <si>
     <t xml:space="preserve">5.46824979782104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47508955001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39985418319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41695308685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4306321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45799016952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50586748123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52980661392212</t>
+    <t xml:space="preserve">5.47509002685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39985466003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41695356369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43063259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45799112319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50586795806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52980709075928</t>
   </si>
   <si>
     <t xml:space="preserve">5.60846138000488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68369770050049</t>
+    <t xml:space="preserve">5.68369722366333</t>
   </si>
   <si>
     <t xml:space="preserve">5.73157453536987</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88204479217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9367618560791</t>
+    <t xml:space="preserve">5.88204526901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93676280975342</t>
   </si>
   <si>
     <t xml:space="preserve">5.94360160827637</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05645370483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94018220901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04961490631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07355403900146</t>
+    <t xml:space="preserve">6.05645418167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94018173217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04961538314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07355356216431</t>
   </si>
   <si>
     <t xml:space="preserve">6.02567720413208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97437906265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04277563095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17272758483887</t>
+    <t xml:space="preserve">5.9743800163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04277515411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17272710800171</t>
   </si>
   <si>
     <t xml:space="preserve">6.39501476287842</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37449550628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46682977676392</t>
+    <t xml:space="preserve">6.37449502944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46682929992676</t>
   </si>
   <si>
     <t xml:space="preserve">6.32661771774292</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11117124557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89914417266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00515842437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2240252494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26506280899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39843273162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40527248382568</t>
+    <t xml:space="preserve">6.11117076873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8991436958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00515699386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22402477264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.265061378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39843368530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40527296066284</t>
   </si>
   <si>
     <t xml:space="preserve">6.48050928115845</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41211366653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44973134994507</t>
+    <t xml:space="preserve">6.41211318969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44973087310791</t>
   </si>
   <si>
     <t xml:space="preserve">6.4360523223877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52838611602783</t>
+    <t xml:space="preserve">6.52838516235352</t>
   </si>
   <si>
     <t xml:space="preserve">6.66859769821167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99689817428589</t>
+    <t xml:space="preserve">6.99689674377441</t>
   </si>
   <si>
     <t xml:space="preserve">6.94218015670776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12001085281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46882963180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66717767715454</t>
+    <t xml:space="preserve">7.12001037597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46883010864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6671781539917</t>
   </si>
   <si>
     <t xml:space="preserve">8.20066452026367</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">8.27590084075928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35113620758057</t>
+    <t xml:space="preserve">8.35113525390625</t>
   </si>
   <si>
     <t xml:space="preserve">8.28957939147949</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">8.33745670318604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33061695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31693935394287</t>
+    <t xml:space="preserve">8.33061790466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31693744659424</t>
   </si>
   <si>
     <t xml:space="preserve">8.26906108856201</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">8.22118473052979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1185884475708</t>
+    <t xml:space="preserve">8.11858940124512</t>
   </si>
   <si>
     <t xml:space="preserve">8.30325889587402</t>
@@ -677,34 +677,34 @@
     <t xml:space="preserve">8.48108863830566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72047328948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71363353729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79469013214111</t>
+    <t xml:space="preserve">8.72047424316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7136344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79469108581543</t>
   </si>
   <si>
     <t xml:space="preserve">8.49782371520996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52751064300537</t>
+    <t xml:space="preserve">8.52750968933105</t>
   </si>
   <si>
     <t xml:space="preserve">8.07478809356689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31228065490723</t>
+    <t xml:space="preserve">8.31228160858154</t>
   </si>
   <si>
     <t xml:space="preserve">8.43102741241455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37165451049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97830581665039</t>
+    <t xml:space="preserve">8.37165546417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97830772399902</t>
   </si>
   <si>
     <t xml:space="preserve">7.88924503326416</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">8.23806476593018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26032829284668</t>
+    <t xml:space="preserve">8.26033020019531</t>
   </si>
   <si>
     <t xml:space="preserve">8.21579933166504</t>
@@ -725,61 +725,61 @@
     <t xml:space="preserve">8.75758266448975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8021125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69078636169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57946109771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66110134124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54977512359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52008724212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53493213653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60172748565674</t>
+    <t xml:space="preserve">8.80211162567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69078826904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5794620513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66110038757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54977416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5200891494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53493118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60172653198242</t>
   </si>
   <si>
     <t xml:space="preserve">8.4829797744751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59430503845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46813774108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14900493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31970405578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12673950195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46071434020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58688354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70563125610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84664344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69820880889893</t>
+    <t xml:space="preserve">8.59430599212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46813583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14900302886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31970310211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12673854827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46071529388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58688259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7056303024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84664249420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69820976257324</t>
   </si>
   <si>
     <t xml:space="preserve">8.74273777008057</t>
@@ -788,58 +788,58 @@
     <t xml:space="preserve">8.56461811065674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43844985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40876293182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34939098358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42360687255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54235458374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63141250610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61657047271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63883399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66852188110352</t>
+    <t xml:space="preserve">8.43845081329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40876197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34938907623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42360591888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54235363006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63141441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61656951904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63883590698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66852283477783</t>
   </si>
   <si>
     <t xml:space="preserve">8.77984714508057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88374996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83922004699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82437801361084</t>
+    <t xml:space="preserve">8.88375091552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83922100067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82437705993652</t>
   </si>
   <si>
     <t xml:space="preserve">8.68336486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60914993286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57203960418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49040031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47555923461914</t>
+    <t xml:space="preserve">8.60914707183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57204151153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49040126800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47555828094482</t>
   </si>
   <si>
     <t xml:space="preserve">8.78726863861084</t>
@@ -848,16 +848,16 @@
     <t xml:space="preserve">8.71305179595947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65367889404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62399196624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75015926361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90601634979248</t>
+    <t xml:space="preserve">8.65367794036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62399101257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75016021728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90601539611816</t>
   </si>
   <si>
     <t xml:space="preserve">8.89859485626221</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">8.77242565155029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9653902053833</t>
+    <t xml:space="preserve">8.96538829803467</t>
   </si>
   <si>
     <t xml:space="preserve">8.87632846832275</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">8.97281074523926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09155750274658</t>
+    <t xml:space="preserve">9.0915584564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.2177267074585</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52201557159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55170154571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5665454864502</t>
+    <t xml:space="preserve">9.52201366424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55170249938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654644012451</t>
   </si>
   <si>
     <t xml:space="preserve">9.45522022247314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47748470306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53685855865479</t>
+    <t xml:space="preserve">9.4774866104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53686046600342</t>
   </si>
   <si>
     <t xml:space="preserve">9.35873794555664</t>
@@ -911,52 +911,52 @@
     <t xml:space="preserve">9.64076137542725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90794277191162</t>
+    <t xml:space="preserve">9.9079418182373</t>
   </si>
   <si>
     <t xml:space="preserve">9.89309978485107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76692962646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72982311248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99700260162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95247173309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0563764572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64818382263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95989418029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8263053894043</t>
+    <t xml:space="preserve">9.76693058013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72982120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99700355529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95247268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.05637550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64818286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95989322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82630348205566</t>
   </si>
   <si>
     <t xml:space="preserve">9.81146049499512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75208759307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85599040985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86341190338135</t>
+    <t xml:space="preserve">9.7520866394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85599136352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86341381072998</t>
   </si>
   <si>
     <t xml:space="preserve">10.0415325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0118455886841</t>
+    <t xml:space="preserve">10.0118465423584</t>
   </si>
   <si>
     <t xml:space="preserve">9.9450511932373</t>
@@ -968,22 +968,22 @@
     <t xml:space="preserve">8.8317985534668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97088289260864</t>
+    <t xml:space="preserve">7.97088432312012</t>
   </si>
   <si>
     <t xml:space="preserve">8.25290775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16384696960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19353485107422</t>
+    <t xml:space="preserve">8.16384792327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1935338973999</t>
   </si>
   <si>
     <t xml:space="preserve">8.67594337463379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50524520874023</t>
+    <t xml:space="preserve">8.50524425506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.02283573150635</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">8.0673656463623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98572826385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7853422164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76307725906372</t>
+    <t xml:space="preserve">7.98572874069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78534078598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76307678222656</t>
   </si>
   <si>
     <t xml:space="preserve">7.7037034034729</t>
@@ -1007,13 +1007,13 @@
     <t xml:space="preserve">7.82987213134766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64433002471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7259693145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04510021209717</t>
+    <t xml:space="preserve">7.6443305015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72596836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04510116577148</t>
   </si>
   <si>
     <t xml:space="preserve">8.14158344268799</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">7.91893291473389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08963203430176</t>
+    <t xml:space="preserve">8.08962917327881</t>
   </si>
   <si>
     <t xml:space="preserve">8.11931705474854</t>
@@ -1031,22 +1031,22 @@
     <t xml:space="preserve">8.11189651489258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09705352783203</t>
+    <t xml:space="preserve">8.0970516204834</t>
   </si>
   <si>
     <t xml:space="preserve">8.00057125091553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13416004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28259468078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20837783813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34196758270264</t>
+    <t xml:space="preserve">8.13416194915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28259563446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20837879180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34196853637695</t>
   </si>
   <si>
     <t xml:space="preserve">8.44587230682373</t>
@@ -1061,34 +1061,34 @@
     <t xml:space="preserve">8.32712459564209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26775074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71854639053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03025817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01541328430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10447311401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17869186401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22322177886963</t>
+    <t xml:space="preserve">8.26775169372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71854686737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0302562713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01541423797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1044750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17869091033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22322082519531</t>
   </si>
   <si>
     <t xml:space="preserve">8.40134143829346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05445003509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93570137023926</t>
+    <t xml:space="preserve">9.05444812774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93570232391357</t>
   </si>
   <si>
     <t xml:space="preserve">8.72789573669434</t>
@@ -1097,19 +1097,19 @@
     <t xml:space="preserve">8.89117240905762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00991916656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27710056304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30678653717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24741268157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35131740570068</t>
+    <t xml:space="preserve">9.00992012023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.277099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30678749084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24741363525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35131645202637</t>
   </si>
   <si>
     <t xml:space="preserve">9.52943706512451</t>
@@ -1121,40 +1121,40 @@
     <t xml:space="preserve">9.39584636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54427909851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87083339691162</t>
+    <t xml:space="preserve">9.54428005218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87083435058594</t>
   </si>
   <si>
     <t xml:space="preserve">9.60365295410156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0637979507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87998390197754</t>
+    <t xml:space="preserve">10.0637989044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87998294830322</t>
   </si>
   <si>
     <t xml:space="preserve">9.54299259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55831050872803</t>
+    <t xml:space="preserve">9.55830955505371</t>
   </si>
   <si>
     <t xml:space="preserve">9.72680473327637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60426330566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46640300750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57362842559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6195821762085</t>
+    <t xml:space="preserve">9.60426425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46640396118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57362747192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61958122253418</t>
   </si>
   <si>
     <t xml:space="preserve">9.6348991394043</t>
@@ -1163,58 +1163,58 @@
     <t xml:space="preserve">9.68085289001465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48172092437744</t>
+    <t xml:space="preserve">9.48172187805176</t>
   </si>
   <si>
     <t xml:space="preserve">9.43576717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3438606262207</t>
+    <t xml:space="preserve">9.34385967254639</t>
   </si>
   <si>
     <t xml:space="preserve">9.31322479248047</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08345890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59328746795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53201675415039</t>
+    <t xml:space="preserve">9.08345794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59328842163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53201770782471</t>
   </si>
   <si>
     <t xml:space="preserve">8.89964389801025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96091461181641</t>
+    <t xml:space="preserve">8.96091556549072</t>
   </si>
   <si>
     <t xml:space="preserve">9.28258895874023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20600032806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49703884124756</t>
+    <t xml:space="preserve">9.20600128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49703788757324</t>
   </si>
   <si>
     <t xml:space="preserve">9.51235675811768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52767276763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38981437683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35917854309082</t>
+    <t xml:space="preserve">9.52767467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38981533050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35917949676514</t>
   </si>
   <si>
     <t xml:space="preserve">9.19068241119385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86466598510742</t>
+    <t xml:space="preserve">9.86466693878174</t>
   </si>
   <si>
     <t xml:space="preserve">9.58894538879395</t>
@@ -1223,19 +1223,19 @@
     <t xml:space="preserve">9.32854270935059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42044830322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22131729125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25195503234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11409282684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14472961425781</t>
+    <t xml:space="preserve">9.42045021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22131824493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11409378051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1447286605835</t>
   </si>
   <si>
     <t xml:space="preserve">9.26727104187012</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">9.45108604431152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69617080688477</t>
+    <t xml:space="preserve">9.69616985321045</t>
   </si>
   <si>
     <t xml:space="preserve">9.65021705627441</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">9.02218627929688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91496181488037</t>
+    <t xml:space="preserve">8.91496276855469</t>
   </si>
   <si>
     <t xml:space="preserve">8.94559860229492</t>
@@ -1292,91 +1292,91 @@
     <t xml:space="preserve">9.97189140319824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78807640075684</t>
+    <t xml:space="preserve">9.78807735443115</t>
   </si>
   <si>
     <t xml:space="preserve">9.75744152069092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09877586364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86900901794434</t>
+    <t xml:space="preserve">9.09877681732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86900997161865</t>
   </si>
   <si>
     <t xml:space="preserve">8.74646663665771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73114776611328</t>
+    <t xml:space="preserve">8.7311487197876</t>
   </si>
   <si>
     <t xml:space="preserve">8.51669883728027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47074604034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42479133605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01121234893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22566032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36352062225342</t>
+    <t xml:space="preserve">8.47074699401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42479228973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01121139526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.225661277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36352157592773</t>
   </si>
   <si>
     <t xml:space="preserve">8.65456008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77710247039795</t>
+    <t xml:space="preserve">8.77710151672363</t>
   </si>
   <si>
     <t xml:space="preserve">8.8383731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9302806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62392330169678</t>
+    <t xml:space="preserve">8.93027973175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62392425537109</t>
   </si>
   <si>
     <t xml:space="preserve">8.7158317565918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50138092041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82305526733398</t>
+    <t xml:space="preserve">8.50138187408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82305431365967</t>
   </si>
   <si>
     <t xml:space="preserve">8.60860633850098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57796955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34820365905762</t>
+    <t xml:space="preserve">8.57797050476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34820175170898</t>
   </si>
   <si>
     <t xml:space="preserve">8.30224990844727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33288669586182</t>
+    <t xml:space="preserve">8.3328857421875</t>
   </si>
   <si>
     <t xml:space="preserve">8.37883853912354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28693294525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27161312103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39415645599365</t>
+    <t xml:space="preserve">8.28693103790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27161407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39415740966797</t>
   </si>
   <si>
     <t xml:space="preserve">8.13375473022461</t>
@@ -1385,37 +1385,37 @@
     <t xml:space="preserve">8.11843681335449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45542907714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79241943359375</t>
+    <t xml:space="preserve">8.4554271697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79242038726807</t>
   </si>
   <si>
     <t xml:space="preserve">8.85369110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70051288604736</t>
+    <t xml:space="preserve">8.70051193237305</t>
   </si>
   <si>
     <t xml:space="preserve">8.66987705230713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68519592285156</t>
+    <t xml:space="preserve">8.68519496917725</t>
   </si>
   <si>
     <t xml:space="preserve">8.54733562469482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44011116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88432788848877</t>
+    <t xml:space="preserve">8.440110206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88432502746582</t>
   </si>
   <si>
     <t xml:space="preserve">9.40513229370117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92593669891357</t>
+    <t xml:space="preserve">9.92593765258789</t>
   </si>
   <si>
     <t xml:space="preserve">9.80339431762695</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">9.22897624969482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07579898834229</t>
+    <t xml:space="preserve">9.0757999420166</t>
   </si>
   <si>
     <t xml:space="preserve">9.15238761901855</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">8.79757022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87754917144775</t>
+    <t xml:space="preserve">8.87755012512207</t>
   </si>
   <si>
     <t xml:space="preserve">8.83755970001221</t>
@@ -1457,19 +1457,19 @@
     <t xml:space="preserve">9.23744964599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27743911743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47738265991211</t>
+    <t xml:space="preserve">9.27743816375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47738361358643</t>
   </si>
   <si>
     <t xml:space="preserve">9.3574161529541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51737117767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67732715606689</t>
+    <t xml:space="preserve">9.51737213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67732810974121</t>
   </si>
   <si>
     <t xml:space="preserve">9.63733863830566</t>
@@ -1478,55 +1478,55 @@
     <t xml:space="preserve">9.39740562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19746017456055</t>
+    <t xml:space="preserve">9.19746112823486</t>
   </si>
   <si>
     <t xml:space="preserve">9.07749462127686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43739604949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55736064910889</t>
+    <t xml:space="preserve">9.4373950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5573616027832</t>
   </si>
   <si>
     <t xml:space="preserve">9.11748218536377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71759223937988</t>
+    <t xml:space="preserve">8.71759128570557</t>
   </si>
   <si>
     <t xml:space="preserve">8.95752620697021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99751567840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15747261047363</t>
+    <t xml:space="preserve">8.99751472473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15747165679932</t>
   </si>
   <si>
     <t xml:space="preserve">8.91753768920898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7970190048218</t>
+    <t xml:space="preserve">10.7970199584961</t>
   </si>
   <si>
     <t xml:space="preserve">10.3571405410767</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772190093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3171510696411</t>
+    <t xml:space="preserve">10.0772171020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3171501159668</t>
   </si>
   <si>
     <t xml:space="preserve">10.1172065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91726207733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99724006652832</t>
+    <t xml:space="preserve">9.91726112365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.997239112854</t>
   </si>
   <si>
     <t xml:space="preserve">10.0372295379639</t>
@@ -1535,13 +1535,13 @@
     <t xml:space="preserve">9.75730609893799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71731758117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79729461669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83728408813477</t>
+    <t xml:space="preserve">9.71731853485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79729557037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83728504180908</t>
   </si>
   <si>
     <t xml:space="preserve">10.1571950912476</t>
@@ -1553,28 +1553,28 @@
     <t xml:space="preserve">10.2371730804443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3971300125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5570840835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4771070480347</t>
+    <t xml:space="preserve">10.3971290588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5570859909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.477108001709</t>
   </si>
   <si>
     <t xml:space="preserve">10.1971845626831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170946121216</t>
+    <t xml:space="preserve">10.5170965194702</t>
   </si>
   <si>
     <t xml:space="preserve">10.9969635009766</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1169300079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.316876411438</t>
+    <t xml:space="preserve">11.1169309616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3168745040894</t>
   </si>
   <si>
     <t xml:space="preserve">11.2368974685669</t>
@@ -1583,31 +1583,31 @@
     <t xml:space="preserve">11.3568639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969079971313</t>
+    <t xml:space="preserve">11.196907043457</t>
   </si>
   <si>
     <t xml:space="preserve">10.837007522583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1569194793701</t>
+    <t xml:space="preserve">11.1569185256958</t>
   </si>
   <si>
     <t xml:space="preserve">11.0369529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8769979476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9169855117798</t>
+    <t xml:space="preserve">10.8769969940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9169845581055</t>
   </si>
   <si>
     <t xml:space="preserve">10.9569749832153</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7570304870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.597074508667</t>
+    <t xml:space="preserve">10.7570295333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5970735549927</t>
   </si>
   <si>
     <t xml:space="preserve">10.4371185302734</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">11.2768859863281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.436842918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5568075180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.676775932312</t>
+    <t xml:space="preserve">11.4368419647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5568084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6767768859863</t>
   </si>
   <si>
     <t xml:space="preserve">10.717041015625</t>
@@ -1631,19 +1631,19 @@
     <t xml:space="preserve">8.11775875091553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1660213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88582181930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46993732452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03805780410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91009187698364</t>
+    <t xml:space="preserve">7.16602230072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88582277297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46993780136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03805637359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9100923538208</t>
   </si>
   <si>
     <t xml:space="preserve">6.39823341369629</t>
@@ -1652,22 +1652,22 @@
     <t xml:space="preserve">6.20628690719604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99834394454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55818939208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30998182296753</t>
+    <t xml:space="preserve">5.9983434677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55818891525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30998134613037</t>
   </si>
   <si>
     <t xml:space="preserve">7.40595531463623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32597780227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11803483963013</t>
+    <t xml:space="preserve">7.32597732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11803436279297</t>
   </si>
   <si>
     <t xml:space="preserve">6.73414087295532</t>
@@ -1676,10 +1676,10 @@
     <t xml:space="preserve">6.9740743637085</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29398584365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15002584457397</t>
+    <t xml:space="preserve">7.29398536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15002489089966</t>
   </si>
   <si>
     <t xml:space="preserve">6.86210489273071</t>
@@ -1688,10 +1688,10 @@
     <t xml:space="preserve">6.8141188621521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76613140106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94208383560181</t>
+    <t xml:space="preserve">6.76613235473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94208288192749</t>
   </si>
   <si>
     <t xml:space="preserve">6.79812288284302</t>
@@ -1703,13 +1703,13 @@
     <t xml:space="preserve">6.78212738037109</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83011436462402</t>
+    <t xml:space="preserve">6.83011388778687</t>
   </si>
   <si>
     <t xml:space="preserve">6.92877960205078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01067972183228</t>
+    <t xml:space="preserve">7.01068019866943</t>
   </si>
   <si>
     <t xml:space="preserve">6.89601898193359</t>
@@ -1724,19 +1724,19 @@
     <t xml:space="preserve">6.74859762191772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05981922149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12533950805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2236213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55122327804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56760215759277</t>
+    <t xml:space="preserve">7.05981969833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1253399848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22362089157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55122232437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56760311126709</t>
   </si>
   <si>
     <t xml:space="preserve">8.0262451171875</t>
@@ -1748,22 +1748,22 @@
     <t xml:space="preserve">8.39479732513428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72239875793457</t>
+    <t xml:space="preserve">8.72239971160889</t>
   </si>
   <si>
     <t xml:space="preserve">8.76334953308105</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88619899749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17285060882568</t>
+    <t xml:space="preserve">8.88619995117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1728515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.41855335235596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92715072631836</t>
+    <t xml:space="preserve">8.92714977264404</t>
   </si>
   <si>
     <t xml:space="preserve">9.13190174102783</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">9.09095191955566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21380233764648</t>
+    <t xml:space="preserve">9.21380138397217</t>
   </si>
   <si>
     <t xml:space="preserve">9.25475311279297</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">9.00904941558838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64049911499023</t>
+    <t xml:space="preserve">8.64050006866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.09176635742188</t>
@@ -1802,22 +1802,22 @@
     <t xml:space="preserve">8.1900463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10814666748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15728664398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9607253074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87882518768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7150239944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78054332733154</t>
+    <t xml:space="preserve">8.10814571380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15728569030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96072483062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87882423400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71502304077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78054428100586</t>
   </si>
   <si>
     <t xml:space="preserve">7.58398294448853</t>
@@ -1826,16 +1826,16 @@
     <t xml:space="preserve">7.51846265792847</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5348424911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33828115463257</t>
+    <t xml:space="preserve">7.53484344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33828210830688</t>
   </si>
   <si>
     <t xml:space="preserve">7.48570203781128</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6167426109314</t>
+    <t xml:space="preserve">7.61674356460571</t>
   </si>
   <si>
     <t xml:space="preserve">7.69864320755005</t>
@@ -1844,13 +1844,13 @@
     <t xml:space="preserve">7.76416349411011</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73140287399292</t>
+    <t xml:space="preserve">7.73140382766724</t>
   </si>
   <si>
     <t xml:space="preserve">7.79692363739014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66588401794434</t>
+    <t xml:space="preserve">7.66588306427002</t>
   </si>
   <si>
     <t xml:space="preserve">7.63312196731567</t>
@@ -1868,22 +1868,22 @@
     <t xml:space="preserve">7.74778413772583</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43656253814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60036373138428</t>
+    <t xml:space="preserve">7.43656206130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60036277770996</t>
   </si>
   <si>
     <t xml:space="preserve">7.354660987854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40380144119263</t>
+    <t xml:space="preserve">7.40380096435547</t>
   </si>
   <si>
     <t xml:space="preserve">7.24000072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1908597946167</t>
+    <t xml:space="preserve">7.19086027145386</t>
   </si>
   <si>
     <t xml:space="preserve">6.79773855209351</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">6.68307733535767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5684175491333</t>
+    <t xml:space="preserve">6.56841707229614</t>
   </si>
   <si>
     <t xml:space="preserve">6.3882360458374</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">6.22443532943726</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48651695251465</t>
+    <t xml:space="preserve">6.48651647567749</t>
   </si>
   <si>
     <t xml:space="preserve">6.42099666595459</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">8.5176477432251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27194690704346</t>
+    <t xml:space="preserve">8.27194595336914</t>
   </si>
   <si>
     <t xml:space="preserve">7.97710418701172</t>
@@ -1931,16 +1931,16 @@
     <t xml:space="preserve">7.84606409072876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12452507019043</t>
+    <t xml:space="preserve">8.12452602386475</t>
   </si>
   <si>
     <t xml:space="preserve">8.59954929351807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43574810028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55859756469727</t>
+    <t xml:space="preserve">8.43574714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55859851837158</t>
   </si>
   <si>
     <t xml:space="preserve">8.6814489364624</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">8.04262638092041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94434404373169</t>
+    <t xml:space="preserve">7.94434499740601</t>
   </si>
   <si>
     <t xml:space="preserve">7.86244440078735</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">9.90995693206787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1556577682495</t>
+    <t xml:space="preserve">10.1556568145752</t>
   </si>
   <si>
     <t xml:space="preserve">9.86900520324707</t>
@@ -1988,10 +1988,10 @@
     <t xml:space="preserve">9.50045299530029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37760353088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58235359191895</t>
+    <t xml:space="preserve">9.37760257720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58235454559326</t>
   </si>
   <si>
     <t xml:space="preserve">9.70520496368408</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">9.54140281677246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22513580322266</t>
+    <t xml:space="preserve">9.22513484954834</t>
   </si>
   <si>
     <t xml:space="preserve">9.18320178985596</t>
@@ -2030,10 +2030,10 @@
     <t xml:space="preserve">9.35093212127686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64446067810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51866149902344</t>
+    <t xml:space="preserve">9.64445972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51866245269775</t>
   </si>
   <si>
     <t xml:space="preserve">9.47672939300537</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">9.6025276184082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72832489013672</t>
+    <t xml:space="preserve">9.72832584381104</t>
   </si>
   <si>
     <t xml:space="preserve">10.3153781890869</t>
@@ -2060,19 +2060,19 @@
     <t xml:space="preserve">10.1057167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.357310295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2734451293945</t>
+    <t xml:space="preserve">10.3573112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2734460830688</t>
   </si>
   <si>
     <t xml:space="preserve">10.1476488113403</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0218515396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85412216186523</t>
+    <t xml:space="preserve">10.0218505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85412120819092</t>
   </si>
   <si>
     <t xml:space="preserve">9.81218910217285</t>
@@ -2096,10 +2096,10 @@
     <t xml:space="preserve">8.97354030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3992433547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5669727325439</t>
+    <t xml:space="preserve">10.399242401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5669736862183</t>
   </si>
   <si>
     <t xml:space="preserve">10.7766351699829</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">10.9443655014038</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2378921508789</t>
+    <t xml:space="preserve">11.2378911972046</t>
   </si>
   <si>
     <t xml:space="preserve">11.1959600448608</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4056215286255</t>
+    <t xml:space="preserve">11.4056224822998</t>
   </si>
   <si>
     <t xml:space="preserve">11.1540279388428</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">12.0346088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6152839660645</t>
+    <t xml:space="preserve">11.6152830123901</t>
   </si>
   <si>
     <t xml:space="preserve">11.6572160720825</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1120939254761</t>
+    <t xml:space="preserve">11.1120948791504</t>
   </si>
   <si>
     <t xml:space="preserve">10.9862976074219</t>
@@ -2153,16 +2153,16 @@
     <t xml:space="preserve">11.070161819458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4894857406616</t>
+    <t xml:space="preserve">11.4894866943359</t>
   </si>
   <si>
     <t xml:space="preserve">11.3636894226074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6991491317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5733518600464</t>
+    <t xml:space="preserve">11.6991481781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5733509063721</t>
   </si>
   <si>
     <t xml:space="preserve">11.5314178466797</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">11.0282297134399</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4831075668335</t>
+    <t xml:space="preserve">10.4831085205078</t>
   </si>
   <si>
     <t xml:space="preserve">10.5250406265259</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">10.608904838562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8185682296753</t>
+    <t xml:space="preserve">10.818567276001</t>
   </si>
   <si>
     <t xml:space="preserve">10.9024324417114</t>
@@ -2189,13 +2189,13 @@
     <t xml:space="preserve">11.4475536346436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1378631591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0948600769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3958826065063</t>
+    <t xml:space="preserve">11.1378622055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.09485912323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3958835601807</t>
   </si>
   <si>
     <t xml:space="preserve">11.6539030075073</t>
@@ -2207,13 +2207,13 @@
     <t xml:space="preserve">11.6108989715576</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6969060897827</t>
+    <t xml:space="preserve">11.696907043457</t>
   </si>
   <si>
     <t xml:space="preserve">11.4388866424561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5248928070068</t>
+    <t xml:space="preserve">11.5248918533325</t>
   </si>
   <si>
     <t xml:space="preserve">11.5678958892822</t>
@@ -2231,19 +2231,19 @@
     <t xml:space="preserve">11.0088529586792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8368396759033</t>
+    <t xml:space="preserve">10.8368406295776</t>
   </si>
   <si>
     <t xml:space="preserve">10.9658489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7508325576782</t>
+    <t xml:space="preserve">10.7508335113525</t>
   </si>
   <si>
     <t xml:space="preserve">10.8798427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6648263931274</t>
+    <t xml:space="preserve">10.6648254394531</t>
   </si>
   <si>
     <t xml:space="preserve">10.9228458404541</t>
@@ -2261,37 +2261,37 @@
     <t xml:space="preserve">10.1487865447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97677326202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89076709747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76175594329834</t>
+    <t xml:space="preserve">9.97677421569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89076614379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76175689697266</t>
   </si>
   <si>
     <t xml:space="preserve">9.84776306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46073341369629</t>
+    <t xml:space="preserve">9.46073246002197</t>
   </si>
   <si>
     <t xml:space="preserve">9.54673957824707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24571704864502</t>
+    <t xml:space="preserve">9.2457160949707</t>
   </si>
   <si>
     <t xml:space="preserve">9.20271301269531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03069972991943</t>
+    <t xml:space="preserve">9.03070068359375</t>
   </si>
   <si>
     <t xml:space="preserve">9.15970993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2777967453003</t>
+    <t xml:space="preserve">10.277795791626</t>
   </si>
   <si>
     <t xml:space="preserve">9.67574977874756</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">9.63274574279785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6218223571777</t>
+    <t xml:space="preserve">10.6218233108521</t>
   </si>
   <si>
     <t xml:space="preserve">11.3098764419556</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">11.4818897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1699419021606</t>
+    <t xml:space="preserve">12.169942855835</t>
   </si>
   <si>
     <t xml:space="preserve">11.9549255371094</t>
@@ -2360,22 +2360,22 @@
     <t xml:space="preserve">12.0409326553345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8689203262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7829122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9979295730591</t>
+    <t xml:space="preserve">11.8689193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7829132080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9979286193848</t>
   </si>
   <si>
     <t xml:space="preserve">12.3419570922852</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4709663391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2989540100098</t>
+    <t xml:space="preserve">12.4709672927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2989530563354</t>
   </si>
   <si>
     <t xml:space="preserve">12.513970375061</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">12.5569734573364</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6429786682129</t>
+    <t xml:space="preserve">12.6429796218872</t>
   </si>
   <si>
     <t xml:space="preserve">12.2559499740601</t>
@@ -2396,22 +2396,22 @@
     <t xml:space="preserve">12.5999755859375</t>
   </si>
   <si>
+    <t xml:space="preserve">12.6859817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7719888687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.728985786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9997711181641</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.6859827041626</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7719898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7289867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9997701644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6859817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8204641342163</t>
+    <t xml:space="preserve">12.820463180542</t>
   </si>
   <si>
     <t xml:space="preserve">12.9549436569214</t>
@@ -2423,28 +2423,28 @@
     <t xml:space="preserve">13.4480381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0894241333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2239046096802</t>
+    <t xml:space="preserve">13.0894250869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2239036560059</t>
   </si>
   <si>
     <t xml:space="preserve">13.3583841323853</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1342496871948</t>
+    <t xml:space="preserve">13.1342506408691</t>
   </si>
   <si>
     <t xml:space="preserve">13.0445976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1790771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3135585784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2687320709229</t>
+    <t xml:space="preserve">13.1790781021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3135576248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2687311172485</t>
   </si>
   <si>
     <t xml:space="preserve">12.8652906417847</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">13.7618265151978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7928419113159</t>
+    <t xml:space="preserve">14.7928428649902</t>
   </si>
   <si>
     <t xml:space="preserve">14.1652669906616</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">13.8963060379028</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4032115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5825176239014</t>
+    <t xml:space="preserve">13.4032106399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5825185775757</t>
   </si>
   <si>
     <t xml:space="preserve">13.492865562439</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">13.6721725463867</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9411325454712</t>
+    <t xml:space="preserve">13.9411334991455</t>
   </si>
   <si>
     <t xml:space="preserve">13.7169990539551</t>
@@ -2495,22 +2495,22 @@
     <t xml:space="preserve">14.3445739746094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9859600067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5238828659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.299747467041</t>
+    <t xml:space="preserve">13.9859609603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5238819122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2997465133667</t>
   </si>
   <si>
     <t xml:space="preserve">14.4342279434204</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2100944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3893995285034</t>
+    <t xml:space="preserve">14.21009349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3894004821777</t>
   </si>
   <si>
     <t xml:space="preserve">14.6135339736938</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">15.0169763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1962842941284</t>
+    <t xml:space="preserve">15.1962833404541</t>
   </si>
   <si>
     <t xml:space="preserve">15.3307638168335</t>
@@ -2546,145 +2546,148 @@
     <t xml:space="preserve">15.4204187393188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3755912780762</t>
+    <t xml:space="preserve">15.3755893707275</t>
   </si>
   <si>
     <t xml:space="preserve">14.8376684188843</t>
   </si>
   <si>
-    <t xml:space="preserve">14.882495880127</t>
+    <t xml:space="preserve">14.8824968338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1514558792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7790327072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0341815948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4514331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5859146118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8686857223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0479907989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7342052459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9583387374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1376457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8100471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7203941345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4066066741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2721271514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0928211212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9135131835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4652442932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1066293716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5687084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7031879425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0618019104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2411098480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2859363555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5997247695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.644552230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8238582611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.689377784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5100698471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5548973083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3385105133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5723295211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5255670547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.291748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7126207351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6190948486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4320392608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4788017272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3852758407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9932041168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.899676322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.852912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8061485290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6658573150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0579290390015</t>
   </si>
   <si>
     <t xml:space="preserve">15.1514568328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.77903175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0341815948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4514331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5859146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8686866760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0479907989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7342042922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9583377838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1376457214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8100490570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7203941345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4066066741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2721252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0928211212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9135122299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4652442932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1066293716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5687084197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7031879425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0618019104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2411098480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2859363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5997247695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.644552230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8238592147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.689377784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5100698471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5548973083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3385105133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5723295211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5255670547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.291748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7126207351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6190948486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4320392608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4788017272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3852758407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9932041168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.899676322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.852912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8061485290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6658573150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0579290390015</t>
   </si>
   <si>
     <t xml:space="preserve">15.1982202529907</t>
@@ -59314,7 +59317,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2153" t="s">
-        <v>847</v>
+        <v>891</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59340,7 +59343,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2154" t="s">
-        <v>847</v>
+        <v>891</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59366,7 +59369,7 @@
         <v>16.25</v>
       </c>
       <c r="G2155" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59418,7 +59421,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2157" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59444,7 +59447,7 @@
         <v>15</v>
       </c>
       <c r="G2158" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59470,7 +59473,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2159" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59496,7 +59499,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2160" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59522,7 +59525,7 @@
         <v>15.25</v>
       </c>
       <c r="G2161" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59548,7 +59551,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2162" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59574,7 +59577,7 @@
         <v>15.25</v>
       </c>
       <c r="G2163" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59600,7 +59603,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2164" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59652,7 +59655,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2166" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59678,7 +59681,7 @@
         <v>16.25</v>
       </c>
       <c r="G2167" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59730,7 +59733,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2169" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59756,7 +59759,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2170" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59808,7 +59811,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59834,7 +59837,7 @@
         <v>16</v>
       </c>
       <c r="G2173" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59886,7 +59889,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2175" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59912,7 +59915,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2176" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59938,7 +59941,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2177" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59964,7 +59967,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2178" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59990,7 +59993,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2179" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60016,7 +60019,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60042,7 +60045,7 @@
         <v>15.25</v>
       </c>
       <c r="G2181" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60068,7 +60071,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60094,7 +60097,7 @@
         <v>15.25</v>
       </c>
       <c r="G2183" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60120,7 +60123,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2184" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60146,7 +60149,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2185" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60172,7 +60175,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2186" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60198,7 +60201,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60224,7 +60227,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2188" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60250,7 +60253,7 @@
         <v>15</v>
       </c>
       <c r="G2189" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60276,7 +60279,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2190" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60302,7 +60305,7 @@
         <v>15</v>
       </c>
       <c r="G2191" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60328,7 +60331,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2192" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60354,7 +60357,7 @@
         <v>15</v>
       </c>
       <c r="G2193" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60380,7 +60383,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2194" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60406,7 +60409,7 @@
         <v>15</v>
       </c>
       <c r="G2195" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60432,7 +60435,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2196" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60458,7 +60461,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2197" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60484,7 +60487,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60510,7 +60513,7 @@
         <v>15</v>
       </c>
       <c r="G2199" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60536,7 +60539,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G2200" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60562,7 +60565,7 @@
         <v>15</v>
       </c>
       <c r="G2201" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60588,7 +60591,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60614,7 +60617,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2203" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60640,7 +60643,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2204" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60666,7 +60669,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60692,7 +60695,7 @@
         <v>14.5</v>
       </c>
       <c r="G2206" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60718,7 +60721,7 @@
         <v>14.5</v>
       </c>
       <c r="G2207" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60744,7 +60747,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60770,7 +60773,7 @@
         <v>14.5</v>
       </c>
       <c r="G2209" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60796,7 +60799,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60822,7 +60825,7 @@
         <v>14.5</v>
       </c>
       <c r="G2211" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60848,7 +60851,7 @@
         <v>14.5</v>
       </c>
       <c r="G2212" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60874,7 +60877,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60900,7 +60903,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2214" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60926,7 +60929,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2215" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60952,7 +60955,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2216" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60978,7 +60981,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2217" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61004,7 +61007,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2218" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61030,7 +61033,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2219" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61056,7 +61059,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2220" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61082,7 +61085,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2221" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61108,7 +61111,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2222" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61134,7 +61137,7 @@
         <v>15</v>
       </c>
       <c r="G2223" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61160,7 +61163,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61186,7 +61189,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2225" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61212,7 +61215,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2226" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61238,7 +61241,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2227" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61264,7 +61267,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61290,7 +61293,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2229" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61316,7 +61319,7 @@
         <v>15.25</v>
       </c>
       <c r="G2230" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61342,7 +61345,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2231" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61368,7 +61371,7 @@
         <v>15.5</v>
       </c>
       <c r="G2232" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61394,7 +61397,7 @@
         <v>15.5</v>
       </c>
       <c r="G2233" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61420,7 +61423,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2234" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61446,7 +61449,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2235" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61472,7 +61475,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2236" t="s">
-        <v>847</v>
+        <v>891</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61498,7 +61501,7 @@
         <v>16</v>
       </c>
       <c r="G2237" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61524,7 +61527,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2238" t="s">
-        <v>847</v>
+        <v>891</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61550,7 +61553,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2239" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61576,7 +61579,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2240" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61680,7 +61683,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2244" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61706,7 +61709,7 @@
         <v>17.25</v>
       </c>
       <c r="G2245" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61758,7 +61761,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2247" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61836,7 +61839,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2250" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61862,7 +61865,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61888,7 +61891,7 @@
         <v>17.25</v>
       </c>
       <c r="G2252" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61914,7 +61917,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2253" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61940,7 +61943,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2254" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61966,7 +61969,7 @@
         <v>17.75</v>
       </c>
       <c r="G2255" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61992,7 +61995,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G2256" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62018,7 +62021,7 @@
         <v>18</v>
       </c>
       <c r="G2257" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62122,7 +62125,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2261" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62278,7 +62281,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2267" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62304,7 +62307,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2268" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62330,7 +62333,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2269" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62356,7 +62359,7 @@
         <v>15.5</v>
       </c>
       <c r="G2270" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62616,7 +62619,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2280" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62642,7 +62645,7 @@
         <v>16</v>
       </c>
       <c r="G2281" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62668,7 +62671,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62694,7 +62697,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2283" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62720,7 +62723,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2284" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62746,7 +62749,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2285" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62772,7 +62775,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62876,7 +62879,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62980,7 +62983,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2294" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63032,7 +63035,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2296" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63058,7 +63061,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2297" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63084,7 +63087,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2298" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63110,7 +63113,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63136,7 +63139,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63162,7 +63165,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63188,7 +63191,7 @@
         <v>16</v>
       </c>
       <c r="G2302" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63214,7 +63217,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2303" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63240,7 +63243,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2304" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63266,7 +63269,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63292,7 +63295,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2306" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63318,7 +63321,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2307" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63344,7 +63347,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2308" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63370,7 +63373,7 @@
         <v>15.75</v>
       </c>
       <c r="G2309" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63396,7 +63399,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2310" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63422,7 +63425,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2311" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63448,7 +63451,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63474,7 +63477,7 @@
         <v>16</v>
       </c>
       <c r="G2313" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63500,7 +63503,7 @@
         <v>16</v>
       </c>
       <c r="G2314" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63526,7 +63529,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2315" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63552,7 +63555,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2316" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63604,7 +63607,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>847</v>
+        <v>891</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63630,7 +63633,7 @@
         <v>16</v>
       </c>
       <c r="G2319" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63656,7 +63659,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2320" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63682,7 +63685,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2321" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63708,7 +63711,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2322" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63734,7 +63737,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2323" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63760,7 +63763,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2324" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63786,7 +63789,7 @@
         <v>16</v>
       </c>
       <c r="G2325" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63812,7 +63815,7 @@
         <v>16</v>
       </c>
       <c r="G2326" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63838,7 +63841,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2327" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63864,7 +63867,7 @@
         <v>16</v>
       </c>
       <c r="G2328" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63890,7 +63893,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2329" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63916,7 +63919,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2330" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63942,7 +63945,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2331" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63968,7 +63971,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63994,7 +63997,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64020,7 +64023,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2334" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64046,7 +64049,7 @@
         <v>15.75</v>
       </c>
       <c r="G2335" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64072,7 +64075,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2336" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64098,7 +64101,7 @@
         <v>15.75</v>
       </c>
       <c r="G2337" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64124,7 +64127,7 @@
         <v>15.25</v>
       </c>
       <c r="G2338" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64150,7 +64153,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2339" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64176,7 +64179,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2340" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64202,7 +64205,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2341" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64228,7 +64231,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64254,7 +64257,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64280,7 +64283,7 @@
         <v>15.5</v>
       </c>
       <c r="G2344" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64306,7 +64309,7 @@
         <v>15.5</v>
       </c>
       <c r="G2345" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64332,7 +64335,7 @@
         <v>15</v>
       </c>
       <c r="G2346" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64358,7 +64361,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64384,7 +64387,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64410,7 +64413,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2349" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64462,7 +64465,7 @@
         <v>16</v>
       </c>
       <c r="G2351" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64488,7 +64491,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64514,7 +64517,7 @@
         <v>15.75</v>
       </c>
       <c r="G2353" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64540,7 +64543,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64566,7 +64569,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2355" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64592,7 +64595,7 @@
         <v>15.25</v>
       </c>
       <c r="G2356" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64618,7 +64621,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2357" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64644,7 +64647,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64670,7 +64673,7 @@
         <v>14</v>
       </c>
       <c r="G2359" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64696,7 +64699,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2360" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64722,7 +64725,7 @@
         <v>15</v>
       </c>
       <c r="G2361" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64748,7 +64751,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2362" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64774,7 +64777,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2363" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64800,7 +64803,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2364" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64826,7 +64829,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64852,7 +64855,7 @@
         <v>14.5</v>
       </c>
       <c r="G2366" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64878,7 +64881,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2367" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64904,7 +64907,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2368" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64930,7 +64933,7 @@
         <v>15</v>
       </c>
       <c r="G2369" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64956,7 +64959,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2370" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64982,7 +64985,7 @@
         <v>15.25</v>
       </c>
       <c r="G2371" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65008,7 +65011,7 @@
         <v>15.25</v>
       </c>
       <c r="G2372" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65034,7 +65037,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2373" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65060,7 +65063,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2374" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65086,7 +65089,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2375" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65112,7 +65115,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2376" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65138,7 +65141,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65164,7 +65167,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2378" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65190,7 +65193,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2379" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65216,7 +65219,7 @@
         <v>15.25</v>
       </c>
       <c r="G2380" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65242,7 +65245,7 @@
         <v>15.25</v>
       </c>
       <c r="G2381" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65268,7 +65271,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2382" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65294,7 +65297,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2383" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65320,7 +65323,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65346,7 +65349,7 @@
         <v>16</v>
       </c>
       <c r="G2385" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65372,7 +65375,7 @@
         <v>16.25</v>
       </c>
       <c r="G2386" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65398,7 +65401,7 @@
         <v>16</v>
       </c>
       <c r="G2387" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65424,7 +65427,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2388" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65450,7 +65453,7 @@
         <v>16.5</v>
       </c>
       <c r="G2389" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65476,7 +65479,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2390" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65502,7 +65505,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2391" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65528,7 +65531,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2392" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65554,7 +65557,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2393" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65580,7 +65583,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2394" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65606,7 +65609,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2395" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65632,7 +65635,7 @@
         <v>16.75</v>
       </c>
       <c r="G2396" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65658,7 +65661,7 @@
         <v>16.5</v>
       </c>
       <c r="G2397" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65684,7 +65687,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2398" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65710,7 +65713,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2399" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65736,7 +65739,7 @@
         <v>16.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65762,7 +65765,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65788,7 +65791,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2402" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65814,7 +65817,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65840,7 +65843,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2404" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65866,7 +65869,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2405" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65892,7 +65895,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2406" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65918,7 +65921,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2407" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65944,7 +65947,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2408" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65970,7 +65973,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G2409" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65996,7 +65999,7 @@
         <v>16</v>
       </c>
       <c r="G2410" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66022,7 +66025,7 @@
         <v>15.75</v>
       </c>
       <c r="G2411" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66048,7 +66051,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2412" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66074,7 +66077,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2413" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66100,7 +66103,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2414" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66126,7 +66129,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2415" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66152,7 +66155,7 @@
         <v>16.25</v>
       </c>
       <c r="G2416" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66178,7 +66181,7 @@
         <v>16.75</v>
       </c>
       <c r="G2417" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66204,7 +66207,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2418" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66230,7 +66233,7 @@
         <v>16.25</v>
       </c>
       <c r="G2419" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66256,7 +66259,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2420" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66282,7 +66285,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2421" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66308,7 +66311,7 @@
         <v>16.25</v>
       </c>
       <c r="G2422" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66334,7 +66337,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2423" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66360,7 +66363,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2424" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66386,7 +66389,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2425" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66412,7 +66415,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2426" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66438,7 +66441,7 @@
         <v>16.25</v>
       </c>
       <c r="G2427" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66464,7 +66467,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2428" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66490,7 +66493,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66516,7 +66519,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2430" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66542,7 +66545,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2431" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66568,7 +66571,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66594,7 +66597,7 @@
         <v>16.5</v>
       </c>
       <c r="G2433" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66620,7 +66623,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2434" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66646,7 +66649,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2435" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66672,7 +66675,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2436" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66698,7 +66701,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2437" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66724,7 +66727,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2438" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66750,7 +66753,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2439" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66776,7 +66779,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2440" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66802,7 +66805,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66828,7 +66831,7 @@
         <v>16.75</v>
       </c>
       <c r="G2442" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66854,7 +66857,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66880,7 +66883,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2444" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66906,7 +66909,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2445" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66932,7 +66935,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2446" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66958,7 +66961,7 @@
         <v>18</v>
       </c>
       <c r="G2447" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66984,7 +66987,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2448" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67010,7 +67013,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67036,7 +67039,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2450" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67062,7 +67065,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2451" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67088,7 +67091,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2452" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67114,7 +67117,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2453" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67140,7 +67143,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2454" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67166,7 +67169,7 @@
         <v>21</v>
       </c>
       <c r="G2455" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67192,7 +67195,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G2456" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67218,7 +67221,7 @@
         <v>19.25</v>
       </c>
       <c r="G2457" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67244,7 +67247,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G2458" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67270,7 +67273,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G2459" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67296,7 +67299,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67322,7 +67325,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2461" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67348,7 +67351,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2462" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67374,7 +67377,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67400,7 +67403,7 @@
         <v>18.5</v>
       </c>
       <c r="G2464" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67426,7 +67429,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G2465" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67452,7 +67455,7 @@
         <v>19</v>
       </c>
       <c r="G2466" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67478,7 +67481,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2467" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67504,7 +67507,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2468" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67530,7 +67533,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2469" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67556,7 +67559,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2470" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67582,7 +67585,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2471" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67608,7 +67611,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2472" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67634,7 +67637,7 @@
         <v>16</v>
       </c>
       <c r="G2473" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67660,7 +67663,7 @@
         <v>16</v>
       </c>
       <c r="G2474" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67686,7 +67689,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2475" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67712,7 +67715,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67738,7 +67741,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67764,7 +67767,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67790,7 +67793,7 @@
         <v>16.25</v>
       </c>
       <c r="G2479" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67816,7 +67819,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67842,7 +67845,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2481" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67868,7 +67871,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67894,7 +67897,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67920,7 +67923,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2484" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67946,7 +67949,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2485" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67972,7 +67975,7 @@
         <v>16</v>
       </c>
       <c r="G2486" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67998,7 +68001,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2487" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68024,7 +68027,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2488" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68050,7 +68053,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68076,7 +68079,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2490" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68102,7 +68105,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2491" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68128,7 +68131,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2492" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68154,7 +68157,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68180,7 +68183,7 @@
         <v>15.25</v>
       </c>
       <c r="G2494" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68206,7 +68209,7 @@
         <v>15.5</v>
       </c>
       <c r="G2495" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68232,7 +68235,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2496" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68258,7 +68261,7 @@
         <v>15.5</v>
       </c>
       <c r="G2497" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68284,7 +68287,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2498" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68310,7 +68313,7 @@
         <v>15.25</v>
       </c>
       <c r="G2499" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -68336,7 +68339,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2500" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -68362,7 +68365,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2501" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -68388,7 +68391,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2502" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68414,7 +68417,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2503" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68440,7 +68443,7 @@
         <v>15.25</v>
       </c>
       <c r="G2504" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -68466,7 +68469,7 @@
         <v>15.25</v>
       </c>
       <c r="G2505" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -68492,7 +68495,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2506" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68518,7 +68521,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2507" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68544,7 +68547,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2508" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68570,7 +68573,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2509" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68596,7 +68599,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G2510" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68622,7 +68625,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2511" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68648,7 +68651,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2512" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68674,7 +68677,7 @@
         <v>15</v>
       </c>
       <c r="G2513" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68700,7 +68703,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2514" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68726,7 +68729,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2515" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68752,7 +68755,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2516" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68778,7 +68781,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2517" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68804,7 +68807,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2518" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -68812,7 +68815,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.6911342593</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>2730</v>
@@ -68821,7 +68824,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="D2519" t="n">
-        <v>15</v>
+        <v>14.9499998092651</v>
       </c>
       <c r="E2519" t="n">
         <v>15.1000003814697</v>
@@ -68830,9 +68833,35 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2519" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.6873611111</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>4152</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>15.1000003814697</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>14.9499998092651</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>998</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BEC.MI.xlsx
+++ b/data/BEC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="998">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,49 +38,49 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96833896636963</t>
+    <t xml:space="preserve">4.96833848953247</t>
   </si>
   <si>
     <t xml:space="preserve">BEC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96181058883667</t>
+    <t xml:space="preserve">4.9618091583252</t>
   </si>
   <si>
     <t xml:space="preserve">4.8704080581665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87693691253662</t>
+    <t xml:space="preserve">4.8769359588623</t>
   </si>
   <si>
     <t xml:space="preserve">4.92916631698608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77247667312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79859161376953</t>
+    <t xml:space="preserve">4.77247762680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79859209060669</t>
   </si>
   <si>
     <t xml:space="preserve">4.83449983596802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73330450057983</t>
+    <t xml:space="preserve">4.73330497741699</t>
   </si>
   <si>
     <t xml:space="preserve">4.79532766342163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80512046813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76594877243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75941896438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60273122787476</t>
+    <t xml:space="preserve">4.80512094497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76594829559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75942039489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60273170471191</t>
   </si>
   <si>
     <t xml:space="preserve">4.69739723205566</t>
@@ -89,31 +89,31 @@
     <t xml:space="preserve">4.69413328170776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63537454605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44277811050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37422609329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18489456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07390737533569</t>
+    <t xml:space="preserve">4.63537502288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44277858734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37422657012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18489503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07390689849854</t>
   </si>
   <si>
     <t xml:space="preserve">4.08043527603149</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23386001586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40360546112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49174404144287</t>
+    <t xml:space="preserve">4.2338604927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40360641479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49174356460571</t>
   </si>
   <si>
     <t xml:space="preserve">4.5309157371521</t>
@@ -125,67 +125,67 @@
     <t xml:space="preserve">4.50480079650879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53744411468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42645645141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42319202423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43951416015625</t>
+    <t xml:space="preserve">4.53744459152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42645692825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4231915473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43951368331909</t>
   </si>
   <si>
     <t xml:space="preserve">4.41666316986084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44930744171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46562910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47868633270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60926055908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89652299880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90958023071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9356951713562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91284370422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0140380859375</t>
+    <t xml:space="preserve">4.44930696487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4656286239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47868585586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60926008224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89652252197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90957927703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93569469451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91284465789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01403951644897</t>
   </si>
   <si>
     <t xml:space="preserve">4.94222354888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03362560272217</t>
+    <t xml:space="preserve">5.03362512588501</t>
   </si>
   <si>
     <t xml:space="preserve">5.04015398025513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09238290786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94875240325928</t>
+    <t xml:space="preserve">5.09238338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94875192642212</t>
   </si>
   <si>
     <t xml:space="preserve">4.99445295333862</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84429311752319</t>
+    <t xml:space="preserve">4.84429216384888</t>
   </si>
   <si>
     <t xml:space="preserve">5.0695333480835</t>
@@ -194,31 +194,31 @@
     <t xml:space="preserve">5.09891223907471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98792457580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04994630813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04341793060303</t>
+    <t xml:space="preserve">4.98792409896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04994773864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04341745376587</t>
   </si>
   <si>
     <t xml:space="preserve">5.05974006652832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98466014862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02709627151489</t>
+    <t xml:space="preserve">4.98466062545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02709674835205</t>
   </si>
   <si>
     <t xml:space="preserve">4.99973773956299</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03393602371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96212100982666</t>
+    <t xml:space="preserve">5.03393650054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9621205329895</t>
   </si>
   <si>
     <t xml:space="preserve">4.91766357421875</t>
@@ -227,16 +227,16 @@
     <t xml:space="preserve">4.9450216293335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85610675811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89030504226685</t>
+    <t xml:space="preserve">4.85610771179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89030599594116</t>
   </si>
   <si>
     <t xml:space="preserve">4.89714431762695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79455089569092</t>
+    <t xml:space="preserve">4.79455041885376</t>
   </si>
   <si>
     <t xml:space="preserve">4.82190895080566</t>
@@ -245,25 +245,25 @@
     <t xml:space="preserve">4.98263931274414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92450332641602</t>
+    <t xml:space="preserve">4.92450284957886</t>
   </si>
   <si>
     <t xml:space="preserve">5.00657749176025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88346529006958</t>
+    <t xml:space="preserve">4.88346481323242</t>
   </si>
   <si>
     <t xml:space="preserve">4.94844150543213</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95870018005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99289894104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86636734008789</t>
+    <t xml:space="preserve">4.95870065689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99289846420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86636638641357</t>
   </si>
   <si>
     <t xml:space="preserve">4.85268688201904</t>
@@ -272,37 +272,37 @@
     <t xml:space="preserve">4.93134260177612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78771114349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78429079055786</t>
+    <t xml:space="preserve">4.78771066665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78429126739502</t>
   </si>
   <si>
     <t xml:space="preserve">4.8253288269043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77403211593628</t>
+    <t xml:space="preserve">4.77403163909912</t>
   </si>
   <si>
     <t xml:space="preserve">4.7227349281311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67485809326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75693273544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56200551986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54148578643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53122663497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60304260253906</t>
+    <t xml:space="preserve">4.67485761642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75693321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56200408935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54148626327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53122711181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6030421257019</t>
   </si>
   <si>
     <t xml:space="preserve">4.63040065765381</t>
@@ -311,139 +311,139 @@
     <t xml:space="preserve">4.55516481399536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58252286911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54832553863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45941114425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53464698791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52780628204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52096748352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64408016204834</t>
+    <t xml:space="preserve">4.58252334594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54832601547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45941019058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53464651107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52780675888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52096700668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64407920837402</t>
   </si>
   <si>
     <t xml:space="preserve">4.74325323104858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73983335494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83558893203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92108297348022</t>
+    <t xml:space="preserve">4.73983383178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83558797836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92108345031738</t>
   </si>
   <si>
     <t xml:space="preserve">4.92792224884033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98605823516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96554088592529</t>
+    <t xml:space="preserve">4.98605966567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96553993225098</t>
   </si>
   <si>
     <t xml:space="preserve">4.91424322128296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97237968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96896028518677</t>
+    <t xml:space="preserve">4.9723801612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96895980834961</t>
   </si>
   <si>
     <t xml:space="preserve">4.86978626251221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93818187713623</t>
+    <t xml:space="preserve">4.93818235397339</t>
   </si>
   <si>
     <t xml:space="preserve">4.88004541397095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9518609046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87320566177368</t>
+    <t xml:space="preserve">4.95186042785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.873206615448</t>
   </si>
   <si>
     <t xml:space="preserve">4.86294651031494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76719188690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80139017105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80822992324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76377201080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8424277305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72957515716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84926700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81164932250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88688564300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02025699615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08865261077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10575199127197</t>
+    <t xml:space="preserve">4.76719284057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80139064788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80823040008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76377296447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84242725372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72957468032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84926795959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81164884567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88688468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02025747299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08865308761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10575103759766</t>
   </si>
   <si>
     <t xml:space="preserve">5.06471395492554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04761505126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09549236297607</t>
+    <t xml:space="preserve">5.04761552810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09549188613892</t>
   </si>
   <si>
     <t xml:space="preserve">5.17756748199463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23228406906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12969064712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13994932174683</t>
+    <t xml:space="preserve">5.23228454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12969017028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13994979858398</t>
   </si>
   <si>
     <t xml:space="preserve">5.16388845443726</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21176528930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30751991271973</t>
+    <t xml:space="preserve">5.2117657661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30752038955688</t>
   </si>
   <si>
     <t xml:space="preserve">5.30068016052246</t>
@@ -452,34 +452,34 @@
     <t xml:space="preserve">5.13311052322388</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22544479370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16730880737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19808721542358</t>
+    <t xml:space="preserve">5.22544384002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16730833053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19808626174927</t>
   </si>
   <si>
     <t xml:space="preserve">5.29726028442383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47166967391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40327405929565</t>
+    <t xml:space="preserve">5.47167015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40327453613281</t>
   </si>
   <si>
     <t xml:space="preserve">5.36565589904785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36223602294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46483039855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36907577514648</t>
+    <t xml:space="preserve">5.36223697662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46482992172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36907625198364</t>
   </si>
   <si>
     <t xml:space="preserve">5.39643430709839</t>
@@ -491,13 +491,13 @@
     <t xml:space="preserve">5.41353321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4614109992981</t>
+    <t xml:space="preserve">5.46141004562378</t>
   </si>
   <si>
     <t xml:space="preserve">5.43747138977051</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45457124710083</t>
+    <t xml:space="preserve">5.45457077026367</t>
   </si>
   <si>
     <t xml:space="preserve">5.46824979782104</t>
@@ -512,43 +512,43 @@
     <t xml:space="preserve">5.41695356369019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43063259124756</t>
+    <t xml:space="preserve">5.43063163757324</t>
   </si>
   <si>
     <t xml:space="preserve">5.45799112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50586795806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52980709075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60846138000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68369722366333</t>
+    <t xml:space="preserve">5.50586843490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52980613708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60846090316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68369770050049</t>
   </si>
   <si>
     <t xml:space="preserve">5.73157453536987</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88204526901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93676280975342</t>
+    <t xml:space="preserve">5.88204574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93676137924194</t>
   </si>
   <si>
     <t xml:space="preserve">5.94360160827637</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05645418167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94018173217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04961538314819</t>
+    <t xml:space="preserve">6.05645513534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94018077850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04961490631104</t>
   </si>
   <si>
     <t xml:space="preserve">6.07355356216431</t>
@@ -557,16 +557,16 @@
     <t xml:space="preserve">6.02567720413208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9743800163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04277515411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17272710800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39501476287842</t>
+    <t xml:space="preserve">5.97437906265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04277467727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17272758483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39501333236694</t>
   </si>
   <si>
     <t xml:space="preserve">6.37449502944946</t>
@@ -575,13 +575,13 @@
     <t xml:space="preserve">6.46682929992676</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32661771774292</t>
+    <t xml:space="preserve">6.32661819458008</t>
   </si>
   <si>
     <t xml:space="preserve">6.11117076873779</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8991436958313</t>
+    <t xml:space="preserve">5.89914512634277</t>
   </si>
   <si>
     <t xml:space="preserve">6.00515699386597</t>
@@ -596,43 +596,43 @@
     <t xml:space="preserve">6.39843368530273</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40527296066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48050928115845</t>
+    <t xml:space="preserve">6.40527391433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48050880432129</t>
   </si>
   <si>
     <t xml:space="preserve">6.41211318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44973087310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4360523223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52838516235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66859769821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99689674377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94218015670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12001037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46883010864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6671781539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20066452026367</t>
+    <t xml:space="preserve">6.44973134994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43605184555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52838706970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66859817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99689722061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94218063354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1200098991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46883058547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66717720031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20066356658936</t>
   </si>
   <si>
     <t xml:space="preserve">8.40585327148438</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">8.27590084075928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35113525390625</t>
+    <t xml:space="preserve">8.35113620758057</t>
   </si>
   <si>
     <t xml:space="preserve">8.28957939147949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24170207977295</t>
+    <t xml:space="preserve">8.24170303344727</t>
   </si>
   <si>
     <t xml:space="preserve">8.33745670318604</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">8.33061790466309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31693744659424</t>
+    <t xml:space="preserve">8.31693840026855</t>
   </si>
   <si>
     <t xml:space="preserve">8.26906108856201</t>
@@ -668,28 +668,28 @@
     <t xml:space="preserve">8.22118473052979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11858940124512</t>
+    <t xml:space="preserve">8.11859035491943</t>
   </si>
   <si>
     <t xml:space="preserve">8.30325889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48108863830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72047424316406</t>
+    <t xml:space="preserve">8.48108768463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72047328948975</t>
   </si>
   <si>
     <t xml:space="preserve">8.7136344909668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79469108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49782371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52750968933105</t>
+    <t xml:space="preserve">8.79469013214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49782276153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52751064300537</t>
   </si>
   <si>
     <t xml:space="preserve">8.07478809356689</t>
@@ -698,31 +698,31 @@
     <t xml:space="preserve">8.31228160858154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43102741241455</t>
+    <t xml:space="preserve">8.43102836608887</t>
   </si>
   <si>
     <t xml:space="preserve">8.37165546417236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97830772399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88924503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23806476593018</t>
+    <t xml:space="preserve">7.97830581665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88924646377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23806381225586</t>
   </si>
   <si>
     <t xml:space="preserve">8.26033020019531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21579933166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64625644683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75758266448975</t>
+    <t xml:space="preserve">8.21579837799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6462574005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75758171081543</t>
   </si>
   <si>
     <t xml:space="preserve">8.80211162567139</t>
@@ -734,79 +734,79 @@
     <t xml:space="preserve">8.5794620513916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66110038757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54977416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5200891494751</t>
+    <t xml:space="preserve">8.66109943389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54977512359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52008819580078</t>
   </si>
   <si>
     <t xml:space="preserve">8.53493118286133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60172653198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4829797744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59430599212646</t>
+    <t xml:space="preserve">8.60172748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48298072814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59430503845215</t>
   </si>
   <si>
     <t xml:space="preserve">8.46813583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14900302886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31970310211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12673854827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46071529388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58688259124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7056303024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84664249420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69820976257324</t>
+    <t xml:space="preserve">8.14900398254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3197021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12673950195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46071434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58688354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70562934875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84664154052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69820880889893</t>
   </si>
   <si>
     <t xml:space="preserve">8.74273777008057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56461811065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43845081329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40876197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34938907623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42360591888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54235363006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63141441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61656951904297</t>
+    <t xml:space="preserve">8.56461906433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43844985961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40876388549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34939002990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42360687255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54235458374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63141250610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61657047271729</t>
   </si>
   <si>
     <t xml:space="preserve">8.63883590698242</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">8.77984714508057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88375091552734</t>
+    <t xml:space="preserve">8.88374996185303</t>
   </si>
   <si>
     <t xml:space="preserve">8.83922100067139</t>
@@ -830,16 +830,16 @@
     <t xml:space="preserve">8.68336486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60914707183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57204151153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49040126800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47555828094482</t>
+    <t xml:space="preserve">8.60914897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57204055786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49040031433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47555923461914</t>
   </si>
   <si>
     <t xml:space="preserve">8.78726863861084</t>
@@ -848,61 +848,61 @@
     <t xml:space="preserve">8.71305179595947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65367794036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62399101257324</t>
+    <t xml:space="preserve">8.65367889404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62399196624756</t>
   </si>
   <si>
     <t xml:space="preserve">8.75016021728516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90601539611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89859485626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94312286376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77242565155029</t>
+    <t xml:space="preserve">8.90601634979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89859390258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94312381744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77242469787598</t>
   </si>
   <si>
     <t xml:space="preserve">8.96538829803467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87632846832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97281074523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0915584564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2177267074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52201366424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55170249938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56654644012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45522022247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4774866104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53686046600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35873794555664</t>
+    <t xml:space="preserve">8.87632942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97281169891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09155750274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21772575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52201557159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55170154571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45522117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47748565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5368595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35873699188232</t>
   </si>
   <si>
     <t xml:space="preserve">9.59623241424561</t>
@@ -911,16 +911,16 @@
     <t xml:space="preserve">9.64076137542725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9079418182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89309978485107</t>
+    <t xml:space="preserve">9.90794277191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89309787750244</t>
   </si>
   <si>
     <t xml:space="preserve">9.76693058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72982120513916</t>
+    <t xml:space="preserve">9.72982215881348</t>
   </si>
   <si>
     <t xml:space="preserve">9.99700355529785</t>
@@ -929,43 +929,43 @@
     <t xml:space="preserve">9.95247268676758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.05637550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64818286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95989322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82630348205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81146049499512</t>
+    <t xml:space="preserve">10.0563764572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64818477630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95989513397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82630252838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81146144866943</t>
   </si>
   <si>
     <t xml:space="preserve">9.7520866394043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85599136352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86341381072998</t>
+    <t xml:space="preserve">9.85599040985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86341094970703</t>
   </si>
   <si>
     <t xml:space="preserve">10.0415325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0118465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9450511932373</t>
+    <t xml:space="preserve">10.0118446350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94504928588867</t>
   </si>
   <si>
     <t xml:space="preserve">9.90052032470703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8317985534668</t>
+    <t xml:space="preserve">8.83179759979248</t>
   </si>
   <si>
     <t xml:space="preserve">7.97088432312012</t>
@@ -980,37 +980,37 @@
     <t xml:space="preserve">8.1935338973999</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67594337463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50524425506592</t>
+    <t xml:space="preserve">8.67594242095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50524520874023</t>
   </si>
   <si>
     <t xml:space="preserve">8.02283573150635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0673656463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98572874069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78534078598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76307678222656</t>
+    <t xml:space="preserve">8.06736469268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98572635650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78534173965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76307725906372</t>
   </si>
   <si>
     <t xml:space="preserve">7.7037034034729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82987213134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6443305015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72596836090088</t>
+    <t xml:space="preserve">7.82987260818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64433193206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72596788406372</t>
   </si>
   <si>
     <t xml:space="preserve">8.04510116577148</t>
@@ -1022,40 +1022,40 @@
     <t xml:space="preserve">7.91893291473389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08962917327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11931705474854</t>
+    <t xml:space="preserve">8.08963012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11931800842285</t>
   </si>
   <si>
     <t xml:space="preserve">8.11189651489258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0970516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00057125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13416194915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28259563446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20837879180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34196853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44587230682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92085933685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02476215362549</t>
+    <t xml:space="preserve">8.09705257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00057220458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1341609954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28259372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20837783813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34196758270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44587135314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92086029052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0247631072998</t>
   </si>
   <si>
     <t xml:space="preserve">8.32712459564209</t>
@@ -1064,61 +1064,61 @@
     <t xml:space="preserve">8.26775169372559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71854686737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0302562713623</t>
+    <t xml:space="preserve">7.71854829788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03025722503662</t>
   </si>
   <si>
     <t xml:space="preserve">8.01541423797607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1044750213623</t>
+    <t xml:space="preserve">8.10447406768799</t>
   </si>
   <si>
     <t xml:space="preserve">8.17869091033936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22322082519531</t>
+    <t xml:space="preserve">8.22322177886963</t>
   </si>
   <si>
     <t xml:space="preserve">8.40134143829346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05444812774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93570232391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72789573669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89117240905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00992012023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.277099609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30678749084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24741363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35131645202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52943706512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47006416320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39584636688232</t>
+    <t xml:space="preserve">9.0544490814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93570327758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72789669036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8911714553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00991916656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27709865570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30678653717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24741268157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35131549835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52943801879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47006225585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39584541320801</t>
   </si>
   <si>
     <t xml:space="preserve">9.54428005218506</t>
@@ -1127,34 +1127,34 @@
     <t xml:space="preserve">9.87083435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60365295410156</t>
+    <t xml:space="preserve">9.60365390777588</t>
   </si>
   <si>
     <t xml:space="preserve">10.0637989044189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87998294830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54299259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55830955505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72680473327637</t>
+    <t xml:space="preserve">9.87998390197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54299163818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55831050872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72680568695068</t>
   </si>
   <si>
     <t xml:space="preserve">9.60426425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46640396118164</t>
+    <t xml:space="preserve">9.46640300750732</t>
   </si>
   <si>
     <t xml:space="preserve">9.57362747192383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61958122253418</t>
+    <t xml:space="preserve">9.6195821762085</t>
   </si>
   <si>
     <t xml:space="preserve">9.6348991394043</t>
@@ -1163,13 +1163,13 @@
     <t xml:space="preserve">9.68085289001465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48172187805176</t>
+    <t xml:space="preserve">9.48172092437744</t>
   </si>
   <si>
     <t xml:space="preserve">9.43576717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34385967254639</t>
+    <t xml:space="preserve">9.3438606262207</t>
   </si>
   <si>
     <t xml:space="preserve">9.31322479248047</t>
@@ -1184,13 +1184,13 @@
     <t xml:space="preserve">8.53201770782471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89964389801025</t>
+    <t xml:space="preserve">8.89964485168457</t>
   </si>
   <si>
     <t xml:space="preserve">8.96091556549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28258895874023</t>
+    <t xml:space="preserve">9.28258991241455</t>
   </si>
   <si>
     <t xml:space="preserve">9.20600128173828</t>
@@ -1214,40 +1214,40 @@
     <t xml:space="preserve">9.19068241119385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86466693878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58894538879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32854270935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42045021057129</t>
+    <t xml:space="preserve">9.86466503143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58894634246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3285436630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42044925689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.22131824493408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.251953125</t>
+    <t xml:space="preserve">9.25195407867432</t>
   </si>
   <si>
     <t xml:space="preserve">9.11409378051758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1447286605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26727104187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45108604431152</t>
+    <t xml:space="preserve">9.14472961425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26727199554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45108509063721</t>
   </si>
   <si>
     <t xml:space="preserve">9.69616985321045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65021705627441</t>
+    <t xml:space="preserve">9.65021514892578</t>
   </si>
   <si>
     <t xml:space="preserve">8.80773735046387</t>
@@ -1274,22 +1274,22 @@
     <t xml:space="preserve">8.94559860229492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17536544799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00686931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95657253265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0331611633301</t>
+    <t xml:space="preserve">9.17536449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00686836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95657348632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0331621170044</t>
   </si>
   <si>
     <t xml:space="preserve">9.91061878204346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97189140319824</t>
+    <t xml:space="preserve">9.97189044952393</t>
   </si>
   <si>
     <t xml:space="preserve">9.78807735443115</t>
@@ -1298,37 +1298,37 @@
     <t xml:space="preserve">9.75744152069092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09877681732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86900997161865</t>
+    <t xml:space="preserve">9.09877586364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86900901794434</t>
   </si>
   <si>
     <t xml:space="preserve">8.74646663665771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7311487197876</t>
+    <t xml:space="preserve">8.73114776611328</t>
   </si>
   <si>
     <t xml:space="preserve">8.51669883728027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47074699401855</t>
+    <t xml:space="preserve">8.47074604034424</t>
   </si>
   <si>
     <t xml:space="preserve">8.42479228973389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01121139526367</t>
+    <t xml:space="preserve">8.01121234893799</t>
   </si>
   <si>
     <t xml:space="preserve">8.225661277771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36352157592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65456008911133</t>
+    <t xml:space="preserve">8.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65456104278564</t>
   </si>
   <si>
     <t xml:space="preserve">8.77710151672363</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">8.8383731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93027973175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62392425537109</t>
+    <t xml:space="preserve">8.9302806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62392330169678</t>
   </si>
   <si>
     <t xml:space="preserve">8.7158317565918</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">8.50138187408447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82305431365967</t>
+    <t xml:space="preserve">8.8230562210083</t>
   </si>
   <si>
     <t xml:space="preserve">8.60860633850098</t>
@@ -1367,34 +1367,34 @@
     <t xml:space="preserve">8.3328857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37883853912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28693103790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27161407470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39415740966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13375473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11843681335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4554271697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79242038726807</t>
+    <t xml:space="preserve">8.37884044647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28693199157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27161502838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39415645599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13375377655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11843585968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45542812347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79241847991943</t>
   </si>
   <si>
     <t xml:space="preserve">8.85369110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70051193237305</t>
+    <t xml:space="preserve">8.70051288604736</t>
   </si>
   <si>
     <t xml:space="preserve">8.66987705230713</t>
@@ -1403,40 +1403,40 @@
     <t xml:space="preserve">8.68519496917725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54733562469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.440110206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88432502746582</t>
+    <t xml:space="preserve">8.54733467102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44011116027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88432693481445</t>
   </si>
   <si>
     <t xml:space="preserve">9.40513229370117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92593765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80339431762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29790782928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22897624969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0757999420166</t>
+    <t xml:space="preserve">9.92593669891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80339622497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29790687561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22897720336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07579898834229</t>
   </si>
   <si>
     <t xml:space="preserve">9.15238761901855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99921035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59735012054443</t>
+    <t xml:space="preserve">8.99921131134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59734916687012</t>
   </si>
   <si>
     <t xml:space="preserve">9.31742668151855</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">8.79757022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87755012512207</t>
+    <t xml:space="preserve">8.87754821777344</t>
   </si>
   <si>
     <t xml:space="preserve">8.83755970001221</t>
@@ -1460,46 +1460,46 @@
     <t xml:space="preserve">9.27743816375732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47738361358643</t>
+    <t xml:space="preserve">9.47738265991211</t>
   </si>
   <si>
     <t xml:space="preserve">9.3574161529541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51737213134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67732810974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63733863830566</t>
+    <t xml:space="preserve">9.51737117767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67732906341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63733959197998</t>
   </si>
   <si>
     <t xml:space="preserve">9.39740562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19746112823486</t>
+    <t xml:space="preserve">9.19746017456055</t>
   </si>
   <si>
     <t xml:space="preserve">9.07749462127686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4373950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5573616027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11748218536377</t>
+    <t xml:space="preserve">9.43739414215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55736064910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11748313903809</t>
   </si>
   <si>
     <t xml:space="preserve">8.71759128570557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95752620697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99751472473145</t>
+    <t xml:space="preserve">8.95752716064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99751567840576</t>
   </si>
   <si>
     <t xml:space="preserve">9.15747165679932</t>
@@ -1514,16 +1514,16 @@
     <t xml:space="preserve">10.3571405410767</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772171020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3171501159668</t>
+    <t xml:space="preserve">10.0772190093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3171510696411</t>
   </si>
   <si>
     <t xml:space="preserve">10.1172065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91726112365723</t>
+    <t xml:space="preserve">9.91726207733154</t>
   </si>
   <si>
     <t xml:space="preserve">9.997239112854</t>
@@ -1535,10 +1535,10 @@
     <t xml:space="preserve">9.75730609893799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71731853485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79729557037354</t>
+    <t xml:space="preserve">9.71731662750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79729461669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.83728504180908</t>
@@ -1550,13 +1550,13 @@
     <t xml:space="preserve">10.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2371730804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3971290588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5570859909058</t>
+    <t xml:space="preserve">10.2371740341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3971300125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5570850372314</t>
   </si>
   <si>
     <t xml:space="preserve">10.477108001709</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">10.5170965194702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9969635009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1169309616089</t>
+    <t xml:space="preserve">10.9969644546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1169300079346</t>
   </si>
   <si>
     <t xml:space="preserve">11.3168745040894</t>
@@ -1580,28 +1580,28 @@
     <t xml:space="preserve">11.2368974685669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3568639755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.196907043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.837007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1569185256958</t>
+    <t xml:space="preserve">11.3568630218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1969089508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8370084762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1569194793701</t>
   </si>
   <si>
     <t xml:space="preserve">11.0369529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8769969940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9169845581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9569749832153</t>
+    <t xml:space="preserve">10.8769979476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9169864654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9569759368896</t>
   </si>
   <si>
     <t xml:space="preserve">10.7570295333862</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">11.2768859863281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4368419647217</t>
+    <t xml:space="preserve">11.4368410110474</t>
   </si>
   <si>
     <t xml:space="preserve">11.5568084716797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6767768859863</t>
+    <t xml:space="preserve">11.676775932312</t>
   </si>
   <si>
     <t xml:space="preserve">10.717041015625</t>
@@ -1631,34 +1631,34 @@
     <t xml:space="preserve">8.11775875091553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16602230072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88582277297974</t>
+    <t xml:space="preserve">7.16602087020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88582134246826</t>
   </si>
   <si>
     <t xml:space="preserve">7.46993780136108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03805637359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9100923538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39823341369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20628690719604</t>
+    <t xml:space="preserve">7.03805780410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91009283065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39823389053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20628643035889</t>
   </si>
   <si>
     <t xml:space="preserve">5.9983434677124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55818891525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30998134613037</t>
+    <t xml:space="preserve">6.55818939208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30998229980469</t>
   </si>
   <si>
     <t xml:space="preserve">7.40595531463623</t>
@@ -1667,16 +1667,16 @@
     <t xml:space="preserve">7.32597732543945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11803436279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73414087295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9740743637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29398536682129</t>
+    <t xml:space="preserve">7.11803483963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73414039611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97407484054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29398584365845</t>
   </si>
   <si>
     <t xml:space="preserve">7.15002489089966</t>
@@ -1688,10 +1688,10 @@
     <t xml:space="preserve">6.8141188621521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76613235473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94208288192749</t>
+    <t xml:space="preserve">6.76613283157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94208335876465</t>
   </si>
   <si>
     <t xml:space="preserve">6.79812288284302</t>
@@ -1706,16 +1706,16 @@
     <t xml:space="preserve">6.83011388778687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92877960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01068019866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89601898193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96153879165649</t>
+    <t xml:space="preserve">6.92877912521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01067972183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89601850509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96153926849365</t>
   </si>
   <si>
     <t xml:space="preserve">6.73221826553345</t>
@@ -1724,31 +1724,31 @@
     <t xml:space="preserve">6.74859762191772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05981969833374</t>
+    <t xml:space="preserve">7.05981922149658</t>
   </si>
   <si>
     <t xml:space="preserve">7.1253399848938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22362089157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55122232437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56760311126709</t>
+    <t xml:space="preserve">7.2236213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55122327804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56760215759277</t>
   </si>
   <si>
     <t xml:space="preserve">8.0262451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31289672851562</t>
+    <t xml:space="preserve">8.31289577484131</t>
   </si>
   <si>
     <t xml:space="preserve">8.39479732513428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72239971160889</t>
+    <t xml:space="preserve">8.72239875793457</t>
   </si>
   <si>
     <t xml:space="preserve">8.76334953308105</t>
@@ -1757,22 +1757,22 @@
     <t xml:space="preserve">8.88619995117188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1728515625</t>
+    <t xml:space="preserve">9.17285060882568</t>
   </si>
   <si>
     <t xml:space="preserve">9.41855335235596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92714977264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13190174102783</t>
+    <t xml:space="preserve">8.92715072631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13190078735352</t>
   </si>
   <si>
     <t xml:space="preserve">8.96810054779053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33665180206299</t>
+    <t xml:space="preserve">9.3366527557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.84524917602539</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">9.09095191955566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21380138397217</t>
+    <t xml:space="preserve">9.2138032913208</t>
   </si>
   <si>
     <t xml:space="preserve">9.25475311279297</t>
@@ -1790,34 +1790,34 @@
     <t xml:space="preserve">9.00904941558838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64050006866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09176635742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17366504669189</t>
+    <t xml:space="preserve">8.64049816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09176540374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17366600036621</t>
   </si>
   <si>
     <t xml:space="preserve">8.1900463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10814571380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15728569030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96072483062744</t>
+    <t xml:space="preserve">8.10814666748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15728664398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9607253074646</t>
   </si>
   <si>
     <t xml:space="preserve">7.87882423400879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71502304077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78054428100586</t>
+    <t xml:space="preserve">7.7150239944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78054332733154</t>
   </si>
   <si>
     <t xml:space="preserve">7.58398294448853</t>
@@ -1826,40 +1826,40 @@
     <t xml:space="preserve">7.51846265792847</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53484344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33828210830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48570203781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61674356460571</t>
+    <t xml:space="preserve">7.5348424911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33828067779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48570251464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6167426109314</t>
   </si>
   <si>
     <t xml:space="preserve">7.69864320755005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76416349411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73140382766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79692363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66588306427002</t>
+    <t xml:space="preserve">7.76416301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73140335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79692411422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66588354110718</t>
   </si>
   <si>
     <t xml:space="preserve">7.63312196731567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64950370788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68226289749146</t>
+    <t xml:space="preserve">7.6495041847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6822624206543</t>
   </si>
   <si>
     <t xml:space="preserve">7.82968425750732</t>
@@ -1871,16 +1871,16 @@
     <t xml:space="preserve">7.43656206130981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60036277770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.354660987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40380096435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24000072479248</t>
+    <t xml:space="preserve">7.60036325454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35466146469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40380144119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24000120162964</t>
   </si>
   <si>
     <t xml:space="preserve">7.19086027145386</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">6.68307733535767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56841707229614</t>
+    <t xml:space="preserve">6.5684175491333</t>
   </si>
   <si>
     <t xml:space="preserve">6.3882360458374</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">6.22443532943726</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48651647567749</t>
+    <t xml:space="preserve">6.48651695251465</t>
   </si>
   <si>
     <t xml:space="preserve">6.42099666595459</t>
@@ -1922,10 +1922,10 @@
     <t xml:space="preserve">8.5176477432251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27194595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97710418701172</t>
+    <t xml:space="preserve">8.27194786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97710466384888</t>
   </si>
   <si>
     <t xml:space="preserve">7.84606409072876</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">8.59954929351807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43574714660645</t>
+    <t xml:space="preserve">8.43574810028076</t>
   </si>
   <si>
     <t xml:space="preserve">8.55859851837158</t>
@@ -1952,16 +1952,16 @@
     <t xml:space="preserve">8.35384559631348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23099613189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04262638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94434499740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86244440078735</t>
+    <t xml:space="preserve">8.23099708557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04262542724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94434356689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86244535446167</t>
   </si>
   <si>
     <t xml:space="preserve">8.00986480712891</t>
@@ -1970,13 +1970,13 @@
     <t xml:space="preserve">8.05900573730469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45950412750244</t>
+    <t xml:space="preserve">9.45950317382812</t>
   </si>
   <si>
     <t xml:space="preserve">9.90995693206787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1556568145752</t>
+    <t xml:space="preserve">10.1556577682495</t>
   </si>
   <si>
     <t xml:space="preserve">9.86900520324707</t>
@@ -1988,10 +1988,10 @@
     <t xml:space="preserve">9.50045299530029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37760257720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58235454559326</t>
+    <t xml:space="preserve">9.37760353088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58235359191895</t>
   </si>
   <si>
     <t xml:space="preserve">9.70520496368408</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">9.05000114440918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54140281677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22513484954834</t>
+    <t xml:space="preserve">9.54140377044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22513580322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.18320178985596</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">9.5605936050415</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4347972869873</t>
+    <t xml:space="preserve">9.43479824066162</t>
   </si>
   <si>
     <t xml:space="preserve">9.35093212127686</t>
@@ -2045,10 +2045,10 @@
     <t xml:space="preserve">9.6025276184082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72832584381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3153781890869</t>
+    <t xml:space="preserve">9.72832489013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3153791427612</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895809173584</t>
@@ -2060,16 +2060,16 @@
     <t xml:space="preserve">10.1057167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3573112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2734460830688</t>
+    <t xml:space="preserve">10.357310295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2734451293945</t>
   </si>
   <si>
     <t xml:space="preserve">10.1476488113403</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0218505859375</t>
+    <t xml:space="preserve">10.0218515396118</t>
   </si>
   <si>
     <t xml:space="preserve">9.85412120819092</t>
@@ -2096,16 +2096,16 @@
     <t xml:space="preserve">8.97354030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.399242401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5669736862183</t>
+    <t xml:space="preserve">10.3992443084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5669727325439</t>
   </si>
   <si>
     <t xml:space="preserve">10.7766351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7347030639648</t>
+    <t xml:space="preserve">10.7347021102905</t>
   </si>
   <si>
     <t xml:space="preserve">11.279824256897</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">10.9443655014038</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2378911972046</t>
+    <t xml:space="preserve">11.2378921508789</t>
   </si>
   <si>
     <t xml:space="preserve">11.1959600448608</t>
@@ -2126,25 +2126,25 @@
     <t xml:space="preserve">11.4056224822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1540279388428</t>
+    <t xml:space="preserve">11.1540269851685</t>
   </si>
   <si>
     <t xml:space="preserve">11.7830142974854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.741081237793</t>
+    <t xml:space="preserve">11.7410802841187</t>
   </si>
   <si>
     <t xml:space="preserve">12.0346088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6152830123901</t>
+    <t xml:space="preserve">11.6152839660645</t>
   </si>
   <si>
     <t xml:space="preserve">11.6572160720825</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1120948791504</t>
+    <t xml:space="preserve">11.1120939254761</t>
   </si>
   <si>
     <t xml:space="preserve">10.9862976074219</t>
@@ -2159,10 +2159,10 @@
     <t xml:space="preserve">11.3636894226074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6991481781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5733509063721</t>
+    <t xml:space="preserve">11.6991491317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5733528137207</t>
   </si>
   <si>
     <t xml:space="preserve">11.5314178466797</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">11.0282297134399</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4831085205078</t>
+    <t xml:space="preserve">10.4831075668335</t>
   </si>
   <si>
     <t xml:space="preserve">10.5250406265259</t>
   </si>
   <si>
-    <t xml:space="preserve">10.608904838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.818567276001</t>
+    <t xml:space="preserve">10.6089057922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8185682296753</t>
   </si>
   <si>
     <t xml:space="preserve">10.9024324417114</t>
@@ -2189,13 +2189,13 @@
     <t xml:space="preserve">11.4475536346436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1378622055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.09485912323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3958835601807</t>
+    <t xml:space="preserve">11.1378631591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0948600769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3958826065063</t>
   </si>
   <si>
     <t xml:space="preserve">11.6539030075073</t>
@@ -2207,13 +2207,13 @@
     <t xml:space="preserve">11.6108989715576</t>
   </si>
   <si>
-    <t xml:space="preserve">11.696907043457</t>
+    <t xml:space="preserve">11.6969060897827</t>
   </si>
   <si>
     <t xml:space="preserve">11.4388866424561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5248918533325</t>
+    <t xml:space="preserve">11.5248928070068</t>
   </si>
   <si>
     <t xml:space="preserve">11.5678958892822</t>
@@ -2231,19 +2231,19 @@
     <t xml:space="preserve">11.0088529586792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8368406295776</t>
+    <t xml:space="preserve">10.8368396759033</t>
   </si>
   <si>
     <t xml:space="preserve">10.9658489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7508335113525</t>
+    <t xml:space="preserve">10.7508325576782</t>
   </si>
   <si>
     <t xml:space="preserve">10.8798427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6648254394531</t>
+    <t xml:space="preserve">10.6648263931274</t>
   </si>
   <si>
     <t xml:space="preserve">10.9228458404541</t>
@@ -2261,37 +2261,37 @@
     <t xml:space="preserve">10.1487865447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97677421569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89076614379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76175689697266</t>
+    <t xml:space="preserve">9.97677326202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89076709747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76175594329834</t>
   </si>
   <si>
     <t xml:space="preserve">9.84776306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46073246002197</t>
+    <t xml:space="preserve">9.46073341369629</t>
   </si>
   <si>
     <t xml:space="preserve">9.54673957824707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2457160949707</t>
+    <t xml:space="preserve">9.24571704864502</t>
   </si>
   <si>
     <t xml:space="preserve">9.20271301269531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03070068359375</t>
+    <t xml:space="preserve">9.03069972991943</t>
   </si>
   <si>
     <t xml:space="preserve">9.15970993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">10.277795791626</t>
+    <t xml:space="preserve">10.2777967453003</t>
   </si>
   <si>
     <t xml:space="preserve">9.67574977874756</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">9.63274574279785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6218233108521</t>
+    <t xml:space="preserve">10.6218223571777</t>
   </si>
   <si>
     <t xml:space="preserve">11.3098764419556</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">11.4818897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.169942855835</t>
+    <t xml:space="preserve">12.1699419021606</t>
   </si>
   <si>
     <t xml:space="preserve">11.9549255371094</t>
@@ -2360,22 +2360,22 @@
     <t xml:space="preserve">12.0409326553345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8689193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7829132080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9979286193848</t>
+    <t xml:space="preserve">11.8689203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7829122543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9979295730591</t>
   </si>
   <si>
     <t xml:space="preserve">12.3419570922852</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4709672927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2989530563354</t>
+    <t xml:space="preserve">12.4709663391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2989540100098</t>
   </si>
   <si>
     <t xml:space="preserve">12.513970375061</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">12.5569734573364</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6429796218872</t>
+    <t xml:space="preserve">12.6429786682129</t>
   </si>
   <si>
     <t xml:space="preserve">12.2559499740601</t>
@@ -2396,22 +2396,22 @@
     <t xml:space="preserve">12.5999755859375</t>
   </si>
   <si>
+    <t xml:space="preserve">12.6859827041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7719898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7289867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9997701644897</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.6859817504883</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7719888687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.728985786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9997711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6859827041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.820463180542</t>
+    <t xml:space="preserve">12.8204641342163</t>
   </si>
   <si>
     <t xml:space="preserve">12.9549436569214</t>
@@ -2423,28 +2423,28 @@
     <t xml:space="preserve">13.4480381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0894250869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2239036560059</t>
+    <t xml:space="preserve">13.0894241333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2239046096802</t>
   </si>
   <si>
     <t xml:space="preserve">13.3583841323853</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1342506408691</t>
+    <t xml:space="preserve">13.1342496871948</t>
   </si>
   <si>
     <t xml:space="preserve">13.0445976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1790781021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3135576248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2687311172485</t>
+    <t xml:space="preserve">13.1790771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3135585784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2687320709229</t>
   </si>
   <si>
     <t xml:space="preserve">12.8652906417847</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">13.7618265151978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7928428649902</t>
+    <t xml:space="preserve">14.7928419113159</t>
   </si>
   <si>
     <t xml:space="preserve">14.1652669906616</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">13.8963060379028</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4032106399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5825185775757</t>
+    <t xml:space="preserve">13.4032115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5825176239014</t>
   </si>
   <si>
     <t xml:space="preserve">13.492865562439</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">13.6721725463867</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9411334991455</t>
+    <t xml:space="preserve">13.9411325454712</t>
   </si>
   <si>
     <t xml:space="preserve">13.7169990539551</t>
@@ -2495,22 +2495,22 @@
     <t xml:space="preserve">14.3445739746094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9859609603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5238819122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2997465133667</t>
+    <t xml:space="preserve">13.9859600067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5238828659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.299747467041</t>
   </si>
   <si>
     <t xml:space="preserve">14.4342279434204</t>
   </si>
   <si>
-    <t xml:space="preserve">14.21009349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3894004821777</t>
+    <t xml:space="preserve">14.2100944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3893995285034</t>
   </si>
   <si>
     <t xml:space="preserve">14.6135339736938</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">15.0169763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1962833404541</t>
+    <t xml:space="preserve">15.1962842941284</t>
   </si>
   <si>
     <t xml:space="preserve">15.3307638168335</t>
@@ -2546,19 +2546,19 @@
     <t xml:space="preserve">15.4204187393188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3755893707275</t>
+    <t xml:space="preserve">15.3755912780762</t>
   </si>
   <si>
     <t xml:space="preserve">14.8376684188843</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8824968338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1514558792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7790327072144</t>
+    <t xml:space="preserve">14.882495880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1514568328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.77903175354</t>
   </si>
   <si>
     <t xml:space="preserve">17.0341815948486</t>
@@ -2570,22 +2570,22 @@
     <t xml:space="preserve">16.5859146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8686857223511</t>
+    <t xml:space="preserve">15.8686866760254</t>
   </si>
   <si>
     <t xml:space="preserve">16.0479907989502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7342052459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9583387374878</t>
+    <t xml:space="preserve">15.7342042922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9583377838135</t>
   </si>
   <si>
     <t xml:space="preserve">16.1376457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8100471496582</t>
+    <t xml:space="preserve">16.8100490570068</t>
   </si>
   <si>
     <t xml:space="preserve">16.7203941345215</t>
@@ -2594,13 +2594,13 @@
     <t xml:space="preserve">16.4066066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2721271514893</t>
+    <t xml:space="preserve">16.2721252441406</t>
   </si>
   <si>
     <t xml:space="preserve">16.0928211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9135131835938</t>
+    <t xml:space="preserve">15.9135122299194</t>
   </si>
   <si>
     <t xml:space="preserve">15.4652442932129</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">15.644552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8238582611084</t>
+    <t xml:space="preserve">15.8238592147827</t>
   </si>
   <si>
     <t xml:space="preserve">15.689377784729</t>
@@ -2685,9 +2685,6 @@
   </si>
   <si>
     <t xml:space="preserve">15.0579290390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1514568328857</t>
   </si>
   <si>
     <t xml:space="preserve">15.1982202529907</t>
@@ -59317,7 +59314,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2153" t="s">
-        <v>891</v>
+        <v>847</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59343,7 +59340,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2154" t="s">
-        <v>891</v>
+        <v>847</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59369,7 +59366,7 @@
         <v>16.25</v>
       </c>
       <c r="G2155" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59421,7 +59418,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2157" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59447,7 +59444,7 @@
         <v>15</v>
       </c>
       <c r="G2158" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59473,7 +59470,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2159" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59499,7 +59496,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2160" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59525,7 +59522,7 @@
         <v>15.25</v>
       </c>
       <c r="G2161" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59551,7 +59548,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2162" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59577,7 +59574,7 @@
         <v>15.25</v>
       </c>
       <c r="G2163" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59603,7 +59600,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2164" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59655,7 +59652,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2166" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59681,7 +59678,7 @@
         <v>16.25</v>
       </c>
       <c r="G2167" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59733,7 +59730,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2169" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59759,7 +59756,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2170" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59811,7 +59808,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59837,7 +59834,7 @@
         <v>16</v>
       </c>
       <c r="G2173" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59889,7 +59886,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2175" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59915,7 +59912,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2176" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59941,7 +59938,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2177" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59967,7 +59964,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2178" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59993,7 +59990,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2179" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60019,7 +60016,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60045,7 +60042,7 @@
         <v>15.25</v>
       </c>
       <c r="G2181" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60071,7 +60068,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60097,7 +60094,7 @@
         <v>15.25</v>
       </c>
       <c r="G2183" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60123,7 +60120,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2184" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60149,7 +60146,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2185" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60175,7 +60172,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2186" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60201,7 +60198,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60227,7 +60224,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2188" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60253,7 +60250,7 @@
         <v>15</v>
       </c>
       <c r="G2189" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60279,7 +60276,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2190" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60305,7 +60302,7 @@
         <v>15</v>
       </c>
       <c r="G2191" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60331,7 +60328,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2192" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60357,7 +60354,7 @@
         <v>15</v>
       </c>
       <c r="G2193" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60383,7 +60380,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2194" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60409,7 +60406,7 @@
         <v>15</v>
       </c>
       <c r="G2195" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60435,7 +60432,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2196" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60461,7 +60458,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2197" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60487,7 +60484,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60513,7 +60510,7 @@
         <v>15</v>
       </c>
       <c r="G2199" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60539,7 +60536,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G2200" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60565,7 +60562,7 @@
         <v>15</v>
       </c>
       <c r="G2201" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60591,7 +60588,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60617,7 +60614,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2203" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60643,7 +60640,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2204" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60669,7 +60666,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60695,7 +60692,7 @@
         <v>14.5</v>
       </c>
       <c r="G2206" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60721,7 +60718,7 @@
         <v>14.5</v>
       </c>
       <c r="G2207" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60747,7 +60744,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60773,7 +60770,7 @@
         <v>14.5</v>
       </c>
       <c r="G2209" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60799,7 +60796,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60825,7 +60822,7 @@
         <v>14.5</v>
       </c>
       <c r="G2211" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60851,7 +60848,7 @@
         <v>14.5</v>
       </c>
       <c r="G2212" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60877,7 +60874,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60903,7 +60900,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2214" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60929,7 +60926,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2215" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60955,7 +60952,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2216" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60981,7 +60978,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2217" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61007,7 +61004,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2218" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61033,7 +61030,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2219" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61059,7 +61056,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2220" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61085,7 +61082,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2221" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61111,7 +61108,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2222" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61137,7 +61134,7 @@
         <v>15</v>
       </c>
       <c r="G2223" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61163,7 +61160,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61189,7 +61186,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2225" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61215,7 +61212,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2226" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61241,7 +61238,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2227" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61267,7 +61264,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61293,7 +61290,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2229" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61319,7 +61316,7 @@
         <v>15.25</v>
       </c>
       <c r="G2230" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61345,7 +61342,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2231" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61371,7 +61368,7 @@
         <v>15.5</v>
       </c>
       <c r="G2232" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61397,7 +61394,7 @@
         <v>15.5</v>
       </c>
       <c r="G2233" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61423,7 +61420,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2234" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61449,7 +61446,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2235" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61475,7 +61472,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2236" t="s">
-        <v>891</v>
+        <v>847</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61501,7 +61498,7 @@
         <v>16</v>
       </c>
       <c r="G2237" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61527,7 +61524,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2238" t="s">
-        <v>891</v>
+        <v>847</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61553,7 +61550,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2239" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61579,7 +61576,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2240" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61683,7 +61680,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2244" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61709,7 +61706,7 @@
         <v>17.25</v>
       </c>
       <c r="G2245" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61761,7 +61758,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2247" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61839,7 +61836,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2250" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61865,7 +61862,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61891,7 +61888,7 @@
         <v>17.25</v>
       </c>
       <c r="G2252" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61917,7 +61914,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2253" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61943,7 +61940,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2254" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61969,7 +61966,7 @@
         <v>17.75</v>
       </c>
       <c r="G2255" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61995,7 +61992,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G2256" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62021,7 +62018,7 @@
         <v>18</v>
       </c>
       <c r="G2257" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62125,7 +62122,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2261" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62281,7 +62278,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2267" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62307,7 +62304,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2268" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62333,7 +62330,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2269" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62359,7 +62356,7 @@
         <v>15.5</v>
       </c>
       <c r="G2270" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62619,7 +62616,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2280" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62645,7 +62642,7 @@
         <v>16</v>
       </c>
       <c r="G2281" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62671,7 +62668,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62697,7 +62694,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2283" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62723,7 +62720,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2284" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62749,7 +62746,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2285" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62775,7 +62772,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62879,7 +62876,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62983,7 +62980,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2294" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63035,7 +63032,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2296" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63061,7 +63058,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2297" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63087,7 +63084,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2298" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63113,7 +63110,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63139,7 +63136,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63165,7 +63162,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63191,7 +63188,7 @@
         <v>16</v>
       </c>
       <c r="G2302" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63217,7 +63214,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2303" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63243,7 +63240,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2304" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63269,7 +63266,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63295,7 +63292,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2306" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63321,7 +63318,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2307" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63347,7 +63344,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2308" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63373,7 +63370,7 @@
         <v>15.75</v>
       </c>
       <c r="G2309" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63399,7 +63396,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2310" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63425,7 +63422,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2311" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63451,7 +63448,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63477,7 +63474,7 @@
         <v>16</v>
       </c>
       <c r="G2313" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63503,7 +63500,7 @@
         <v>16</v>
       </c>
       <c r="G2314" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63529,7 +63526,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2315" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63555,7 +63552,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2316" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63607,7 +63604,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>891</v>
+        <v>847</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63633,7 +63630,7 @@
         <v>16</v>
       </c>
       <c r="G2319" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63659,7 +63656,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2320" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63685,7 +63682,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2321" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63711,7 +63708,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2322" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63737,7 +63734,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2323" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63763,7 +63760,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2324" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63789,7 +63786,7 @@
         <v>16</v>
       </c>
       <c r="G2325" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63815,7 +63812,7 @@
         <v>16</v>
       </c>
       <c r="G2326" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63841,7 +63838,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2327" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63867,7 +63864,7 @@
         <v>16</v>
       </c>
       <c r="G2328" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63893,7 +63890,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2329" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63919,7 +63916,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2330" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63945,7 +63942,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2331" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63971,7 +63968,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63997,7 +63994,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64023,7 +64020,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2334" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64049,7 +64046,7 @@
         <v>15.75</v>
       </c>
       <c r="G2335" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64075,7 +64072,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2336" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64101,7 +64098,7 @@
         <v>15.75</v>
       </c>
       <c r="G2337" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64127,7 +64124,7 @@
         <v>15.25</v>
       </c>
       <c r="G2338" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64153,7 +64150,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2339" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64179,7 +64176,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2340" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64205,7 +64202,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2341" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64231,7 +64228,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64257,7 +64254,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64283,7 +64280,7 @@
         <v>15.5</v>
       </c>
       <c r="G2344" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64309,7 +64306,7 @@
         <v>15.5</v>
       </c>
       <c r="G2345" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64335,7 +64332,7 @@
         <v>15</v>
       </c>
       <c r="G2346" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64361,7 +64358,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64387,7 +64384,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64413,7 +64410,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2349" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64465,7 +64462,7 @@
         <v>16</v>
       </c>
       <c r="G2351" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64491,7 +64488,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64517,7 +64514,7 @@
         <v>15.75</v>
       </c>
       <c r="G2353" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64543,7 +64540,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64569,7 +64566,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2355" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64595,7 +64592,7 @@
         <v>15.25</v>
       </c>
       <c r="G2356" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64621,7 +64618,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2357" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64647,7 +64644,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64673,7 +64670,7 @@
         <v>14</v>
       </c>
       <c r="G2359" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64699,7 +64696,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2360" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64725,7 +64722,7 @@
         <v>15</v>
       </c>
       <c r="G2361" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64751,7 +64748,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2362" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64777,7 +64774,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2363" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64803,7 +64800,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2364" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64829,7 +64826,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64855,7 +64852,7 @@
         <v>14.5</v>
       </c>
       <c r="G2366" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64881,7 +64878,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2367" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64907,7 +64904,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2368" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64933,7 +64930,7 @@
         <v>15</v>
       </c>
       <c r="G2369" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64959,7 +64956,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2370" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64985,7 +64982,7 @@
         <v>15.25</v>
       </c>
       <c r="G2371" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65011,7 +65008,7 @@
         <v>15.25</v>
       </c>
       <c r="G2372" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65037,7 +65034,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2373" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65063,7 +65060,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2374" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65089,7 +65086,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2375" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65115,7 +65112,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2376" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65141,7 +65138,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65167,7 +65164,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2378" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65193,7 +65190,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2379" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65219,7 +65216,7 @@
         <v>15.25</v>
       </c>
       <c r="G2380" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65245,7 +65242,7 @@
         <v>15.25</v>
       </c>
       <c r="G2381" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65271,7 +65268,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2382" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65297,7 +65294,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2383" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65323,7 +65320,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65349,7 +65346,7 @@
         <v>16</v>
       </c>
       <c r="G2385" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65375,7 +65372,7 @@
         <v>16.25</v>
       </c>
       <c r="G2386" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65401,7 +65398,7 @@
         <v>16</v>
       </c>
       <c r="G2387" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65427,7 +65424,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2388" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65453,7 +65450,7 @@
         <v>16.5</v>
       </c>
       <c r="G2389" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65479,7 +65476,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2390" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65505,7 +65502,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2391" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65531,7 +65528,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2392" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65557,7 +65554,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2393" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65583,7 +65580,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2394" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65609,7 +65606,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2395" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65635,7 +65632,7 @@
         <v>16.75</v>
       </c>
       <c r="G2396" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65661,7 +65658,7 @@
         <v>16.5</v>
       </c>
       <c r="G2397" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65687,7 +65684,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2398" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65713,7 +65710,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2399" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65739,7 +65736,7 @@
         <v>16.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65765,7 +65762,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65791,7 +65788,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2402" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65817,7 +65814,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65843,7 +65840,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2404" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65869,7 +65866,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2405" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65895,7 +65892,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2406" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65921,7 +65918,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2407" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65947,7 +65944,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2408" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65973,7 +65970,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G2409" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65999,7 +65996,7 @@
         <v>16</v>
       </c>
       <c r="G2410" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66025,7 +66022,7 @@
         <v>15.75</v>
       </c>
       <c r="G2411" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66051,7 +66048,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2412" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66077,7 +66074,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2413" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66103,7 +66100,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2414" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66129,7 +66126,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2415" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66155,7 +66152,7 @@
         <v>16.25</v>
       </c>
       <c r="G2416" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66181,7 +66178,7 @@
         <v>16.75</v>
       </c>
       <c r="G2417" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66207,7 +66204,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2418" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66233,7 +66230,7 @@
         <v>16.25</v>
       </c>
       <c r="G2419" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66259,7 +66256,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2420" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66285,7 +66282,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2421" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66311,7 +66308,7 @@
         <v>16.25</v>
       </c>
       <c r="G2422" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66337,7 +66334,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2423" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66363,7 +66360,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2424" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66389,7 +66386,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2425" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66415,7 +66412,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2426" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66441,7 +66438,7 @@
         <v>16.25</v>
       </c>
       <c r="G2427" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66467,7 +66464,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2428" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66493,7 +66490,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66519,7 +66516,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2430" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66545,7 +66542,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2431" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66571,7 +66568,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66597,7 +66594,7 @@
         <v>16.5</v>
       </c>
       <c r="G2433" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66623,7 +66620,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2434" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66649,7 +66646,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2435" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66675,7 +66672,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2436" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66701,7 +66698,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2437" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66727,7 +66724,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2438" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66753,7 +66750,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2439" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66779,7 +66776,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2440" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66805,7 +66802,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66831,7 +66828,7 @@
         <v>16.75</v>
       </c>
       <c r="G2442" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66857,7 +66854,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66883,7 +66880,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2444" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66909,7 +66906,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2445" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66935,7 +66932,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2446" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66961,7 +66958,7 @@
         <v>18</v>
       </c>
       <c r="G2447" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66987,7 +66984,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2448" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67013,7 +67010,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67039,7 +67036,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2450" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67065,7 +67062,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2451" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67091,7 +67088,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2452" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67117,7 +67114,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2453" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67143,7 +67140,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2454" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67169,7 +67166,7 @@
         <v>21</v>
       </c>
       <c r="G2455" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67195,7 +67192,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G2456" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67221,7 +67218,7 @@
         <v>19.25</v>
       </c>
       <c r="G2457" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67247,7 +67244,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G2458" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67273,7 +67270,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G2459" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67299,7 +67296,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67325,7 +67322,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2461" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67351,7 +67348,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2462" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67377,7 +67374,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67403,7 +67400,7 @@
         <v>18.5</v>
       </c>
       <c r="G2464" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67429,7 +67426,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G2465" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67455,7 +67452,7 @@
         <v>19</v>
       </c>
       <c r="G2466" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67481,7 +67478,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2467" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67507,7 +67504,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2468" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67533,7 +67530,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2469" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67559,7 +67556,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2470" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67585,7 +67582,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2471" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67611,7 +67608,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2472" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67637,7 +67634,7 @@
         <v>16</v>
       </c>
       <c r="G2473" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67663,7 +67660,7 @@
         <v>16</v>
       </c>
       <c r="G2474" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67689,7 +67686,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2475" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67715,7 +67712,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67741,7 +67738,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67767,7 +67764,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67793,7 +67790,7 @@
         <v>16.25</v>
       </c>
       <c r="G2479" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67819,7 +67816,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67845,7 +67842,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2481" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67871,7 +67868,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67897,7 +67894,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67923,7 +67920,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2484" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67949,7 +67946,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2485" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67975,7 +67972,7 @@
         <v>16</v>
       </c>
       <c r="G2486" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68001,7 +67998,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2487" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68027,7 +68024,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2488" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68053,7 +68050,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68079,7 +68076,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2490" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68105,7 +68102,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2491" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68131,7 +68128,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2492" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68157,7 +68154,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68183,7 +68180,7 @@
         <v>15.25</v>
       </c>
       <c r="G2494" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68209,7 +68206,7 @@
         <v>15.5</v>
       </c>
       <c r="G2495" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68235,7 +68232,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2496" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68261,7 +68258,7 @@
         <v>15.5</v>
       </c>
       <c r="G2497" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68287,7 +68284,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2498" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68313,7 +68310,7 @@
         <v>15.25</v>
       </c>
       <c r="G2499" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -68339,7 +68336,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2500" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -68365,7 +68362,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2501" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -68391,7 +68388,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2502" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68417,7 +68414,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2503" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68443,7 +68440,7 @@
         <v>15.25</v>
       </c>
       <c r="G2504" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -68469,7 +68466,7 @@
         <v>15.25</v>
       </c>
       <c r="G2505" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -68495,7 +68492,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2506" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68521,7 +68518,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2507" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68547,7 +68544,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2508" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68573,7 +68570,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2509" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68599,7 +68596,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G2510" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68625,7 +68622,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2511" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68651,7 +68648,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2512" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68677,7 +68674,7 @@
         <v>15</v>
       </c>
       <c r="G2513" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68703,7 +68700,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2514" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68729,7 +68726,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2515" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68755,7 +68752,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2516" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68781,7 +68778,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2517" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68807,7 +68804,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2518" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -68833,7 +68830,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2519" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -68841,7 +68838,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.6873611111</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>4152</v>
@@ -68859,9 +68856,35 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2520" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.6928472222</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>21231</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>15.1499996185303</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>940</v>
+      </c>
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BEC.MI.xlsx
+++ b/data/BEC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="999">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,82 +38,82 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96833801269531</t>
+    <t xml:space="preserve">4.96833848953247</t>
   </si>
   <si>
     <t xml:space="preserve">BEC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9618091583252</t>
+    <t xml:space="preserve">4.96180963516235</t>
   </si>
   <si>
     <t xml:space="preserve">4.8704080581665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8769359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92916584014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7724781036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79859161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83450031280518</t>
+    <t xml:space="preserve">4.87693691253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92916631698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77247762680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79859209060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83449983596802</t>
   </si>
   <si>
     <t xml:space="preserve">4.73330497741699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79532766342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80512142181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76594877243042</t>
+    <t xml:space="preserve">4.79532814025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80512046813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76594924926758</t>
   </si>
   <si>
     <t xml:space="preserve">4.75942039489746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60273122787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69739723205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69413232803345</t>
+    <t xml:space="preserve">4.60273170471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69739770889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69413328170776</t>
   </si>
   <si>
     <t xml:space="preserve">4.63537454605103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44277763366699</t>
+    <t xml:space="preserve">4.44277858734131</t>
   </si>
   <si>
     <t xml:space="preserve">4.37422704696655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18489456176758</t>
+    <t xml:space="preserve">4.18489551544189</t>
   </si>
   <si>
     <t xml:space="preserve">4.07390689849854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08043479919434</t>
+    <t xml:space="preserve">4.08043575286865</t>
   </si>
   <si>
     <t xml:space="preserve">4.23386001586914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40360641479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49174404144287</t>
+    <t xml:space="preserve">4.40360593795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49174308776855</t>
   </si>
   <si>
     <t xml:space="preserve">4.53091526031494</t>
@@ -122,22 +122,22 @@
     <t xml:space="preserve">4.43298482894897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50480175018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53744411468506</t>
+    <t xml:space="preserve">4.50480079650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53744459152222</t>
   </si>
   <si>
     <t xml:space="preserve">4.42645645141602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4231915473938</t>
+    <t xml:space="preserve">4.42319250106812</t>
   </si>
   <si>
     <t xml:space="preserve">4.43951368331909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41666316986084</t>
+    <t xml:space="preserve">4.416663646698</t>
   </si>
   <si>
     <t xml:space="preserve">4.44930696487427</t>
@@ -155,10 +155,10 @@
     <t xml:space="preserve">4.8965220451355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90958023071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9356951713562</t>
+    <t xml:space="preserve">4.90957975387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93569421768188</t>
   </si>
   <si>
     <t xml:space="preserve">4.91284465789795</t>
@@ -167,115 +167,115 @@
     <t xml:space="preserve">5.01403903961182</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94222402572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03362560272217</t>
+    <t xml:space="preserve">4.942223072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03362607955933</t>
   </si>
   <si>
     <t xml:space="preserve">5.04015398025513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09238386154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94875288009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99445295333862</t>
+    <t xml:space="preserve">5.09238338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94875192642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99445390701294</t>
   </si>
   <si>
     <t xml:space="preserve">4.84429264068604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0695333480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09891223907471</t>
+    <t xml:space="preserve">5.06953287124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09891271591187</t>
   </si>
   <si>
     <t xml:space="preserve">4.98792457580566</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0499472618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04341793060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05973958969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98466062545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02709674835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99973917007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03393650054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9621205329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91766309738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94502115249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85610723495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.890305519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89714479446411</t>
+    <t xml:space="preserve">5.04994678497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04341840744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05974054336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98466014862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02709722518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99973821640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03393602371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96212005615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91766357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9450216293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85610675811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89030504226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89714384078979</t>
   </si>
   <si>
     <t xml:space="preserve">4.79455089569092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82190895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98263931274414</t>
+    <t xml:space="preserve">4.82190942764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9826397895813</t>
   </si>
   <si>
     <t xml:space="preserve">4.92450284957886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00657844543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88346529006958</t>
+    <t xml:space="preserve">5.00657796859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88346481323242</t>
   </si>
   <si>
     <t xml:space="preserve">4.94844150543213</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95870065689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99289846420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86636638641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85268640518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93134164810181</t>
+    <t xml:space="preserve">4.95870113372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9928994178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86636590957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85268688201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93134260177612</t>
   </si>
   <si>
     <t xml:space="preserve">4.78771114349365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78429079055786</t>
+    <t xml:space="preserve">4.78429126739502</t>
   </si>
   <si>
     <t xml:space="preserve">4.82532835006714</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">4.77403163909912</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7227349281311</t>
+    <t xml:space="preserve">4.72273540496826</t>
   </si>
   <si>
     <t xml:space="preserve">4.67485761642456</t>
@@ -296,40 +296,40 @@
     <t xml:space="preserve">4.56200504302979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54148530960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53122663497925</t>
+    <t xml:space="preserve">4.54148578643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53122711181641</t>
   </si>
   <si>
     <t xml:space="preserve">4.6030421257019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63040018081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55516481399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58252334594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54832553863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45941066741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53464603424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52780723571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52096748352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64407968521118</t>
+    <t xml:space="preserve">4.63040065765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55516529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58252382278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54832601547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45941114425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53464651107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52780675888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52096796035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64407920837402</t>
   </si>
   <si>
     <t xml:space="preserve">4.74325370788574</t>
@@ -338,31 +338,31 @@
     <t xml:space="preserve">4.73983383178711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83558797836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92108249664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92792272567749</t>
+    <t xml:space="preserve">4.8355884552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92108297348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92792320251465</t>
   </si>
   <si>
     <t xml:space="preserve">4.98605918884277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96554040908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91424322128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97237968444824</t>
+    <t xml:space="preserve">4.96553993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91424369812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9723801612854</t>
   </si>
   <si>
     <t xml:space="preserve">4.96896028518677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86978530883789</t>
+    <t xml:space="preserve">4.86978578567505</t>
   </si>
   <si>
     <t xml:space="preserve">4.93818187713623</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">4.87320613861084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8629469871521</t>
+    <t xml:space="preserve">4.86294651031494</t>
   </si>
   <si>
     <t xml:space="preserve">4.76719236373901</t>
@@ -389,46 +389,46 @@
     <t xml:space="preserve">4.80822992324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76377201080322</t>
+    <t xml:space="preserve">4.76377296447754</t>
   </si>
   <si>
     <t xml:space="preserve">4.8424277305603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72957420349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84926700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81164932250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88688468933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02025699615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08865261077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10575103759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0647144317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04761600494385</t>
+    <t xml:space="preserve">4.72957468032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84926748275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81165027618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88688516616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02025651931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08865308761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10575199127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06471395492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04761552810669</t>
   </si>
   <si>
     <t xml:space="preserve">5.09549236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17756795883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23228454589844</t>
+    <t xml:space="preserve">5.17756748199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23228549957275</t>
   </si>
   <si>
     <t xml:space="preserve">5.12969017028809</t>
@@ -437,16 +437,16 @@
     <t xml:space="preserve">5.13994979858398</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1638879776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21176528930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30751895904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3006796836853</t>
+    <t xml:space="preserve">5.16388893127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2117657661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30751991271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30068063735962</t>
   </si>
   <si>
     <t xml:space="preserve">5.13311004638672</t>
@@ -458,31 +458,31 @@
     <t xml:space="preserve">5.16730785369873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19808578491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29725980758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47167015075684</t>
+    <t xml:space="preserve">5.19808626174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29726028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47166967391968</t>
   </si>
   <si>
     <t xml:space="preserve">5.40327405929565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36565637588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36223745346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46483039855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36907577514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39643383026123</t>
+    <t xml:space="preserve">5.36565589904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36223697662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46483087539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36907625198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39643526077271</t>
   </si>
   <si>
     <t xml:space="preserve">5.25964260101318</t>
@@ -494,85 +494,85 @@
     <t xml:space="preserve">5.46141052246094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43747186660767</t>
+    <t xml:space="preserve">5.43747234344482</t>
   </si>
   <si>
     <t xml:space="preserve">5.45457077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46824979782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47509002685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39985370635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41695213317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4306321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45799016952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50586795806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52980661392212</t>
+    <t xml:space="preserve">5.46824932098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47508955001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39985418319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41695261001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43063259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4579906463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50586843490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52980613708496</t>
   </si>
   <si>
     <t xml:space="preserve">5.60846185684204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68369722366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73157405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88204479217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93676233291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94360065460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05645370483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94018173217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04961490631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07355308532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02567625045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97437953948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04277563095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17272758483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39501428604126</t>
+    <t xml:space="preserve">5.68369817733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73157453536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88204526901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9367618560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94360160827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0564546585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94018220901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04961585998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07355260848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02567672729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97437906265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04277515411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17272806167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39501476287842</t>
   </si>
   <si>
     <t xml:space="preserve">6.37449550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46683025360107</t>
+    <t xml:space="preserve">6.46682929992676</t>
   </si>
   <si>
     <t xml:space="preserve">6.32661867141724</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">6.11117124557495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8991436958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00515747070312</t>
+    <t xml:space="preserve">5.89914417266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00515699386597</t>
   </si>
   <si>
     <t xml:space="preserve">6.22402429580688</t>
@@ -599,34 +599,34 @@
     <t xml:space="preserve">6.40527391433716</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48050975799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41211318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44973039627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4360523223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52838563919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66859817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99689769744873</t>
+    <t xml:space="preserve">6.48050928115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41211366653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44973134994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43605184555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52838611602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66859769821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99689722061157</t>
   </si>
   <si>
     <t xml:space="preserve">6.94218111038208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12001037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46882963180542</t>
+    <t xml:space="preserve">7.1200098991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4688286781311</t>
   </si>
   <si>
     <t xml:space="preserve">7.66717767715454</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">8.20066452026367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40585136413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64523696899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27590179443359</t>
+    <t xml:space="preserve">8.40585231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64523887634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27590274810791</t>
   </si>
   <si>
     <t xml:space="preserve">8.35113620758057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28957939147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24170207977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33745574951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33061695098877</t>
+    <t xml:space="preserve">8.28958034515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24170303344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33745670318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33061790466309</t>
   </si>
   <si>
     <t xml:space="preserve">8.31693840026855</t>
@@ -665,46 +665,46 @@
     <t xml:space="preserve">8.26906108856201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22118282318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1185884475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30325794219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48108863830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72047328948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7136344909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7946891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49782371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52750968933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07478713989258</t>
+    <t xml:space="preserve">8.22118473052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11859035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30325984954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48108768463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72047424316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71363544464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79469013214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49782276153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52751064300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07478809356689</t>
   </si>
   <si>
     <t xml:space="preserve">8.31228160858154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43102836608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37165451049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97830486297607</t>
+    <t xml:space="preserve">8.43102741241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37165355682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97830677032471</t>
   </si>
   <si>
     <t xml:space="preserve">7.88924551010132</t>
@@ -716,43 +716,43 @@
     <t xml:space="preserve">8.26033020019531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21580028533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64625549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75758266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80211067199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69078826904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57946300506592</t>
+    <t xml:space="preserve">8.21579933166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64625644683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75758171081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8021125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69078731536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57946109771729</t>
   </si>
   <si>
     <t xml:space="preserve">8.66109943389893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54977607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52008724212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53493022918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60172653198242</t>
+    <t xml:space="preserve">8.54977512359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52008819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53493213653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60172748565674</t>
   </si>
   <si>
     <t xml:space="preserve">8.48298072814941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59430599212646</t>
+    <t xml:space="preserve">8.59430503845215</t>
   </si>
   <si>
     <t xml:space="preserve">8.46813678741455</t>
@@ -761,10 +761,10 @@
     <t xml:space="preserve">8.14900398254395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3197021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12673950195312</t>
+    <t xml:space="preserve">8.31970310211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12673854827881</t>
   </si>
   <si>
     <t xml:space="preserve">8.46071434020996</t>
@@ -773,37 +773,37 @@
     <t xml:space="preserve">8.58688354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70562934875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84664249420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69820880889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74273872375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56461906433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43844890594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40876293182373</t>
+    <t xml:space="preserve">8.7056303024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84664154052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69820785522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7427396774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56461811065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43844985961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40876388549805</t>
   </si>
   <si>
     <t xml:space="preserve">8.34939002990723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42360687255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54235458374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63141441345215</t>
+    <t xml:space="preserve">8.42360591888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54235363006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63141250610352</t>
   </si>
   <si>
     <t xml:space="preserve">8.61657047271729</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">8.63883495330811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66852188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77984809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88374996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83922004699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82437801361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68336391448975</t>
+    <t xml:space="preserve">8.66852283477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77984619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88375091552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83922100067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82437896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68336582183838</t>
   </si>
   <si>
     <t xml:space="preserve">8.6091480255127</t>
@@ -836,34 +836,34 @@
     <t xml:space="preserve">8.57204055786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49040126800537</t>
+    <t xml:space="preserve">8.49040031433105</t>
   </si>
   <si>
     <t xml:space="preserve">8.47555828094482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78726959228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71305179595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65367889404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62399101257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75016021728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90601634979248</t>
+    <t xml:space="preserve">8.78726863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71305274963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65367794036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62399291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75015926361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9060173034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.89859390258789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94312477111816</t>
+    <t xml:space="preserve">8.94312381744385</t>
   </si>
   <si>
     <t xml:space="preserve">8.77242565155029</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">8.87632846832275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97281169891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09155654907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21772575378418</t>
+    <t xml:space="preserve">8.97281074523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0915584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2177267074585</t>
   </si>
   <si>
     <t xml:space="preserve">9.52201461791992</t>
@@ -896,46 +896,46 @@
     <t xml:space="preserve">9.45522117614746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47748565673828</t>
+    <t xml:space="preserve">9.47748470306396</t>
   </si>
   <si>
     <t xml:space="preserve">9.5368595123291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35873794555664</t>
+    <t xml:space="preserve">9.35873699188232</t>
   </si>
   <si>
     <t xml:space="preserve">9.59623146057129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64076232910156</t>
+    <t xml:space="preserve">9.64076137542725</t>
   </si>
   <si>
     <t xml:space="preserve">9.90794277191162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89309883117676</t>
+    <t xml:space="preserve">9.89309787750244</t>
   </si>
   <si>
     <t xml:space="preserve">9.76693058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72982215881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99700164794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95247268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.05637550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64818382263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95989418029785</t>
+    <t xml:space="preserve">9.72982120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99700260162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95247364044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0563764572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64818477630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95989513397217</t>
   </si>
   <si>
     <t xml:space="preserve">9.82630443572998</t>
@@ -944,46 +944,46 @@
     <t xml:space="preserve">9.81146144866943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75208759307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85598945617676</t>
+    <t xml:space="preserve">9.75208854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85599040985107</t>
   </si>
   <si>
     <t xml:space="preserve">9.86341190338135</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0415325164795</t>
+    <t xml:space="preserve">10.0415334701538</t>
   </si>
   <si>
     <t xml:space="preserve">10.0118465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94505023956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90052032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83179950714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97088289260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25290679931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16384887695312</t>
+    <t xml:space="preserve">9.9450511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90052127838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83180046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97088432312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25290775299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16384792327881</t>
   </si>
   <si>
     <t xml:space="preserve">8.19353485107422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67594432830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50524616241455</t>
+    <t xml:space="preserve">8.67594337463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50524520874023</t>
   </si>
   <si>
     <t xml:space="preserve">8.02283573150635</t>
@@ -992,94 +992,94 @@
     <t xml:space="preserve">8.06736660003662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98572826385498</t>
+    <t xml:space="preserve">7.98572683334351</t>
   </si>
   <si>
     <t xml:space="preserve">7.7853422164917</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76307678222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70370483398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82987213134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64433145523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7259693145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04510021209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14158344268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91893291473389</t>
+    <t xml:space="preserve">7.76307773590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70370388031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82987308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64433097839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72596836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04510116577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14158248901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91893243789673</t>
   </si>
   <si>
     <t xml:space="preserve">8.08963108062744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11931800842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11189556121826</t>
+    <t xml:space="preserve">8.11931705474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11189651489258</t>
   </si>
   <si>
     <t xml:space="preserve">8.09705257415771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00057029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1341609954834</t>
+    <t xml:space="preserve">8.00057125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13416004180908</t>
   </si>
   <si>
     <t xml:space="preserve">8.28259468078613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20837783813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34196758270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4458703994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92085838317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0247631072998</t>
+    <t xml:space="preserve">8.20837879180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34196662902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44587135314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92086029052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02476406097412</t>
   </si>
   <si>
     <t xml:space="preserve">8.32712459564209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26775169372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71854782104492</t>
+    <t xml:space="preserve">8.2677526473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">8.03025817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01541423797607</t>
+    <t xml:space="preserve">8.01541328430176</t>
   </si>
   <si>
     <t xml:space="preserve">8.10447406768799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17869091033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22322082519531</t>
+    <t xml:space="preserve">8.17869281768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22321891784668</t>
   </si>
   <si>
     <t xml:space="preserve">8.40134143829346</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">9.0544490814209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93570232391357</t>
+    <t xml:space="preserve">8.93570327758789</t>
   </si>
   <si>
     <t xml:space="preserve">8.72789573669434</t>
@@ -1097,88 +1097,88 @@
     <t xml:space="preserve">8.89117240905762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00991821289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.277099609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30678558349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24741268157959</t>
+    <t xml:space="preserve">9.00992012023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27710056304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30678749084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24741363525391</t>
   </si>
   <si>
     <t xml:space="preserve">9.35131645202637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52943706512451</t>
+    <t xml:space="preserve">9.52943801879883</t>
   </si>
   <si>
     <t xml:space="preserve">9.47006320953369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39584636688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54428005218506</t>
+    <t xml:space="preserve">9.39584732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54428100585938</t>
   </si>
   <si>
     <t xml:space="preserve">9.87083435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6036548614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0637969970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87998390197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54299354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55830955505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.726806640625</t>
+    <t xml:space="preserve">9.60365295410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0637979507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87998485565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54299163818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55831050872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72680568695068</t>
   </si>
   <si>
     <t xml:space="preserve">9.60426330566406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46640205383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57362747192383</t>
+    <t xml:space="preserve">9.46640300750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57362842559814</t>
   </si>
   <si>
     <t xml:space="preserve">9.6195821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63489818572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68085384368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48172187805176</t>
+    <t xml:space="preserve">9.63490009307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68085289001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48172092437744</t>
   </si>
   <si>
     <t xml:space="preserve">9.43576812744141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34385967254639</t>
+    <t xml:space="preserve">9.3438606262207</t>
   </si>
   <si>
     <t xml:space="preserve">9.3132266998291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08345794677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59328746795654</t>
+    <t xml:space="preserve">9.08345699310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59328842163086</t>
   </si>
   <si>
     <t xml:space="preserve">8.53201770782471</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">9.28258991241455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20600128173828</t>
+    <t xml:space="preserve">9.20600032806396</t>
   </si>
   <si>
     <t xml:space="preserve">9.49703884124756</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">9.51235675811768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52767467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38981437683105</t>
+    <t xml:space="preserve">9.52767372131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38981533050537</t>
   </si>
   <si>
     <t xml:space="preserve">9.35917854309082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19068241119385</t>
+    <t xml:space="preserve">9.19068336486816</t>
   </si>
   <si>
     <t xml:space="preserve">9.86466598510742</t>
@@ -1226,61 +1226,61 @@
     <t xml:space="preserve">9.42045021057129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2213191986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25195407867432</t>
+    <t xml:space="preserve">9.22131824493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25195503234863</t>
   </si>
   <si>
     <t xml:space="preserve">9.11409473419189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1447286605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26727294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45108509063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69616985321045</t>
+    <t xml:space="preserve">9.14472961425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26727199554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45108699798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69617080688477</t>
   </si>
   <si>
     <t xml:space="preserve">9.6502161026001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80773830413818</t>
+    <t xml:space="preserve">8.80773735046387</t>
   </si>
   <si>
     <t xml:space="preserve">9.06814002990723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37449836730957</t>
+    <t xml:space="preserve">9.37449645996094</t>
   </si>
   <si>
     <t xml:space="preserve">9.03750419616699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12941074371338</t>
+    <t xml:space="preserve">9.1294116973877</t>
   </si>
   <si>
     <t xml:space="preserve">9.02218723297119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91496276855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94559860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17536449432373</t>
+    <t xml:space="preserve">8.91496181488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94559764862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17536544799805</t>
   </si>
   <si>
     <t xml:space="preserve">9.00686931610107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95657253265381</t>
+    <t xml:space="preserve">9.95657348632812</t>
   </si>
   <si>
     <t xml:space="preserve">10.0331621170044</t>
@@ -1289,31 +1289,31 @@
     <t xml:space="preserve">9.91061878204346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97189140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78807640075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7574405670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09877681732178</t>
+    <t xml:space="preserve">9.97189044952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78807544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75744247436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09877586364746</t>
   </si>
   <si>
     <t xml:space="preserve">8.86900901794434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74646663665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73114681243896</t>
+    <t xml:space="preserve">8.7464656829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7311487197876</t>
   </si>
   <si>
     <t xml:space="preserve">8.51669883728027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47074508666992</t>
+    <t xml:space="preserve">8.47074604034424</t>
   </si>
   <si>
     <t xml:space="preserve">8.42479228973389</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">8.01121139526367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.225661277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36352157592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65455913543701</t>
+    <t xml:space="preserve">8.22566032409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3635196685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65456008911133</t>
   </si>
   <si>
     <t xml:space="preserve">8.77710151672363</t>
@@ -1337,16 +1337,16 @@
     <t xml:space="preserve">8.8383731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9302806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62392425537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71582984924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50138187408447</t>
+    <t xml:space="preserve">8.93027973175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62392330169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71583080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50138092041016</t>
   </si>
   <si>
     <t xml:space="preserve">8.82305526733398</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">8.60860443115234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57796955108643</t>
+    <t xml:space="preserve">8.57797050476074</t>
   </si>
   <si>
     <t xml:space="preserve">8.34820365905762</t>
@@ -1370,49 +1370,49 @@
     <t xml:space="preserve">8.37883853912354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28693199157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27161407470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39415740966797</t>
+    <t xml:space="preserve">8.28693294525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27161502838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39415645599365</t>
   </si>
   <si>
     <t xml:space="preserve">8.13375473022461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11843681335449</t>
+    <t xml:space="preserve">8.11843585968018</t>
   </si>
   <si>
     <t xml:space="preserve">8.45542812347412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79242038726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85369205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70051193237305</t>
+    <t xml:space="preserve">8.79241943359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85369110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70051288604736</t>
   </si>
   <si>
     <t xml:space="preserve">8.66987705230713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68519592285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54733467102051</t>
+    <t xml:space="preserve">8.68519496917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54733562469482</t>
   </si>
   <si>
     <t xml:space="preserve">8.440110206604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88432693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40513229370117</t>
+    <t xml:space="preserve">8.88432598114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40513134002686</t>
   </si>
   <si>
     <t xml:space="preserve">9.92593765258789</t>
@@ -1421,25 +1421,25 @@
     <t xml:space="preserve">9.80339527130127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29790687561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22897815704346</t>
+    <t xml:space="preserve">9.29790782928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22897720336914</t>
   </si>
   <si>
     <t xml:space="preserve">9.07579898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15238857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99921131134033</t>
+    <t xml:space="preserve">9.15238761901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99921035766602</t>
   </si>
   <si>
     <t xml:space="preserve">9.59735012054443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31742668151855</t>
+    <t xml:space="preserve">9.31742763519287</t>
   </si>
   <si>
     <t xml:space="preserve">8.79757022857666</t>
@@ -1457,61 +1457,61 @@
     <t xml:space="preserve">9.23744964599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27743911743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47738265991211</t>
+    <t xml:space="preserve">9.27743816375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47738361358643</t>
   </si>
   <si>
     <t xml:space="preserve">9.3574161529541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51737308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67732906341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63733959197998</t>
+    <t xml:space="preserve">9.51737213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67732810974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63733863830566</t>
   </si>
   <si>
     <t xml:space="preserve">9.39740657806396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19746112823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07749366760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43739414215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5573616027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11748123168945</t>
+    <t xml:space="preserve">9.19746208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07749462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4373950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55736064910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11748313903809</t>
   </si>
   <si>
     <t xml:space="preserve">8.7175931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95752620697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99751663208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.157470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91753768920898</t>
+    <t xml:space="preserve">8.9575252532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99751567840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15747165679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91753673553467</t>
   </si>
   <si>
     <t xml:space="preserve">10.7970190048218</t>
   </si>
   <si>
-    <t xml:space="preserve">10.357141494751</t>
+    <t xml:space="preserve">10.3571405410767</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772171020508</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">10.117205619812</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91726207733154</t>
+    <t xml:space="preserve">9.91726112365723</t>
   </si>
   <si>
     <t xml:space="preserve">9.997239112854</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">9.71731662750244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7972936630249</t>
+    <t xml:space="preserve">9.79729461669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.83728408813477</t>
@@ -1550,22 +1550,22 @@
     <t xml:space="preserve">10.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2371740341187</t>
+    <t xml:space="preserve">10.2371730804443</t>
   </si>
   <si>
     <t xml:space="preserve">10.3971290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5570850372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4771070480347</t>
+    <t xml:space="preserve">10.5570859909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4771089553833</t>
   </si>
   <si>
     <t xml:space="preserve">10.1971845626831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170965194702</t>
+    <t xml:space="preserve">10.5170955657959</t>
   </si>
   <si>
     <t xml:space="preserve">10.9969635009766</t>
@@ -1577,13 +1577,13 @@
     <t xml:space="preserve">11.3168754577637</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2368965148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3568639755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1969089508057</t>
+    <t xml:space="preserve">11.2368974685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3568630218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1969079971313</t>
   </si>
   <si>
     <t xml:space="preserve">10.8370084762573</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">11.1569194793701</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0369529724121</t>
+    <t xml:space="preserve">11.0369520187378</t>
   </si>
   <si>
     <t xml:space="preserve">10.8769979476929</t>
@@ -1601,13 +1601,13 @@
     <t xml:space="preserve">10.9169855117798</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9569730758667</t>
+    <t xml:space="preserve">10.9569749832153</t>
   </si>
   <si>
     <t xml:space="preserve">10.7570295333862</t>
   </si>
   <si>
-    <t xml:space="preserve">10.597074508667</t>
+    <t xml:space="preserve">10.5970735549927</t>
   </si>
   <si>
     <t xml:space="preserve">10.4371185302734</t>
@@ -1628,28 +1628,28 @@
     <t xml:space="preserve">10.7170400619507</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11775684356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16602182388306</t>
+    <t xml:space="preserve">8.11775779724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1660213470459</t>
   </si>
   <si>
     <t xml:space="preserve">7.88582229614258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46993780136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03805637359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91009187698364</t>
+    <t xml:space="preserve">7.46993732452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03805685043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9100923538208</t>
   </si>
   <si>
     <t xml:space="preserve">6.39823341369629</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20628643035889</t>
+    <t xml:space="preserve">6.20628595352173</t>
   </si>
   <si>
     <t xml:space="preserve">5.99834394454956</t>
@@ -1658,19 +1658,19 @@
     <t xml:space="preserve">6.55818891525269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30998277664185</t>
+    <t xml:space="preserve">7.30998229980469</t>
   </si>
   <si>
     <t xml:space="preserve">7.40595531463623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32597827911377</t>
+    <t xml:space="preserve">7.32597732543945</t>
   </si>
   <si>
     <t xml:space="preserve">7.11803436279297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73414039611816</t>
+    <t xml:space="preserve">6.73414087295532</t>
   </si>
   <si>
     <t xml:space="preserve">6.9740743637085</t>
@@ -1679,31 +1679,31 @@
     <t xml:space="preserve">7.29398584365845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15002536773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86210489273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8141188621521</t>
+    <t xml:space="preserve">7.15002489089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86210536956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81411933898926</t>
   </si>
   <si>
     <t xml:space="preserve">6.76613140106201</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94208335876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79812240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92608785629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78212690353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83011341094971</t>
+    <t xml:space="preserve">6.94208383560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79812288284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92608690261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78212738037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83011436462402</t>
   </si>
   <si>
     <t xml:space="preserve">6.92877864837646</t>
@@ -1715,16 +1715,16 @@
     <t xml:space="preserve">6.89601898193359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96153879165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73221778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74859762191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05981922149658</t>
+    <t xml:space="preserve">6.96153926849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73221826553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74859809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05981874465942</t>
   </si>
   <si>
     <t xml:space="preserve">7.12533950805664</t>
@@ -1733,13 +1733,13 @@
     <t xml:space="preserve">7.22362041473389</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55122327804565</t>
+    <t xml:space="preserve">7.5512228012085</t>
   </si>
   <si>
     <t xml:space="preserve">7.56760263442993</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02624607086182</t>
+    <t xml:space="preserve">8.0262451171875</t>
   </si>
   <si>
     <t xml:space="preserve">8.31289577484131</t>
@@ -1748,31 +1748,31 @@
     <t xml:space="preserve">8.39479732513428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72239875793457</t>
+    <t xml:space="preserve">8.72239971160889</t>
   </si>
   <si>
     <t xml:space="preserve">8.76334953308105</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88620185852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41855335235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92714977264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13190174102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96809959411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33665180206299</t>
+    <t xml:space="preserve">8.88620090484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17285060882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41855430603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92715072631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13190078735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96810054779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3366527557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.84524917602539</t>
@@ -1784,43 +1784,43 @@
     <t xml:space="preserve">9.21380233764648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25475120544434</t>
+    <t xml:space="preserve">9.25475215911865</t>
   </si>
   <si>
     <t xml:space="preserve">9.0090503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64049816131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09176540374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17366600036621</t>
+    <t xml:space="preserve">8.64049911499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09176635742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17366695404053</t>
   </si>
   <si>
     <t xml:space="preserve">8.1900463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10814571380615</t>
+    <t xml:space="preserve">8.10814476013184</t>
   </si>
   <si>
     <t xml:space="preserve">8.15728664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96072626113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87882375717163</t>
+    <t xml:space="preserve">7.9607253074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87882423400879</t>
   </si>
   <si>
     <t xml:space="preserve">7.71502304077148</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7805438041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58398342132568</t>
+    <t xml:space="preserve">7.78054332733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58398294448853</t>
   </si>
   <si>
     <t xml:space="preserve">7.51846265792847</t>
@@ -1829,64 +1829,64 @@
     <t xml:space="preserve">7.5348424911499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33828163146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48570346832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61674404144287</t>
+    <t xml:space="preserve">7.33828115463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4857029914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61674356460571</t>
   </si>
   <si>
     <t xml:space="preserve">7.69864320755005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76416397094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73140382766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79692459106445</t>
+    <t xml:space="preserve">7.76416301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73140335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79692506790161</t>
   </si>
   <si>
     <t xml:space="preserve">7.66588306427002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63312339782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64950323104858</t>
+    <t xml:space="preserve">7.63312292098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64950275421143</t>
   </si>
   <si>
     <t xml:space="preserve">7.68226385116577</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82968473434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74778366088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43656253814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6003623008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35466194152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40380239486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24000072479248</t>
+    <t xml:space="preserve">7.82968521118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74778413772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43656206130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60036277770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35466146469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40380191802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2400016784668</t>
   </si>
   <si>
     <t xml:space="preserve">7.1908597946167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79773855209351</t>
+    <t xml:space="preserve">6.79773807525635</t>
   </si>
   <si>
     <t xml:space="preserve">6.68307733535767</t>
@@ -1895,10 +1895,10 @@
     <t xml:space="preserve">6.56841707229614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38823652267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22443532943726</t>
+    <t xml:space="preserve">6.3882360458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2244348526001</t>
   </si>
   <si>
     <t xml:space="preserve">6.48651647567749</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">6.42099618911743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71583795547485</t>
+    <t xml:space="preserve">6.7158374786377</t>
   </si>
   <si>
     <t xml:space="preserve">6.84687852859497</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">7.04344034194946</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92796468734741</t>
+    <t xml:space="preserve">7.92796516418457</t>
   </si>
   <si>
     <t xml:space="preserve">8.5176477432251</t>
@@ -1925,13 +1925,13 @@
     <t xml:space="preserve">8.27194690704346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97710418701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8460636138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12452507019043</t>
+    <t xml:space="preserve">7.97710466384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84606313705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12452697753906</t>
   </si>
   <si>
     <t xml:space="preserve">8.59954833984375</t>
@@ -1940,34 +1940,34 @@
     <t xml:space="preserve">8.43574810028076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55859851837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68144989013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47669887542725</t>
+    <t xml:space="preserve">8.5585994720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6814489364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47669792175293</t>
   </si>
   <si>
     <t xml:space="preserve">8.35384654998779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23099613189697</t>
+    <t xml:space="preserve">8.23099803924561</t>
   </si>
   <si>
     <t xml:space="preserve">8.04262447357178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94434452056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86244487762451</t>
+    <t xml:space="preserve">7.94434547424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86244535446167</t>
   </si>
   <si>
     <t xml:space="preserve">8.00986576080322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05900573730469</t>
+    <t xml:space="preserve">8.059006690979</t>
   </si>
   <si>
     <t xml:space="preserve">9.45950317382812</t>
@@ -1979,25 +1979,25 @@
     <t xml:space="preserve">10.1556568145752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86900615692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62330436706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50045394897461</t>
+    <t xml:space="preserve">9.86900520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62330532073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50045299530029</t>
   </si>
   <si>
     <t xml:space="preserve">9.37760257720947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58235454559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70520401000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05000019073486</t>
+    <t xml:space="preserve">9.58235359191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70520496368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05000114440918</t>
   </si>
   <si>
     <t xml:space="preserve">9.54140377044678</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">9.22513580322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18320083618164</t>
+    <t xml:space="preserve">9.18320274353027</t>
   </si>
   <si>
     <t xml:space="preserve">9.09933853149414</t>
@@ -2027,13 +2027,13 @@
     <t xml:space="preserve">9.4347972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35093212127686</t>
+    <t xml:space="preserve">9.35093116760254</t>
   </si>
   <si>
     <t xml:space="preserve">9.64445972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51866245269775</t>
+    <t xml:space="preserve">9.51866340637207</t>
   </si>
   <si>
     <t xml:space="preserve">9.47672939300537</t>
@@ -2042,10 +2042,10 @@
     <t xml:space="preserve">9.77025604248047</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6025276184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7283239364624</t>
+    <t xml:space="preserve">9.60252666473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72832489013672</t>
   </si>
   <si>
     <t xml:space="preserve">10.3153791427612</t>
@@ -2054,19 +2054,19 @@
     <t xml:space="preserve">10.1895809173584</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2315139770508</t>
+    <t xml:space="preserve">10.2315130233765</t>
   </si>
   <si>
     <t xml:space="preserve">10.1057167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.357310295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2734451293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1476488113403</t>
+    <t xml:space="preserve">10.3573112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2734460830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.147647857666</t>
   </si>
   <si>
     <t xml:space="preserve">10.0218515396118</t>
@@ -2078,10 +2078,10 @@
     <t xml:space="preserve">9.81218910217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8960542678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26706790924072</t>
+    <t xml:space="preserve">9.89605522155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26706695556641</t>
   </si>
   <si>
     <t xml:space="preserve">9.97991847991943</t>
@@ -2090,19 +2090,19 @@
     <t xml:space="preserve">9.68639183044434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05740547180176</t>
+    <t xml:space="preserve">9.05740451812744</t>
   </si>
   <si>
     <t xml:space="preserve">8.97354030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.399242401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5669736862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7766361236572</t>
+    <t xml:space="preserve">10.3992433547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5669727325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7766351699829</t>
   </si>
   <si>
     <t xml:space="preserve">10.7347030639648</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">11.321756362915</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9443655014038</t>
+    <t xml:space="preserve">10.9443645477295</t>
   </si>
   <si>
     <t xml:space="preserve">11.2378911972046</t>
@@ -2123,67 +2123,67 @@
     <t xml:space="preserve">11.1959600448608</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4056224822998</t>
+    <t xml:space="preserve">11.4056234359741</t>
   </si>
   <si>
     <t xml:space="preserve">11.1540269851685</t>
   </si>
   <si>
-    <t xml:space="preserve">11.783013343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7410821914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0346088409424</t>
+    <t xml:space="preserve">11.7830142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.741081237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0346078872681</t>
   </si>
   <si>
     <t xml:space="preserve">11.6152839660645</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6572160720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1120939254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9862976074219</t>
+    <t xml:space="preserve">11.6572151184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1120948791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9862985610962</t>
   </si>
   <si>
     <t xml:space="preserve">11.0701627731323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4894857406616</t>
+    <t xml:space="preserve">11.4894866943359</t>
   </si>
   <si>
     <t xml:space="preserve">11.3636894226074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6991481781006</t>
+    <t xml:space="preserve">11.6991491317749</t>
   </si>
   <si>
     <t xml:space="preserve">11.5733509063721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5314197540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0282297134399</t>
+    <t xml:space="preserve">11.531418800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0282287597656</t>
   </si>
   <si>
     <t xml:space="preserve">10.4831075668335</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5250415802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.608904838562</t>
+    <t xml:space="preserve">10.5250406265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6089057922363</t>
   </si>
   <si>
     <t xml:space="preserve">10.818567276001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9024314880371</t>
+    <t xml:space="preserve">10.9024324417114</t>
   </si>
   <si>
     <t xml:space="preserve">11.4475536346436</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">11.1378631591797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.09485912323</t>
+    <t xml:space="preserve">11.0948600769043</t>
   </si>
   <si>
     <t xml:space="preserve">11.3958826065063</t>
@@ -2201,10 +2201,10 @@
     <t xml:space="preserve">11.6539030075073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8259162902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6108999252319</t>
+    <t xml:space="preserve">11.8259153366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6108989715576</t>
   </si>
   <si>
     <t xml:space="preserve">11.6969060897827</t>
@@ -2225,10 +2225,10 @@
     <t xml:space="preserve">11.2238702774048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0518569946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0088539123535</t>
+    <t xml:space="preserve">11.0518560409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0088529586792</t>
   </si>
   <si>
     <t xml:space="preserve">10.8368396759033</t>
@@ -2237,13 +2237,13 @@
     <t xml:space="preserve">10.9658489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7508335113525</t>
+    <t xml:space="preserve">10.7508325576782</t>
   </si>
   <si>
     <t xml:space="preserve">10.8798427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6648254394531</t>
+    <t xml:space="preserve">10.6648263931274</t>
   </si>
   <si>
     <t xml:space="preserve">10.9228458404541</t>
@@ -2261,16 +2261,16 @@
     <t xml:space="preserve">10.1487865447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97677230834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89076614379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76175689697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84776210784912</t>
+    <t xml:space="preserve">9.97677326202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89076709747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76175594329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84776306152344</t>
   </si>
   <si>
     <t xml:space="preserve">9.46073341369629</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">9.54673957824707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2457160949707</t>
+    <t xml:space="preserve">9.24571704864502</t>
   </si>
   <si>
     <t xml:space="preserve">9.20271301269531</t>
@@ -2291,10 +2291,10 @@
     <t xml:space="preserve">9.15970993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">10.277795791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67574882507324</t>
+    <t xml:space="preserve">10.2777967453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67574977874756</t>
   </si>
   <si>
     <t xml:space="preserve">10.0197763442993</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">9.93377017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80475997924805</t>
+    <t xml:space="preserve">9.80475902557373</t>
   </si>
   <si>
     <t xml:space="preserve">9.71875286102295</t>
@@ -2315,10 +2315,10 @@
     <t xml:space="preserve">9.58974266052246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41772937774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3317232131958</t>
+    <t xml:space="preserve">9.41772842407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33172225952148</t>
   </si>
   <si>
     <t xml:space="preserve">9.37472534179688</t>
@@ -2327,22 +2327,22 @@
     <t xml:space="preserve">9.50373649597168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63274669647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6218233108521</t>
+    <t xml:space="preserve">9.63274574279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6218223571777</t>
   </si>
   <si>
     <t xml:space="preserve">11.3098764419556</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2668724060059</t>
+    <t xml:space="preserve">11.2668733596802</t>
   </si>
   <si>
     <t xml:space="preserve">11.1808662414551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7938356399536</t>
+    <t xml:space="preserve">10.7938365936279</t>
   </si>
   <si>
     <t xml:space="preserve">11.352879524231</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">11.4818897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.169942855835</t>
+    <t xml:space="preserve">12.1699419021606</t>
   </si>
   <si>
     <t xml:space="preserve">11.9549255371094</t>
@@ -2375,37 +2375,40 @@
     <t xml:space="preserve">12.4709663391113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2989530563354</t>
+    <t xml:space="preserve">12.2989540100098</t>
   </si>
   <si>
     <t xml:space="preserve">12.513970375061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5569725036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6429796218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2559490203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3849582672119</t>
+    <t xml:space="preserve">12.5569734573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6429786682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2559499740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3849592208862</t>
   </si>
   <si>
     <t xml:space="preserve">12.5999755859375</t>
   </si>
   <si>
+    <t xml:space="preserve">12.6859827041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7719898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7289867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9997701644897</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.6859817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7719898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7289867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9997701644897</t>
   </si>
   <si>
     <t xml:space="preserve">12.8204641342163</t>
@@ -51982,7 +51985,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1871" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -52008,7 +52011,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52034,7 +52037,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1873" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52086,7 +52089,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1875" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -52112,7 +52115,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1876" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -52138,7 +52141,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1877" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52164,7 +52167,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -52216,7 +52219,7 @@
         <v>15</v>
       </c>
       <c r="G1880" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52268,7 +52271,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1882" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52294,7 +52297,7 @@
         <v>14.75</v>
       </c>
       <c r="G1883" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52320,7 +52323,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52346,7 +52349,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1885" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52372,7 +52375,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52398,7 +52401,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1887" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52424,7 +52427,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1888" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52450,7 +52453,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1889" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52476,7 +52479,7 @@
         <v>15</v>
       </c>
       <c r="G1890" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52502,7 +52505,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52528,7 +52531,7 @@
         <v>14.75</v>
       </c>
       <c r="G1892" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52554,7 +52557,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1893" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52580,7 +52583,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52606,7 +52609,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1895" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52632,7 +52635,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52658,7 +52661,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1897" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52684,7 +52687,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1898" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52710,7 +52713,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1899" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52736,7 +52739,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1900" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52762,7 +52765,7 @@
         <v>14.75</v>
       </c>
       <c r="G1901" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52788,7 +52791,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1902" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52814,7 +52817,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52840,7 +52843,7 @@
         <v>14.75</v>
       </c>
       <c r="G1904" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52866,7 +52869,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1905" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52892,7 +52895,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1906" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52918,7 +52921,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52944,7 +52947,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52970,7 +52973,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1909" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52996,7 +52999,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1910" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53022,7 +53025,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1911" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53048,7 +53051,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1912" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -53074,7 +53077,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1913" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53100,7 +53103,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1914" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53126,7 +53129,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53204,7 +53207,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1918" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53256,7 +53259,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1920" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53282,7 +53285,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1921" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53308,7 +53311,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53334,7 +53337,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1923" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53360,7 +53363,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1924" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53386,7 +53389,7 @@
         <v>14.75</v>
       </c>
       <c r="G1925" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53412,7 +53415,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1926" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53438,7 +53441,7 @@
         <v>14.75</v>
       </c>
       <c r="G1927" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53464,7 +53467,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1928" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53490,7 +53493,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1929" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53516,7 +53519,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1930" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53542,7 +53545,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1931" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53568,7 +53571,7 @@
         <v>15.75</v>
       </c>
       <c r="G1932" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53594,7 +53597,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53620,7 +53623,7 @@
         <v>15.75</v>
       </c>
       <c r="G1934" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53646,7 +53649,7 @@
         <v>16.5</v>
       </c>
       <c r="G1935" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53672,7 +53675,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1936" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53698,7 +53701,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53724,7 +53727,7 @@
         <v>15.5</v>
       </c>
       <c r="G1938" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53750,7 +53753,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1939" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53776,7 +53779,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1940" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53802,7 +53805,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53828,7 +53831,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1942" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53854,7 +53857,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1943" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53880,7 +53883,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1944" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53906,7 +53909,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1945" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53932,7 +53935,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1946" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53958,7 +53961,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1947" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53984,7 +53987,7 @@
         <v>15.75</v>
       </c>
       <c r="G1948" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54010,7 +54013,7 @@
         <v>15.5</v>
       </c>
       <c r="G1949" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54036,7 +54039,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54062,7 +54065,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1951" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54088,7 +54091,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1952" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54114,7 +54117,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1953" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54140,7 +54143,7 @@
         <v>15.25</v>
       </c>
       <c r="G1954" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54166,7 +54169,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1955" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54192,7 +54195,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1956" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54218,7 +54221,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1957" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54244,7 +54247,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1958" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54270,7 +54273,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54296,7 +54299,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1960" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54322,7 +54325,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1961" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54348,7 +54351,7 @@
         <v>15.5</v>
       </c>
       <c r="G1962" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54374,7 +54377,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1963" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54400,7 +54403,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54426,7 +54429,7 @@
         <v>16</v>
       </c>
       <c r="G1965" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54452,7 +54455,7 @@
         <v>16</v>
       </c>
       <c r="G1966" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -54478,7 +54481,7 @@
         <v>15.75</v>
       </c>
       <c r="G1967" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54504,7 +54507,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1968" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54530,7 +54533,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1969" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54556,7 +54559,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1970" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54582,7 +54585,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1971" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54608,7 +54611,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1972" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54634,7 +54637,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1973" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54660,7 +54663,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1974" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54686,7 +54689,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1975" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54712,7 +54715,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1976" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54738,7 +54741,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54764,7 +54767,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1978" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54790,7 +54793,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1979" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54816,7 +54819,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1980" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54842,7 +54845,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1981" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54868,7 +54871,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54894,7 +54897,7 @@
         <v>16</v>
       </c>
       <c r="G1983" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54920,7 +54923,7 @@
         <v>16.5</v>
       </c>
       <c r="G1984" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54946,7 +54949,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1985" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54972,7 +54975,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1986" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54998,7 +55001,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1987" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55024,7 +55027,7 @@
         <v>15.75</v>
       </c>
       <c r="G1988" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55050,7 +55053,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1989" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55076,7 +55079,7 @@
         <v>15.75</v>
       </c>
       <c r="G1990" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55102,7 +55105,7 @@
         <v>15.75</v>
       </c>
       <c r="G1991" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55128,7 +55131,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1992" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55154,7 +55157,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1993" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55180,7 +55183,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1994" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55206,7 +55209,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1995" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55232,7 +55235,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1996" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55258,7 +55261,7 @@
         <v>15.75</v>
       </c>
       <c r="G1997" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55284,7 +55287,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1998" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55310,7 +55313,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1999" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55336,7 +55339,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2000" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55362,7 +55365,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2001" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55388,7 +55391,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2002" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55414,7 +55417,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55440,7 +55443,7 @@
         <v>16</v>
       </c>
       <c r="G2004" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55466,7 +55469,7 @@
         <v>16</v>
       </c>
       <c r="G2005" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55492,7 +55495,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2006" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55518,7 +55521,7 @@
         <v>16</v>
       </c>
       <c r="G2007" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55544,7 +55547,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2008" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55570,7 +55573,7 @@
         <v>16</v>
       </c>
       <c r="G2009" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55596,7 +55599,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2010" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55622,7 +55625,7 @@
         <v>16</v>
       </c>
       <c r="G2011" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55648,7 +55651,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55674,7 +55677,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2013" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55700,7 +55703,7 @@
         <v>16</v>
       </c>
       <c r="G2014" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55726,7 +55729,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55752,7 +55755,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2016" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55778,7 +55781,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55804,7 +55807,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2018" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55830,7 +55833,7 @@
         <v>15.75</v>
       </c>
       <c r="G2019" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55856,7 +55859,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2020" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55882,7 +55885,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2021" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55908,7 +55911,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2022" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55934,7 +55937,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2023" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55960,7 +55963,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2024" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55986,7 +55989,7 @@
         <v>16.75</v>
       </c>
       <c r="G2025" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56012,7 +56015,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2026" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56038,7 +56041,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2027" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56064,7 +56067,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56090,7 +56093,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2029" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56116,7 +56119,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2030" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56142,7 +56145,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2031" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56168,7 +56171,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2032" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56194,7 +56197,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2033" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56220,7 +56223,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2034" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56246,7 +56249,7 @@
         <v>19</v>
       </c>
       <c r="G2035" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56272,7 +56275,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G2036" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56298,7 +56301,7 @@
         <v>18.5</v>
       </c>
       <c r="G2037" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56324,7 +56327,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2038" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56350,7 +56353,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2039" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56376,7 +56379,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2040" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56402,7 +56405,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2041" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56428,7 +56431,7 @@
         <v>18</v>
       </c>
       <c r="G2042" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56454,7 +56457,7 @@
         <v>18.5</v>
       </c>
       <c r="G2043" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56480,7 +56483,7 @@
         <v>18.75</v>
       </c>
       <c r="G2044" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56506,7 +56509,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2045" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56532,7 +56535,7 @@
         <v>18.5</v>
       </c>
       <c r="G2046" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56558,7 +56561,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2047" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56584,7 +56587,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G2048" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56610,7 +56613,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2049" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56636,7 +56639,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2050" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56662,7 +56665,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2051" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56688,7 +56691,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2052" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56714,7 +56717,7 @@
         <v>17.75</v>
       </c>
       <c r="G2053" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56740,7 +56743,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2054" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56766,7 +56769,7 @@
         <v>17.25</v>
       </c>
       <c r="G2055" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56792,7 +56795,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2056" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56818,7 +56821,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2057" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56844,7 +56847,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2058" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56870,7 +56873,7 @@
         <v>16.25</v>
       </c>
       <c r="G2059" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56896,7 +56899,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2060" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56922,7 +56925,7 @@
         <v>16.5</v>
       </c>
       <c r="G2061" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56948,7 +56951,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2062" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56974,7 +56977,7 @@
         <v>16.5</v>
       </c>
       <c r="G2063" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -57000,7 +57003,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2064" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57026,7 +57029,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2065" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57052,7 +57055,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2066" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57078,7 +57081,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2067" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57104,7 +57107,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2068" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57130,7 +57133,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2069" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57156,7 +57159,7 @@
         <v>16.75</v>
       </c>
       <c r="G2070" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57182,7 +57185,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2071" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57208,7 +57211,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2072" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57234,7 +57237,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2073" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57260,7 +57263,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2074" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57286,7 +57289,7 @@
         <v>17</v>
       </c>
       <c r="G2075" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57312,7 +57315,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2076" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57338,7 +57341,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2077" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -57364,7 +57367,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2078" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -57390,7 +57393,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57416,7 +57419,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2080" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57442,7 +57445,7 @@
         <v>17.75</v>
       </c>
       <c r="G2081" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57468,7 +57471,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G2082" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57494,7 +57497,7 @@
         <v>17.5</v>
       </c>
       <c r="G2083" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57520,7 +57523,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2084" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57546,7 +57549,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2085" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57572,7 +57575,7 @@
         <v>17.5</v>
       </c>
       <c r="G2086" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57598,7 +57601,7 @@
         <v>17</v>
       </c>
       <c r="G2087" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57624,7 +57627,7 @@
         <v>17</v>
       </c>
       <c r="G2088" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57650,7 +57653,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2089" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57676,7 +57679,7 @@
         <v>17.75</v>
       </c>
       <c r="G2090" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57702,7 +57705,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2091" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57728,7 +57731,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2092" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57754,7 +57757,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2093" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57780,7 +57783,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2094" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57806,7 +57809,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2095" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57832,7 +57835,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2096" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -57858,7 +57861,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2097" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57884,7 +57887,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57910,7 +57913,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2099" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57936,7 +57939,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2100" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57962,7 +57965,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2101" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57988,7 +57991,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2102" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58014,7 +58017,7 @@
         <v>17</v>
       </c>
       <c r="G2103" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58040,7 +58043,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2104" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58066,7 +58069,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2105" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58092,7 +58095,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2106" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58118,7 +58121,7 @@
         <v>17.5</v>
       </c>
       <c r="G2107" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -58144,7 +58147,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2108" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58170,7 +58173,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2109" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -58196,7 +58199,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2110" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58222,7 +58225,7 @@
         <v>17</v>
       </c>
       <c r="G2111" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58248,7 +58251,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2112" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58274,7 +58277,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2113" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58300,7 +58303,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2114" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58326,7 +58329,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2115" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58352,7 +58355,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2116" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58378,7 +58381,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2117" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -58404,7 +58407,7 @@
         <v>17</v>
       </c>
       <c r="G2118" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58430,7 +58433,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2119" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58456,7 +58459,7 @@
         <v>17</v>
       </c>
       <c r="G2120" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58482,7 +58485,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2121" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58508,7 +58511,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2122" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58534,7 +58537,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2123" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58560,7 +58563,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2124" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58586,7 +58589,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2125" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58612,7 +58615,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2126" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58638,7 +58641,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2127" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58664,7 +58667,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2128" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58690,7 +58693,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2129" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58716,7 +58719,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2130" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58742,7 +58745,7 @@
         <v>16.5</v>
       </c>
       <c r="G2131" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58768,7 +58771,7 @@
         <v>16.5</v>
       </c>
       <c r="G2132" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58794,7 +58797,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2133" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58820,7 +58823,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2134" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58846,7 +58849,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2135" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58872,7 +58875,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2136" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58898,7 +58901,7 @@
         <v>17</v>
       </c>
       <c r="G2137" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58924,7 +58927,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2138" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58950,7 +58953,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2139" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58976,7 +58979,7 @@
         <v>16.5</v>
       </c>
       <c r="G2140" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59002,7 +59005,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2141" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59028,7 +59031,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2142" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59054,7 +59057,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2143" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59080,7 +59083,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2144" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59106,7 +59109,7 @@
         <v>16.75</v>
       </c>
       <c r="G2145" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59132,7 +59135,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2146" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59158,7 +59161,7 @@
         <v>16.75</v>
       </c>
       <c r="G2147" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59184,7 +59187,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2148" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59210,7 +59213,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2149" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59236,7 +59239,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2150" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59262,7 +59265,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2151" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59288,7 +59291,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2152" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59314,7 +59317,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2153" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59340,7 +59343,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2154" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59366,7 +59369,7 @@
         <v>16.25</v>
       </c>
       <c r="G2155" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59392,7 +59395,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2156" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59418,7 +59421,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2157" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59444,7 +59447,7 @@
         <v>15</v>
       </c>
       <c r="G2158" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59470,7 +59473,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2159" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59496,7 +59499,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2160" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59522,7 +59525,7 @@
         <v>15.25</v>
       </c>
       <c r="G2161" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59548,7 +59551,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2162" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59574,7 +59577,7 @@
         <v>15.25</v>
       </c>
       <c r="G2163" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59600,7 +59603,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2164" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59626,7 +59629,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2165" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59652,7 +59655,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2166" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59678,7 +59681,7 @@
         <v>16.25</v>
       </c>
       <c r="G2167" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59704,7 +59707,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2168" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59730,7 +59733,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2169" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59756,7 +59759,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2170" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59782,7 +59785,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2171" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59808,7 +59811,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59834,7 +59837,7 @@
         <v>16</v>
       </c>
       <c r="G2173" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59860,7 +59863,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2174" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -59886,7 +59889,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2175" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59912,7 +59915,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2176" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59938,7 +59941,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2177" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59964,7 +59967,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2178" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59990,7 +59993,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2179" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60016,7 +60019,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60042,7 +60045,7 @@
         <v>15.25</v>
       </c>
       <c r="G2181" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60068,7 +60071,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60094,7 +60097,7 @@
         <v>15.25</v>
       </c>
       <c r="G2183" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60120,7 +60123,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2184" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60146,7 +60149,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2185" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60172,7 +60175,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2186" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60198,7 +60201,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60224,7 +60227,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2188" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60250,7 +60253,7 @@
         <v>15</v>
       </c>
       <c r="G2189" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60276,7 +60279,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2190" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60302,7 +60305,7 @@
         <v>15</v>
       </c>
       <c r="G2191" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60328,7 +60331,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2192" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60354,7 +60357,7 @@
         <v>15</v>
       </c>
       <c r="G2193" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60380,7 +60383,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2194" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60406,7 +60409,7 @@
         <v>15</v>
       </c>
       <c r="G2195" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60432,7 +60435,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2196" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60458,7 +60461,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2197" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60484,7 +60487,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60510,7 +60513,7 @@
         <v>15</v>
       </c>
       <c r="G2199" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60536,7 +60539,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G2200" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60562,7 +60565,7 @@
         <v>15</v>
       </c>
       <c r="G2201" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60588,7 +60591,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60614,7 +60617,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2203" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60640,7 +60643,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2204" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60666,7 +60669,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60692,7 +60695,7 @@
         <v>14.5</v>
       </c>
       <c r="G2206" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60718,7 +60721,7 @@
         <v>14.5</v>
       </c>
       <c r="G2207" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60744,7 +60747,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60770,7 +60773,7 @@
         <v>14.5</v>
       </c>
       <c r="G2209" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60796,7 +60799,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60822,7 +60825,7 @@
         <v>14.5</v>
       </c>
       <c r="G2211" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60848,7 +60851,7 @@
         <v>14.5</v>
       </c>
       <c r="G2212" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60874,7 +60877,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60900,7 +60903,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2214" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60926,7 +60929,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2215" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60952,7 +60955,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2216" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60978,7 +60981,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2217" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61004,7 +61007,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2218" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61030,7 +61033,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2219" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61056,7 +61059,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2220" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61082,7 +61085,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2221" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61108,7 +61111,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2222" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61134,7 +61137,7 @@
         <v>15</v>
       </c>
       <c r="G2223" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61160,7 +61163,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61186,7 +61189,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2225" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61212,7 +61215,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2226" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61238,7 +61241,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2227" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61264,7 +61267,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61290,7 +61293,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2229" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61316,7 +61319,7 @@
         <v>15.25</v>
       </c>
       <c r="G2230" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61342,7 +61345,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2231" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61368,7 +61371,7 @@
         <v>15.5</v>
       </c>
       <c r="G2232" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61394,7 +61397,7 @@
         <v>15.5</v>
       </c>
       <c r="G2233" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61420,7 +61423,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2234" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61446,7 +61449,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2235" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61472,7 +61475,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2236" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61498,7 +61501,7 @@
         <v>16</v>
       </c>
       <c r="G2237" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61524,7 +61527,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2238" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61550,7 +61553,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2239" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61576,7 +61579,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2240" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61602,7 +61605,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2241" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61628,7 +61631,7 @@
         <v>16.5</v>
       </c>
       <c r="G2242" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61654,7 +61657,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2243" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61680,7 +61683,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2244" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61706,7 +61709,7 @@
         <v>17.25</v>
       </c>
       <c r="G2245" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61732,7 +61735,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2246" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61758,7 +61761,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2247" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61784,7 +61787,7 @@
         <v>17</v>
       </c>
       <c r="G2248" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61810,7 +61813,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2249" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61836,7 +61839,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2250" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61862,7 +61865,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61888,7 +61891,7 @@
         <v>17.25</v>
       </c>
       <c r="G2252" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61914,7 +61917,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2253" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61940,7 +61943,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2254" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61966,7 +61969,7 @@
         <v>17.75</v>
       </c>
       <c r="G2255" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61992,7 +61995,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G2256" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62018,7 +62021,7 @@
         <v>18</v>
       </c>
       <c r="G2257" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62044,7 +62047,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2258" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62070,7 +62073,7 @@
         <v>17</v>
       </c>
       <c r="G2259" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62096,7 +62099,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2260" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62122,7 +62125,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2261" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62148,7 +62151,7 @@
         <v>16.5</v>
       </c>
       <c r="G2262" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62174,7 +62177,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2263" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62200,7 +62203,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2264" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62226,7 +62229,7 @@
         <v>16.5</v>
       </c>
       <c r="G2265" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62252,7 +62255,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2266" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62278,7 +62281,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2267" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62304,7 +62307,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2268" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62330,7 +62333,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2269" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62356,7 +62359,7 @@
         <v>15.5</v>
       </c>
       <c r="G2270" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62382,7 +62385,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2271" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62408,7 +62411,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2272" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62434,7 +62437,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2273" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62460,7 +62463,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2274" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62486,7 +62489,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2275" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62512,7 +62515,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2276" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62538,7 +62541,7 @@
         <v>17</v>
       </c>
       <c r="G2277" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62564,7 +62567,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2278" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62590,7 +62593,7 @@
         <v>16.5</v>
       </c>
       <c r="G2279" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62616,7 +62619,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2280" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62642,7 +62645,7 @@
         <v>16</v>
       </c>
       <c r="G2281" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62668,7 +62671,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62694,7 +62697,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2283" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62720,7 +62723,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2284" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62746,7 +62749,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2285" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62772,7 +62775,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62798,7 +62801,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2287" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62824,7 +62827,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2288" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62850,7 +62853,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2289" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62876,7 +62879,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62902,7 +62905,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2291" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62928,7 +62931,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2292" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62954,7 +62957,7 @@
         <v>16.5</v>
       </c>
       <c r="G2293" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62980,7 +62983,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2294" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63006,7 +63009,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2295" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63032,7 +63035,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2296" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63058,7 +63061,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2297" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63084,7 +63087,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2298" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63110,7 +63113,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63136,7 +63139,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63162,7 +63165,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63188,7 +63191,7 @@
         <v>16</v>
       </c>
       <c r="G2302" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63214,7 +63217,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2303" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63240,7 +63243,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2304" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63266,7 +63269,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63292,7 +63295,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2306" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63318,7 +63321,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2307" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63344,7 +63347,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2308" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63370,7 +63373,7 @@
         <v>15.75</v>
       </c>
       <c r="G2309" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63396,7 +63399,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2310" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63422,7 +63425,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2311" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63448,7 +63451,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63474,7 +63477,7 @@
         <v>16</v>
       </c>
       <c r="G2313" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63500,7 +63503,7 @@
         <v>16</v>
       </c>
       <c r="G2314" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63526,7 +63529,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2315" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63552,7 +63555,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2316" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63578,7 +63581,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2317" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63604,7 +63607,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63630,7 +63633,7 @@
         <v>16</v>
       </c>
       <c r="G2319" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63656,7 +63659,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2320" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63682,7 +63685,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2321" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63708,7 +63711,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2322" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63734,7 +63737,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2323" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63760,7 +63763,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2324" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63786,7 +63789,7 @@
         <v>16</v>
       </c>
       <c r="G2325" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63812,7 +63815,7 @@
         <v>16</v>
       </c>
       <c r="G2326" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63838,7 +63841,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2327" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63864,7 +63867,7 @@
         <v>16</v>
       </c>
       <c r="G2328" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63890,7 +63893,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2329" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63916,7 +63919,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2330" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63942,7 +63945,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2331" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63968,7 +63971,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63994,7 +63997,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64020,7 +64023,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2334" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64046,7 +64049,7 @@
         <v>15.75</v>
       </c>
       <c r="G2335" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64072,7 +64075,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2336" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64098,7 +64101,7 @@
         <v>15.75</v>
       </c>
       <c r="G2337" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64124,7 +64127,7 @@
         <v>15.25</v>
       </c>
       <c r="G2338" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64150,7 +64153,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2339" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64176,7 +64179,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2340" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64202,7 +64205,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2341" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64228,7 +64231,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64254,7 +64257,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64280,7 +64283,7 @@
         <v>15.5</v>
       </c>
       <c r="G2344" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64306,7 +64309,7 @@
         <v>15.5</v>
       </c>
       <c r="G2345" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64332,7 +64335,7 @@
         <v>15</v>
       </c>
       <c r="G2346" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64358,7 +64361,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64384,7 +64387,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64410,7 +64413,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2349" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64436,7 +64439,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2350" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64462,7 +64465,7 @@
         <v>16</v>
       </c>
       <c r="G2351" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64488,7 +64491,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64514,7 +64517,7 @@
         <v>15.75</v>
       </c>
       <c r="G2353" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64540,7 +64543,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64566,7 +64569,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2355" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64592,7 +64595,7 @@
         <v>15.25</v>
       </c>
       <c r="G2356" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64618,7 +64621,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2357" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64644,7 +64647,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64670,7 +64673,7 @@
         <v>14</v>
       </c>
       <c r="G2359" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64696,7 +64699,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2360" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64722,7 +64725,7 @@
         <v>15</v>
       </c>
       <c r="G2361" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64748,7 +64751,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2362" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64774,7 +64777,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2363" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64800,7 +64803,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2364" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64826,7 +64829,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64852,7 +64855,7 @@
         <v>14.5</v>
       </c>
       <c r="G2366" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64878,7 +64881,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2367" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64904,7 +64907,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2368" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64930,7 +64933,7 @@
         <v>15</v>
       </c>
       <c r="G2369" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64956,7 +64959,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2370" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64982,7 +64985,7 @@
         <v>15.25</v>
       </c>
       <c r="G2371" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65008,7 +65011,7 @@
         <v>15.25</v>
       </c>
       <c r="G2372" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65034,7 +65037,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2373" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65060,7 +65063,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2374" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65086,7 +65089,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2375" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65112,7 +65115,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2376" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65138,7 +65141,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65164,7 +65167,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2378" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65190,7 +65193,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2379" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65216,7 +65219,7 @@
         <v>15.25</v>
       </c>
       <c r="G2380" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65242,7 +65245,7 @@
         <v>15.25</v>
       </c>
       <c r="G2381" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65268,7 +65271,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2382" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65294,7 +65297,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2383" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65320,7 +65323,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65346,7 +65349,7 @@
         <v>16</v>
       </c>
       <c r="G2385" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65372,7 +65375,7 @@
         <v>16.25</v>
       </c>
       <c r="G2386" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65398,7 +65401,7 @@
         <v>16</v>
       </c>
       <c r="G2387" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65424,7 +65427,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2388" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65450,7 +65453,7 @@
         <v>16.5</v>
       </c>
       <c r="G2389" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65476,7 +65479,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2390" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65502,7 +65505,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2391" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65528,7 +65531,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2392" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65554,7 +65557,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2393" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65580,7 +65583,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2394" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65606,7 +65609,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2395" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65632,7 +65635,7 @@
         <v>16.75</v>
       </c>
       <c r="G2396" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65658,7 +65661,7 @@
         <v>16.5</v>
       </c>
       <c r="G2397" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65684,7 +65687,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2398" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65710,7 +65713,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2399" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65736,7 +65739,7 @@
         <v>16.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65762,7 +65765,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65788,7 +65791,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2402" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65814,7 +65817,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65840,7 +65843,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2404" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65866,7 +65869,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2405" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65892,7 +65895,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2406" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65918,7 +65921,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2407" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65944,7 +65947,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2408" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65970,7 +65973,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G2409" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65996,7 +65999,7 @@
         <v>16</v>
       </c>
       <c r="G2410" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66022,7 +66025,7 @@
         <v>15.75</v>
       </c>
       <c r="G2411" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66048,7 +66051,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2412" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66074,7 +66077,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2413" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66100,7 +66103,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2414" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66126,7 +66129,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2415" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66152,7 +66155,7 @@
         <v>16.25</v>
       </c>
       <c r="G2416" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66178,7 +66181,7 @@
         <v>16.75</v>
       </c>
       <c r="G2417" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66204,7 +66207,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2418" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66230,7 +66233,7 @@
         <v>16.25</v>
       </c>
       <c r="G2419" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66256,7 +66259,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2420" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66282,7 +66285,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2421" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66308,7 +66311,7 @@
         <v>16.25</v>
       </c>
       <c r="G2422" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66334,7 +66337,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2423" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66360,7 +66363,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2424" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66386,7 +66389,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2425" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66412,7 +66415,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2426" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66438,7 +66441,7 @@
         <v>16.25</v>
       </c>
       <c r="G2427" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66464,7 +66467,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2428" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66490,7 +66493,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66516,7 +66519,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2430" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66542,7 +66545,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2431" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66568,7 +66571,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66594,7 +66597,7 @@
         <v>16.5</v>
       </c>
       <c r="G2433" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66620,7 +66623,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2434" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66646,7 +66649,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2435" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66672,7 +66675,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2436" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66698,7 +66701,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2437" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66724,7 +66727,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2438" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66750,7 +66753,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2439" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66776,7 +66779,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2440" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66802,7 +66805,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66828,7 +66831,7 @@
         <v>16.75</v>
       </c>
       <c r="G2442" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66854,7 +66857,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66880,7 +66883,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2444" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66906,7 +66909,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2445" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66932,7 +66935,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2446" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66958,7 +66961,7 @@
         <v>18</v>
       </c>
       <c r="G2447" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66984,7 +66987,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2448" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67010,7 +67013,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67036,7 +67039,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2450" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67062,7 +67065,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2451" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67088,7 +67091,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2452" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67114,7 +67117,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2453" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67140,7 +67143,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2454" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67166,7 +67169,7 @@
         <v>21</v>
       </c>
       <c r="G2455" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67192,7 +67195,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G2456" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67218,7 +67221,7 @@
         <v>19.25</v>
       </c>
       <c r="G2457" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67244,7 +67247,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G2458" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67270,7 +67273,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G2459" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67296,7 +67299,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67322,7 +67325,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2461" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67348,7 +67351,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2462" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67374,7 +67377,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67400,7 +67403,7 @@
         <v>18.5</v>
       </c>
       <c r="G2464" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67426,7 +67429,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G2465" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67452,7 +67455,7 @@
         <v>19</v>
       </c>
       <c r="G2466" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67478,7 +67481,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2467" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67504,7 +67507,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2468" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67530,7 +67533,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2469" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67556,7 +67559,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2470" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67582,7 +67585,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2471" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67608,7 +67611,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2472" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67634,7 +67637,7 @@
         <v>16</v>
       </c>
       <c r="G2473" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67660,7 +67663,7 @@
         <v>16</v>
       </c>
       <c r="G2474" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67686,7 +67689,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2475" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67712,7 +67715,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67738,7 +67741,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67764,7 +67767,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67790,7 +67793,7 @@
         <v>16.25</v>
       </c>
       <c r="G2479" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67816,7 +67819,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67842,7 +67845,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2481" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67868,7 +67871,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67894,7 +67897,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67920,7 +67923,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2484" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67946,7 +67949,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2485" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67972,7 +67975,7 @@
         <v>16</v>
       </c>
       <c r="G2486" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67998,7 +68001,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2487" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68024,7 +68027,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2488" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68050,7 +68053,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68076,7 +68079,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2490" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68102,7 +68105,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2491" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68128,7 +68131,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2492" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68154,7 +68157,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68180,7 +68183,7 @@
         <v>15.25</v>
       </c>
       <c r="G2494" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68206,7 +68209,7 @@
         <v>15.5</v>
       </c>
       <c r="G2495" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68232,7 +68235,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2496" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68258,7 +68261,7 @@
         <v>15.5</v>
       </c>
       <c r="G2497" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68284,7 +68287,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2498" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68310,7 +68313,7 @@
         <v>15.25</v>
       </c>
       <c r="G2499" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -68336,7 +68339,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2500" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -68362,7 +68365,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2501" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -68388,7 +68391,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2502" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68414,7 +68417,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2503" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68440,7 +68443,7 @@
         <v>15.25</v>
       </c>
       <c r="G2504" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -68466,7 +68469,7 @@
         <v>15.25</v>
       </c>
       <c r="G2505" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -68492,7 +68495,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2506" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68518,7 +68521,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2507" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68544,7 +68547,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2508" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68570,7 +68573,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2509" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68596,7 +68599,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G2510" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68622,7 +68625,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2511" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68648,7 +68651,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2512" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68674,7 +68677,7 @@
         <v>15</v>
       </c>
       <c r="G2513" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68700,7 +68703,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2514" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68726,7 +68729,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2515" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68752,7 +68755,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2516" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68778,7 +68781,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2517" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68804,7 +68807,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2518" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -68830,7 +68833,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2519" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -68856,7 +68859,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2520" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -68882,7 +68885,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2521" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -68908,7 +68911,7 @@
         <v>14.75</v>
       </c>
       <c r="G2522" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -68934,7 +68937,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2523" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -68942,13 +68945,13 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.6911805556</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>43737</v>
       </c>
       <c r="C2524" t="n">
-        <v>15.3999996185303</v>
+        <v>15.4499998092651</v>
       </c>
       <c r="D2524" t="n">
         <v>15.0500001907349</v>
@@ -68960,9 +68963,35 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2524" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.6910300926</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>9505</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>15.5500001907349</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>15.3500003814697</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>15.3999996185303</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>15.3500003814697</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>989</v>
+      </c>
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BEC.MI.xlsx
+++ b/data/BEC.MI.xlsx
@@ -50,37 +50,37 @@
     <t xml:space="preserve">4.8704080581665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87693691253662</t>
+    <t xml:space="preserve">4.87693643569946</t>
   </si>
   <si>
     <t xml:space="preserve">4.92916631698608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77247762680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79859209060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83449983596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73330497741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79532814025879</t>
+    <t xml:space="preserve">4.77247714996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79859161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83450031280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73330545425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79532766342163</t>
   </si>
   <si>
     <t xml:space="preserve">4.80512046813965</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76594924926758</t>
+    <t xml:space="preserve">4.76594877243042</t>
   </si>
   <si>
     <t xml:space="preserve">4.75942039489746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60273170471191</t>
+    <t xml:space="preserve">4.60273122787476</t>
   </si>
   <si>
     <t xml:space="preserve">4.69739770889282</t>
@@ -95,55 +95,55 @@
     <t xml:space="preserve">4.44277858734131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37422704696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18489551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07390689849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08043575286865</t>
+    <t xml:space="preserve">4.37422609329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18489408493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07390642166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08043622970581</t>
   </si>
   <si>
     <t xml:space="preserve">4.23386001586914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40360593795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49174308776855</t>
+    <t xml:space="preserve">4.40360641479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49174356460571</t>
   </si>
   <si>
     <t xml:space="preserve">4.53091526031494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43298482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50480079650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53744459152222</t>
+    <t xml:space="preserve">4.43298530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50480031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53744411468506</t>
   </si>
   <si>
     <t xml:space="preserve">4.42645645141602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42319250106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43951368331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.416663646698</t>
+    <t xml:space="preserve">4.42319297790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43951416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41666316986084</t>
   </si>
   <si>
     <t xml:space="preserve">4.44930696487427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4656286239624</t>
+    <t xml:space="preserve">4.46562814712524</t>
   </si>
   <si>
     <t xml:space="preserve">4.47868585586548</t>
@@ -152,100 +152,100 @@
     <t xml:space="preserve">4.60926008224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8965220451355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90957975387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93569421768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91284465789795</t>
+    <t xml:space="preserve">4.89652299880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90957927703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9356951713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91284418106079</t>
   </si>
   <si>
     <t xml:space="preserve">5.01403903961182</t>
   </si>
   <si>
-    <t xml:space="preserve">4.942223072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03362607955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04015398025513</t>
+    <t xml:space="preserve">4.94222402572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03362512588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04015445709229</t>
   </si>
   <si>
     <t xml:space="preserve">5.09238338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94875192642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99445390701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84429264068604</t>
+    <t xml:space="preserve">4.94875240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99445247650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84429359436035</t>
   </si>
   <si>
     <t xml:space="preserve">5.06953287124634</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09891271591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98792457580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04994678497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04341840744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05974054336548</t>
+    <t xml:space="preserve">5.09891223907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98792409896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0499472618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04341745376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05973958969116</t>
   </si>
   <si>
     <t xml:space="preserve">4.98466014862061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02709722518921</t>
+    <t xml:space="preserve">5.02709579467773</t>
   </si>
   <si>
     <t xml:space="preserve">4.99973821640015</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03393602371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96212005615234</t>
+    <t xml:space="preserve">5.03393650054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96212100982666</t>
   </si>
   <si>
     <t xml:space="preserve">4.91766357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9450216293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85610675811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89030504226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89714384078979</t>
+    <t xml:space="preserve">4.94502210617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85610723495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89030456542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89714431762695</t>
   </si>
   <si>
     <t xml:space="preserve">4.79455089569092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82190942764282</t>
+    <t xml:space="preserve">4.82190895080566</t>
   </si>
   <si>
     <t xml:space="preserve">4.9826397895813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92450284957886</t>
+    <t xml:space="preserve">4.9245023727417</t>
   </si>
   <si>
     <t xml:space="preserve">5.00657796859741</t>
@@ -254,103 +254,103 @@
     <t xml:space="preserve">4.88346481323242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94844150543213</t>
+    <t xml:space="preserve">4.94844198226929</t>
   </si>
   <si>
     <t xml:space="preserve">4.95870113372803</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9928994178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86636590957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85268688201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93134260177612</t>
+    <t xml:space="preserve">4.99289894104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86636638641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8526873588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93134164810181</t>
   </si>
   <si>
     <t xml:space="preserve">4.78771114349365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78429126739502</t>
+    <t xml:space="preserve">4.78429079055786</t>
   </si>
   <si>
     <t xml:space="preserve">4.82532835006714</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77403163909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72273540496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67485761642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75693273544312</t>
+    <t xml:space="preserve">4.77403211593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7227349281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67485809326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75693321228027</t>
   </si>
   <si>
     <t xml:space="preserve">4.56200504302979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54148578643799</t>
+    <t xml:space="preserve">4.54148626327515</t>
   </si>
   <si>
     <t xml:space="preserve">4.53122711181641</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6030421257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63040065765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55516529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58252382278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54832601547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45941114425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53464651107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52780675888062</t>
+    <t xml:space="preserve">4.60304164886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63040113449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55516481399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58252334594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54832553863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45941066741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53464603424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52780723571777</t>
   </si>
   <si>
     <t xml:space="preserve">4.52096796035767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64407920837402</t>
+    <t xml:space="preserve">4.64407968521118</t>
   </si>
   <si>
     <t xml:space="preserve">4.74325370788574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73983383178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8355884552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92108297348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92792320251465</t>
+    <t xml:space="preserve">4.73983335494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83558797836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92108345031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92792224884033</t>
   </si>
   <si>
     <t xml:space="preserve">4.98605918884277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96553993225098</t>
+    <t xml:space="preserve">4.96554040908813</t>
   </si>
   <si>
     <t xml:space="preserve">4.91424369812012</t>
@@ -374,19 +374,19 @@
     <t xml:space="preserve">4.9518609046936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87320613861084</t>
+    <t xml:space="preserve">4.873206615448</t>
   </si>
   <si>
     <t xml:space="preserve">4.86294651031494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76719236373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80138969421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80822992324829</t>
+    <t xml:space="preserve">4.76719188690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80138921737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80823040008545</t>
   </si>
   <si>
     <t xml:space="preserve">4.76377296447754</t>
@@ -395,28 +395,28 @@
     <t xml:space="preserve">4.8424277305603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72957468032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84926748275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81165027618408</t>
+    <t xml:space="preserve">4.72957515716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84926795959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81164979934692</t>
   </si>
   <si>
     <t xml:space="preserve">4.88688516616821</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02025651931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08865308761597</t>
+    <t xml:space="preserve">5.02025699615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08865261077881</t>
   </si>
   <si>
     <t xml:space="preserve">5.10575199127197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06471395492554</t>
+    <t xml:space="preserve">5.0647144317627</t>
   </si>
   <si>
     <t xml:space="preserve">5.04761552810669</t>
@@ -425,28 +425,28 @@
     <t xml:space="preserve">5.09549236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17756748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23228549957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12969017028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13994979858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16388893127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2117657661438</t>
+    <t xml:space="preserve">5.17756843566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23228406906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12969064712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13995027542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16388845443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21176481246948</t>
   </si>
   <si>
     <t xml:space="preserve">5.30751991271973</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30068063735962</t>
+    <t xml:space="preserve">5.3006796836853</t>
   </si>
   <si>
     <t xml:space="preserve">5.13311004638672</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">5.22544479370117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16730785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19808626174927</t>
+    <t xml:space="preserve">5.16730833053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19808673858643</t>
   </si>
   <si>
     <t xml:space="preserve">5.29726028442383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47166967391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40327405929565</t>
+    <t xml:space="preserve">5.47167015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40327453613281</t>
   </si>
   <si>
     <t xml:space="preserve">5.36565589904785</t>
@@ -476,13 +476,13 @@
     <t xml:space="preserve">5.36223697662354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46483087539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36907625198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39643526077271</t>
+    <t xml:space="preserve">5.46482992172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36907577514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39643430709839</t>
   </si>
   <si>
     <t xml:space="preserve">5.25964260101318</t>
@@ -491,10 +491,10 @@
     <t xml:space="preserve">5.41353321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46141052246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43747234344482</t>
+    <t xml:space="preserve">5.4614109992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43747091293335</t>
   </si>
   <si>
     <t xml:space="preserve">5.45457077026367</t>
@@ -503,97 +503,97 @@
     <t xml:space="preserve">5.46824932098389</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47508955001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39985418319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41695261001587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43063259124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4579906463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50586843490601</t>
+    <t xml:space="preserve">5.47508907318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39985370635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41695308685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43063306808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45799016952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50586748123169</t>
   </si>
   <si>
     <t xml:space="preserve">5.52980613708496</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60846185684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68369817733765</t>
+    <t xml:space="preserve">5.60846090316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68369722366333</t>
   </si>
   <si>
     <t xml:space="preserve">5.73157453536987</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88204526901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9367618560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94360160827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0564546585083</t>
+    <t xml:space="preserve">5.88204574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93676280975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94360113143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05645370483398</t>
   </si>
   <si>
     <t xml:space="preserve">5.94018220901489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04961585998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07355260848999</t>
+    <t xml:space="preserve">6.04961442947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07355356216431</t>
   </si>
   <si>
     <t xml:space="preserve">6.02567672729492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97437906265259</t>
+    <t xml:space="preserve">5.97437953948975</t>
   </si>
   <si>
     <t xml:space="preserve">6.04277515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17272806167603</t>
+    <t xml:space="preserve">6.17272758483887</t>
   </si>
   <si>
     <t xml:space="preserve">6.39501476287842</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37449550628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46682929992676</t>
+    <t xml:space="preserve">6.37449502944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46682977676392</t>
   </si>
   <si>
     <t xml:space="preserve">6.32661867141724</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11117124557495</t>
+    <t xml:space="preserve">6.11117172241211</t>
   </si>
   <si>
     <t xml:space="preserve">5.89914417266846</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00515699386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22402429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.265061378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39843320846558</t>
+    <t xml:space="preserve">6.00515794754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22402477264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26506185531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39843368530273</t>
   </si>
   <si>
     <t xml:space="preserve">6.40527391433716</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">6.48050928115845</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41211366653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44973134994507</t>
+    <t xml:space="preserve">6.41211318969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44973087310791</t>
   </si>
   <si>
     <t xml:space="preserve">6.43605184555054</t>
@@ -614,106 +614,106 @@
     <t xml:space="preserve">6.52838611602783</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66859769821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99689722061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94218111038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1200098991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4688286781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66717767715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20066452026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40585231781006</t>
+    <t xml:space="preserve">6.66859674453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99689769744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94218063354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12000942230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46883010864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66717720031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20066547393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40585327148438</t>
   </si>
   <si>
     <t xml:space="preserve">8.64523887634277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27590274810791</t>
+    <t xml:space="preserve">8.27590179443359</t>
   </si>
   <si>
     <t xml:space="preserve">8.35113620758057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28958034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24170303344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33745670318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33061790466309</t>
+    <t xml:space="preserve">8.28957939147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24170398712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33745765686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33061695098877</t>
   </si>
   <si>
     <t xml:space="preserve">8.31693840026855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26906108856201</t>
+    <t xml:space="preserve">8.2690601348877</t>
   </si>
   <si>
     <t xml:space="preserve">8.22118473052979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11859035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30325984954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48108768463135</t>
+    <t xml:space="preserve">8.11859130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30325794219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48108673095703</t>
   </si>
   <si>
     <t xml:space="preserve">8.72047424316406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71363544464111</t>
+    <t xml:space="preserve">8.7136344909668</t>
   </si>
   <si>
     <t xml:space="preserve">8.79469013214111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49782276153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52751064300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07478809356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31228160858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43102741241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37165355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97830677032471</t>
+    <t xml:space="preserve">8.49782466888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52750968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07478713989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31228065490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43102836608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37165451049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97830629348755</t>
   </si>
   <si>
     <t xml:space="preserve">7.88924551010132</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23806381225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26033020019531</t>
+    <t xml:space="preserve">8.23806476593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.260329246521</t>
   </si>
   <si>
     <t xml:space="preserve">8.21579933166504</t>
@@ -731,25 +731,25 @@
     <t xml:space="preserve">8.69078731536865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57946109771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66109943389893</t>
+    <t xml:space="preserve">8.57946300506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66110134124756</t>
   </si>
   <si>
     <t xml:space="preserve">8.54977512359619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52008819580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53493213653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60172748565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48298072814941</t>
+    <t xml:space="preserve">8.52008724212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53493118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60172653198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48297882080078</t>
   </si>
   <si>
     <t xml:space="preserve">8.59430503845215</t>
@@ -758,13 +758,13 @@
     <t xml:space="preserve">8.46813678741455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14900398254395</t>
+    <t xml:space="preserve">8.14900302886963</t>
   </si>
   <si>
     <t xml:space="preserve">8.31970310211182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12673854827881</t>
+    <t xml:space="preserve">8.12673950195312</t>
   </si>
   <si>
     <t xml:space="preserve">8.46071434020996</t>
@@ -773,97 +773,97 @@
     <t xml:space="preserve">8.58688354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7056303024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84664154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69820785522461</t>
+    <t xml:space="preserve">8.70562934875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84664249420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69820880889893</t>
   </si>
   <si>
     <t xml:space="preserve">8.7427396774292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56461811065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43844985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40876388549805</t>
+    <t xml:space="preserve">8.56461906433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43844890594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40876483917236</t>
   </si>
   <si>
     <t xml:space="preserve">8.34939002990723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42360591888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54235363006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63141250610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61657047271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63883495330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66852283477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77984619140625</t>
+    <t xml:space="preserve">8.42360687255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54235458374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63141441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61656951904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63883590698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66852188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77984714508057</t>
   </si>
   <si>
     <t xml:space="preserve">8.88375091552734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83922100067139</t>
+    <t xml:space="preserve">8.83922004699707</t>
   </si>
   <si>
     <t xml:space="preserve">8.82437896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68336582183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6091480255127</t>
+    <t xml:space="preserve">8.68336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60915088653564</t>
   </si>
   <si>
     <t xml:space="preserve">8.57204055786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49040031433105</t>
+    <t xml:space="preserve">8.49040126800537</t>
   </si>
   <si>
     <t xml:space="preserve">8.47555828094482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78726863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71305274963379</t>
+    <t xml:space="preserve">8.78726959228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71305179595947</t>
   </si>
   <si>
     <t xml:space="preserve">8.65367794036865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62399291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75015926361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9060173034668</t>
+    <t xml:space="preserve">8.62399196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75016021728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90601539611816</t>
   </si>
   <si>
     <t xml:space="preserve">8.89859390258789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94312381744385</t>
+    <t xml:space="preserve">8.94312477111816</t>
   </si>
   <si>
     <t xml:space="preserve">8.77242565155029</t>
@@ -872,16 +872,16 @@
     <t xml:space="preserve">8.96538925170898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87632846832275</t>
+    <t xml:space="preserve">8.87632942199707</t>
   </si>
   <si>
     <t xml:space="preserve">8.97281074523926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0915584564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2177267074585</t>
+    <t xml:space="preserve">9.09155750274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21772575378418</t>
   </si>
   <si>
     <t xml:space="preserve">9.52201461791992</t>
@@ -893,46 +893,46 @@
     <t xml:space="preserve">9.5665454864502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45522117614746</t>
+    <t xml:space="preserve">9.45521831512451</t>
   </si>
   <si>
     <t xml:space="preserve">9.47748470306396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5368595123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35873699188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59623146057129</t>
+    <t xml:space="preserve">9.53685855865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35873985290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59623336791992</t>
   </si>
   <si>
     <t xml:space="preserve">9.64076137542725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90794277191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89309787750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76693058013916</t>
+    <t xml:space="preserve">9.90794372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89309883117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76692962646484</t>
   </si>
   <si>
     <t xml:space="preserve">9.72982120513916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99700260162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95247364044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0563764572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64818477630615</t>
+    <t xml:space="preserve">9.99700450897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95247268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.05637550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64818382263184</t>
   </si>
   <si>
     <t xml:space="preserve">9.95989513397217</t>
@@ -944,73 +944,73 @@
     <t xml:space="preserve">9.81146144866943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75208854675293</t>
+    <t xml:space="preserve">9.7520866394043</t>
   </si>
   <si>
     <t xml:space="preserve">9.85599040985107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86341190338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0415334701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0118465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9450511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90052127838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83180046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97088432312012</t>
+    <t xml:space="preserve">9.86341094970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0415325164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0118455886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94505023956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90052032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83179950714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97088289260864</t>
   </si>
   <si>
     <t xml:space="preserve">8.25290775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16384792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19353485107422</t>
+    <t xml:space="preserve">8.16384887695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1935338973999</t>
   </si>
   <si>
     <t xml:space="preserve">8.67594337463379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50524520874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02283573150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06736660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98572683334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7853422164917</t>
+    <t xml:space="preserve">8.5052433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02283668518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06736469268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98572826385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78534269332886</t>
   </si>
   <si>
     <t xml:space="preserve">7.76307773590088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70370388031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82987308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64433097839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72596836090088</t>
+    <t xml:space="preserve">7.7037034034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82987260818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6443305015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72596788406372</t>
   </si>
   <si>
     <t xml:space="preserve">8.04510116577148</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">7.91893243789673</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08963108062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11931705474854</t>
+    <t xml:space="preserve">8.08963012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11931610107422</t>
   </si>
   <si>
     <t xml:space="preserve">8.11189651489258</t>
@@ -1037,49 +1037,49 @@
     <t xml:space="preserve">8.00057125091553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13416004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28259468078613</t>
+    <t xml:space="preserve">8.13416194915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2825927734375</t>
   </si>
   <si>
     <t xml:space="preserve">8.20837879180908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34196662902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44587135314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92086029052734</t>
+    <t xml:space="preserve">8.34196758270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44587230682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92085933685303</t>
   </si>
   <si>
     <t xml:space="preserve">9.02476406097412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32712459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2677526473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71854639053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03025817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01541328430176</t>
+    <t xml:space="preserve">8.32712554931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26775074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71854686737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03025722503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01541423797607</t>
   </si>
   <si>
     <t xml:space="preserve">8.10447406768799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17869281768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22321891784668</t>
+    <t xml:space="preserve">8.17869186401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22322177886963</t>
   </si>
   <si>
     <t xml:space="preserve">8.40134143829346</t>
@@ -1091,37 +1091,37 @@
     <t xml:space="preserve">8.93570327758789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72789573669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89117240905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00992012023926</t>
+    <t xml:space="preserve">8.72789478302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8911714553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00991916656494</t>
   </si>
   <si>
     <t xml:space="preserve">9.27710056304932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30678749084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24741363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35131645202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52943801879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47006320953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39584732055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54428100585938</t>
+    <t xml:space="preserve">9.30678558349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24741268157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35131740570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5294361114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47006511688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39584636688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54427909851074</t>
   </si>
   <si>
     <t xml:space="preserve">9.87083435058594</t>
@@ -1130,37 +1130,37 @@
     <t xml:space="preserve">9.60365295410156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0637979507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87998485565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54299163818359</t>
+    <t xml:space="preserve">10.0637969970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87998390197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54299068450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.55831050872803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72680568695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60426330566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46640300750732</t>
+    <t xml:space="preserve">9.726806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60426425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46640205383301</t>
   </si>
   <si>
     <t xml:space="preserve">9.57362842559814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6195821762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63490009307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68085289001465</t>
+    <t xml:space="preserve">9.61958122253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63489818572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68085193634033</t>
   </si>
   <si>
     <t xml:space="preserve">9.48172092437744</t>
@@ -1169,19 +1169,19 @@
     <t xml:space="preserve">9.43576812744141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3438606262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3132266998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08345699310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59328842163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53201770782471</t>
+    <t xml:space="preserve">9.34385967254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31322574615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08345794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59328937530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53201675415039</t>
   </si>
   <si>
     <t xml:space="preserve">8.89964389801025</t>
@@ -1193,19 +1193,19 @@
     <t xml:space="preserve">9.28258991241455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20600032806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49703884124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51235675811768</t>
+    <t xml:space="preserve">9.20600128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49703693389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51235580444336</t>
   </si>
   <si>
     <t xml:space="preserve">9.52767372131348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38981533050537</t>
+    <t xml:space="preserve">9.38981628417969</t>
   </si>
   <si>
     <t xml:space="preserve">9.35917854309082</t>
@@ -1214,40 +1214,40 @@
     <t xml:space="preserve">9.19068336486816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86466598510742</t>
+    <t xml:space="preserve">9.86466693878174</t>
   </si>
   <si>
     <t xml:space="preserve">9.58894634246826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3285436630249</t>
+    <t xml:space="preserve">9.32854270935059</t>
   </si>
   <si>
     <t xml:space="preserve">9.42045021057129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22131824493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25195503234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11409473419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14472961425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26727199554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45108699798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69617080688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6502161026001</t>
+    <t xml:space="preserve">9.2213191986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11409282684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1447286605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26727294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45108604431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69616985321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65021800994873</t>
   </si>
   <si>
     <t xml:space="preserve">8.80773735046387</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">9.02218723297119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91496181488037</t>
+    <t xml:space="preserve">8.91496276855469</t>
   </si>
   <si>
     <t xml:space="preserve">8.94559764862061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17536544799805</t>
+    <t xml:space="preserve">9.17536449432373</t>
   </si>
   <si>
     <t xml:space="preserve">9.00686931610107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95657348632812</t>
+    <t xml:space="preserve">9.95657253265381</t>
   </si>
   <si>
     <t xml:space="preserve">10.0331621170044</t>
@@ -1292,22 +1292,22 @@
     <t xml:space="preserve">9.97189044952393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78807544708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75744247436523</t>
+    <t xml:space="preserve">9.78807735443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7574405670166</t>
   </si>
   <si>
     <t xml:space="preserve">9.09877586364746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86900901794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7464656829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7311487197876</t>
+    <t xml:space="preserve">8.86900997161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74646663665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73114776611328</t>
   </si>
   <si>
     <t xml:space="preserve">8.51669883728027</t>
@@ -1316,16 +1316,16 @@
     <t xml:space="preserve">8.47074604034424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42479228973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01121139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22566032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3635196685791</t>
+    <t xml:space="preserve">8.4247932434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01121234893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.225661277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36352157592773</t>
   </si>
   <si>
     <t xml:space="preserve">8.65456008911133</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">8.77710151672363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8383731842041</t>
+    <t xml:space="preserve">8.83837413787842</t>
   </si>
   <si>
     <t xml:space="preserve">8.93027973175049</t>
@@ -1352,37 +1352,37 @@
     <t xml:space="preserve">8.82305526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60860443115234</t>
+    <t xml:space="preserve">8.60860538482666</t>
   </si>
   <si>
     <t xml:space="preserve">8.57797050476074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34820365905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30224990844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3328857421875</t>
+    <t xml:space="preserve">8.3482027053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30225086212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33288478851318</t>
   </si>
   <si>
     <t xml:space="preserve">8.37883853912354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28693294525146</t>
+    <t xml:space="preserve">8.28693199157715</t>
   </si>
   <si>
     <t xml:space="preserve">8.27161502838135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39415645599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13375473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11843585968018</t>
+    <t xml:space="preserve">8.39415740966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13375377655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11843681335449</t>
   </si>
   <si>
     <t xml:space="preserve">8.45542812347412</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">8.79241943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85369110107422</t>
+    <t xml:space="preserve">8.85369205474854</t>
   </si>
   <si>
     <t xml:space="preserve">8.70051288604736</t>
@@ -1400,22 +1400,22 @@
     <t xml:space="preserve">8.66987705230713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68519496917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54733562469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.440110206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88432598114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40513134002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92593765258789</t>
+    <t xml:space="preserve">8.68519592285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54733371734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44011116027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88432788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40513324737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92593669891357</t>
   </si>
   <si>
     <t xml:space="preserve">9.80339527130127</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">9.29790782928467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22897720336914</t>
+    <t xml:space="preserve">9.22897815704346</t>
   </si>
   <si>
     <t xml:space="preserve">9.07579898834229</t>
@@ -1433,34 +1433,34 @@
     <t xml:space="preserve">9.15238761901855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99921035766602</t>
+    <t xml:space="preserve">8.9992094039917</t>
   </si>
   <si>
     <t xml:space="preserve">9.59735012054443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31742763519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79757022857666</t>
+    <t xml:space="preserve">9.31742668151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79757118225098</t>
   </si>
   <si>
     <t xml:space="preserve">8.87754917144775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83755970001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63761425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23744964599609</t>
+    <t xml:space="preserve">8.83756065368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63761520385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23744869232178</t>
   </si>
   <si>
     <t xml:space="preserve">9.27743816375732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47738361358643</t>
+    <t xml:space="preserve">9.47738265991211</t>
   </si>
   <si>
     <t xml:space="preserve">9.3574161529541</t>
@@ -1472,19 +1472,19 @@
     <t xml:space="preserve">9.67732810974121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63733863830566</t>
+    <t xml:space="preserve">9.63733959197998</t>
   </si>
   <si>
     <t xml:space="preserve">9.39740657806396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19746208190918</t>
+    <t xml:space="preserve">9.19746017456055</t>
   </si>
   <si>
     <t xml:space="preserve">9.07749462127686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4373950958252</t>
+    <t xml:space="preserve">9.43739414215088</t>
   </si>
   <si>
     <t xml:space="preserve">9.55736064910889</t>
@@ -1493,37 +1493,37 @@
     <t xml:space="preserve">9.11748313903809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7175931930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9575252532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99751567840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15747165679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91753673553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7970190048218</t>
+    <t xml:space="preserve">8.71759223937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95752620697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99751663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.157470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91753768920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7970180511475</t>
   </si>
   <si>
     <t xml:space="preserve">10.3571405410767</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772171020508</t>
+    <t xml:space="preserve">10.0772180557251</t>
   </si>
   <si>
     <t xml:space="preserve">10.3171510696411</t>
   </si>
   <si>
-    <t xml:space="preserve">10.117205619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91726112365723</t>
+    <t xml:space="preserve">10.1172065734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91726207733154</t>
   </si>
   <si>
     <t xml:space="preserve">9.997239112854</t>
@@ -1532,16 +1532,16 @@
     <t xml:space="preserve">10.0372285842896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75730514526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71731662750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79729461669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83728408813477</t>
+    <t xml:space="preserve">9.75730609893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71731758117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7972936630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83728313446045</t>
   </si>
   <si>
     <t xml:space="preserve">10.1571960449219</t>
@@ -1550,16 +1550,16 @@
     <t xml:space="preserve">10.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2371730804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3971290588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5570859909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4771089553833</t>
+    <t xml:space="preserve">10.2371740341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3971281051636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5570840835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.477108001709</t>
   </si>
   <si>
     <t xml:space="preserve">10.1971845626831</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">10.5170955657959</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9969635009766</t>
+    <t xml:space="preserve">10.9969644546509</t>
   </si>
   <si>
     <t xml:space="preserve">11.1169300079346</t>
@@ -1580,19 +1580,19 @@
     <t xml:space="preserve">11.2368974685669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3568630218506</t>
+    <t xml:space="preserve">11.3568639755249</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969079971313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8370084762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1569194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0369520187378</t>
+    <t xml:space="preserve">10.837007522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1569185256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0369529724121</t>
   </si>
   <si>
     <t xml:space="preserve">10.8769979476929</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">10.9569749832153</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7570295333862</t>
+    <t xml:space="preserve">10.7570304870605</t>
   </si>
   <si>
     <t xml:space="preserve">10.5970735549927</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">10.4371185302734</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2768869400024</t>
+    <t xml:space="preserve">11.2768878936768</t>
   </si>
   <si>
     <t xml:space="preserve">11.4368419647217</t>
@@ -1622,10 +1622,10 @@
     <t xml:space="preserve">11.556809425354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.676775932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7170400619507</t>
+    <t xml:space="preserve">11.6767768859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.717041015625</t>
   </si>
   <si>
     <t xml:space="preserve">8.11775779724121</t>
@@ -1634,13 +1634,13 @@
     <t xml:space="preserve">7.1660213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88582229614258</t>
+    <t xml:space="preserve">7.88582277297974</t>
   </si>
   <si>
     <t xml:space="preserve">7.46993732452393</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03805685043335</t>
+    <t xml:space="preserve">7.03805732727051</t>
   </si>
   <si>
     <t xml:space="preserve">6.9100923538208</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">6.39823341369629</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20628595352173</t>
+    <t xml:space="preserve">6.20628690719604</t>
   </si>
   <si>
     <t xml:space="preserve">5.99834394454956</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">7.40595531463623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32597732543945</t>
+    <t xml:space="preserve">7.32597637176514</t>
   </si>
   <si>
     <t xml:space="preserve">7.11803436279297</t>
@@ -1676,19 +1676,19 @@
     <t xml:space="preserve">6.9740743637085</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29398584365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15002489089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86210536956787</t>
+    <t xml:space="preserve">7.29398679733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15002584457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86210489273071</t>
   </si>
   <si>
     <t xml:space="preserve">6.81411933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76613140106201</t>
+    <t xml:space="preserve">6.76613235473633</t>
   </si>
   <si>
     <t xml:space="preserve">6.94208383560181</t>
@@ -1700,13 +1700,13 @@
     <t xml:space="preserve">6.92608690261841</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78212738037109</t>
+    <t xml:space="preserve">6.78212690353394</t>
   </si>
   <si>
     <t xml:space="preserve">6.83011436462402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92877864837646</t>
+    <t xml:space="preserve">6.92877912521362</t>
   </si>
   <si>
     <t xml:space="preserve">7.01067972183228</t>
@@ -1715,55 +1715,55 @@
     <t xml:space="preserve">6.89601898193359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96153926849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73221826553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74859809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05981874465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12533950805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22362041473389</t>
+    <t xml:space="preserve">6.96153974533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73221778869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74859762191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05981969833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1253399848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22361993789673</t>
   </si>
   <si>
     <t xml:space="preserve">7.5512228012085</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56760263442993</t>
+    <t xml:space="preserve">7.56760168075562</t>
   </si>
   <si>
     <t xml:space="preserve">8.0262451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31289577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39479732513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72239971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76334953308105</t>
+    <t xml:space="preserve">8.31289672851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39479827880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72239875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76335048675537</t>
   </si>
   <si>
     <t xml:space="preserve">8.88620090484619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17285060882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41855430603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92715072631836</t>
+    <t xml:space="preserve">9.1728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41855239868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92714977264404</t>
   </si>
   <si>
     <t xml:space="preserve">9.13190078735352</t>
@@ -1772,10 +1772,10 @@
     <t xml:space="preserve">8.96810054779053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3366527557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84524917602539</t>
+    <t xml:space="preserve">9.33665180206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84525108337402</t>
   </si>
   <si>
     <t xml:space="preserve">9.09095191955566</t>
@@ -1787,52 +1787,52 @@
     <t xml:space="preserve">9.25475215911865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0090503692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64049911499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09176635742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17366695404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1900463104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10814476013184</t>
+    <t xml:space="preserve">9.00905132293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64049816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09176540374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17366504669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19004726409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10814571380615</t>
   </si>
   <si>
     <t xml:space="preserve">8.15728664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9607253074646</t>
+    <t xml:space="preserve">7.96072483062744</t>
   </si>
   <si>
     <t xml:space="preserve">7.87882423400879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71502304077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78054332733154</t>
+    <t xml:space="preserve">7.71502351760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7805438041687</t>
   </si>
   <si>
     <t xml:space="preserve">7.58398294448853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51846265792847</t>
+    <t xml:space="preserve">7.51846313476562</t>
   </si>
   <si>
     <t xml:space="preserve">7.5348424911499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33828115463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4857029914856</t>
+    <t xml:space="preserve">7.33828163146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48570156097412</t>
   </si>
   <si>
     <t xml:space="preserve">7.61674356460571</t>
@@ -1844,58 +1844,58 @@
     <t xml:space="preserve">7.76416301727295</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73140335083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79692506790161</t>
+    <t xml:space="preserve">7.73140430450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79692411422729</t>
   </si>
   <si>
     <t xml:space="preserve">7.66588306427002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63312292098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64950275421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68226385116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82968521118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74778413772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43656206130981</t>
+    <t xml:space="preserve">7.63312244415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64950323104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68226289749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82968425750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74778270721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43656158447266</t>
   </si>
   <si>
     <t xml:space="preserve">7.60036277770996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35466146469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40380191802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2400016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1908597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79773807525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68307733535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56841707229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3882360458374</t>
+    <t xml:space="preserve">7.354660987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40380096435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24000120162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19086027145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79773902893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68307781219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5684175491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38823652267456</t>
   </si>
   <si>
     <t xml:space="preserve">6.2244348526001</t>
@@ -1904,121 +1904,121 @@
     <t xml:space="preserve">6.48651647567749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42099618911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7158374786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84687852859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04344034194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92796516418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5176477432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27194690704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97710466384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84606313705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12452697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59954833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43574810028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5585994720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6814489364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47669792175293</t>
+    <t xml:space="preserve">6.42099571228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71583795547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84687805175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04344081878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92796468734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51764678955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27194786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97710514068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8460636138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12452507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59954929351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43574714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55859851837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68144989013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47669887542725</t>
   </si>
   <si>
     <t xml:space="preserve">8.35384654998779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23099803924561</t>
+    <t xml:space="preserve">8.23099708557129</t>
   </si>
   <si>
     <t xml:space="preserve">8.04262447357178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94434547424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86244535446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00986576080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.059006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45950317382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90995597839355</t>
+    <t xml:space="preserve">7.94434452056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86244487762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00986385345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05900573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45950412750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90995693206787</t>
   </si>
   <si>
     <t xml:space="preserve">10.1556568145752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86900520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62330532073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50045299530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37760257720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58235359191895</t>
+    <t xml:space="preserve">9.86900615692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62330436706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50045490264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37760353088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58235454559326</t>
   </si>
   <si>
     <t xml:space="preserve">9.70520496368408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05000114440918</t>
+    <t xml:space="preserve">9.0500020980835</t>
   </si>
   <si>
     <t xml:space="preserve">9.54140377044678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22513580322266</t>
+    <t xml:space="preserve">9.22513484954834</t>
   </si>
   <si>
     <t xml:space="preserve">9.18320274353027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09933853149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14126968383789</t>
+    <t xml:space="preserve">9.09933757781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14127063751221</t>
   </si>
   <si>
     <t xml:space="preserve">9.39286422729492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30900096893311</t>
+    <t xml:space="preserve">9.30900001525879</t>
   </si>
   <si>
     <t xml:space="preserve">9.56059455871582</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">9.4347972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35093116760254</t>
+    <t xml:space="preserve">9.35093212127686</t>
   </si>
   <si>
     <t xml:space="preserve">9.64445972442627</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">9.51866340637207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47672939300537</t>
+    <t xml:space="preserve">9.47673034667969</t>
   </si>
   <si>
     <t xml:space="preserve">9.77025604248047</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">9.72832489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3153791427612</t>
+    <t xml:space="preserve">10.3153781890869</t>
   </si>
   <si>
     <t xml:space="preserve">10.1895809173584</t>
@@ -2060,28 +2060,28 @@
     <t xml:space="preserve">10.1057167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3573112487793</t>
+    <t xml:space="preserve">10.357310295105</t>
   </si>
   <si>
     <t xml:space="preserve">10.2734460830688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.147647857666</t>
+    <t xml:space="preserve">10.1476488113403</t>
   </si>
   <si>
     <t xml:space="preserve">10.0218515396118</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85412216186523</t>
+    <t xml:space="preserve">9.85412120819092</t>
   </si>
   <si>
     <t xml:space="preserve">9.81218910217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89605522155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26706695556641</t>
+    <t xml:space="preserve">9.8960542678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26706886291504</t>
   </si>
   <si>
     <t xml:space="preserve">9.97991847991943</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">9.68639183044434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05740451812744</t>
+    <t xml:space="preserve">9.05740642547607</t>
   </si>
   <si>
     <t xml:space="preserve">8.97354030609131</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">10.3992433547974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5669727325439</t>
+    <t xml:space="preserve">10.5669736862183</t>
   </si>
   <si>
     <t xml:space="preserve">10.7766351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7347030639648</t>
+    <t xml:space="preserve">10.7347021102905</t>
   </si>
   <si>
     <t xml:space="preserve">11.279824256897</t>
@@ -2114,16 +2114,16 @@
     <t xml:space="preserve">11.321756362915</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9443645477295</t>
+    <t xml:space="preserve">10.9443655014038</t>
   </si>
   <si>
     <t xml:space="preserve">11.2378911972046</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1959600448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4056234359741</t>
+    <t xml:space="preserve">11.1959590911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4056224822998</t>
   </si>
   <si>
     <t xml:space="preserve">11.1540269851685</t>
@@ -2135,13 +2135,13 @@
     <t xml:space="preserve">11.741081237793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0346078872681</t>
+    <t xml:space="preserve">12.0346088409424</t>
   </si>
   <si>
     <t xml:space="preserve">11.6152839660645</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6572151184082</t>
+    <t xml:space="preserve">11.6572160720825</t>
   </si>
   <si>
     <t xml:space="preserve">11.1120948791504</t>
@@ -2150,16 +2150,16 @@
     <t xml:space="preserve">10.9862985610962</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0701627731323</t>
+    <t xml:space="preserve">11.070161819458</t>
   </si>
   <si>
     <t xml:space="preserve">11.4894866943359</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3636894226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6991491317749</t>
+    <t xml:space="preserve">11.3636903762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6991472244263</t>
   </si>
   <si>
     <t xml:space="preserve">11.5733509063721</t>
@@ -2168,22 +2168,22 @@
     <t xml:space="preserve">11.531418800354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0282287597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4831075668335</t>
+    <t xml:space="preserve">11.0282297134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4831085205078</t>
   </si>
   <si>
     <t xml:space="preserve">10.5250406265259</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6089057922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.818567276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9024324417114</t>
+    <t xml:space="preserve">10.608904838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8185663223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9024333953857</t>
   </si>
   <si>
     <t xml:space="preserve">11.4475536346436</t>
@@ -2192,22 +2192,22 @@
     <t xml:space="preserve">11.1378631591797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0948600769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3958826065063</t>
+    <t xml:space="preserve">11.09485912323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3958835601807</t>
   </si>
   <si>
     <t xml:space="preserve">11.6539030075073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8259153366089</t>
+    <t xml:space="preserve">11.8259162902832</t>
   </si>
   <si>
     <t xml:space="preserve">11.6108989715576</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6969060897827</t>
+    <t xml:space="preserve">11.696907043457</t>
   </si>
   <si>
     <t xml:space="preserve">11.4388866424561</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">11.0088529586792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8368396759033</t>
+    <t xml:space="preserve">10.8368406295776</t>
   </si>
   <si>
     <t xml:space="preserve">10.9658489227295</t>
@@ -2240,13 +2240,13 @@
     <t xml:space="preserve">10.7508325576782</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8798427581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6648263931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9228458404541</t>
+    <t xml:space="preserve">10.8798418045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6648254394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9228467941284</t>
   </si>
   <si>
     <t xml:space="preserve">10.7078294754028</t>
@@ -2264,34 +2264,34 @@
     <t xml:space="preserve">9.97677326202393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89076709747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76175594329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84776306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46073341369629</t>
+    <t xml:space="preserve">9.89076614379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76175689697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84776210784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46073246002197</t>
   </si>
   <si>
     <t xml:space="preserve">9.54673957824707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24571704864502</t>
+    <t xml:space="preserve">9.2457160949707</t>
   </si>
   <si>
     <t xml:space="preserve">9.20271301269531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03069972991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15970993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2777967453003</t>
+    <t xml:space="preserve">9.03070068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15970897674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.277795791626</t>
   </si>
   <si>
     <t xml:space="preserve">9.67574977874756</t>
@@ -2315,22 +2315,22 @@
     <t xml:space="preserve">9.58974266052246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41772842407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33172225952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37472534179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50373649597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63274574279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6218223571777</t>
+    <t xml:space="preserve">9.41772937774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3317232131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37472629547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.503737449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63274669647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6218233108521</t>
   </si>
   <si>
     <t xml:space="preserve">11.3098764419556</t>
@@ -2345,52 +2345,52 @@
     <t xml:space="preserve">10.7938365936279</t>
   </si>
   <si>
-    <t xml:space="preserve">11.352879524231</t>
+    <t xml:space="preserve">11.3528785705566</t>
   </si>
   <si>
     <t xml:space="preserve">11.4818897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1699419021606</t>
+    <t xml:space="preserve">12.169942855835</t>
   </si>
   <si>
     <t xml:space="preserve">11.9549255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0409326553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8689203262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7829122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9979295730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3419570922852</t>
+    <t xml:space="preserve">12.0409336090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8689193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7829132080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9979286193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3419561386108</t>
   </si>
   <si>
     <t xml:space="preserve">12.4709663391113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2989540100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.513970375061</t>
+    <t xml:space="preserve">12.2989530563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5139694213867</t>
   </si>
   <si>
     <t xml:space="preserve">12.5569734573364</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6429786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2559499740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3849592208862</t>
+    <t xml:space="preserve">12.6429796218872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2559490203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3849582672119</t>
   </si>
   <si>
     <t xml:space="preserve">12.5999755859375</t>
@@ -2405,13 +2405,10 @@
     <t xml:space="preserve">12.7289867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9997701644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6859817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8204641342163</t>
+    <t xml:space="preserve">12.9997711181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.820463180542</t>
   </si>
   <si>
     <t xml:space="preserve">12.9549436569214</t>
@@ -2423,28 +2420,28 @@
     <t xml:space="preserve">13.4480381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0894241333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2239046096802</t>
+    <t xml:space="preserve">13.0894250869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2239036560059</t>
   </si>
   <si>
     <t xml:space="preserve">13.3583841323853</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1342496871948</t>
+    <t xml:space="preserve">13.1342506408691</t>
   </si>
   <si>
     <t xml:space="preserve">13.0445976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1790771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3135585784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2687320709229</t>
+    <t xml:space="preserve">13.1790781021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3135576248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2687311172485</t>
   </si>
   <si>
     <t xml:space="preserve">12.8652906417847</t>
@@ -2462,7 +2459,7 @@
     <t xml:space="preserve">13.7618265151978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7928419113159</t>
+    <t xml:space="preserve">14.7928428649902</t>
   </si>
   <si>
     <t xml:space="preserve">14.1652669906616</t>
@@ -2474,10 +2471,10 @@
     <t xml:space="preserve">13.8963060379028</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4032115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5825176239014</t>
+    <t xml:space="preserve">13.4032106399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5825185775757</t>
   </si>
   <si>
     <t xml:space="preserve">13.492865562439</t>
@@ -2486,7 +2483,7 @@
     <t xml:space="preserve">13.6721725463867</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9411325454712</t>
+    <t xml:space="preserve">13.9411334991455</t>
   </si>
   <si>
     <t xml:space="preserve">13.7169990539551</t>
@@ -2495,22 +2492,22 @@
     <t xml:space="preserve">14.3445739746094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9859600067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5238828659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.299747467041</t>
+    <t xml:space="preserve">13.9859609603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5238819122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2997465133667</t>
   </si>
   <si>
     <t xml:space="preserve">14.4342279434204</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2100944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3893995285034</t>
+    <t xml:space="preserve">14.21009349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3894004821777</t>
   </si>
   <si>
     <t xml:space="preserve">14.6135339736938</t>
@@ -2537,7 +2534,7 @@
     <t xml:space="preserve">15.0169763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1962842941284</t>
+    <t xml:space="preserve">15.1962833404541</t>
   </si>
   <si>
     <t xml:space="preserve">15.3307638168335</t>
@@ -2546,145 +2543,148 @@
     <t xml:space="preserve">15.4204187393188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3755912780762</t>
+    <t xml:space="preserve">15.3755893707275</t>
   </si>
   <si>
     <t xml:space="preserve">14.8376684188843</t>
   </si>
   <si>
-    <t xml:space="preserve">14.882495880127</t>
+    <t xml:space="preserve">14.8824968338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1514558792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7790327072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0341815948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4514331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5859146118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8686857223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0479907989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7342052459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9583387374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1376457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8100471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7203941345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4066066741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2721271514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0928211212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9135131835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4652442932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1066293716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5687084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7031879425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0618019104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2411098480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2859363555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5997247695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.644552230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8238582611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.689377784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5100698471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5548973083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3385105133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5723295211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5255670547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.291748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7126207351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6190948486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4320392608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4788017272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3852758407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9932041168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.899676322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.852912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8061485290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6658573150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0579290390015</t>
   </si>
   <si>
     <t xml:space="preserve">15.1514568328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.77903175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0341815948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4514331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5859146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8686866760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0479907989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7342042922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9583377838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1376457214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8100490570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7203941345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4066066741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2721252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0928211212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9135122299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4652442932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1066293716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5687084197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7031879425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0618019104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2411098480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2859363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5997247695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.644552230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8238592147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.689377784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5100698471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5548973083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3385105133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5723295211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5255670547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.291748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7126207351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6190948486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4320392608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4788017272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3852758407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9932041168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.899676322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.852912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8061485290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6658573150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0579290390015</t>
   </si>
   <si>
     <t xml:space="preserve">15.1982202529907</t>
@@ -51985,7 +51985,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1871" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -52011,7 +52011,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52037,7 +52037,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1873" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52089,7 +52089,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1875" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -52115,7 +52115,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1876" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -52141,7 +52141,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1877" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52167,7 +52167,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -52219,7 +52219,7 @@
         <v>15</v>
       </c>
       <c r="G1880" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52271,7 +52271,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1882" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52297,7 +52297,7 @@
         <v>14.75</v>
       </c>
       <c r="G1883" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52323,7 +52323,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52349,7 +52349,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1885" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52375,7 +52375,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52401,7 +52401,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1887" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52427,7 +52427,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1888" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52453,7 +52453,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1889" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52479,7 +52479,7 @@
         <v>15</v>
       </c>
       <c r="G1890" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52505,7 +52505,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52531,7 +52531,7 @@
         <v>14.75</v>
       </c>
       <c r="G1892" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52557,7 +52557,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1893" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52583,7 +52583,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52609,7 +52609,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1895" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52635,7 +52635,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52661,7 +52661,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1897" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52687,7 +52687,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1898" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52713,7 +52713,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1899" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52739,7 +52739,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1900" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52765,7 +52765,7 @@
         <v>14.75</v>
       </c>
       <c r="G1901" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52791,7 +52791,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1902" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52817,7 +52817,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52843,7 +52843,7 @@
         <v>14.75</v>
       </c>
       <c r="G1904" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52869,7 +52869,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1905" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52895,7 +52895,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1906" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52921,7 +52921,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52947,7 +52947,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52973,7 +52973,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1909" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52999,7 +52999,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1910" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53025,7 +53025,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1911" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53051,7 +53051,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1912" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -53077,7 +53077,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1913" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53103,7 +53103,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1914" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53129,7 +53129,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53207,7 +53207,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1918" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53259,7 +53259,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1920" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53285,7 +53285,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1921" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53311,7 +53311,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53337,7 +53337,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1923" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53363,7 +53363,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1924" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53389,7 +53389,7 @@
         <v>14.75</v>
       </c>
       <c r="G1925" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53415,7 +53415,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1926" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53441,7 +53441,7 @@
         <v>14.75</v>
       </c>
       <c r="G1927" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53467,7 +53467,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1928" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53493,7 +53493,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1929" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53519,7 +53519,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1930" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53545,7 +53545,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1931" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53571,7 +53571,7 @@
         <v>15.75</v>
       </c>
       <c r="G1932" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53597,7 +53597,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53623,7 +53623,7 @@
         <v>15.75</v>
       </c>
       <c r="G1934" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53649,7 +53649,7 @@
         <v>16.5</v>
       </c>
       <c r="G1935" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53675,7 +53675,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1936" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53701,7 +53701,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53727,7 +53727,7 @@
         <v>15.5</v>
       </c>
       <c r="G1938" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53753,7 +53753,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1939" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53779,7 +53779,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1940" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53805,7 +53805,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53831,7 +53831,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1942" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53857,7 +53857,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1943" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53883,7 +53883,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1944" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53909,7 +53909,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1945" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53935,7 +53935,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1946" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53961,7 +53961,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1947" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53987,7 +53987,7 @@
         <v>15.75</v>
       </c>
       <c r="G1948" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54013,7 +54013,7 @@
         <v>15.5</v>
       </c>
       <c r="G1949" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54039,7 +54039,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54065,7 +54065,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1951" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54091,7 +54091,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1952" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54117,7 +54117,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1953" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54143,7 +54143,7 @@
         <v>15.25</v>
       </c>
       <c r="G1954" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54169,7 +54169,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1955" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54195,7 +54195,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1956" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54221,7 +54221,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1957" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54247,7 +54247,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1958" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54273,7 +54273,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54299,7 +54299,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1960" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54325,7 +54325,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1961" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54351,7 +54351,7 @@
         <v>15.5</v>
       </c>
       <c r="G1962" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54377,7 +54377,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1963" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54403,7 +54403,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54429,7 +54429,7 @@
         <v>16</v>
       </c>
       <c r="G1965" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54455,7 +54455,7 @@
         <v>16</v>
       </c>
       <c r="G1966" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -54481,7 +54481,7 @@
         <v>15.75</v>
       </c>
       <c r="G1967" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54507,7 +54507,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1968" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54533,7 +54533,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1969" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54559,7 +54559,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1970" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54585,7 +54585,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1971" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54611,7 +54611,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1972" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54637,7 +54637,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1973" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54663,7 +54663,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1974" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54689,7 +54689,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1975" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54715,7 +54715,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1976" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54741,7 +54741,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54767,7 +54767,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1978" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54793,7 +54793,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1979" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54819,7 +54819,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1980" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54845,7 +54845,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1981" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54871,7 +54871,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54897,7 +54897,7 @@
         <v>16</v>
       </c>
       <c r="G1983" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54923,7 +54923,7 @@
         <v>16.5</v>
       </c>
       <c r="G1984" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54949,7 +54949,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1985" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54975,7 +54975,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1986" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55001,7 +55001,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1987" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55027,7 +55027,7 @@
         <v>15.75</v>
       </c>
       <c r="G1988" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55053,7 +55053,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1989" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55079,7 +55079,7 @@
         <v>15.75</v>
       </c>
       <c r="G1990" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55105,7 +55105,7 @@
         <v>15.75</v>
       </c>
       <c r="G1991" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55131,7 +55131,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1992" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55157,7 +55157,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1993" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55183,7 +55183,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1994" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55209,7 +55209,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1995" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55235,7 +55235,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1996" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55261,7 +55261,7 @@
         <v>15.75</v>
       </c>
       <c r="G1997" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55287,7 +55287,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1998" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55313,7 +55313,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1999" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55339,7 +55339,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2000" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55365,7 +55365,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2001" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55391,7 +55391,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2002" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55417,7 +55417,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55443,7 +55443,7 @@
         <v>16</v>
       </c>
       <c r="G2004" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55469,7 +55469,7 @@
         <v>16</v>
       </c>
       <c r="G2005" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55495,7 +55495,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2006" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55521,7 +55521,7 @@
         <v>16</v>
       </c>
       <c r="G2007" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55547,7 +55547,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2008" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55573,7 +55573,7 @@
         <v>16</v>
       </c>
       <c r="G2009" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55599,7 +55599,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2010" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55625,7 +55625,7 @@
         <v>16</v>
       </c>
       <c r="G2011" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55651,7 +55651,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55677,7 +55677,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2013" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55703,7 +55703,7 @@
         <v>16</v>
       </c>
       <c r="G2014" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55729,7 +55729,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55755,7 +55755,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2016" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55781,7 +55781,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55807,7 +55807,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2018" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55833,7 +55833,7 @@
         <v>15.75</v>
       </c>
       <c r="G2019" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55859,7 +55859,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2020" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55885,7 +55885,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2021" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55911,7 +55911,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2022" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55937,7 +55937,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2023" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55963,7 +55963,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2024" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55989,7 +55989,7 @@
         <v>16.75</v>
       </c>
       <c r="G2025" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56015,7 +56015,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2026" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56041,7 +56041,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2027" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56067,7 +56067,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56093,7 +56093,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2029" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56119,7 +56119,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2030" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56145,7 +56145,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2031" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56171,7 +56171,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2032" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56197,7 +56197,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2033" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56223,7 +56223,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2034" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56249,7 +56249,7 @@
         <v>19</v>
       </c>
       <c r="G2035" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56275,7 +56275,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G2036" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56301,7 +56301,7 @@
         <v>18.5</v>
       </c>
       <c r="G2037" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56327,7 +56327,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2038" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56353,7 +56353,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2039" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56379,7 +56379,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2040" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56405,7 +56405,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2041" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56431,7 +56431,7 @@
         <v>18</v>
       </c>
       <c r="G2042" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56457,7 +56457,7 @@
         <v>18.5</v>
       </c>
       <c r="G2043" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56483,7 +56483,7 @@
         <v>18.75</v>
       </c>
       <c r="G2044" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56509,7 +56509,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2045" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56535,7 +56535,7 @@
         <v>18.5</v>
       </c>
       <c r="G2046" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56561,7 +56561,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2047" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56587,7 +56587,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G2048" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56613,7 +56613,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2049" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56639,7 +56639,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2050" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56665,7 +56665,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2051" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56691,7 +56691,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2052" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56717,7 +56717,7 @@
         <v>17.75</v>
       </c>
       <c r="G2053" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56743,7 +56743,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2054" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56769,7 +56769,7 @@
         <v>17.25</v>
       </c>
       <c r="G2055" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56795,7 +56795,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2056" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56821,7 +56821,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2057" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56847,7 +56847,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2058" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56873,7 +56873,7 @@
         <v>16.25</v>
       </c>
       <c r="G2059" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56899,7 +56899,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2060" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56925,7 +56925,7 @@
         <v>16.5</v>
       </c>
       <c r="G2061" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56951,7 +56951,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2062" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56977,7 +56977,7 @@
         <v>16.5</v>
       </c>
       <c r="G2063" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -57003,7 +57003,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2064" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57029,7 +57029,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2065" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57055,7 +57055,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2066" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57081,7 +57081,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2067" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57107,7 +57107,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2068" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57133,7 +57133,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2069" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57159,7 +57159,7 @@
         <v>16.75</v>
       </c>
       <c r="G2070" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57185,7 +57185,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2071" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57211,7 +57211,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2072" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57237,7 +57237,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2073" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57263,7 +57263,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2074" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57289,7 +57289,7 @@
         <v>17</v>
       </c>
       <c r="G2075" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57315,7 +57315,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2076" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57341,7 +57341,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2077" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -57367,7 +57367,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2078" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -57393,7 +57393,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57419,7 +57419,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2080" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57445,7 +57445,7 @@
         <v>17.75</v>
       </c>
       <c r="G2081" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57471,7 +57471,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G2082" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57497,7 +57497,7 @@
         <v>17.5</v>
       </c>
       <c r="G2083" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57523,7 +57523,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2084" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57549,7 +57549,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2085" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57575,7 +57575,7 @@
         <v>17.5</v>
       </c>
       <c r="G2086" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57601,7 +57601,7 @@
         <v>17</v>
       </c>
       <c r="G2087" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57627,7 +57627,7 @@
         <v>17</v>
       </c>
       <c r="G2088" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57653,7 +57653,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2089" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57679,7 +57679,7 @@
         <v>17.75</v>
       </c>
       <c r="G2090" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57705,7 +57705,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2091" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57731,7 +57731,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2092" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57757,7 +57757,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2093" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57783,7 +57783,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2094" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57809,7 +57809,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2095" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57835,7 +57835,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2096" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -57861,7 +57861,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2097" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57887,7 +57887,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57913,7 +57913,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2099" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57939,7 +57939,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2100" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57965,7 +57965,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2101" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57991,7 +57991,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2102" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58017,7 +58017,7 @@
         <v>17</v>
       </c>
       <c r="G2103" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58043,7 +58043,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2104" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58069,7 +58069,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2105" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58095,7 +58095,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2106" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58121,7 +58121,7 @@
         <v>17.5</v>
       </c>
       <c r="G2107" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -58147,7 +58147,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2108" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58173,7 +58173,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2109" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -58199,7 +58199,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2110" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58225,7 +58225,7 @@
         <v>17</v>
       </c>
       <c r="G2111" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58251,7 +58251,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2112" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58277,7 +58277,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2113" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58303,7 +58303,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2114" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58329,7 +58329,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2115" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58355,7 +58355,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2116" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58381,7 +58381,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2117" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -58407,7 +58407,7 @@
         <v>17</v>
       </c>
       <c r="G2118" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58433,7 +58433,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2119" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58459,7 +58459,7 @@
         <v>17</v>
       </c>
       <c r="G2120" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58485,7 +58485,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2121" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58511,7 +58511,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2122" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58537,7 +58537,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2123" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58563,7 +58563,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2124" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58589,7 +58589,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2125" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58615,7 +58615,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2126" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58641,7 +58641,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2127" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58667,7 +58667,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2128" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58693,7 +58693,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2129" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58719,7 +58719,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2130" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58745,7 +58745,7 @@
         <v>16.5</v>
       </c>
       <c r="G2131" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58771,7 +58771,7 @@
         <v>16.5</v>
       </c>
       <c r="G2132" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58797,7 +58797,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2133" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58823,7 +58823,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2134" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58849,7 +58849,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2135" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58875,7 +58875,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2136" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58901,7 +58901,7 @@
         <v>17</v>
       </c>
       <c r="G2137" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58927,7 +58927,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2138" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58953,7 +58953,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2139" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58979,7 +58979,7 @@
         <v>16.5</v>
       </c>
       <c r="G2140" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59005,7 +59005,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2141" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59031,7 +59031,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2142" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59057,7 +59057,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2143" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59083,7 +59083,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2144" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59109,7 +59109,7 @@
         <v>16.75</v>
       </c>
       <c r="G2145" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59135,7 +59135,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2146" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59161,7 +59161,7 @@
         <v>16.75</v>
       </c>
       <c r="G2147" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59187,7 +59187,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2148" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59213,7 +59213,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2149" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59239,7 +59239,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2150" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59265,7 +59265,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2151" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59291,7 +59291,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2152" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59317,7 +59317,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2153" t="s">
-        <v>847</v>
+        <v>890</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59343,7 +59343,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2154" t="s">
-        <v>847</v>
+        <v>890</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59395,7 +59395,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2156" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59629,7 +59629,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2165" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59707,7 +59707,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2168" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59785,7 +59785,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2171" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59863,7 +59863,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2174" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -61475,7 +61475,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2236" t="s">
-        <v>847</v>
+        <v>890</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61527,7 +61527,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2238" t="s">
-        <v>847</v>
+        <v>890</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61605,7 +61605,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2241" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61631,7 +61631,7 @@
         <v>16.5</v>
       </c>
       <c r="G2242" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61657,7 +61657,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2243" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61735,7 +61735,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2246" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61787,7 +61787,7 @@
         <v>17</v>
       </c>
       <c r="G2248" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61813,7 +61813,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2249" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62047,7 +62047,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2258" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62073,7 +62073,7 @@
         <v>17</v>
       </c>
       <c r="G2259" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62099,7 +62099,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2260" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62151,7 +62151,7 @@
         <v>16.5</v>
       </c>
       <c r="G2262" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62177,7 +62177,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2263" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62203,7 +62203,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2264" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62229,7 +62229,7 @@
         <v>16.5</v>
       </c>
       <c r="G2265" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62255,7 +62255,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2266" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62385,7 +62385,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2271" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62411,7 +62411,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2272" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62437,7 +62437,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2273" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62463,7 +62463,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2274" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62489,7 +62489,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2275" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62515,7 +62515,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2276" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62541,7 +62541,7 @@
         <v>17</v>
       </c>
       <c r="G2277" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62567,7 +62567,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2278" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62593,7 +62593,7 @@
         <v>16.5</v>
       </c>
       <c r="G2279" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62801,7 +62801,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2287" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62827,7 +62827,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2288" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62853,7 +62853,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2289" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62905,7 +62905,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2291" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62931,7 +62931,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2292" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62957,7 +62957,7 @@
         <v>16.5</v>
       </c>
       <c r="G2293" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63009,7 +63009,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2295" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63581,7 +63581,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2317" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63607,7 +63607,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>847</v>
+        <v>890</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64439,7 +64439,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2350" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -68971,7 +68971,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.6910300926</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>9505</v>
@@ -68992,6 +68992,32 @@
         <v>989</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.6911689815</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>30739</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>15.3000001907349</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>15.3000001907349</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>15.1999998092651</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>993</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BEC.MI.xlsx
+++ b/data/BEC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="1000">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,46 +47,46 @@
     <t xml:space="preserve">4.96181011199951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8704080581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87693548202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92916584014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77247714996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79859256744385</t>
+    <t xml:space="preserve">4.87040758132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87693691253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92916631698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77247762680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79859209060669</t>
   </si>
   <si>
     <t xml:space="preserve">4.83449983596802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73330497741699</t>
+    <t xml:space="preserve">4.73330593109131</t>
   </si>
   <si>
     <t xml:space="preserve">4.79532814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80512094497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76594877243042</t>
+    <t xml:space="preserve">4.80512046813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76594829559326</t>
   </si>
   <si>
     <t xml:space="preserve">4.75942039489746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60273170471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69739770889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69413280487061</t>
+    <t xml:space="preserve">4.6027307510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69739723205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69413328170776</t>
   </si>
   <si>
     <t xml:space="preserve">4.63537502288818</t>
@@ -104,49 +104,49 @@
     <t xml:space="preserve">4.07390689849854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08043527603149</t>
+    <t xml:space="preserve">4.08043575286865</t>
   </si>
   <si>
     <t xml:space="preserve">4.23386001586914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40360641479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49174308776855</t>
+    <t xml:space="preserve">4.40360546112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49174356460571</t>
   </si>
   <si>
     <t xml:space="preserve">4.5309157371521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43298482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50480031967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5374436378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42645740509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42319297790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43951368331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41666316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44930696487427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46562910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47868633270264</t>
+    <t xml:space="preserve">4.43298530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50480079650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53744411468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42645645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4231915473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43951416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.416663646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44930744171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4656286239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47868585586548</t>
   </si>
   <si>
     <t xml:space="preserve">4.60926055908203</t>
@@ -155,10 +155,10 @@
     <t xml:space="preserve">4.89652252197266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90957975387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93569469451904</t>
+    <t xml:space="preserve">4.90958070755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9356951713562</t>
   </si>
   <si>
     <t xml:space="preserve">4.91284418106079</t>
@@ -167,16 +167,16 @@
     <t xml:space="preserve">5.01403951644897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94222402572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03362607955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04015302658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09238386154175</t>
+    <t xml:space="preserve">4.942223072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03362512588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04015398025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09238338470459</t>
   </si>
   <si>
     <t xml:space="preserve">4.94875192642212</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">4.84429311752319</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0695333480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09891223907471</t>
+    <t xml:space="preserve">5.06953287124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09891176223755</t>
   </si>
   <si>
     <t xml:space="preserve">4.98792409896851</t>
@@ -200,70 +200,70 @@
     <t xml:space="preserve">5.0499472618103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04341793060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05973958969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98466014862061</t>
+    <t xml:space="preserve">5.04341745376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05974006652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98465967178345</t>
   </si>
   <si>
     <t xml:space="preserve">5.02709674835205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99973773956299</t>
+    <t xml:space="preserve">4.99973821640015</t>
   </si>
   <si>
     <t xml:space="preserve">5.03393602371216</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9621205329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91766262054443</t>
+    <t xml:space="preserve">4.96212100982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91766309738159</t>
   </si>
   <si>
     <t xml:space="preserve">4.9450216293335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85610675811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89030504226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89714479446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79455041885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82190942764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98263931274414</t>
+    <t xml:space="preserve">4.85610723495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.890305519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89714431762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79455089569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82190895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9826397895813</t>
   </si>
   <si>
     <t xml:space="preserve">4.92450284957886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00657796859741</t>
+    <t xml:space="preserve">5.00657844543457</t>
   </si>
   <si>
     <t xml:space="preserve">4.88346529006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94844150543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95870018005371</t>
+    <t xml:space="preserve">4.94844102859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95870065689087</t>
   </si>
   <si>
     <t xml:space="preserve">4.99289846420288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86636590957642</t>
+    <t xml:space="preserve">4.86636638641357</t>
   </si>
   <si>
     <t xml:space="preserve">4.8526873588562</t>
@@ -272,40 +272,40 @@
     <t xml:space="preserve">4.93134260177612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78771066665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78429079055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8253288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77403211593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72273588180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67485761642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75693225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56200504302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54148578643799</t>
+    <t xml:space="preserve">4.78771114349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78429126739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82532835006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77403163909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72273540496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67485809326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75693273544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56200456619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54148626327515</t>
   </si>
   <si>
     <t xml:space="preserve">4.53122615814209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60304260253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63040113449097</t>
+    <t xml:space="preserve">4.6030421257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63040065765381</t>
   </si>
   <si>
     <t xml:space="preserve">4.55516481399536</t>
@@ -314,28 +314,28 @@
     <t xml:space="preserve">4.58252334594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54832601547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45941066741943</t>
+    <t xml:space="preserve">4.54832553863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45941162109375</t>
   </si>
   <si>
     <t xml:space="preserve">4.53464651107788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52780628204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52096700668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64407920837402</t>
+    <t xml:space="preserve">4.52780723571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52096748352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64407968521118</t>
   </si>
   <si>
     <t xml:space="preserve">4.74325323104858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73983430862427</t>
+    <t xml:space="preserve">4.73983335494995</t>
   </si>
   <si>
     <t xml:space="preserve">4.8355884552002</t>
@@ -347,28 +347,28 @@
     <t xml:space="preserve">4.92792272567749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98605823516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96554088592529</t>
+    <t xml:space="preserve">4.98605966567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96553993225098</t>
   </si>
   <si>
     <t xml:space="preserve">4.91424322128296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97237920761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96896028518677</t>
+    <t xml:space="preserve">4.97237968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96895980834961</t>
   </si>
   <si>
     <t xml:space="preserve">4.86978578567505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93818235397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88004541397095</t>
+    <t xml:space="preserve">4.93818140029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88004589080811</t>
   </si>
   <si>
     <t xml:space="preserve">4.95186138153076</t>
@@ -377,94 +377,94 @@
     <t xml:space="preserve">4.87320566177368</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86294651031494</t>
+    <t xml:space="preserve">4.8629469871521</t>
   </si>
   <si>
     <t xml:space="preserve">4.76719236373901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80138969421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80823040008545</t>
+    <t xml:space="preserve">4.80139064788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80822992324829</t>
   </si>
   <si>
     <t xml:space="preserve">4.76377296447754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8424277305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72957468032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84926795959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81164884567261</t>
+    <t xml:space="preserve">4.84242820739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72957420349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84926700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81164932250977</t>
   </si>
   <si>
     <t xml:space="preserve">4.88688516616821</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02025699615479</t>
+    <t xml:space="preserve">5.02025747299194</t>
   </si>
   <si>
     <t xml:space="preserve">5.08865308761597</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10575199127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06471490859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04761600494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09549236297607</t>
+    <t xml:space="preserve">5.10575151443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0647144317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04761552810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09549188613892</t>
   </si>
   <si>
     <t xml:space="preserve">5.17756748199463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23228454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12969017028809</t>
+    <t xml:space="preserve">5.23228406906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12969064712524</t>
   </si>
   <si>
     <t xml:space="preserve">5.13994979858398</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16388845443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2117657661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30751991271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30068063735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13311004638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22544479370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16730833053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19808626174927</t>
+    <t xml:space="preserve">5.16388893127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21176481246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30752038955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3006796836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13310956954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22544431686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16730785369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19808673858643</t>
   </si>
   <si>
     <t xml:space="preserve">5.29726028442383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47167015075684</t>
+    <t xml:space="preserve">5.47167062759399</t>
   </si>
   <si>
     <t xml:space="preserve">5.40327405929565</t>
@@ -473,16 +473,16 @@
     <t xml:space="preserve">5.36565589904785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36223602294922</t>
+    <t xml:space="preserve">5.36223697662354</t>
   </si>
   <si>
     <t xml:space="preserve">5.46482992172241</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907577514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39643430709839</t>
+    <t xml:space="preserve">5.36907529830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39643383026123</t>
   </si>
   <si>
     <t xml:space="preserve">5.25964260101318</t>
@@ -491,43 +491,43 @@
     <t xml:space="preserve">5.41353321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4614109992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43747138977051</t>
+    <t xml:space="preserve">5.46141052246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43747186660767</t>
   </si>
   <si>
     <t xml:space="preserve">5.45457077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46825075149536</t>
+    <t xml:space="preserve">5.46824979782104</t>
   </si>
   <si>
     <t xml:space="preserve">5.47508955001831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39985466003418</t>
+    <t xml:space="preserve">5.39985418319702</t>
   </si>
   <si>
     <t xml:space="preserve">5.41695356369019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4306321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45799112319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50586748123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52980661392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60846185684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68369674682617</t>
+    <t xml:space="preserve">5.43063259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4579906463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50586843490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52980613708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60846138000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68369722366333</t>
   </si>
   <si>
     <t xml:space="preserve">5.73157453536987</t>
@@ -536,25 +536,25 @@
     <t xml:space="preserve">5.88204479217529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9367618560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94360065460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05645370483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94018173217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04961490631104</t>
+    <t xml:space="preserve">5.93676233291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94360160827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0564546585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94018268585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04961538314819</t>
   </si>
   <si>
     <t xml:space="preserve">6.07355356216431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02567720413208</t>
+    <t xml:space="preserve">6.02567672729492</t>
   </si>
   <si>
     <t xml:space="preserve">5.97437906265259</t>
@@ -563,31 +563,31 @@
     <t xml:space="preserve">6.04277515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17272758483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39501333236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3744945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46682977676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32661867141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11117172241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89914321899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00515794754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2240252494812</t>
+    <t xml:space="preserve">6.17272710800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3950138092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37449502944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46682929992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32661771774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11117124557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8991436958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00515699386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22402477264404</t>
   </si>
   <si>
     <t xml:space="preserve">6.26506185531616</t>
@@ -596,70 +596,70 @@
     <t xml:space="preserve">6.39843368530273</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48050880432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41211318969727</t>
+    <t xml:space="preserve">6.40527296066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48050975799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41211366653442</t>
   </si>
   <si>
     <t xml:space="preserve">6.44973087310791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43605136871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52838659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66859722137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99689674377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94218063354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12000942230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46882915496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66717720031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20066547393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40585327148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64523887634277</t>
+    <t xml:space="preserve">6.43605184555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52838563919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66859769821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99689722061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94217967987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12001132965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4688286781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66717767715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20066452026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40585231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64523792266846</t>
   </si>
   <si>
     <t xml:space="preserve">8.27590084075928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35113525390625</t>
+    <t xml:space="preserve">8.35113620758057</t>
   </si>
   <si>
     <t xml:space="preserve">8.28958034515381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24170207977295</t>
+    <t xml:space="preserve">8.24170303344727</t>
   </si>
   <si>
     <t xml:space="preserve">8.33745765686035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33061790466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31693840026855</t>
+    <t xml:space="preserve">8.33061695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31693744659424</t>
   </si>
   <si>
     <t xml:space="preserve">8.26906108856201</t>
@@ -668,19 +668,19 @@
     <t xml:space="preserve">8.22118377685547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11858940124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30325794219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48108863830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72047519683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7136344909668</t>
+    <t xml:space="preserve">8.11859035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30326080322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48108768463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72047424316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71363353729248</t>
   </si>
   <si>
     <t xml:space="preserve">8.79469108581543</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">8.52751064300537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07478713989258</t>
+    <t xml:space="preserve">8.07478809356689</t>
   </si>
   <si>
     <t xml:space="preserve">8.31228065490723</t>
@@ -701,40 +701,40 @@
     <t xml:space="preserve">8.43102836608887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37165355682373</t>
+    <t xml:space="preserve">8.37165451049805</t>
   </si>
   <si>
     <t xml:space="preserve">7.97830581665039</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88924503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23806476593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26033020019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21579933166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64625549316406</t>
+    <t xml:space="preserve">7.88924551010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23806285858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26033115386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21579837799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6462574005127</t>
   </si>
   <si>
     <t xml:space="preserve">8.75758171081543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80211162567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69078731536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5794620513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66110038757324</t>
+    <t xml:space="preserve">8.8021125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69078636169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57946109771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66110134124756</t>
   </si>
   <si>
     <t xml:space="preserve">8.54977607727051</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">8.52008819580078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53493213653564</t>
+    <t xml:space="preserve">8.53493118286133</t>
   </si>
   <si>
     <t xml:space="preserve">8.60172653198242</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">8.12673950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46071529388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58688354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70563125610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72047424316406</t>
+    <t xml:space="preserve">8.46071434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58688259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70562934875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72047328948975</t>
   </si>
   <si>
     <t xml:space="preserve">8.84664154052734</t>
@@ -785,19 +785,19 @@
     <t xml:space="preserve">8.69820880889893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74273872375488</t>
+    <t xml:space="preserve">8.7427396774292</t>
   </si>
   <si>
     <t xml:space="preserve">8.56461811065674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43845081329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40876388549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34938907623291</t>
+    <t xml:space="preserve">8.43844985961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40876197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34939002990723</t>
   </si>
   <si>
     <t xml:space="preserve">8.42360687255859</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">8.54235458374023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63141345977783</t>
+    <t xml:space="preserve">8.63141441345215</t>
   </si>
   <si>
     <t xml:space="preserve">8.61656951904297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63883590698242</t>
+    <t xml:space="preserve">8.63883399963379</t>
   </si>
   <si>
     <t xml:space="preserve">8.66852188110352</t>
@@ -821,55 +821,55 @@
     <t xml:space="preserve">8.77984619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88375186920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83922100067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82437705993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60914897918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57204151153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49040126800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47555828094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78726959228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71305179595947</t>
+    <t xml:space="preserve">8.88374996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83922004699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82437610626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68336582183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60914993286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57204055786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49040222167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47555923461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78726863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71305274963379</t>
   </si>
   <si>
     <t xml:space="preserve">8.65367794036865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62399101257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75016117095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90601539611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89859485626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94312381744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77242565155029</t>
+    <t xml:space="preserve">8.62399196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75016021728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90601634979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89859390258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94312477111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77242374420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.96538925170898</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">8.87632846832275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97281074523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09155750274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2177267074585</t>
+    <t xml:space="preserve">8.97281169891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09155654907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21772766113281</t>
   </si>
   <si>
     <t xml:space="preserve">9.52201461791992</t>
@@ -893,91 +893,91 @@
     <t xml:space="preserve">9.55170154571533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56654453277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45522022247314</t>
+    <t xml:space="preserve">9.56654644012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45521926879883</t>
   </si>
   <si>
     <t xml:space="preserve">9.47748565673828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5368595123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35873794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59623146057129</t>
+    <t xml:space="preserve">9.53685855865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35873699188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59623241424561</t>
   </si>
   <si>
     <t xml:space="preserve">9.64076137542725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90794277191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89309978485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76693058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72982215881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99700260162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95247268676758</t>
+    <t xml:space="preserve">9.9079418182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89309883117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76692962646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72982311248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99700355529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95247173309326</t>
   </si>
   <si>
     <t xml:space="preserve">10.05637550354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64818382263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95989418029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82630348205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8114595413208</t>
+    <t xml:space="preserve">9.64818286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95989322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82630443572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81146144866943</t>
   </si>
   <si>
     <t xml:space="preserve">9.75208759307861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85599136352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86341190338135</t>
+    <t xml:space="preserve">9.85599040985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86341285705566</t>
   </si>
   <si>
     <t xml:space="preserve">10.0415325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0118465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94505023956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90052127838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83179759979248</t>
+    <t xml:space="preserve">10.0118446350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9450511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90052032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8317985534668</t>
   </si>
   <si>
     <t xml:space="preserve">7.9708833694458</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25290870666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16384887695312</t>
+    <t xml:space="preserve">8.25290679931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16384792327881</t>
   </si>
   <si>
     <t xml:space="preserve">8.19353485107422</t>
@@ -989,55 +989,55 @@
     <t xml:space="preserve">8.50524520874023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02283668518066</t>
+    <t xml:space="preserve">8.02283573150635</t>
   </si>
   <si>
     <t xml:space="preserve">8.06736469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98572778701782</t>
+    <t xml:space="preserve">7.98572731018066</t>
   </si>
   <si>
     <t xml:space="preserve">7.78534173965454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76307678222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70370388031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82987213134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64433002471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72596740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04510116577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14158248901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91893196105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08962917327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11931705474854</t>
+    <t xml:space="preserve">7.76307725906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7037034034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82987260818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64432954788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72596979141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04510021209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14158344268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91893339157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08963203430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11931610107422</t>
   </si>
   <si>
     <t xml:space="preserve">8.11189651489258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09705257415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00057125091553</t>
+    <t xml:space="preserve">8.0970516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00057029724121</t>
   </si>
   <si>
     <t xml:space="preserve">8.1341609954834</t>
@@ -1064,10 +1064,10 @@
     <t xml:space="preserve">8.32712459564209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26775169372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71854782104492</t>
+    <t xml:space="preserve">8.26775074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">8.03025817871094</t>
@@ -1085,40 +1085,40 @@
     <t xml:space="preserve">8.223219871521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40134143829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05444812774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93570327758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72789669036865</t>
+    <t xml:space="preserve">8.40134239196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0544490814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93570232391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72789478302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.89117240905762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00991916656494</t>
+    <t xml:space="preserve">9.00992107391357</t>
   </si>
   <si>
     <t xml:space="preserve">9.27710056304932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30678653717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24741363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35131645202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52943706512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47006416320801</t>
+    <t xml:space="preserve">9.30678558349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24741268157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35131549835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52943801879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47006320953369</t>
   </si>
   <si>
     <t xml:space="preserve">9.39584732055664</t>
@@ -1133,16 +1133,16 @@
     <t xml:space="preserve">9.60365295410156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.063796043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87998390197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54299259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55831146240234</t>
+    <t xml:space="preserve">10.0637979507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87998294830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54299163818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55831050872803</t>
   </si>
   <si>
     <t xml:space="preserve">9.72680568695068</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">9.60426330566406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46640396118164</t>
+    <t xml:space="preserve">9.46640205383301</t>
   </si>
   <si>
     <t xml:space="preserve">9.57362842559814</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">9.6195821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63489818572998</t>
+    <t xml:space="preserve">9.6348991394043</t>
   </si>
   <si>
     <t xml:space="preserve">9.68085289001465</t>
@@ -1169,31 +1169,31 @@
     <t xml:space="preserve">9.48172092437744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43576622009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34385967254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31322574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08345794677734</t>
+    <t xml:space="preserve">9.43576717376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3438606262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31322479248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08345890045166</t>
   </si>
   <si>
     <t xml:space="preserve">8.59328842163086</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53201770782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89964389801025</t>
+    <t xml:space="preserve">8.53201675415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89964485168457</t>
   </si>
   <si>
     <t xml:space="preserve">8.96091556549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28258991241455</t>
+    <t xml:space="preserve">9.28258895874023</t>
   </si>
   <si>
     <t xml:space="preserve">9.20600032806396</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">9.49703884124756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51235675811768</t>
+    <t xml:space="preserve">9.51235771179199</t>
   </si>
   <si>
     <t xml:space="preserve">9.52767372131348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38981342315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35917854309082</t>
+    <t xml:space="preserve">9.38981437683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35917949676514</t>
   </si>
   <si>
     <t xml:space="preserve">9.19068241119385</t>
@@ -1223,67 +1223,67 @@
     <t xml:space="preserve">9.58894634246826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3285436630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42045021057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2213191986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25195407867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11409282684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1447286605835</t>
+    <t xml:space="preserve">9.32854270935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42044925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22131824493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11409378051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14472961425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.26727199554443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45108509063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69617080688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65021705627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80773830413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06814098358154</t>
+    <t xml:space="preserve">9.45108604431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69616985321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6502161026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80773735046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06814002990723</t>
   </si>
   <si>
     <t xml:space="preserve">9.37449645996094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03750419616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12941074371338</t>
+    <t xml:space="preserve">9.03750514984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1294116973877</t>
   </si>
   <si>
     <t xml:space="preserve">9.02218723297119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91496276855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94559764862061</t>
+    <t xml:space="preserve">8.91496181488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94559860229492</t>
   </si>
   <si>
     <t xml:space="preserve">9.17536449432373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00687026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95657348632812</t>
+    <t xml:space="preserve">9.00686931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95657253265381</t>
   </si>
   <si>
     <t xml:space="preserve">10.0331630706787</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">9.97189140319824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78807640075684</t>
+    <t xml:space="preserve">9.78807735443115</t>
   </si>
   <si>
     <t xml:space="preserve">9.75744152069092</t>
@@ -1304,16 +1304,16 @@
     <t xml:space="preserve">9.09877586364746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86900997161865</t>
+    <t xml:space="preserve">8.86900901794434</t>
   </si>
   <si>
     <t xml:space="preserve">8.74646663665771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7311487197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51669979095459</t>
+    <t xml:space="preserve">8.73114776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51669883728027</t>
   </si>
   <si>
     <t xml:space="preserve">8.47074699401855</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">8.4247932434082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01121139526367</t>
+    <t xml:space="preserve">8.01121234893799</t>
   </si>
   <si>
     <t xml:space="preserve">8.22566032409668</t>
@@ -1334,16 +1334,16 @@
     <t xml:space="preserve">8.65456008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77710247039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8383731842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93027973175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62392330169678</t>
+    <t xml:space="preserve">8.77710151672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83837223052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9302806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62392425537109</t>
   </si>
   <si>
     <t xml:space="preserve">8.7158317565918</t>
@@ -1352,16 +1352,16 @@
     <t xml:space="preserve">8.50138187408447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8230562210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60860633850098</t>
+    <t xml:space="preserve">8.82305717468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60860538482666</t>
   </si>
   <si>
     <t xml:space="preserve">8.57796955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34820175170898</t>
+    <t xml:space="preserve">8.34820461273193</t>
   </si>
   <si>
     <t xml:space="preserve">8.30224990844727</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">8.28693294525146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27161502838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39415645599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13375473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11843681335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45542812347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79241943359375</t>
+    <t xml:space="preserve">8.27161598205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39415740966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13375377655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11843776702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45542907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79241847991943</t>
   </si>
   <si>
     <t xml:space="preserve">8.85369110107422</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">8.70051288604736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66987705230713</t>
+    <t xml:space="preserve">8.66987800598145</t>
   </si>
   <si>
     <t xml:space="preserve">8.68519496917725</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">9.40513229370117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92593669891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80339527130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29790687561035</t>
+    <t xml:space="preserve">9.92593765258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80339431762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29790878295898</t>
   </si>
   <si>
     <t xml:space="preserve">9.22897720336914</t>
@@ -1442,25 +1442,25 @@
     <t xml:space="preserve">9.59735012054443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31742668151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79757022857666</t>
+    <t xml:space="preserve">9.31742763519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79757118225098</t>
   </si>
   <si>
     <t xml:space="preserve">8.87754821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83755970001221</t>
+    <t xml:space="preserve">8.83755874633789</t>
   </si>
   <si>
     <t xml:space="preserve">8.63761520385742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23745155334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27743816375732</t>
+    <t xml:space="preserve">9.23745059967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27743911743164</t>
   </si>
   <si>
     <t xml:space="preserve">9.47738361358643</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">9.3574161529541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51737117767334</t>
+    <t xml:space="preserve">9.51737213134766</t>
   </si>
   <si>
     <t xml:space="preserve">9.67732810974121</t>
@@ -1484,34 +1484,34 @@
     <t xml:space="preserve">9.19746017456055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07749462127686</t>
+    <t xml:space="preserve">9.07749366760254</t>
   </si>
   <si>
     <t xml:space="preserve">9.4373950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5573616027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11748218536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71759223937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95752620697021</t>
+    <t xml:space="preserve">9.55736064910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11748123168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71759414672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9575252532959</t>
   </si>
   <si>
     <t xml:space="preserve">8.99751567840576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15747261047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9175386428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7970190048218</t>
+    <t xml:space="preserve">9.15747165679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91753768920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7970199584961</t>
   </si>
   <si>
     <t xml:space="preserve">10.3571405410767</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">10.0772180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3171520233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.117205619812</t>
+    <t xml:space="preserve">10.3171510696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1172065734863</t>
   </si>
   <si>
     <t xml:space="preserve">9.91726207733154</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">9.99724006652832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0372276306152</t>
+    <t xml:space="preserve">10.0372295379639</t>
   </si>
   <si>
     <t xml:space="preserve">9.75730609893799</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">9.83728408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1571950912476</t>
+    <t xml:space="preserve">10.1571960449219</t>
   </si>
   <si>
     <t xml:space="preserve">10.2771625518799</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">10.2371730804443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3971300125122</t>
+    <t xml:space="preserve">10.3971290588379</t>
   </si>
   <si>
     <t xml:space="preserve">10.5570850372314</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">10.1971845626831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170965194702</t>
+    <t xml:space="preserve">10.5170955657959</t>
   </si>
   <si>
     <t xml:space="preserve">10.9969635009766</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">11.1169309616089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3168745040894</t>
+    <t xml:space="preserve">11.3168754577637</t>
   </si>
   <si>
     <t xml:space="preserve">11.2368974685669</t>
@@ -1586,10 +1586,10 @@
     <t xml:space="preserve">11.3568630218506</t>
   </si>
   <si>
-    <t xml:space="preserve">11.196907043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8370084762573</t>
+    <t xml:space="preserve">11.1969089508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.837007522583</t>
   </si>
   <si>
     <t xml:space="preserve">11.1569194793701</t>
@@ -1598,49 +1598,49 @@
     <t xml:space="preserve">11.0369529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8769969940186</t>
+    <t xml:space="preserve">10.8769989013672</t>
   </si>
   <si>
     <t xml:space="preserve">10.9169864654541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9569749832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7570295333862</t>
+    <t xml:space="preserve">10.956974029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7570304870605</t>
   </si>
   <si>
     <t xml:space="preserve">10.597074508667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4371185302734</t>
+    <t xml:space="preserve">10.4371194839478</t>
   </si>
   <si>
     <t xml:space="preserve">11.2768859863281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4368419647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.556809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6767768859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7170400619507</t>
+    <t xml:space="preserve">11.436842918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5568084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6767749786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.717041015625</t>
   </si>
   <si>
     <t xml:space="preserve">8.11775779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16602230072021</t>
+    <t xml:space="preserve">7.1660213470459</t>
   </si>
   <si>
     <t xml:space="preserve">7.88582229614258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46993827819824</t>
+    <t xml:space="preserve">7.46993684768677</t>
   </si>
   <si>
     <t xml:space="preserve">7.03805685043335</t>
@@ -1652,67 +1652,67 @@
     <t xml:space="preserve">6.39823389053345</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20628643035889</t>
+    <t xml:space="preserve">6.20628690719604</t>
   </si>
   <si>
     <t xml:space="preserve">5.9983434677124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55818939208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30998134613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40595531463623</t>
+    <t xml:space="preserve">6.55818891525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30998229980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40595483779907</t>
   </si>
   <si>
     <t xml:space="preserve">7.32597780227661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11803483963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73414134979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97407484054565</t>
+    <t xml:space="preserve">7.11803531646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73414039611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9740743637085</t>
   </si>
   <si>
     <t xml:space="preserve">7.29398536682129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15002489089966</t>
+    <t xml:space="preserve">7.15002536773682</t>
   </si>
   <si>
     <t xml:space="preserve">6.86210536956787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81411933898926</t>
+    <t xml:space="preserve">6.81411838531494</t>
   </si>
   <si>
     <t xml:space="preserve">6.76613235473633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94208335876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79812240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92608785629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78212785720825</t>
+    <t xml:space="preserve">6.94208383560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79812288284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92608737945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78212738037109</t>
   </si>
   <si>
     <t xml:space="preserve">6.83011436462402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92877960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01068067550659</t>
+    <t xml:space="preserve">6.92877864837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01067972183228</t>
   </si>
   <si>
     <t xml:space="preserve">6.89601945877075</t>
@@ -1721,58 +1721,58 @@
     <t xml:space="preserve">6.96153879165649</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73221778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74859762191772</t>
+    <t xml:space="preserve">6.73221826553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74859809875488</t>
   </si>
   <si>
     <t xml:space="preserve">7.05981969833374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1253399848938</t>
+    <t xml:space="preserve">7.12534046173096</t>
   </si>
   <si>
     <t xml:space="preserve">7.22362041473389</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55122184753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56760263442993</t>
+    <t xml:space="preserve">7.5512228012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56760168075562</t>
   </si>
   <si>
     <t xml:space="preserve">8.0262451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31289577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39479732513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72239875793457</t>
+    <t xml:space="preserve">8.31289672851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39479827880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72239971160889</t>
   </si>
   <si>
     <t xml:space="preserve">8.76334953308105</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88619899749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41855239868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92714977264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13190269470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96810054779053</t>
+    <t xml:space="preserve">8.88619995117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17285060882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41855430603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92715072631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13190174102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96809959411621</t>
   </si>
   <si>
     <t xml:space="preserve">9.33665180206299</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">9.09095096588135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21380233764648</t>
+    <t xml:space="preserve">9.2138032913208</t>
   </si>
   <si>
     <t xml:space="preserve">9.25475215911865</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">9.0090503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64049816131592</t>
+    <t xml:space="preserve">8.64049911499023</t>
   </si>
   <si>
     <t xml:space="preserve">8.09176540374756</t>
@@ -1802,43 +1802,43 @@
     <t xml:space="preserve">8.17366600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19004726409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10814571380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15728569030762</t>
+    <t xml:space="preserve">8.19004535675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10814476013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15728664398193</t>
   </si>
   <si>
     <t xml:space="preserve">7.9607253074646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87882423400879</t>
+    <t xml:space="preserve">7.87882328033447</t>
   </si>
   <si>
     <t xml:space="preserve">7.71502304077148</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7805438041687</t>
+    <t xml:space="preserve">7.78054428100586</t>
   </si>
   <si>
     <t xml:space="preserve">7.58398294448853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51846313476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53484201431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33828210830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48570203781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6167426109314</t>
+    <t xml:space="preserve">7.51846265792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5348424911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33828163146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48570251464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61674356460571</t>
   </si>
   <si>
     <t xml:space="preserve">7.69864320755005</t>
@@ -1847,31 +1847,31 @@
     <t xml:space="preserve">7.76416301727295</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73140382766724</t>
+    <t xml:space="preserve">7.73140335083008</t>
   </si>
   <si>
     <t xml:space="preserve">7.79692411422729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66588354110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63312244415283</t>
+    <t xml:space="preserve">7.6658821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63312292098999</t>
   </si>
   <si>
     <t xml:space="preserve">7.64950370788574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68226289749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82968425750732</t>
+    <t xml:space="preserve">7.68226385116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82968521118164</t>
   </si>
   <si>
     <t xml:space="preserve">7.74778413772583</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43656206130981</t>
+    <t xml:space="preserve">7.43656158447266</t>
   </si>
   <si>
     <t xml:space="preserve">7.60036277770996</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">7.35466146469116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40380096435547</t>
+    <t xml:space="preserve">7.40380239486694</t>
   </si>
   <si>
     <t xml:space="preserve">7.24000120162964</t>
@@ -1892,52 +1892,52 @@
     <t xml:space="preserve">6.79773855209351</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68307685852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56841707229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38823652267456</t>
+    <t xml:space="preserve">6.68307781219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5684175491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3882360458374</t>
   </si>
   <si>
     <t xml:space="preserve">6.22443532943726</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48651647567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42099618911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71583795547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84687805175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0434398651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92796421051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51764869689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27194690704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97710418701172</t>
+    <t xml:space="preserve">6.48651695251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42099666595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7158374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84687757492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04344034194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92796516418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5176477432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27194786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97710466384888</t>
   </si>
   <si>
     <t xml:space="preserve">7.84606409072876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12452507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59954929351807</t>
+    <t xml:space="preserve">8.12452602386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59954833984375</t>
   </si>
   <si>
     <t xml:space="preserve">8.43574810028076</t>
@@ -1946,37 +1946,37 @@
     <t xml:space="preserve">8.55859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68144989013672</t>
+    <t xml:space="preserve">8.6814489364624</t>
   </si>
   <si>
     <t xml:space="preserve">8.47669696807861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35384750366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23099613189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04262638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94434404373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86244440078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00986480712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05900478363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45950508117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90995597839355</t>
+    <t xml:space="preserve">8.35384654998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23099803924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04262542724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94434452056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86244535446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00986576080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.059006690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45950412750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90995693206787</t>
   </si>
   <si>
     <t xml:space="preserve">10.1556577682495</t>
@@ -2000,34 +2000,34 @@
     <t xml:space="preserve">9.70520496368408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05000114440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54140281677246</t>
+    <t xml:space="preserve">9.0500020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54140472412109</t>
   </si>
   <si>
     <t xml:space="preserve">9.22513580322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18320274353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09933853149414</t>
+    <t xml:space="preserve">9.18320178985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09933757781982</t>
   </si>
   <si>
     <t xml:space="preserve">9.14126968383789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39286518096924</t>
+    <t xml:space="preserve">9.39286422729492</t>
   </si>
   <si>
     <t xml:space="preserve">9.30900001525879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56059455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43479633331299</t>
+    <t xml:space="preserve">9.5605936050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43479824066162</t>
   </si>
   <si>
     <t xml:space="preserve">9.35093212127686</t>
@@ -2045,10 +2045,10 @@
     <t xml:space="preserve">9.77025699615479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60252666473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7283239364624</t>
+    <t xml:space="preserve">9.6025276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72832489013672</t>
   </si>
   <si>
     <t xml:space="preserve">10.3153791427612</t>
@@ -2060,22 +2060,22 @@
     <t xml:space="preserve">10.2315130233765</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1057157516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3573112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2734460830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1476497650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0218505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85412216186523</t>
+    <t xml:space="preserve">10.1057167053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.357310295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2734451293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1476488113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0218515396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85412120819092</t>
   </si>
   <si>
     <t xml:space="preserve">9.81218910217285</t>
@@ -2093,28 +2093,28 @@
     <t xml:space="preserve">9.68639278411865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05740451812744</t>
+    <t xml:space="preserve">9.05740547180176</t>
   </si>
   <si>
     <t xml:space="preserve">8.97354030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.399242401123</t>
+    <t xml:space="preserve">10.3992443084717</t>
   </si>
   <si>
     <t xml:space="preserve">10.5669727325439</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7766361236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7347040176392</t>
+    <t xml:space="preserve">10.7766351699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7347021102905</t>
   </si>
   <si>
     <t xml:space="preserve">11.279824256897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3217573165894</t>
+    <t xml:space="preserve">11.321756362915</t>
   </si>
   <si>
     <t xml:space="preserve">10.9443655014038</t>
@@ -2126,16 +2126,16 @@
     <t xml:space="preserve">11.1959600448608</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4056215286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1540279388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.783013343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.741081237793</t>
+    <t xml:space="preserve">11.4056224822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1540269851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7830142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7410802841187</t>
   </si>
   <si>
     <t xml:space="preserve">12.0346088409424</t>
@@ -2150,13 +2150,13 @@
     <t xml:space="preserve">11.1120939254761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9862966537476</t>
+    <t xml:space="preserve">10.9862976074219</t>
   </si>
   <si>
     <t xml:space="preserve">11.070161819458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4894857406616</t>
+    <t xml:space="preserve">11.4894866943359</t>
   </si>
   <si>
     <t xml:space="preserve">11.3636894226074</t>
@@ -2165,25 +2165,25 @@
     <t xml:space="preserve">11.6991491317749</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5733518600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.531418800354</t>
+    <t xml:space="preserve">11.5733528137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5314178466797</t>
   </si>
   <si>
     <t xml:space="preserve">11.0282297134399</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4831085205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5250396728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.608904838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.818567276001</t>
+    <t xml:space="preserve">10.4831075668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5250406265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6089057922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8185682296753</t>
   </si>
   <si>
     <t xml:space="preserve">10.9024324417114</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">11.1378631591797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.09485912323</t>
+    <t xml:space="preserve">11.0948600769043</t>
   </si>
   <si>
     <t xml:space="preserve">11.3958826065063</t>
@@ -2204,10 +2204,10 @@
     <t xml:space="preserve">11.6539030075073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8259162902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6108999252319</t>
+    <t xml:space="preserve">11.8259153366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6108989715576</t>
   </si>
   <si>
     <t xml:space="preserve">11.6969060897827</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">11.2238702774048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0518569946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0088539123535</t>
+    <t xml:space="preserve">11.0518560409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0088529586792</t>
   </si>
   <si>
     <t xml:space="preserve">10.8368396759033</t>
@@ -2240,13 +2240,13 @@
     <t xml:space="preserve">10.9658489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7508335113525</t>
+    <t xml:space="preserve">10.7508325576782</t>
   </si>
   <si>
     <t xml:space="preserve">10.8798427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6648254394531</t>
+    <t xml:space="preserve">10.6648263931274</t>
   </si>
   <si>
     <t xml:space="preserve">10.9228458404541</t>
@@ -2264,16 +2264,16 @@
     <t xml:space="preserve">10.1487865447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97677230834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89076614379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76175689697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84776210784912</t>
+    <t xml:space="preserve">9.97677326202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89076709747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76175594329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84776306152344</t>
   </si>
   <si>
     <t xml:space="preserve">9.46073341369629</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">9.54673957824707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2457160949707</t>
+    <t xml:space="preserve">9.24571704864502</t>
   </si>
   <si>
     <t xml:space="preserve">9.20271301269531</t>
@@ -2294,10 +2294,10 @@
     <t xml:space="preserve">9.15970993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">10.277795791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67574882507324</t>
+    <t xml:space="preserve">10.2777967453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67574977874756</t>
   </si>
   <si>
     <t xml:space="preserve">10.0197763442993</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">9.93377017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80475997924805</t>
+    <t xml:space="preserve">9.80475902557373</t>
   </si>
   <si>
     <t xml:space="preserve">9.71875286102295</t>
@@ -2318,10 +2318,10 @@
     <t xml:space="preserve">9.58974266052246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41772937774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3317232131958</t>
+    <t xml:space="preserve">9.41772842407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33172225952148</t>
   </si>
   <si>
     <t xml:space="preserve">9.37472534179688</t>
@@ -2330,22 +2330,22 @@
     <t xml:space="preserve">9.50373649597168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63274669647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6218233108521</t>
+    <t xml:space="preserve">9.63274574279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6218223571777</t>
   </si>
   <si>
     <t xml:space="preserve">11.3098764419556</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2668724060059</t>
+    <t xml:space="preserve">11.2668733596802</t>
   </si>
   <si>
     <t xml:space="preserve">11.1808662414551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7938356399536</t>
+    <t xml:space="preserve">10.7938365936279</t>
   </si>
   <si>
     <t xml:space="preserve">11.352879524231</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">11.4818897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.169942855835</t>
+    <t xml:space="preserve">12.1699419021606</t>
   </si>
   <si>
     <t xml:space="preserve">11.9549255371094</t>
@@ -2378,37 +2378,40 @@
     <t xml:space="preserve">12.4709663391113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2989530563354</t>
+    <t xml:space="preserve">12.2989540100098</t>
   </si>
   <si>
     <t xml:space="preserve">12.513970375061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5569725036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6429796218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2559490203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3849582672119</t>
+    <t xml:space="preserve">12.5569734573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6429786682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2559499740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3849592208862</t>
   </si>
   <si>
     <t xml:space="preserve">12.5999755859375</t>
   </si>
   <si>
+    <t xml:space="preserve">12.6859827041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7719898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7289867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9997701644897</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.6859817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7719898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7289867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9997701644897</t>
   </si>
   <si>
     <t xml:space="preserve">12.8204641342163</t>
@@ -51985,7 +51988,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1871" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -52011,7 +52014,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52037,7 +52040,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1873" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52089,7 +52092,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1875" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -52115,7 +52118,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1876" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -52141,7 +52144,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1877" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52167,7 +52170,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -52219,7 +52222,7 @@
         <v>15</v>
       </c>
       <c r="G1880" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52271,7 +52274,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1882" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52297,7 +52300,7 @@
         <v>14.75</v>
       </c>
       <c r="G1883" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52323,7 +52326,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52349,7 +52352,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1885" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52375,7 +52378,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52401,7 +52404,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1887" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52427,7 +52430,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1888" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52453,7 +52456,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1889" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52479,7 +52482,7 @@
         <v>15</v>
       </c>
       <c r="G1890" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52505,7 +52508,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52531,7 +52534,7 @@
         <v>14.75</v>
       </c>
       <c r="G1892" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52557,7 +52560,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1893" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52583,7 +52586,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52609,7 +52612,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1895" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52635,7 +52638,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52661,7 +52664,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1897" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52687,7 +52690,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1898" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52713,7 +52716,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1899" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52739,7 +52742,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1900" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52765,7 +52768,7 @@
         <v>14.75</v>
       </c>
       <c r="G1901" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52791,7 +52794,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1902" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52817,7 +52820,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52843,7 +52846,7 @@
         <v>14.75</v>
       </c>
       <c r="G1904" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52869,7 +52872,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1905" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52895,7 +52898,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1906" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52921,7 +52924,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52947,7 +52950,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52973,7 +52976,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1909" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52999,7 +53002,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1910" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53025,7 +53028,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1911" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53051,7 +53054,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1912" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -53077,7 +53080,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1913" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53103,7 +53106,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1914" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53129,7 +53132,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53207,7 +53210,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1918" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53259,7 +53262,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1920" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53285,7 +53288,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1921" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53311,7 +53314,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53337,7 +53340,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1923" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53363,7 +53366,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1924" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53389,7 +53392,7 @@
         <v>14.75</v>
       </c>
       <c r="G1925" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53415,7 +53418,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1926" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53441,7 +53444,7 @@
         <v>14.75</v>
       </c>
       <c r="G1927" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53467,7 +53470,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1928" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53493,7 +53496,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1929" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53519,7 +53522,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1930" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53545,7 +53548,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1931" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53571,7 +53574,7 @@
         <v>15.75</v>
       </c>
       <c r="G1932" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53597,7 +53600,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53623,7 +53626,7 @@
         <v>15.75</v>
       </c>
       <c r="G1934" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53649,7 +53652,7 @@
         <v>16.5</v>
       </c>
       <c r="G1935" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53675,7 +53678,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1936" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53701,7 +53704,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53727,7 +53730,7 @@
         <v>15.5</v>
       </c>
       <c r="G1938" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53753,7 +53756,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1939" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53779,7 +53782,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1940" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53805,7 +53808,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53831,7 +53834,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1942" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53857,7 +53860,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1943" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53883,7 +53886,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1944" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53909,7 +53912,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1945" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53935,7 +53938,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1946" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53961,7 +53964,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1947" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53987,7 +53990,7 @@
         <v>15.75</v>
       </c>
       <c r="G1948" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54013,7 +54016,7 @@
         <v>15.5</v>
       </c>
       <c r="G1949" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54039,7 +54042,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54065,7 +54068,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1951" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54091,7 +54094,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1952" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54117,7 +54120,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1953" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54143,7 +54146,7 @@
         <v>15.25</v>
       </c>
       <c r="G1954" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54169,7 +54172,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1955" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54195,7 +54198,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1956" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54221,7 +54224,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1957" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54247,7 +54250,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1958" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54273,7 +54276,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1959" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54299,7 +54302,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1960" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54325,7 +54328,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1961" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54351,7 +54354,7 @@
         <v>15.5</v>
       </c>
       <c r="G1962" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54377,7 +54380,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1963" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54403,7 +54406,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54429,7 +54432,7 @@
         <v>16</v>
       </c>
       <c r="G1965" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54455,7 +54458,7 @@
         <v>16</v>
       </c>
       <c r="G1966" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -54481,7 +54484,7 @@
         <v>15.75</v>
       </c>
       <c r="G1967" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54507,7 +54510,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1968" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54533,7 +54536,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1969" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54559,7 +54562,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1970" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54585,7 +54588,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1971" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54611,7 +54614,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1972" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54637,7 +54640,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1973" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54663,7 +54666,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1974" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54689,7 +54692,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1975" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54715,7 +54718,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1976" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54741,7 +54744,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54767,7 +54770,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1978" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54793,7 +54796,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1979" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54819,7 +54822,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1980" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54845,7 +54848,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1981" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54871,7 +54874,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54897,7 +54900,7 @@
         <v>16</v>
       </c>
       <c r="G1983" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54923,7 +54926,7 @@
         <v>16.5</v>
       </c>
       <c r="G1984" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54949,7 +54952,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1985" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54975,7 +54978,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1986" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55001,7 +55004,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1987" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55027,7 +55030,7 @@
         <v>15.75</v>
       </c>
       <c r="G1988" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55053,7 +55056,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1989" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55079,7 +55082,7 @@
         <v>15.75</v>
       </c>
       <c r="G1990" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55105,7 +55108,7 @@
         <v>15.75</v>
       </c>
       <c r="G1991" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55131,7 +55134,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1992" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55157,7 +55160,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1993" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55183,7 +55186,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1994" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55209,7 +55212,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1995" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55235,7 +55238,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1996" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55261,7 +55264,7 @@
         <v>15.75</v>
       </c>
       <c r="G1997" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55287,7 +55290,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1998" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55313,7 +55316,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1999" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55339,7 +55342,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2000" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55365,7 +55368,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2001" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55391,7 +55394,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2002" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55417,7 +55420,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55443,7 +55446,7 @@
         <v>16</v>
       </c>
       <c r="G2004" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55469,7 +55472,7 @@
         <v>16</v>
       </c>
       <c r="G2005" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55495,7 +55498,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2006" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55521,7 +55524,7 @@
         <v>16</v>
       </c>
       <c r="G2007" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55547,7 +55550,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2008" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55573,7 +55576,7 @@
         <v>16</v>
       </c>
       <c r="G2009" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55599,7 +55602,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2010" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55625,7 +55628,7 @@
         <v>16</v>
       </c>
       <c r="G2011" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55651,7 +55654,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55677,7 +55680,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2013" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55703,7 +55706,7 @@
         <v>16</v>
       </c>
       <c r="G2014" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55729,7 +55732,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55755,7 +55758,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2016" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55781,7 +55784,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55807,7 +55810,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2018" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55833,7 +55836,7 @@
         <v>15.75</v>
       </c>
       <c r="G2019" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55859,7 +55862,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2020" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55885,7 +55888,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2021" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55911,7 +55914,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2022" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55937,7 +55940,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2023" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55963,7 +55966,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2024" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55989,7 +55992,7 @@
         <v>16.75</v>
       </c>
       <c r="G2025" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56015,7 +56018,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2026" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56041,7 +56044,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2027" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56067,7 +56070,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56093,7 +56096,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2029" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56119,7 +56122,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2030" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56145,7 +56148,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2031" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56171,7 +56174,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2032" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56197,7 +56200,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2033" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56223,7 +56226,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2034" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56249,7 +56252,7 @@
         <v>19</v>
       </c>
       <c r="G2035" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56275,7 +56278,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G2036" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56301,7 +56304,7 @@
         <v>18.5</v>
       </c>
       <c r="G2037" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56327,7 +56330,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2038" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56353,7 +56356,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2039" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56379,7 +56382,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2040" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56405,7 +56408,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2041" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56431,7 +56434,7 @@
         <v>18</v>
       </c>
       <c r="G2042" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56457,7 +56460,7 @@
         <v>18.5</v>
       </c>
       <c r="G2043" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56483,7 +56486,7 @@
         <v>18.75</v>
       </c>
       <c r="G2044" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56509,7 +56512,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2045" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56535,7 +56538,7 @@
         <v>18.5</v>
       </c>
       <c r="G2046" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56561,7 +56564,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2047" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56587,7 +56590,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G2048" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56613,7 +56616,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2049" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56639,7 +56642,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2050" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56665,7 +56668,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2051" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56691,7 +56694,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2052" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56717,7 +56720,7 @@
         <v>17.75</v>
       </c>
       <c r="G2053" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56743,7 +56746,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2054" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56769,7 +56772,7 @@
         <v>17.25</v>
       </c>
       <c r="G2055" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56795,7 +56798,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2056" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56821,7 +56824,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2057" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56847,7 +56850,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2058" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56873,7 +56876,7 @@
         <v>16.25</v>
       </c>
       <c r="G2059" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56899,7 +56902,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2060" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56925,7 +56928,7 @@
         <v>16.5</v>
       </c>
       <c r="G2061" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56951,7 +56954,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2062" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56977,7 +56980,7 @@
         <v>16.5</v>
       </c>
       <c r="G2063" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -57003,7 +57006,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2064" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57029,7 +57032,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2065" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57055,7 +57058,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2066" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57081,7 +57084,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2067" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57107,7 +57110,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2068" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57133,7 +57136,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2069" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57159,7 +57162,7 @@
         <v>16.75</v>
       </c>
       <c r="G2070" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57185,7 +57188,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2071" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57211,7 +57214,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2072" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57237,7 +57240,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2073" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57263,7 +57266,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2074" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57289,7 +57292,7 @@
         <v>17</v>
       </c>
       <c r="G2075" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57315,7 +57318,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2076" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57341,7 +57344,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2077" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -57367,7 +57370,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2078" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -57393,7 +57396,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57419,7 +57422,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2080" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57445,7 +57448,7 @@
         <v>17.75</v>
       </c>
       <c r="G2081" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57471,7 +57474,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G2082" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57497,7 +57500,7 @@
         <v>17.5</v>
       </c>
       <c r="G2083" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57523,7 +57526,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2084" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57549,7 +57552,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2085" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57575,7 +57578,7 @@
         <v>17.5</v>
       </c>
       <c r="G2086" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57601,7 +57604,7 @@
         <v>17</v>
       </c>
       <c r="G2087" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57627,7 +57630,7 @@
         <v>17</v>
       </c>
       <c r="G2088" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57653,7 +57656,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2089" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57679,7 +57682,7 @@
         <v>17.75</v>
       </c>
       <c r="G2090" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57705,7 +57708,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2091" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57731,7 +57734,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2092" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57757,7 +57760,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2093" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57783,7 +57786,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2094" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57809,7 +57812,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2095" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57835,7 +57838,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2096" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -57861,7 +57864,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2097" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57887,7 +57890,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57913,7 +57916,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2099" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57939,7 +57942,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2100" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57965,7 +57968,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2101" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57991,7 +57994,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2102" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58017,7 +58020,7 @@
         <v>17</v>
       </c>
       <c r="G2103" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58043,7 +58046,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2104" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58069,7 +58072,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2105" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58095,7 +58098,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2106" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58121,7 +58124,7 @@
         <v>17.5</v>
       </c>
       <c r="G2107" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -58147,7 +58150,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2108" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58173,7 +58176,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2109" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -58199,7 +58202,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2110" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58225,7 +58228,7 @@
         <v>17</v>
       </c>
       <c r="G2111" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58251,7 +58254,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2112" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58277,7 +58280,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2113" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58303,7 +58306,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2114" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58329,7 +58332,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2115" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58355,7 +58358,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2116" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58381,7 +58384,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G2117" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -58407,7 +58410,7 @@
         <v>17</v>
       </c>
       <c r="G2118" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58433,7 +58436,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2119" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58459,7 +58462,7 @@
         <v>17</v>
       </c>
       <c r="G2120" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58485,7 +58488,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2121" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58511,7 +58514,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2122" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58537,7 +58540,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2123" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58563,7 +58566,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2124" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58589,7 +58592,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2125" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58615,7 +58618,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2126" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58641,7 +58644,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2127" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58667,7 +58670,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2128" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58693,7 +58696,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2129" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58719,7 +58722,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2130" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58745,7 +58748,7 @@
         <v>16.5</v>
       </c>
       <c r="G2131" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58771,7 +58774,7 @@
         <v>16.5</v>
       </c>
       <c r="G2132" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58797,7 +58800,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2133" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58823,7 +58826,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2134" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58849,7 +58852,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2135" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58875,7 +58878,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2136" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58901,7 +58904,7 @@
         <v>17</v>
       </c>
       <c r="G2137" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58927,7 +58930,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2138" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58953,7 +58956,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2139" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58979,7 +58982,7 @@
         <v>16.5</v>
       </c>
       <c r="G2140" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59005,7 +59008,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2141" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59031,7 +59034,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2142" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59057,7 +59060,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2143" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59083,7 +59086,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2144" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59109,7 +59112,7 @@
         <v>16.75</v>
       </c>
       <c r="G2145" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59135,7 +59138,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2146" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59161,7 +59164,7 @@
         <v>16.75</v>
       </c>
       <c r="G2147" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59187,7 +59190,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2148" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59213,7 +59216,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2149" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59239,7 +59242,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2150" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59265,7 +59268,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2151" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59291,7 +59294,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2152" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59317,7 +59320,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2153" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59343,7 +59346,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2154" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59369,7 +59372,7 @@
         <v>16.25</v>
       </c>
       <c r="G2155" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59395,7 +59398,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2156" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59421,7 +59424,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2157" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59447,7 +59450,7 @@
         <v>15</v>
       </c>
       <c r="G2158" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59473,7 +59476,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2159" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59499,7 +59502,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2160" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59525,7 +59528,7 @@
         <v>15.25</v>
       </c>
       <c r="G2161" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59551,7 +59554,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2162" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59577,7 +59580,7 @@
         <v>15.25</v>
       </c>
       <c r="G2163" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59603,7 +59606,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2164" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59629,7 +59632,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2165" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59655,7 +59658,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2166" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59681,7 +59684,7 @@
         <v>16.25</v>
       </c>
       <c r="G2167" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59707,7 +59710,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2168" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59733,7 +59736,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2169" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59759,7 +59762,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2170" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59785,7 +59788,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2171" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59811,7 +59814,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59837,7 +59840,7 @@
         <v>16</v>
       </c>
       <c r="G2173" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59863,7 +59866,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2174" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -59889,7 +59892,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2175" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59915,7 +59918,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2176" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59941,7 +59944,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2177" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59967,7 +59970,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2178" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59993,7 +59996,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2179" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60019,7 +60022,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60045,7 +60048,7 @@
         <v>15.25</v>
       </c>
       <c r="G2181" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60071,7 +60074,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2182" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60097,7 +60100,7 @@
         <v>15.25</v>
       </c>
       <c r="G2183" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60123,7 +60126,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2184" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60149,7 +60152,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2185" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60175,7 +60178,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2186" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60201,7 +60204,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2187" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60227,7 +60230,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2188" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60253,7 +60256,7 @@
         <v>15</v>
       </c>
       <c r="G2189" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60279,7 +60282,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2190" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60305,7 +60308,7 @@
         <v>15</v>
       </c>
       <c r="G2191" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60331,7 +60334,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2192" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60357,7 +60360,7 @@
         <v>15</v>
       </c>
       <c r="G2193" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60383,7 +60386,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2194" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60409,7 +60412,7 @@
         <v>15</v>
       </c>
       <c r="G2195" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60435,7 +60438,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2196" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60461,7 +60464,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2197" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60487,7 +60490,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60513,7 +60516,7 @@
         <v>15</v>
       </c>
       <c r="G2199" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60539,7 +60542,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G2200" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60565,7 +60568,7 @@
         <v>15</v>
       </c>
       <c r="G2201" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60591,7 +60594,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2202" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60617,7 +60620,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2203" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60643,7 +60646,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2204" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60669,7 +60672,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60695,7 +60698,7 @@
         <v>14.5</v>
       </c>
       <c r="G2206" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60721,7 +60724,7 @@
         <v>14.5</v>
       </c>
       <c r="G2207" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60747,7 +60750,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60773,7 +60776,7 @@
         <v>14.5</v>
       </c>
       <c r="G2209" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60799,7 +60802,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60825,7 +60828,7 @@
         <v>14.5</v>
       </c>
       <c r="G2211" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60851,7 +60854,7 @@
         <v>14.5</v>
       </c>
       <c r="G2212" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60877,7 +60880,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60903,7 +60906,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2214" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60929,7 +60932,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2215" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60955,7 +60958,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2216" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60981,7 +60984,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2217" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61007,7 +61010,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2218" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61033,7 +61036,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2219" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61059,7 +61062,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2220" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61085,7 +61088,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2221" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61111,7 +61114,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2222" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61137,7 +61140,7 @@
         <v>15</v>
       </c>
       <c r="G2223" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61163,7 +61166,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61189,7 +61192,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2225" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61215,7 +61218,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2226" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61241,7 +61244,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2227" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61267,7 +61270,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61293,7 +61296,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2229" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61319,7 +61322,7 @@
         <v>15.25</v>
       </c>
       <c r="G2230" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61345,7 +61348,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2231" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61371,7 +61374,7 @@
         <v>15.5</v>
       </c>
       <c r="G2232" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61397,7 +61400,7 @@
         <v>15.5</v>
       </c>
       <c r="G2233" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61423,7 +61426,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2234" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61449,7 +61452,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2235" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61475,7 +61478,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2236" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61501,7 +61504,7 @@
         <v>16</v>
       </c>
       <c r="G2237" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61527,7 +61530,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2238" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61553,7 +61556,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2239" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61579,7 +61582,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2240" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61605,7 +61608,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2241" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61631,7 +61634,7 @@
         <v>16.5</v>
       </c>
       <c r="G2242" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61657,7 +61660,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2243" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61683,7 +61686,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2244" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61709,7 +61712,7 @@
         <v>17.25</v>
       </c>
       <c r="G2245" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61735,7 +61738,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2246" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61761,7 +61764,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2247" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61787,7 +61790,7 @@
         <v>17</v>
       </c>
       <c r="G2248" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61813,7 +61816,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2249" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61839,7 +61842,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G2250" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61865,7 +61868,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G2251" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61891,7 +61894,7 @@
         <v>17.25</v>
       </c>
       <c r="G2252" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61917,7 +61920,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2253" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61943,7 +61946,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G2254" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61969,7 +61972,7 @@
         <v>17.75</v>
       </c>
       <c r="G2255" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61995,7 +61998,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G2256" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62021,7 +62024,7 @@
         <v>18</v>
       </c>
       <c r="G2257" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62047,7 +62050,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2258" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62073,7 +62076,7 @@
         <v>17</v>
       </c>
       <c r="G2259" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62099,7 +62102,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G2260" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62125,7 +62128,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2261" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62151,7 +62154,7 @@
         <v>16.5</v>
       </c>
       <c r="G2262" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62177,7 +62180,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2263" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62203,7 +62206,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2264" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62229,7 +62232,7 @@
         <v>16.5</v>
       </c>
       <c r="G2265" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62255,7 +62258,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2266" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62281,7 +62284,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2267" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62307,7 +62310,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2268" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62333,7 +62336,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2269" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62359,7 +62362,7 @@
         <v>15.5</v>
       </c>
       <c r="G2270" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62385,7 +62388,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2271" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62411,7 +62414,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2272" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62437,7 +62440,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G2273" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62463,7 +62466,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2274" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62489,7 +62492,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2275" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62515,7 +62518,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2276" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62541,7 +62544,7 @@
         <v>17</v>
       </c>
       <c r="G2277" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62567,7 +62570,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2278" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62593,7 +62596,7 @@
         <v>16.5</v>
       </c>
       <c r="G2279" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62619,7 +62622,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2280" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62645,7 +62648,7 @@
         <v>16</v>
       </c>
       <c r="G2281" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62671,7 +62674,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2282" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62697,7 +62700,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2283" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62723,7 +62726,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2284" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62749,7 +62752,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2285" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62775,7 +62778,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62801,7 +62804,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2287" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62827,7 +62830,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2288" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62853,7 +62856,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2289" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62879,7 +62882,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2290" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62905,7 +62908,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2291" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62931,7 +62934,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2292" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62957,7 +62960,7 @@
         <v>16.5</v>
       </c>
       <c r="G2293" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62983,7 +62986,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2294" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63009,7 +63012,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2295" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63035,7 +63038,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2296" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63061,7 +63064,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2297" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63087,7 +63090,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2298" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63113,7 +63116,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63139,7 +63142,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63165,7 +63168,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2301" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63191,7 +63194,7 @@
         <v>16</v>
       </c>
       <c r="G2302" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63217,7 +63220,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2303" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63243,7 +63246,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2304" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63269,7 +63272,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63295,7 +63298,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2306" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63321,7 +63324,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2307" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63347,7 +63350,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2308" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63373,7 +63376,7 @@
         <v>15.75</v>
       </c>
       <c r="G2309" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63399,7 +63402,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2310" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63425,7 +63428,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2311" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63451,7 +63454,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2312" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63477,7 +63480,7 @@
         <v>16</v>
       </c>
       <c r="G2313" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63503,7 +63506,7 @@
         <v>16</v>
       </c>
       <c r="G2314" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63529,7 +63532,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2315" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63555,7 +63558,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G2316" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63581,7 +63584,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2317" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63607,7 +63610,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63633,7 +63636,7 @@
         <v>16</v>
       </c>
       <c r="G2319" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63659,7 +63662,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2320" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63685,7 +63688,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2321" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63711,7 +63714,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2322" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63737,7 +63740,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2323" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63763,7 +63766,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2324" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63789,7 +63792,7 @@
         <v>16</v>
       </c>
       <c r="G2325" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63815,7 +63818,7 @@
         <v>16</v>
       </c>
       <c r="G2326" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63841,7 +63844,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2327" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63867,7 +63870,7 @@
         <v>16</v>
       </c>
       <c r="G2328" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63893,7 +63896,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2329" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63919,7 +63922,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2330" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63945,7 +63948,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2331" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63971,7 +63974,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2332" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63997,7 +64000,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2333" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64023,7 +64026,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2334" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64049,7 +64052,7 @@
         <v>15.75</v>
       </c>
       <c r="G2335" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64075,7 +64078,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2336" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64101,7 +64104,7 @@
         <v>15.75</v>
       </c>
       <c r="G2337" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64127,7 +64130,7 @@
         <v>15.25</v>
       </c>
       <c r="G2338" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64153,7 +64156,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2339" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64179,7 +64182,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2340" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64205,7 +64208,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2341" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64231,7 +64234,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64257,7 +64260,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64283,7 +64286,7 @@
         <v>15.5</v>
       </c>
       <c r="G2344" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64309,7 +64312,7 @@
         <v>15.5</v>
       </c>
       <c r="G2345" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64335,7 +64338,7 @@
         <v>15</v>
       </c>
       <c r="G2346" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64361,7 +64364,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64387,7 +64390,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64413,7 +64416,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2349" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64439,7 +64442,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2350" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64465,7 +64468,7 @@
         <v>16</v>
       </c>
       <c r="G2351" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64491,7 +64494,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2352" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64517,7 +64520,7 @@
         <v>15.75</v>
       </c>
       <c r="G2353" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64543,7 +64546,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2354" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64569,7 +64572,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2355" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64595,7 +64598,7 @@
         <v>15.25</v>
       </c>
       <c r="G2356" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64621,7 +64624,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2357" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64647,7 +64650,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64673,7 +64676,7 @@
         <v>14</v>
       </c>
       <c r="G2359" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64699,7 +64702,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2360" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64725,7 +64728,7 @@
         <v>15</v>
       </c>
       <c r="G2361" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64751,7 +64754,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2362" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64777,7 +64780,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2363" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64803,7 +64806,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2364" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64829,7 +64832,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G2365" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64855,7 +64858,7 @@
         <v>14.5</v>
       </c>
       <c r="G2366" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64881,7 +64884,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G2367" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64907,7 +64910,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2368" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64933,7 +64936,7 @@
         <v>15</v>
       </c>
       <c r="G2369" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64959,7 +64962,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2370" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64985,7 +64988,7 @@
         <v>15.25</v>
       </c>
       <c r="G2371" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65011,7 +65014,7 @@
         <v>15.25</v>
       </c>
       <c r="G2372" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65037,7 +65040,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2373" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65063,7 +65066,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2374" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65089,7 +65092,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2375" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65115,7 +65118,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2376" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65141,7 +65144,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2377" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65167,7 +65170,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2378" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65193,7 +65196,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2379" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65219,7 +65222,7 @@
         <v>15.25</v>
       </c>
       <c r="G2380" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65245,7 +65248,7 @@
         <v>15.25</v>
       </c>
       <c r="G2381" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65271,7 +65274,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2382" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65297,7 +65300,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G2383" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65323,7 +65326,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2384" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65349,7 +65352,7 @@
         <v>16</v>
       </c>
       <c r="G2385" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65375,7 +65378,7 @@
         <v>16.25</v>
       </c>
       <c r="G2386" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65401,7 +65404,7 @@
         <v>16</v>
       </c>
       <c r="G2387" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65427,7 +65430,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2388" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65453,7 +65456,7 @@
         <v>16.5</v>
       </c>
       <c r="G2389" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65479,7 +65482,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2390" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65505,7 +65508,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2391" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65531,7 +65534,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2392" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65557,7 +65560,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2393" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65583,7 +65586,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2394" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65609,7 +65612,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G2395" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65635,7 +65638,7 @@
         <v>16.75</v>
       </c>
       <c r="G2396" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65661,7 +65664,7 @@
         <v>16.5</v>
       </c>
       <c r="G2397" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65687,7 +65690,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2398" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65713,7 +65716,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2399" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65739,7 +65742,7 @@
         <v>16.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65765,7 +65768,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65791,7 +65794,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2402" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65817,7 +65820,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65843,7 +65846,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2404" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65869,7 +65872,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2405" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65895,7 +65898,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2406" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65921,7 +65924,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2407" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65947,7 +65950,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2408" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65973,7 +65976,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G2409" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65999,7 +66002,7 @@
         <v>16</v>
       </c>
       <c r="G2410" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66025,7 +66028,7 @@
         <v>15.75</v>
       </c>
       <c r="G2411" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66051,7 +66054,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G2412" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66077,7 +66080,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G2413" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66103,7 +66106,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2414" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66129,7 +66132,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2415" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66155,7 +66158,7 @@
         <v>16.25</v>
       </c>
       <c r="G2416" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66181,7 +66184,7 @@
         <v>16.75</v>
       </c>
       <c r="G2417" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66207,7 +66210,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2418" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66233,7 +66236,7 @@
         <v>16.25</v>
       </c>
       <c r="G2419" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66259,7 +66262,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2420" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66285,7 +66288,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2421" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66311,7 +66314,7 @@
         <v>16.25</v>
       </c>
       <c r="G2422" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66337,7 +66340,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2423" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66363,7 +66366,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2424" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66389,7 +66392,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2425" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66415,7 +66418,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2426" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66441,7 +66444,7 @@
         <v>16.25</v>
       </c>
       <c r="G2427" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66467,7 +66470,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2428" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66493,7 +66496,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66519,7 +66522,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2430" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66545,7 +66548,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2431" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66571,7 +66574,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66597,7 +66600,7 @@
         <v>16.5</v>
       </c>
       <c r="G2433" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66623,7 +66626,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2434" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66649,7 +66652,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2435" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66675,7 +66678,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2436" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66701,7 +66704,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2437" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66727,7 +66730,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2438" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66753,7 +66756,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2439" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66779,7 +66782,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2440" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66805,7 +66808,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66831,7 +66834,7 @@
         <v>16.75</v>
       </c>
       <c r="G2442" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66857,7 +66860,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66883,7 +66886,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2444" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66909,7 +66912,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2445" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66935,7 +66938,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2446" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66961,7 +66964,7 @@
         <v>18</v>
       </c>
       <c r="G2447" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66987,7 +66990,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2448" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67013,7 +67016,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67039,7 +67042,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2450" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67065,7 +67068,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G2451" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67091,7 +67094,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2452" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67117,7 +67120,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2453" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67143,7 +67146,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2454" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67169,7 +67172,7 @@
         <v>21</v>
       </c>
       <c r="G2455" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67195,7 +67198,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G2456" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67221,7 +67224,7 @@
         <v>19.25</v>
       </c>
       <c r="G2457" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67247,7 +67250,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G2458" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67273,7 +67276,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G2459" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67299,7 +67302,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67325,7 +67328,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G2461" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67351,7 +67354,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2462" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67377,7 +67380,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67403,7 +67406,7 @@
         <v>18.5</v>
       </c>
       <c r="G2464" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67429,7 +67432,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G2465" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67455,7 +67458,7 @@
         <v>19</v>
       </c>
       <c r="G2466" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67481,7 +67484,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2467" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67507,7 +67510,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G2468" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67533,7 +67536,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2469" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67559,7 +67562,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2470" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67585,7 +67588,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2471" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67611,7 +67614,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2472" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67637,7 +67640,7 @@
         <v>16</v>
       </c>
       <c r="G2473" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67663,7 +67666,7 @@
         <v>16</v>
       </c>
       <c r="G2474" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67689,7 +67692,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2475" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67715,7 +67718,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67741,7 +67744,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67767,7 +67770,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67793,7 +67796,7 @@
         <v>16.25</v>
       </c>
       <c r="G2479" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67819,7 +67822,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67845,7 +67848,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2481" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67871,7 +67874,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67897,7 +67900,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67923,7 +67926,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G2484" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67949,7 +67952,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G2485" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67975,7 +67978,7 @@
         <v>16</v>
       </c>
       <c r="G2486" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68001,7 +68004,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2487" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68027,7 +68030,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2488" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68053,7 +68056,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68079,7 +68082,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G2490" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68105,7 +68108,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2491" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68131,7 +68134,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2492" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68157,7 +68160,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2493" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68183,7 +68186,7 @@
         <v>15.25</v>
       </c>
       <c r="G2494" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68209,7 +68212,7 @@
         <v>15.5</v>
       </c>
       <c r="G2495" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68235,7 +68238,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2496" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68261,7 +68264,7 @@
         <v>15.5</v>
       </c>
       <c r="G2497" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68287,7 +68290,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2498" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68313,7 +68316,7 @@
         <v>15.25</v>
       </c>
       <c r="G2499" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -68339,7 +68342,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2500" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -68365,7 +68368,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2501" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -68391,7 +68394,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2502" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68417,7 +68420,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2503" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68443,7 +68446,7 @@
         <v>15.25</v>
       </c>
       <c r="G2504" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -68469,7 +68472,7 @@
         <v>15.25</v>
       </c>
       <c r="G2505" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -68495,7 +68498,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2506" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68521,7 +68524,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2507" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68547,7 +68550,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2508" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68573,7 +68576,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2509" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68599,7 +68602,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G2510" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68625,7 +68628,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2511" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68651,7 +68654,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2512" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68677,7 +68680,7 @@
         <v>15</v>
       </c>
       <c r="G2513" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68703,7 +68706,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2514" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68729,7 +68732,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2515" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68755,7 +68758,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2516" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68781,7 +68784,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2517" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68807,7 +68810,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G2518" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -68833,7 +68836,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2519" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -68859,7 +68862,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G2520" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -68885,7 +68888,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2521" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -68911,7 +68914,7 @@
         <v>14.75</v>
       </c>
       <c r="G2522" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -68937,7 +68940,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2523" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -68963,7 +68966,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G2524" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -68989,7 +68992,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2525" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -69015,7 +69018,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2526" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -69041,7 +69044,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2527" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -69067,7 +69070,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2528" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -69075,13 +69078,13 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6911805556</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>1847</v>
       </c>
       <c r="C2529" t="n">
-        <v>15.3000001907349</v>
+        <v>15.3500003814697</v>
       </c>
       <c r="D2529" t="n">
         <v>15.1499996185303</v>
@@ -69093,9 +69096,35 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G2529" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.6818518519</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>1403</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>15.1000003814697</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>15.1499996185303</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>944</v>
+      </c>
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BEC.MI.xlsx
+++ b/data/BEC.MI.xlsx
@@ -44,22 +44,22 @@
     <t xml:space="preserve">BEC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96180963516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87040758132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87693643569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92916679382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77247714996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79859209060669</t>
+    <t xml:space="preserve">4.96181011199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8704080581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8769359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92916631698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77247762680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79859256744385</t>
   </si>
   <si>
     <t xml:space="preserve">4.83449983596802</t>
@@ -71,10 +71,10 @@
     <t xml:space="preserve">4.79532814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80512046813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76594829559326</t>
+    <t xml:space="preserve">4.80512142181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76594877243042</t>
   </si>
   <si>
     <t xml:space="preserve">4.7594199180603</t>
@@ -89,25 +89,25 @@
     <t xml:space="preserve">4.69413232803345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63537502288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44277811050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37422704696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18489503860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07390642166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08043622970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23385953903198</t>
+    <t xml:space="preserve">4.63537454605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44277763366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37422657012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18489408493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07390689849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08043575286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2338604927063</t>
   </si>
   <si>
     <t xml:space="preserve">4.40360641479492</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">4.49174356460571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53091621398926</t>
+    <t xml:space="preserve">4.53091526031494</t>
   </si>
   <si>
     <t xml:space="preserve">4.43298482894897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50480079650879</t>
+    <t xml:space="preserve">4.50480127334595</t>
   </si>
   <si>
     <t xml:space="preserve">4.53744411468506</t>
@@ -131,37 +131,37 @@
     <t xml:space="preserve">4.42645692825317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42319202423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43951368331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41666316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44930744171143</t>
+    <t xml:space="preserve">4.42319250106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43951416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.416663646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44930696487427</t>
   </si>
   <si>
     <t xml:space="preserve">4.4656286239624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47868585586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60926008224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89652252197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90958070755005</t>
+    <t xml:space="preserve">4.47868633270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60926055908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8965220451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90958023071289</t>
   </si>
   <si>
     <t xml:space="preserve">4.93569469451904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91284418106079</t>
+    <t xml:space="preserve">4.91284465789795</t>
   </si>
   <si>
     <t xml:space="preserve">5.01403951644897</t>
@@ -173,16 +173,16 @@
     <t xml:space="preserve">5.03362512588501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04015398025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09238386154175</t>
+    <t xml:space="preserve">5.04015350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09238433837891</t>
   </si>
   <si>
     <t xml:space="preserve">4.94875192642212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99445295333862</t>
+    <t xml:space="preserve">4.99445343017578</t>
   </si>
   <si>
     <t xml:space="preserve">4.84429264068604</t>
@@ -191,67 +191,67 @@
     <t xml:space="preserve">5.0695333480835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09891223907471</t>
+    <t xml:space="preserve">5.09891176223755</t>
   </si>
   <si>
     <t xml:space="preserve">4.98792409896851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04994773864746</t>
+    <t xml:space="preserve">5.04994678497314</t>
   </si>
   <si>
     <t xml:space="preserve">5.04341793060303</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05974006652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98466014862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02709722518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99973773956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.033935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96212148666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91766262054443</t>
+    <t xml:space="preserve">5.05974054336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98466062545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02709674835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9997386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03393602371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96212100982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91766309738159</t>
   </si>
   <si>
     <t xml:space="preserve">4.9450216293335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85610723495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89030504226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89714431762695</t>
+    <t xml:space="preserve">4.85610675811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89030456542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89714527130127</t>
   </si>
   <si>
     <t xml:space="preserve">4.79455089569092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82190895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98263931274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9245023727417</t>
+    <t xml:space="preserve">4.82190799713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9826397895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92450284957886</t>
   </si>
   <si>
     <t xml:space="preserve">5.00657796859741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88346481323242</t>
+    <t xml:space="preserve">4.88346529006958</t>
   </si>
   <si>
     <t xml:space="preserve">4.94844198226929</t>
@@ -269,19 +269,19 @@
     <t xml:space="preserve">4.85268688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93134260177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78771114349365</t>
+    <t xml:space="preserve">4.93134212493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78771162033081</t>
   </si>
   <si>
     <t xml:space="preserve">4.78429079055786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82532835006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77403259277344</t>
+    <t xml:space="preserve">4.8253288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77403163909912</t>
   </si>
   <si>
     <t xml:space="preserve">4.7227349281311</t>
@@ -290,127 +290,127 @@
     <t xml:space="preserve">4.67485809326172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75693273544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56200456619263</t>
+    <t xml:space="preserve">4.75693321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56200504302979</t>
   </si>
   <si>
     <t xml:space="preserve">4.54148578643799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53122711181641</t>
+    <t xml:space="preserve">4.53122663497925</t>
   </si>
   <si>
     <t xml:space="preserve">4.6030421257019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63040113449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55516481399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58252334594727</t>
+    <t xml:space="preserve">4.63040065765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55516529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58252286911011</t>
   </si>
   <si>
     <t xml:space="preserve">4.54832553863525</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45941066741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53464698791504</t>
+    <t xml:space="preserve">4.45941114425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53464651107788</t>
   </si>
   <si>
     <t xml:space="preserve">4.52780675888062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52096700668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64407968521118</t>
+    <t xml:space="preserve">4.52096748352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64408016204834</t>
   </si>
   <si>
     <t xml:space="preserve">4.74325370788574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73983383178711</t>
+    <t xml:space="preserve">4.73983335494995</t>
   </si>
   <si>
     <t xml:space="preserve">4.8355884552002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92108345031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92792272567749</t>
+    <t xml:space="preserve">4.92108297348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92792320251465</t>
   </si>
   <si>
     <t xml:space="preserve">4.98605918884277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96554088592529</t>
+    <t xml:space="preserve">4.96554040908813</t>
   </si>
   <si>
     <t xml:space="preserve">4.91424369812012</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97237920761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96895980834961</t>
+    <t xml:space="preserve">4.97237968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96896028518677</t>
   </si>
   <si>
     <t xml:space="preserve">4.86978626251221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93818187713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88004541397095</t>
+    <t xml:space="preserve">4.93818235397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88004493713379</t>
   </si>
   <si>
     <t xml:space="preserve">4.95186138153076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87320566177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8629469871521</t>
+    <t xml:space="preserve">4.87320613861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86294651031494</t>
   </si>
   <si>
     <t xml:space="preserve">4.76719236373901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80139017105103</t>
+    <t xml:space="preserve">4.80138969421387</t>
   </si>
   <si>
     <t xml:space="preserve">4.80822992324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7637734413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8424277305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72957468032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84926748275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81164884567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88688516616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02025699615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08865356445312</t>
+    <t xml:space="preserve">4.76377296447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84242820739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72957420349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84926652908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81164932250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88688468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02025651931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08865261077881</t>
   </si>
   <si>
     <t xml:space="preserve">5.10575151443481</t>
@@ -419,16 +419,16 @@
     <t xml:space="preserve">5.0647144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04761505126953</t>
+    <t xml:space="preserve">5.04761552810669</t>
   </si>
   <si>
     <t xml:space="preserve">5.09549236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17756748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23228406906128</t>
+    <t xml:space="preserve">5.17756795883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23228454589844</t>
   </si>
   <si>
     <t xml:space="preserve">5.12969017028809</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">5.16388893127441</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2117657661438</t>
+    <t xml:space="preserve">5.21176528930664</t>
   </si>
   <si>
     <t xml:space="preserve">5.30752038955688</t>
@@ -452,13 +452,13 @@
     <t xml:space="preserve">5.13311004638672</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22544384002686</t>
+    <t xml:space="preserve">5.22544431686401</t>
   </si>
   <si>
     <t xml:space="preserve">5.16730785369873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19808578491211</t>
+    <t xml:space="preserve">5.19808673858643</t>
   </si>
   <si>
     <t xml:space="preserve">5.29726028442383</t>
@@ -467,19 +467,19 @@
     <t xml:space="preserve">5.47166967391968</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40327453613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36565542221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36223649978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46482992172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36907577514648</t>
+    <t xml:space="preserve">5.40327405929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36565589904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36223697662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46483039855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36907529830933</t>
   </si>
   <si>
     <t xml:space="preserve">5.39643430709839</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">5.41353368759155</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46140956878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43747186660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45457029342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46824979782104</t>
+    <t xml:space="preserve">5.46141052246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43747138977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45457077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4682502746582</t>
   </si>
   <si>
     <t xml:space="preserve">5.47509002685547</t>
@@ -518,10 +518,10 @@
     <t xml:space="preserve">5.45799016952515</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50586843490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52980661392212</t>
+    <t xml:space="preserve">5.50586891174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52980709075928</t>
   </si>
   <si>
     <t xml:space="preserve">5.60846185684204</t>
@@ -530,22 +530,22 @@
     <t xml:space="preserve">5.68369674682617</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73157453536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88204526901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9367618560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94360113143921</t>
+    <t xml:space="preserve">5.73157405853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88204574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93676233291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94360208511353</t>
   </si>
   <si>
     <t xml:space="preserve">6.05645418167114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94018220901489</t>
+    <t xml:space="preserve">5.94018268585205</t>
   </si>
   <si>
     <t xml:space="preserve">6.04961490631104</t>
@@ -563,40 +563,40 @@
     <t xml:space="preserve">6.04277515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17272710800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39501476287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3744945526123</t>
+    <t xml:space="preserve">6.17272758483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39501428604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37449550628662</t>
   </si>
   <si>
     <t xml:space="preserve">6.46682929992676</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32661771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11117172241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89914321899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00515651702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2240252494812</t>
+    <t xml:space="preserve">6.32661867141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11117076873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8991436958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00515699386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22402572631836</t>
   </si>
   <si>
     <t xml:space="preserve">6.26506233215332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39843320846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40527248382568</t>
+    <t xml:space="preserve">6.39843416213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4052734375</t>
   </si>
   <si>
     <t xml:space="preserve">6.48050928115845</t>
@@ -605,40 +605,40 @@
     <t xml:space="preserve">6.41211318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44973182678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43605136871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52838611602783</t>
+    <t xml:space="preserve">6.44973134994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43605184555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52838754653931</t>
   </si>
   <si>
     <t xml:space="preserve">6.66859722137451</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99689817428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94218015670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12001132965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4688286781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66717767715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20066547393799</t>
+    <t xml:space="preserve">6.99689769744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94218063354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12001037597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46882915496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66717672348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20066452026367</t>
   </si>
   <si>
     <t xml:space="preserve">8.40585327148438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64523887634277</t>
+    <t xml:space="preserve">8.64523983001709</t>
   </si>
   <si>
     <t xml:space="preserve">8.27590084075928</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">8.35113620758057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28957939147949</t>
+    <t xml:space="preserve">8.28957843780518</t>
   </si>
   <si>
     <t xml:space="preserve">8.24170207977295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33745574951172</t>
+    <t xml:space="preserve">8.33745765686035</t>
   </si>
   <si>
     <t xml:space="preserve">8.33061790466309</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">8.31693744659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2690601348877</t>
+    <t xml:space="preserve">8.26906108856201</t>
   </si>
   <si>
     <t xml:space="preserve">8.22118377685547</t>
@@ -671,25 +671,25 @@
     <t xml:space="preserve">8.11859035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30325889587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48108768463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72047328948975</t>
+    <t xml:space="preserve">8.30325984954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48108863830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72047424316406</t>
   </si>
   <si>
     <t xml:space="preserve">8.7136344909668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79469013214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49782371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52751064300537</t>
+    <t xml:space="preserve">8.79469203948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49782276153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52750968933105</t>
   </si>
   <si>
     <t xml:space="preserve">8.07478809356689</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">8.31228065490723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43102836608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37165546417236</t>
+    <t xml:space="preserve">8.43102741241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37165451049805</t>
   </si>
   <si>
     <t xml:space="preserve">7.97830581665039</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88924551010132</t>
+    <t xml:space="preserve">7.88924646377563</t>
   </si>
   <si>
     <t xml:space="preserve">8.23806476593018</t>
@@ -716,16 +716,16 @@
     <t xml:space="preserve">8.26032829284668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21579742431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64625644683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75758266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80211162567139</t>
+    <t xml:space="preserve">8.21579933166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6462574005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75758171081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8021125793457</t>
   </si>
   <si>
     <t xml:space="preserve">8.69078636169434</t>
@@ -734,16 +734,16 @@
     <t xml:space="preserve">8.5794620513916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66110038757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54977703094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5200891494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53493213653564</t>
+    <t xml:space="preserve">8.66109943389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54977607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52008819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53493118286133</t>
   </si>
   <si>
     <t xml:space="preserve">8.60172653198242</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">8.59430503845215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46813678741455</t>
+    <t xml:space="preserve">8.46813583374023</t>
   </si>
   <si>
     <t xml:space="preserve">8.14900302886963</t>
@@ -764,40 +764,40 @@
     <t xml:space="preserve">8.31970310211182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12674045562744</t>
+    <t xml:space="preserve">8.12673854827881</t>
   </si>
   <si>
     <t xml:space="preserve">8.46071434020996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58688354492188</t>
+    <t xml:space="preserve">8.58688259124756</t>
   </si>
   <si>
     <t xml:space="preserve">8.7056303024292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84664154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69820785522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74273777008057</t>
+    <t xml:space="preserve">8.84664249420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69820976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74273872375488</t>
   </si>
   <si>
     <t xml:space="preserve">8.56461811065674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43844985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40876388549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34939098358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42360782623291</t>
+    <t xml:space="preserve">8.43845081329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40876197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34938907623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42360687255859</t>
   </si>
   <si>
     <t xml:space="preserve">8.54235363006592</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">8.63141441345215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61656951904297</t>
+    <t xml:space="preserve">8.61657047271729</t>
   </si>
   <si>
     <t xml:space="preserve">8.63883495330811</t>
@@ -818,46 +818,46 @@
     <t xml:space="preserve">8.77984619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88374996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83922004699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82437705993652</t>
+    <t xml:space="preserve">8.88375091552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83921909332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82437801361084</t>
   </si>
   <si>
     <t xml:space="preserve">8.68336486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60914993286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57204055786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49040222167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47555923461914</t>
+    <t xml:space="preserve">8.60915088653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57204151153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49040126800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47555732727051</t>
   </si>
   <si>
     <t xml:space="preserve">8.78726863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71305179595947</t>
+    <t xml:space="preserve">8.71305084228516</t>
   </si>
   <si>
     <t xml:space="preserve">8.65367889404297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62399196624756</t>
+    <t xml:space="preserve">8.62399101257324</t>
   </si>
   <si>
     <t xml:space="preserve">8.75016021728516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90601634979248</t>
+    <t xml:space="preserve">8.90601539611816</t>
   </si>
   <si>
     <t xml:space="preserve">8.89859390258789</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">8.77242469787598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9653902053833</t>
+    <t xml:space="preserve">8.96538925170898</t>
   </si>
   <si>
     <t xml:space="preserve">8.87632846832275</t>
@@ -878,22 +878,22 @@
     <t xml:space="preserve">8.97281074523926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09155750274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21772575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52201557159424</t>
+    <t xml:space="preserve">9.09155654907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2177267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52201461791992</t>
   </si>
   <si>
     <t xml:space="preserve">9.55170249938965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56654644012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45522022247314</t>
+    <t xml:space="preserve">9.5665454864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45522117614746</t>
   </si>
   <si>
     <t xml:space="preserve">9.47748565673828</t>
@@ -905,25 +905,25 @@
     <t xml:space="preserve">9.35873699188232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59623241424561</t>
+    <t xml:space="preserve">9.59623146057129</t>
   </si>
   <si>
     <t xml:space="preserve">9.64076137542725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9079418182373</t>
+    <t xml:space="preserve">9.90794277191162</t>
   </si>
   <si>
     <t xml:space="preserve">9.89309978485107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76692962646484</t>
+    <t xml:space="preserve">9.76693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">9.72982215881348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99700355529785</t>
+    <t xml:space="preserve">9.99700260162354</t>
   </si>
   <si>
     <t xml:space="preserve">9.95247173309326</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">9.64818382263184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95989322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82630443572998</t>
+    <t xml:space="preserve">9.95989513397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82630348205566</t>
   </si>
   <si>
     <t xml:space="preserve">9.81146049499512</t>
@@ -950,13 +950,13 @@
     <t xml:space="preserve">9.85599040985107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86341190338135</t>
+    <t xml:space="preserve">9.86341285705566</t>
   </si>
   <si>
     <t xml:space="preserve">10.0415325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0118446350098</t>
+    <t xml:space="preserve">10.0118455886841</t>
   </si>
   <si>
     <t xml:space="preserve">9.94505023956299</t>
@@ -968,22 +968,22 @@
     <t xml:space="preserve">8.8317985534668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97088432312012</t>
+    <t xml:space="preserve">7.97088384628296</t>
   </si>
   <si>
     <t xml:space="preserve">8.25290679931641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16384696960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1935338973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67594146728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50524520874023</t>
+    <t xml:space="preserve">8.16384792327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19353485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67594337463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50524616241455</t>
   </si>
   <si>
     <t xml:space="preserve">8.02283573150635</t>
@@ -992,61 +992,61 @@
     <t xml:space="preserve">8.06736660003662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98572826385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78534269332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76307725906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7037034034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82987260818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64433002471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72596883773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04510116577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14158344268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91893196105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08963203430176</t>
+    <t xml:space="preserve">7.98572731018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7853422164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76307678222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70370388031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82987213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64432954788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7259693145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04510021209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1415843963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91893291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08963108062744</t>
   </si>
   <si>
     <t xml:space="preserve">8.11931705474854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11189556121826</t>
+    <t xml:space="preserve">8.11189651489258</t>
   </si>
   <si>
     <t xml:space="preserve">8.09705257415771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00057029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1341609954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28259372711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20837688446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34196853637695</t>
+    <t xml:space="preserve">8.00056934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13416194915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28259468078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20837783813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34196662902832</t>
   </si>
   <si>
     <t xml:space="preserve">8.44587230682373</t>
@@ -1055,22 +1055,22 @@
     <t xml:space="preserve">8.92085933685303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0247631072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32712459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26775074005127</t>
+    <t xml:space="preserve">9.02476215362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32712554931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26775169372559</t>
   </si>
   <si>
     <t xml:space="preserve">7.71854639053345</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03025913238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01541423797607</t>
+    <t xml:space="preserve">8.03025722503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01541519165039</t>
   </si>
   <si>
     <t xml:space="preserve">8.1044750213623</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">8.17869186401367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.223219871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40134143829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05445003509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93570137023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72789478302002</t>
+    <t xml:space="preserve">8.22322082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40134048461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0544490814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93570232391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72789573669434</t>
   </si>
   <si>
     <t xml:space="preserve">8.89117240905762</t>
@@ -1100,19 +1100,19 @@
     <t xml:space="preserve">9.00992012023926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27709865570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30678653717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24741363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35131645202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52943801879883</t>
+    <t xml:space="preserve">9.277099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30678558349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24741268157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35131549835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52943706512451</t>
   </si>
   <si>
     <t xml:space="preserve">9.47006320953369</t>
@@ -1121,22 +1121,22 @@
     <t xml:space="preserve">9.39584636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54428100585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87083435058594</t>
+    <t xml:space="preserve">9.54428005218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87083339691162</t>
   </si>
   <si>
     <t xml:space="preserve">9.60365390777588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0637989044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87998294830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54299354553223</t>
+    <t xml:space="preserve">10.0637969970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87998485565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54299163818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.55830955505371</t>
@@ -1145,25 +1145,25 @@
     <t xml:space="preserve">9.72680568695068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60426425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46640300750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57362842559814</t>
+    <t xml:space="preserve">9.60426330566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46640205383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57362937927246</t>
   </si>
   <si>
     <t xml:space="preserve">9.6195821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63489818572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68085289001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48172092437744</t>
+    <t xml:space="preserve">9.6348991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68085384368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48171997070312</t>
   </si>
   <si>
     <t xml:space="preserve">9.43576717376709</t>
@@ -1175,13 +1175,13 @@
     <t xml:space="preserve">9.31322479248047</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08345890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59328842163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53201675415039</t>
+    <t xml:space="preserve">9.08345794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59328937530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53201770782471</t>
   </si>
   <si>
     <t xml:space="preserve">8.89964485168457</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">9.28258895874023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20599937438965</t>
+    <t xml:space="preserve">9.20600128173828</t>
   </si>
   <si>
     <t xml:space="preserve">9.49703884124756</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">9.51235771179199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52767372131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38981533050537</t>
+    <t xml:space="preserve">9.52767467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38981342315674</t>
   </si>
   <si>
     <t xml:space="preserve">9.35917949676514</t>
@@ -1220,10 +1220,10 @@
     <t xml:space="preserve">9.58894634246826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32854270935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42044925689697</t>
+    <t xml:space="preserve">9.3285436630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42045021057129</t>
   </si>
   <si>
     <t xml:space="preserve">9.22131824493408</t>
@@ -1238,58 +1238,58 @@
     <t xml:space="preserve">9.14472961425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26727199554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45108604431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69616889953613</t>
+    <t xml:space="preserve">9.26727294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45108509063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69616985321045</t>
   </si>
   <si>
     <t xml:space="preserve">9.6502161026001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80773830413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06814002990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37449550628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03750610351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12941265106201</t>
+    <t xml:space="preserve">8.80773735046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06814098358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37449645996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03750419616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1294116973877</t>
   </si>
   <si>
     <t xml:space="preserve">9.02218627929688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91496181488037</t>
+    <t xml:space="preserve">8.91496276855469</t>
   </si>
   <si>
     <t xml:space="preserve">8.94559860229492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17536544799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00686836242676</t>
+    <t xml:space="preserve">9.17536354064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00686931610107</t>
   </si>
   <si>
     <t xml:space="preserve">9.95657253265381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0331621170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91061973571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97189044952393</t>
+    <t xml:space="preserve">10.0331630706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91061782836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97189140319824</t>
   </si>
   <si>
     <t xml:space="preserve">9.78807640075684</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">9.75744152069092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09877586364746</t>
+    <t xml:space="preserve">9.09877490997314</t>
   </si>
   <si>
     <t xml:space="preserve">8.86900806427002</t>
@@ -1307,10 +1307,10 @@
     <t xml:space="preserve">8.74646663665771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73114776611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51669883728027</t>
+    <t xml:space="preserve">8.73114681243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51669788360596</t>
   </si>
   <si>
     <t xml:space="preserve">8.47074604034424</t>
@@ -1319,37 +1319,37 @@
     <t xml:space="preserve">8.42479228973389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01121139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22566032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36352062225342</t>
+    <t xml:space="preserve">8.01121234893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.225661277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36352157592773</t>
   </si>
   <si>
     <t xml:space="preserve">8.65456008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77710151672363</t>
+    <t xml:space="preserve">8.77710247039795</t>
   </si>
   <si>
     <t xml:space="preserve">8.8383731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9302806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62392330169678</t>
+    <t xml:space="preserve">8.93027973175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62392425537109</t>
   </si>
   <si>
     <t xml:space="preserve">8.7158317565918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50138187408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82305526733398</t>
+    <t xml:space="preserve">8.50138092041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8230562210083</t>
   </si>
   <si>
     <t xml:space="preserve">8.60860633850098</t>
@@ -1361,13 +1361,13 @@
     <t xml:space="preserve">8.34820365905762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30224990844727</t>
+    <t xml:space="preserve">8.30225086212158</t>
   </si>
   <si>
     <t xml:space="preserve">8.3328857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37883853912354</t>
+    <t xml:space="preserve">8.37883949279785</t>
   </si>
   <si>
     <t xml:space="preserve">8.28693294525146</t>
@@ -1394,52 +1394,52 @@
     <t xml:space="preserve">8.85369110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70051383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66987800598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68519496917725</t>
+    <t xml:space="preserve">8.70051288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66987705230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68519592285156</t>
   </si>
   <si>
     <t xml:space="preserve">8.54733467102051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44011211395264</t>
+    <t xml:space="preserve">8.440110206604</t>
   </si>
   <si>
     <t xml:space="preserve">8.88432693481445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40513229370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92593669891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80339622497559</t>
+    <t xml:space="preserve">9.40513134002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92593765258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80339431762695</t>
   </si>
   <si>
     <t xml:space="preserve">9.29790782928467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22897624969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07579898834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15238857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9992094039917</t>
+    <t xml:space="preserve">9.22897720336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0757999420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15238761901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99921035766602</t>
   </si>
   <si>
     <t xml:space="preserve">9.59735012054443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31742668151855</t>
+    <t xml:space="preserve">9.31742763519287</t>
   </si>
   <si>
     <t xml:space="preserve">9.03750514984131</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">8.79757022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87754917144775</t>
+    <t xml:space="preserve">8.87754821777344</t>
   </si>
   <si>
     <t xml:space="preserve">8.83755970001221</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">8.63761520385742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23744869232178</t>
+    <t xml:space="preserve">9.23744964599609</t>
   </si>
   <si>
     <t xml:space="preserve">9.27743911743164</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">9.51737117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67732810974121</t>
+    <t xml:space="preserve">9.67732906341553</t>
   </si>
   <si>
     <t xml:space="preserve">9.63733863830566</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">9.19746017456055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07749462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4373950958252</t>
+    <t xml:space="preserve">9.07749366760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43739414215088</t>
   </si>
   <si>
     <t xml:space="preserve">9.55736064910889</t>
@@ -1508,16 +1508,16 @@
     <t xml:space="preserve">9.15747165679932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91753673553467</t>
+    <t xml:space="preserve">8.91753768920898</t>
   </si>
   <si>
  